--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -604,17 +604,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Matemática Básica</t>
+          <t>Fundamentos De Engenharia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Ferramentas Básicas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1089,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1120,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3720,9 +3720,188 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>91</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Subdivisão da Engenharia de Métodos</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Projeto de Métodos&lt;/li&gt;
+	&lt;li&gt;Padronização e Treinamento&lt;/li&gt;
+	&lt;li&gt;Medida do Trabalho&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>92</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Etapas para o estudo de métodos</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Escolher o trabalho&lt;/li&gt;
+	&lt;li&gt;Registrar,&lt;/li&gt;
+	&lt;li&gt;Examinar com espírito crítico&lt;/li&gt;
+	&lt;li&gt;Desenvolver o método mais rápido&lt;/li&gt;
+	&lt;li&gt;Definir o novo método&lt;/li&gt;
+	&lt;li&gt;Implantar o novo método.&lt;/li&gt;
+	&lt;li&gt;Controlar o novo método&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>93</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ortografia Oficial</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Grafias Corretas</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Paralizado; Exceção; Adivinhar; Cabeleireiro</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>94</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Quesitos a serem levados em consideração para análise de operações</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Materias&lt;/li&gt;
+	&lt;li&gt;Manuseio de Materiais&lt;/li&gt;
+	&lt;li&gt;Ferramentas, Dispositivos e Gabaritos&lt;/li&gt;
+	&lt;li&gt;Máquina&lt;/li&gt;
+	&lt;li&gt;Operador&lt;/li&gt;
+	&lt;li&gt;Condições de Trabalho&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>95</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Perguntas fundamentais para a análise crítica de operações</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Qual é o objetivo?&lt;/li&gt;
+	&lt;li&gt;Por que é necessário?&lt;/li&gt;
+	&lt;li&gt;Onde, quando e como é feito?&lt;/li&gt;
+	&lt;li&gt;Quem executa?&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>4</v>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G90" t="n">
         <v>1</v>
@@ -3905,6 +3905,134 @@
         <v>0</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>96</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Estruturas Lógicas</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Ordem de precedência da negação e dos conectivos</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1. Realizar a negação abrangendo o menor enunciado possível (~);
+2. Conjunção (∧) e disjunção inclusiva (∨), na ordem em que aparecerem;
+3. Disjunção exclusiva (∨);
+4. Condicional (→);
+5. Bicondicional (&lt;-&gt;).</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>97</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Fundamentos De Engenharia</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Conceitos Básicos</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Área de um triângulo equilátero</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>A = (l^2√3)/4</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>98</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fórmula do Tempo Normal</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Tempo Normal = 𝑡𝑒𝑚𝑝𝑜 𝑠𝑒𝑙𝑒𝑐𝑖𝑜𝑛𝑎𝑑𝑜 𝑥 (𝑟𝑖𝑡𝑚𝑜 𝑝𝑒𝑟𝑐𝑒𝑛𝑡𝑢𝑎𝑙)/100</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>99</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Fórmula do Tempo Padrão</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Tempo padrão = tempo normal x fator de tolerância.</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,8 +982,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1007,7 +1009,7 @@
 	&lt;li&gt;Mapofluxograma;&lt;/li&gt;
 	&lt;li&gt;Carta de-para;&lt;/li&gt;
 	&lt;li&gt;Gráfico homem-máquina;&lt;/li&gt;
-	&lt;li&gt;Gráfico das duas mãos.&lt;/li&gt;
+	&lt;li&gt;Gráfico das duas mãos ou gráfico de operações.&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -4003,8 +4005,10 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>99</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -4018,18 +4022,52 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Fórmula do Tempo Padrão</t>
+          <t>Fórmulas do Tempo Padrão</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tempo padrão = tempo normal x fator de tolerância.</t>
+          <t>Tempo padrão = tempo normal x fator de tolerância.
+Tempo padrão = Tempo normal + Tolerâncias
+Tempo padrão = Tempo normal + (Tempo normal x tolerâncias, em %)</t>
         </is>
       </c>
       <c r="F99" t="n">
         <v>1</v>
       </c>
       <c r="G99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>100</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Fórmula do Fator de Tolerância</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Fator de Tolerância = 1/(1-p)
+onde p é “tempo de intervalo/tempo de trabalho”</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4071,6 +4071,255 @@
         <v>0</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>101</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Definição de Inovação</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Inovação é definida como ‘a criação, e a implementação de uma nova ideia</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>102</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Modelo de Etapas da Inovação</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1. Geração de Ideias:
+2. Avaliação:
+3. Experimentação:
+4. Comercialização:
+5. Acompanhamento:</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>103</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Inovação aberta</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>influência externa, com a ajuda de colaboradores externos e empresas externas.
+&lt;ul&gt;
+	&lt;li&gt;Inbound:&lt;/li&gt;
+	&lt;li&gt;Outbound:&lt;/li&gt;
+	&lt;li&gt;Coupled:&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>104</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Inovação Fechada</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;precede a inovação aberta&lt;/li&gt;
+	&lt;li&gt;não cruza as paredes do ambiente da empresa&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>105</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Indicadores de Inovação</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Financeiros&lt;/li&gt;
+	&lt;li&gt;de Cultura&lt;/li&gt;
+	&lt;li&gt;de Intensidade&lt;/li&gt;
+	&lt;li&gt;de Eficácia&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Tipos de Inovação Segundo o Manual de Oslo (2005)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;de Produtos&lt;/li&gt;
+	&lt;li&gt;de Processo&lt;/li&gt;
+	&lt;li&gt;de Marketing&lt;/li&gt;
+	&lt;li&gt;Organizacional&lt;/li&gt;
+	&lt;li&gt;de Serviços&lt;/li&gt;
+	&lt;li&gt;Incremental&lt;/li&gt;
+	&lt;li&gt;Radical&lt;/li&gt;
+	&lt;li&gt;Disruptiva&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>107</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>três princípios basilares que definem e justificam um modelo de negócio</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Criação de Valor&lt;/li&gt;
+	&lt;li&gt;Entrega de Valor&lt;/li&gt;
+	&lt;li&gt;Captura de valor&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4320,6 +4320,99 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>108</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Análise Combinatória</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Fórmula da Permutação com Repetição</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>P&lt;sub&gt;n&lt;/sub&gt;&lt;sup&gt;k&lt;sub&gt;1&lt;/sub&gt;,k&lt;sub&gt;2&lt;/sub&gt;,...k&lt;sub&gt;i&lt;/sub&gt;&lt;/sup&gt; = n!/(k&lt;sub&gt;1&lt;/sub&gt;! x k&lt;sub&gt;2&lt;/sub&gt;! x ... x k&lt;sub&gt;i&lt;/sub&gt;!)</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>109</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Análise Combinatória</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Fórmula da Permutação Circular</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>PC&lt;sub&gt;n&lt;/sub&gt; = (n - 1)!</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>110</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Análise Combinatória</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Fórmula da Combinhação com Repetiçao (ou Completa)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>CR&lt;sup&gt;p&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = P&lt;sup&gt;n-1,p&lt;/sup&gt;&lt;sub&gt;n-1+p&lt;/sub&gt; = [(n-1+p)!]/[(n-1)!xp!]</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -4383,8 +4383,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>110</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4403,7 +4405,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CR&lt;sup&gt;p&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = P&lt;sup&gt;n-1,p&lt;/sup&gt;&lt;sub&gt;n-1+p&lt;/sub&gt; = [(n-1+p)!]/[(n-1)!xp!]</t>
+          <t>CR&lt;sup&gt;p&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = P&lt;sup&gt;n-1,p&lt;/sup&gt;&lt;sub&gt;n-1+p&lt;/sub&gt; = C&lt;sup&gt;n+p-1&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = [(n-1+p)!]/[(n-1)!xp!]</t>
         </is>
       </c>
       <c r="F110" t="n">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4415,6 +4415,115 @@
         <v>0</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>111</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>quatro dimensões em que se pode inovar num modelo de negócios</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Oferta&lt;/li&gt;
+	&lt;li&gt;Consumidores&lt;/li&gt;
+	&lt;li&gt;Processos&lt;/li&gt;
+	&lt;li&gt;Canais de Entrega&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>112</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>fatores gerais que levam uma empresa a investir na inovação de Modelo de Negócios</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Reação&lt;/li&gt;
+	&lt;li&gt;Adaptação&lt;/li&gt;
+	&lt;li&gt;Expansão&lt;/li&gt;
+	&lt;li&gt;Proatividade&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>113</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>guia para como inovar em modelo de negócios, ‘’Business Model Generation’’</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Mobilização&lt;/li&gt;
+	&lt;li&gt;Compreensão&lt;/li&gt;
+	&lt;li&gt;Design&lt;/li&gt;
+	&lt;li&gt;Implementação&lt;/li&gt;
+	&lt;li&gt;Gerenciamento&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4170,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -4524,6 +4524,45 @@
         <v>0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>114</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>conceitos pilares para uma cultura inovadora</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Valores&lt;/li&gt;
+	&lt;li&gt;Visão&lt;/li&gt;
+	&lt;li&gt;Transparência&lt;/li&gt;
+	&lt;li&gt;Regras&lt;/li&gt;
+	&lt;li&gt;Ambientes&lt;/li&gt;
+	&lt;li&gt;Flexibilidade&lt;/li&gt;
+	&lt;li&gt;Gestão do Tempo&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -723,8 +723,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -743,17 +745,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Estoque de Segurança ou estoque isolado&lt;/li&gt;
-	&lt;li&gt;Estoque cíclico&lt;/li&gt;
-	&lt;li&gt;Estoque de desacoplamento&lt;/li&gt;
-	&lt;li&gt;Estoque de antecipação&lt;/li&gt;
-	&lt;li&gt;Estoques no canal de distribuição&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>&lt;ul&gt; &lt;li&gt;Estoque de Segurança ou estoque isolado &lt;ul&gt; &lt;li&gt;Compensa as incertezas entre fornecimento e demanda&lt;/li&gt; &lt;li&gt;é definido como uma % do estoque total&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque cíclico &lt;ul&gt; &lt;li&gt;empresas que possuem vários produtos e precisam produzir ciclos de produtos&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de desacoplamento &lt;ul&gt; &lt;li&gt;arranjo físico de processo&lt;/li&gt; &lt;li&gt;Promove uma independência entre os estágios do processo produtivo&lt;/li&gt; &lt;li&gt;o estoque fica aguardando uma fila em cada um dos estágios&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de antecipação &lt;ul&gt; &lt;li&gt;usado para lidar com a demanda sazonal&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoques no canal de distribuição &lt;ul&gt; &lt;li&gt;Também chamado de estoque em trânsito&lt;/li&gt; &lt;li&gt;sendo transportado ou mesmo aguardando em centros de distribuição&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>5</v>
@@ -789,7 +785,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
         <v>5</v>
@@ -826,15 +822,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -855,23 +853,35 @@
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;Sistema de duas gavetas;&lt;/li&gt;
-	&lt;li&gt;Sistema dos máximos-mínimos;&lt;/li&gt;
-	&lt;li&gt;Sistema de reposições periódicas; e&lt;/li&gt;
+	&lt;li&gt;Sistema dos máximos-mínimos;
+&lt;ul&gt;
+	&lt;li&gt;Estoque mínimo = d*t, d = consumo médio do material e t = tempo de espera médio, em dias, para reposição do material.&lt;/li&gt;
+	&lt;li&gt;Estoque máximo = Emín + Lote de compra.&lt;/li&gt;
+	&lt;li&gt;ponto de ressuprimento ou ponto de pedido: &lt;ul&gt; &lt;li&gt;PR = (C X TR) + ES, onde &lt;ul&gt; &lt;li&gt;C = consumo médio do item&lt;/li&gt; &lt;li&gt;TR = tempo de reposição&lt;/li&gt; &lt;li&gt;ES = estoque mínimo ou de segurança&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Sistema de reposições periódicas;
+&lt;ul&gt;
+	&lt;li&gt;a quantidade de material pedida deverá ser igual à necessidade da demanda do próximo período.&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 	&lt;li&gt;MRP.&lt;/li&gt;
 &lt;/ul&gt;
 </t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -894,12 +904,21 @@
 	&lt;li&gt;LIFO&lt;/li&gt;
 	&lt;li&gt;FIFO&lt;/li&gt;
 	&lt;li&gt;Custo Médio&lt;/li&gt;
-	&lt;li&gt;Custo de Reposição.&lt;/li&gt;
+	&lt;li&gt;Custo de Reposição.
+&lt;ul&gt;
+	&lt;li&gt;CR= PU+ACR onde:&lt;/li&gt;
+	&lt;li&gt;&lt;ul&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;li&gt;CR = Custo de Reposição;&lt;/li&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;li&gt;PU = Preço Unitário do material; e&lt;/li&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;li&gt;ACR = Acréscimo do Custo de Reposição em porcentagem (%).&lt;/li&gt;&lt;/li&gt;
+	&lt;li&gt;&lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
         <v>5</v>
@@ -907,7 +926,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -921,47 +940,10 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fórmula do LEC</t>
+          <t>Limitações da LEC (Segundo Dias, 2010)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Q = sqrt((2xDxCp)/Ce)&lt;/b&gt;
-&lt;ul&gt;
-	&lt;li&gt;Q = Lote&lt;/li&gt;
-	&lt;li&gt;D = Demanada&lt;/li&gt;
-	&lt;li&gt;Cp = Custo de Pedido Unitário&lt;/li&gt;
-	&lt;li&gt;Ce = Custo de manutenção de armazenamento&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Gestão de Estoques</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Limitações da LEC (Segundo Dias, 2010)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Admite que;&lt;/li&gt;
@@ -974,35 +956,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>gráficos ou recursos esquemáticos mais usualmente utilizados na Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Gráfico do fluxo do processo;&lt;/li&gt;
@@ -1013,8 +995,42 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>principais sistemas de medição do trabalho:</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;cronometragem&lt;/li&gt;
+	&lt;li&gt;amostragem do trabalho&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
@@ -1022,7 +1038,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1036,44 +1052,10 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>principais sistemas de medição do trabalho:</t>
+          <t>sistema de medição do trabalho: &lt;b&gt;cronometragem&lt;/b&gt;</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;cronometragem&lt;/li&gt;
-	&lt;li&gt;amostragem do trabalho&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Engenharia de Métodos e Processos</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sistema de medição do trabalho: &lt;b&gt;cronometragem&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Obter e registrar&lt;/li&gt;
@@ -1087,6 +1069,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sistema de medição de trabalho: &lt;b&gt;amostragem do trabalho&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>estimativa da proporção de tempo gasto em uma determinada atividade, durante um certo período, por meio de observações instantâneas, ininterruptas e espaçadas aleatoriamente.</t>
+        </is>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
@@ -1096,55 +1109,24 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Conhecimentos Específicos</t>
+          <t>Português</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Engenharia de Métodos e Processos</t>
+          <t>Travessão</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sistema de medição de trabalho: &lt;b&gt;amostragem do trabalho&lt;/b&gt;</t>
+          <t>Classificação e significado da palavra &lt;b&gt;dúbio&lt;/b&gt;</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>estimativa da proporção de tempo gasto em uma determinada atividade, durante um certo período, por meio de observações instantâneas, ininterruptas e espaçadas aleatoriamente.</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Travessão</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Classificação e significado da palavra &lt;b&gt;dúbio&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>&lt;b&gt;adjetivo&lt;/b&gt;
 &lt;ul&gt;
@@ -1153,33 +1135,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Sinônimo E Antônimo</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Classficação e significado da palavra &lt;b&gt;reminiscência&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>&lt;b&gt;substantivo feminino&lt;/b&gt;
 &lt;ol&gt;
@@ -1188,33 +1170,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Sinônimo E Antônimo</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Classificação e significado da palavra &lt;b&gt;resignação&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>&lt;b&gt;substantivo feminino&lt;/b&gt;
 &lt;ol&gt;
@@ -1223,6 +1205,38 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>21</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Inglês</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Semantic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>classificação e significado da palavra, &lt;i&gt;em inglês&lt;/i&gt;, &lt;b&gt;Hence&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Adverb&lt;/b&gt;
+Por isso</t>
+        </is>
+      </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
@@ -1232,7 +1246,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1246,42 +1260,10 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>classificação e significado da palavra, &lt;i&gt;em inglês&lt;/i&gt;, &lt;b&gt;Hence&lt;/b&gt;</t>
+          <t>Classificação e significado da palavra. &lt;i&gt;em inglês&lt;/i&gt;, &lt;b&gt;yield&lt;/b&gt;</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Adverb&lt;/b&gt;
-Por isso</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Inglês</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Semantic</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Classificação e significado da palavra. &lt;i&gt;em inglês&lt;/i&gt;, &lt;b&gt;yield&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>&lt;b&gt;Nouns&lt;/b&gt;
 &lt;ul&gt;
@@ -1295,6 +1277,39 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Estatística</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Medidas de Variabilidade</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Fórmula do &lt;b&gt;desvio padrão&lt;/b&gt;
+&lt;i&gt;amostral e populacional&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>populacional: sig&lt;sup&gt;2&lt;/sup&gt; = (sum&lt;sub&gt;i=1&lt;/sub&gt;&lt;sup&gt;n&lt;/sup&gt;(x&lt;sub&gt;i&lt;/sub&gt; - mu)&lt;sup&gt;2&lt;/sup&gt;)/n
+amostral: S&lt;sup&gt;2&lt;/sup&gt; = (sum&lt;sub&gt;i=1&lt;/sub&gt;&lt;sup&gt;n&lt;/sup&gt;(x&lt;sub&gt;i&lt;/sub&gt; - x&lt;sup&gt;-&lt;/sup&gt;)&lt;sup&gt;2&lt;/sup&gt;)/(n-1)</t>
+        </is>
+      </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
@@ -1304,57 +1319,24 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estatística</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Medidas de Variabilidade</t>
+          <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fórmula do &lt;b&gt;desvio padrão&lt;/b&gt;
-&lt;i&gt;amostral e populacional&lt;/i&gt;</t>
+          <t>Tipos de manutenção</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>populacional: sig&lt;sup&gt;2&lt;/sup&gt; = (sum&lt;sub&gt;i=1&lt;/sub&gt;&lt;sup&gt;n&lt;/sup&gt;(x&lt;sub&gt;i&lt;/sub&gt; - mu)&lt;sup&gt;2&lt;/sup&gt;)/n
-amostral: S&lt;sup&gt;2&lt;/sup&gt; = (sum&lt;sub&gt;i=1&lt;/sub&gt;&lt;sup&gt;n&lt;/sup&gt;(x&lt;sub&gt;i&lt;/sub&gt; - x&lt;sup&gt;-&lt;/sup&gt;)&lt;sup&gt;2&lt;/sup&gt;)/(n-1)</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Gestão da Manutenção e Confiabilidade</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Tipos de manutenção</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
         <is>
           <t>&lt;b&gt;Manutenção não-planejada&lt;/b&gt;
 &lt;ul&gt;
@@ -1370,33 +1352,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Princípios Fundamentais da TPM</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maximizar a eficiência global&lt;/li&gt;
@@ -1406,33 +1388,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Objetivos da TPM</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Aumentar a disponibilidade&lt;/li&gt;
@@ -1442,33 +1424,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Os 8 Pilares da TPM</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Manutenção autônoma&lt;/li&gt;
@@ -1482,33 +1464,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>seis grandes perdas da TPM</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;por quebra de equipamento&lt;/li&gt;
@@ -1520,33 +1502,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>três fatores importantes da TPM</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;busca pelo lucro através da economicidade&lt;/li&gt;
@@ -1555,33 +1537,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Pontos-chave para implementação da TPM:</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Capacitação;&lt;/li&gt;
@@ -1591,40 +1573,72 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Fórmula do MTBF</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>&lt;b&gt;Tempo Médio Entre Falhas&lt;/b&gt;
 MTBF = (Tempo Total Disponível - Tempo das Paradas ou Tempo Perdido)/Quantidade de Paradas;</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>32</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Gestão da Manutenção e Confiabilidade</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Fórmula do MTTR</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Tempo Médio de Reparo&lt;/b&gt;
+MTTR = (Tempo de Parada)/Quantidade de Paradas;</t>
+        </is>
+      </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
@@ -1634,7 +1648,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1647,44 +1661,12 @@
         </is>
       </c>
       <c r="D33" t="inlineStr">
-        <is>
-          <t>Fórmula do MTTR</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Tempo Médio de Reparo&lt;/b&gt;
-MTTR = (Tempo de Parada)/Quantidade de Paradas;</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Gestão da Manutenção e Confiabilidade</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
         <is>
           <t>&lt;b&gt;Disponibilidade&lt;/b&gt;
 &lt;i&gt;Definição e Fórmula&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>&lt;b&gt;Definição&lt;/b&gt;
 expressa como a porcentagem de tempo em que um ativo está operando, em comparação com o tempo total de operação programado
@@ -1693,6 +1675,37 @@
 Disponibilidade = Tempo disponível/(Tempo disponível + Tempo em manutenção)</t>
         </is>
       </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>34</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gestão da Manutenção e Confiabilidade</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Taxa de Falha (λ)&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Taxa de Falha (λ) = 1/MTBF</t>
+        </is>
+      </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
@@ -1702,7 +1715,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1716,12 +1729,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Taxa de Falha (λ)&lt;/b&gt;</t>
+          <t>Manutenabilidade</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Taxa de Falha (λ) = 1/MTBF</t>
+          <t>facilidade com que as atividades de manutenção podem ser realizadas em um ativo ou equipamento</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1733,7 +1746,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1747,12 +1760,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Manutenabilidade</t>
+          <t>Confiabilidade</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>facilidade com que as atividades de manutenção podem ser realizadas em um ativo ou equipamento</t>
+          <t>probabilidade de que um produto, sistema ou serviço desempenhe sua função pretendida adequadamente por um período de tempo especificado</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1764,7 +1777,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1778,41 +1791,10 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Confiabilidade</t>
+          <t>Curva P-F</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>probabilidade de que um produto, sistema ou serviço desempenhe sua função pretendida adequadamente por um período de tempo especificado</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Gestão da Manutenção e Confiabilidade</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Curva P-F</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
         <is>
           <t>Curva que mostra a performance do equipamento em função do tempo, trazendo dois pontos.
 &lt;ul&gt;
@@ -1821,6 +1803,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>38</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gestão da Manutenção e Confiabilidade</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Fórmula da Confiabilidade</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>R(t) = e&lt;sup&gt;-λt&lt;/sup&gt;</t>
+        </is>
+      </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
@@ -1830,7 +1843,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1844,41 +1857,10 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Fórmula da Confiabilidade</t>
+          <t>Formulas para a confiabilidade de sistemas &lt;b&gt;em série&lt;/b&gt; e &lt;b&gt;em paralelo&lt;/b&gt;</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>R(t) = e&lt;sup&gt;-λt&lt;/sup&gt;</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Gestão da Manutenção e Confiabilidade</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Formulas para a confiabilidade de sistemas &lt;b&gt;em série&lt;/b&gt; e &lt;b&gt;em paralelo&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>&lt;b&gt;Em série&lt;/b&gt;
 R&lt;sub&gt;s&lt;/sub&gt; = P&lt;sub&gt;1&lt;/sub&gt; × P&lt;sub&gt;2&lt;/sub&gt; × ... × P&lt;sub&gt;n&lt;/sub&gt;
@@ -1886,33 +1868,33 @@
 Rs = 1 - [(1 - P&lt;sub&gt;1&lt;/sub&gt;) x (1 - P&lt;sub&gt;2&lt;/sub&gt;) x (1 - P&lt;sub&gt;3&lt;/sub&gt;) x ... x (1 - P&lt;sub&gt;n&lt;/sub&gt;)]</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>40</v>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>etapas do FMEA</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Função do equipamento&lt;/li&gt;
@@ -1926,33 +1908,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Etapas do processo do RCFA</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Identificação dos sintomas&lt;/li&gt;
@@ -1964,33 +1946,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>3 fases da FTA</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Identificar o perigo;&lt;/li&gt;
@@ -1999,6 +1981,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>43</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Gestão da Manutenção e Confiabilidade</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Fórmula da função densidade de probabilidade exponencial f(t)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>f(t) = λe&lt;sup&gt;−λt&lt;/sup&gt;, t ≥ 0</t>
+        </is>
+      </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
@@ -2008,7 +2021,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2022,12 +2035,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Fórmula da função densidade de probabilidade exponencial f(t)</t>
+          <t>Fórmula da função de distribuição exponencial acumulada F(t)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>f(t) = λe&lt;sup&gt;−λt&lt;/sup&gt;, t ≥ 0</t>
+          <t>F(t) = 1−e&lt;sup&gt;−λt&lt;/sup&gt;</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2039,7 +2052,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2052,43 +2065,12 @@
         </is>
       </c>
       <c r="D45" t="inlineStr">
-        <is>
-          <t>Fórmula da função de distribuição exponencial acumulada F(t)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>F(t) = 1−e&lt;sup&gt;−λt&lt;/sup&gt;</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Gestão da Manutenção e Confiabilidade</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
         <is>
           <t>&lt;b&gt;Função confiabilidade&lt;/b&gt;
 &lt;i&gt;Definição e fórmula&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>&lt;b&gt;Definição&lt;/b&gt;
 representa a probabilidade de que um equipamento permaneça em funcionamento até o tempo t, &lt;u&gt;sem apresentar falhas&lt;/u&gt;:
@@ -2096,33 +2078,33 @@
 R(t) = e&lt;sup&gt;−λt&lt;/sup&gt;</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>46</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Fórmula para estimar a taxa de falhas</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>λ=k/n⋅Δt 
 &lt;ul&gt;
@@ -2134,33 +2116,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
         <v>47</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Tipos de Arranjo Físico</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Posicional (posição fixa)&lt;/li&gt;
@@ -2175,34 +2157,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Físico Posicional&lt;/b&gt;
 &lt;i&gt;Caracterísitcas&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;recurso transformado permanece fixo&lt;/li&gt;
@@ -2220,34 +2202,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
         <v>49</v>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Físico Funcional (Por processo)&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Recursos similares são agrupados em áreas especializadas&lt;/li&gt;
@@ -2263,34 +2245,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
         <v>50</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Físico Celular&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Forma híbrida entre os arranjos &lt;b&gt;funcional &lt;/b&gt;e &lt;b&gt;em linha&lt;/b&gt;&lt;/li&gt;
@@ -2310,34 +2292,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Celular por Produto&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;cada célula é organizada para atender a um produto específico ou uma família de produtos semelhantes&lt;/li&gt;
@@ -2353,34 +2335,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Celular por Processo&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;a célula é formada por processos similares ou complementares&lt;/li&gt;
@@ -2396,34 +2378,34 @@
 </t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
         <v>53</v>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
         <is>
           <t>Layout e Arranjos Físicos</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>&lt;b&gt;Arranjo Físico por Produto (ou Em linha/Fluxo)&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sequência lógica de transformação do produto&lt;/li&gt;
@@ -2439,33 +2421,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
         <v>54</v>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>&lt;b&gt;Processo de Inovação&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Geração de Ideias&lt;/li&gt;
@@ -2476,33 +2458,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
         <v>55</v>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Modelos de Inovação:  &lt;b&gt;Inovação aberta&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;cunhado pelo pesquisador Henry Chesbrough, em 2003&lt;/li&gt;
@@ -2511,33 +2493,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
         <v>56</v>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Modelos de Inovação: &lt;b&gt;Inovação fechada&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;modelo de inovação que precede a inovação aberta&lt;/li&gt;
@@ -2546,33 +2528,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Indicadores de Inovação</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Redução de Custos&lt;/li&gt;
@@ -2590,35 +2572,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Tipos de Inovação</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Inovação de Processos:&lt;/li&gt;
@@ -2632,33 +2614,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Inovação em modelo de negócios</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>baseada no conceito do BMC (Business Model Canvas), criado por Osterwalder e Pigneur (2010)
 princípios e dimensões &lt;ul&gt; &lt;li&gt;Criação de Valor: &lt;ul&gt; &lt;li&gt;Atividades-chave:&lt;/li&gt; &lt;li&gt;Recursos-chave:&lt;/li&gt; &lt;li&gt;Parcerias-chave:&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Entrega de Valor: &lt;ul&gt; &lt;li&gt;Canais:&lt;/li&gt; &lt;li&gt;Segmento de Clientes:&lt;/li&gt; &lt;li&gt;Relacionamento com o cliente:&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Captura de Valor: &lt;ul&gt; &lt;li&gt;Estrutura de Custos:&lt;/li&gt; &lt;li&gt;Fontes de Receita:&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;
@@ -2671,6 +2653,38 @@
 Processo de inovação em modelo de negócios (Business Model Generation): &lt;ul&gt; &lt;li&gt;Mobilização&lt;/li&gt; &lt;li&gt;Compreensão&lt;/li&gt; &lt;li&gt;Design&lt;/li&gt; &lt;li&gt;Implementação&lt;/li&gt; &lt;li&gt;Gerenciamento&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cultura Organizacional para a Inovação</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;pilares de uma organização com cultura inovadora:&lt;/b&gt;
+&lt;ul&gt; &lt;li&gt;Valores&lt;/li&gt; &lt;li&gt;Visão&lt;/li&gt; &lt;li&gt;Transparência&lt;/li&gt; &lt;li&gt;Regras&lt;/li&gt; &lt;li&gt;Ambientes&lt;/li&gt; &lt;li&gt;Flexibilidade&lt;/li&gt; &lt;li&gt;Gestão do Tempo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
@@ -2680,7 +2694,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2689,47 +2703,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão de Projetos</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cultura Organizacional para a Inovação</t>
+          <t>Tipos de Projetos</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;pilares de uma organização com cultura inovadora:&lt;/b&gt;
-&lt;ul&gt; &lt;li&gt;Valores&lt;/li&gt; &lt;li&gt;Visão&lt;/li&gt; &lt;li&gt;Transparência&lt;/li&gt; &lt;li&gt;Regras&lt;/li&gt; &lt;li&gt;Ambientes&lt;/li&gt; &lt;li&gt;Flexibilidade&lt;/li&gt; &lt;li&gt;Gestão do Tempo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Gestão de Projetos</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Tipos de Projetos</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;social&lt;/li&gt;
@@ -2740,33 +2722,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Etapas/Fases de um projeto</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Concepção/Iniciação;&lt;/li&gt;
@@ -2777,33 +2759,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Etapas/Fases de um projeto</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Concepção/Iniciação;&lt;/li&gt;
@@ -2814,6 +2796,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fórmula do IDC</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>IDC = Valor agregado/Custo real</t>
+        </is>
+      </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
@@ -2823,7 +2836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2837,41 +2850,10 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Fórmula do IDC</t>
+          <t>&lt;b&gt;PMBOK&lt;/b&gt; - &lt;i&gt;áreas de conhecimento&lt;/i&gt;</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
-        <is>
-          <t>IDC = Valor agregado/Custo real</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Gestão de Projetos</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;PMBOK&lt;/b&gt; - &lt;i&gt;áreas de conhecimento&lt;/i&gt;</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gerenciamento de integração de projetos &lt;ul&gt; &lt;li&gt;Preparação do termo de abertura do Projeto&lt;/li&gt; &lt;li&gt;Desenvolvimento do Plano de Gerenciamento&lt;/li&gt; &lt;li&gt;Orientação e gerenciamento da execução&lt;/li&gt; &lt;li&gt;Monitoramento do trabalho realizado&lt;/li&gt; &lt;li&gt;Controle integrado das Mudanças&lt;/li&gt; &lt;li&gt;Encerramento do projeto ou de uma fase do projeto&lt;/li&gt; &lt;/ul&gt;
 Gerenciamento de escopo de projetos &lt;ul&gt; &lt;li&gt;Planejamento do gerenciamento de escopo&lt;/li&gt; &lt;li&gt;Coleta dos requisitos&lt;/li&gt; &lt;li&gt;Definição do escopo de gerenciamento&lt;/li&gt; &lt;li&gt;Criação da EAP&lt;/li&gt; &lt;li&gt;Validação do Escopo&lt;/li&gt; &lt;li&gt;Controle do Escopo&lt;/li&gt; &lt;/ul&gt;
@@ -2885,49 +2867,80 @@
 </t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>CPM: definições de &lt;b&gt;folga livre&lt;/b&gt; e &lt;b&gt;folga total&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;b&gt;folga livre:&lt;/b&gt; É a quantidade de tempo que uma atividade pode atrasar sem atrasar as atividades posteriores;
 &lt;b&gt;folga total:&lt;/b&gt; E a quantidade de tempo que uma atividade pode atrasar sem atrasar a data final do projeto;
 </t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Conceito de Logística (&lt;i&gt;Council of Logistics Management&lt;/i&gt;):</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>é o processo de controle, planejamento e implementação do fluxo</t>
+        </is>
+      </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2941,16 +2954,16 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Conceito de Logística (&lt;i&gt;Council of Logistics Management&lt;/i&gt;):</t>
+          <t>objetivo da logística, Ballou (2005):</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>é o processo de controle, planejamento e implementação do fluxo</t>
+          <t>dispor a mercadoria ou o serviço certo, no lugar certo, no tempo certo e nas condições desejadas</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -2958,7 +2971,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2972,41 +2985,10 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>objetivo da logística, Ballou (2005):</t>
+          <t>tripé logístico</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>dispor a mercadoria ou o serviço certo, no lugar certo, no tempo certo e nas condições desejadas</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>tripé logístico</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Transporte;&lt;/li&gt;
@@ -3015,16 +2997,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>divisão da logística segundo algumas literaturas</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Atividades primárias: &lt;ul&gt; &lt;li&gt;Transportes,&lt;/li&gt; &lt;li&gt;Processamento de Pedidos e&lt;/li&gt; &lt;li&gt;Manutenção de estoques;&lt;/li&gt; &lt;/ul&gt; &lt;i&gt;Minemônico (TPM)&lt;/i&gt;&lt;/li&gt;
+	&lt;li&gt;Atividades de apoio: &lt;ul&gt; &lt;li&gt;Armazenagem,&lt;/li&gt; &lt;li&gt;Manuseio de Materiais,&lt;/li&gt; &lt;li&gt;Embalagem de Proteção,&lt;/li&gt; &lt;li&gt;Obtenção, Programação de Produtos e&lt;/li&gt; &lt;li&gt;Manutenção de Informação.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
         <v>2</v>
-      </c>
-      <c r="G70" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3038,44 +3054,10 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>divisão da logística segundo algumas literaturas</t>
+          <t>Processo de fluxo de materias:</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Atividades primárias: &lt;ul&gt; &lt;li&gt;Transportes,&lt;/li&gt; &lt;li&gt;Processamento de Pedidos e&lt;/li&gt; &lt;li&gt;Manutenção de estoques;&lt;/li&gt; &lt;/ul&gt; &lt;i&gt;Minemônico (TPM)&lt;/i&gt;&lt;/li&gt;
-	&lt;li&gt;Atividades de apoio: &lt;ul&gt; &lt;li&gt;Armazenagem,&lt;/li&gt; &lt;li&gt;Manuseio de Materiais,&lt;/li&gt; &lt;li&gt;Embalagem de Proteção,&lt;/li&gt; &lt;li&gt;Obtenção, Programação de Produtos e&lt;/li&gt; &lt;li&gt;Manutenção de Informação.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Processo de fluxo de materias:</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Entradas - Fornecedores&lt;/li&gt;
@@ -3086,33 +3068,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="72">
+      <c r="A72" t="n">
         <v>72</v>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Classe de materiais ao longo do processo produtivo</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Matéria-prima&lt;/li&gt;
@@ -3123,52 +3105,83 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="73">
+      <c r="A73" t="n">
         <v>73</v>
       </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>&lt;b&gt;Transporte:&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Conceito: &lt;ul&gt; &lt;li&gt;parte do processo logístico responsável por levar os produtos ao consumidor final e/ou entre fornecedor e produtor&lt;/li&gt; &lt;/ul&gt;
 corresponde, em média, a 2/3 de todo o custo logístico
 fatores determinantes em relação ao transporte é a escolha do modal: &lt;ul&gt; &lt;li&gt;Custo do transporte;&lt;/li&gt; &lt;li&gt;Velocidade com que o produto é transportado;&lt;/li&gt; &lt;li&gt;Tipo de manuseio do produto durante o transporte; e&lt;/li&gt; &lt;li&gt;Quantidade de viagens&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Classificação dos Modais:</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt; &lt;li&gt;&lt;b&gt;Velocidade de Transporte:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Disponibilidade:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Confiabilidade: &lt;/b&gt;&lt;ol&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Capacidade de Carga:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Frequência:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="A75" t="n">
+        <v>76</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3181,43 +3194,12 @@
         </is>
       </c>
       <c r="D75" t="inlineStr">
-        <is>
-          <t>Classificação dos Modais:</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt; &lt;li&gt;&lt;b&gt;Velocidade de Transporte:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Disponibilidade:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Confiabilidade: &lt;/b&gt;&lt;ol&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Capacidade de Carga:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;Frequência:&lt;/b&gt; &lt;ol&gt; &lt;li&gt;Dutoviário&lt;/li&gt; &lt;li&gt;Rodoviário&lt;/li&gt; &lt;li&gt;Aeroviário&lt;/li&gt; &lt;li&gt;Ferroviário&lt;/li&gt; &lt;li&gt;Aquaviário&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>76</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
         <is>
           <t>&lt;b&gt;Distribuição&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Caonceito:&lt;/b&gt; &lt;ul&gt; &lt;li&gt;conjunto de ações voltadas à gestão de materiais, iniciando com a saída do produto do processo produtivo e terminando com a entrega no ponto final de consumo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -3226,34 +3208,34 @@
 </t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="76">
+      <c r="A76" t="n">
         <v>77</v>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>&lt;b&gt;Armazenamento&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;atividades que compreende a armazenagem: &lt;ul&gt; &lt;li&gt;receber&lt;/li&gt; &lt;li&gt;carregar&lt;/li&gt; &lt;li&gt;descarregar&lt;/li&gt; &lt;li&gt;conservar&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -3266,33 +3248,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="77">
+      <c r="A77" t="n">
         <v>78</v>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Sistemas Logísticos</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;TMS&lt;/li&gt;
@@ -3303,34 +3285,34 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="78">
+      <c r="A78" t="n">
         <v>79</v>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>&lt;b&gt;Logística Reversa&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;responsabilidade sobre os resíduos produzidos em decorrência do consumo de bens&lt;/li&gt;
@@ -3343,6 +3325,38 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>80</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Logística Verde&lt;/b&gt;
+&lt;i&gt;Conceito&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>procedimentos de logística que objetivam a preservação do meio ambiente, que incluem desde a embalagem até o modal de transporte utilizado</t>
+        </is>
+      </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
@@ -3352,7 +3366,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3365,44 +3379,12 @@
         </is>
       </c>
       <c r="D80" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Logística Verde&lt;/b&gt;
-&lt;i&gt;Conceito&lt;/i&gt;</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>procedimentos de logística que objetivam a preservação do meio ambiente, que incluem desde a embalagem até o modal de transporte utilizado</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>81</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
         <is>
           <t>&lt;b&gt;Logística de Pós-consumo&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;favorece o retorno dos produtos após serem utilizados pelos clientes, visando: &lt;ul&gt; &lt;li&gt;reciclagem&lt;/li&gt; &lt;li&gt;reutilização ou&lt;/li&gt; &lt;li&gt;descarte apropriado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -3411,67 +3393,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="81">
+      <c r="A81" t="n">
         <v>82</v>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>&lt;b&gt;Logística de Pós-venda&lt;/b&gt;
 &lt;i&gt;Características&lt;/i&gt;</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;uma das suas preocupações-chave: &lt;/b&gt;&lt;ul&gt; &lt;li&gt;criar um canal acessível para clientes retornarem &lt;b&gt;produtos&lt;/b&gt;. &lt;ul&gt; &lt;li&gt;defeitos de fabricação ou&lt;/li&gt; &lt;li&gt;erros no pedido&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Matemática Básica</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Logarítimos</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Propriedades dos logaritmos</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;uma das suas preocupações-chave: &lt;/b&gt;&lt;ul&gt; &lt;li&gt;criar um canal acessível para clientes retornarem &lt;b&gt;produtos&lt;/b&gt;. &lt;ul&gt; &lt;li&gt;defeitos de fabricação ou&lt;/li&gt; &lt;li&gt;erros no pedido&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Matemática Básica</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Logarítimos</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Propriedades dos logaritmos</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;log&lt;sub&gt;a&lt;/sub&gt;(b &amp;sdot; c) =log&lt;sub&gt;a&lt;/sub&gt;b + log&lt;sub&gt;a&lt;/sub&gt;c&lt;/li&gt;
@@ -3482,8 +3464,42 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>84</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Modais de Transporte&lt;/b&gt;: Aeroviário</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;vantagens:&lt;ul&gt; &lt;li&gt;longas distâncias, independente de acidentes ou formações geográficas&lt;/li&gt; &lt;li&gt;mais rápido dentre os modais&lt;/li&gt; &lt;li&gt;Menor custo com embalagens&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;desvantagens:&lt;ul&gt; &lt;li&gt;volume pequeno de cargas&lt;/li&gt; &lt;li&gt;custo mais elevado&lt;/li&gt; &lt;li&gt;grande chance de precisar de outro modal para que o produto chegue ao destino&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>1</v>
@@ -3491,7 +3507,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -3505,44 +3521,10 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Modais de Transporte&lt;/b&gt;: Aeroviário</t>
+          <t>&lt;b&gt;Modais de transporte&lt;/b&gt;: Aquaviário</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;vantagens:&lt;ul&gt; &lt;li&gt;longas distâncias, independente de acidentes ou formações geográficas&lt;/li&gt; &lt;li&gt;mais rápido dentre os modais&lt;/li&gt; &lt;li&gt;Menor custo com embalagens&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;desvantagens:&lt;ul&gt; &lt;li&gt;volume pequeno de cargas&lt;/li&gt; &lt;li&gt;custo mais elevado&lt;/li&gt; &lt;li&gt;grande chance de precisar de outro modal para que o produto chegue ao destino&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>0</v>
-      </c>
-      <c r="G84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>85</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Modais de transporte&lt;/b&gt;: Aquaviário</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Marítimo: mares e oceanos;&lt;/li&gt;
@@ -3553,6 +3535,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>86</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Modasi de Transporte&lt;/b&gt;: Ferroviário</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;vantagens: &lt;ul&gt; &lt;li&gt;Baixo custo&lt;/li&gt; &lt;li&gt;Menor risco de acidentes&lt;/li&gt; &lt;li&gt;grande capacidade de transporte de cargas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;desvantagens: &lt;ul&gt; &lt;li&gt;grande chance de precisar de outro modal para que o produto chegue ao destino;&lt;/li&gt; &lt;li&gt;Baixo investimento governamental&lt;/li&gt; &lt;li&gt;Rotas fixas e inflexíveis&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
@@ -3562,7 +3578,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3576,44 +3592,10 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Modasi de Transporte&lt;/b&gt;: Ferroviário</t>
+          <t>&lt;b&gt;Modais de Transporte&lt;/b&gt;: Rodoviário</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;vantagens: &lt;ul&gt; &lt;li&gt;Baixo custo&lt;/li&gt; &lt;li&gt;Menor risco de acidentes&lt;/li&gt; &lt;li&gt;grande capacidade de transporte de cargas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;desvantagens: &lt;ul&gt; &lt;li&gt;grande chance de precisar de outro modal para que o produto chegue ao destino;&lt;/li&gt; &lt;li&gt;Baixo investimento governamental&lt;/li&gt; &lt;li&gt;Rotas fixas e inflexíveis&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>0</v>
-      </c>
-      <c r="G86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>87</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Logística</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;Modais de Transporte&lt;/b&gt;: Rodoviário</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;realizado por meio de caminhões, carretas, carros e veículos em geral através de rodovias.&lt;/li&gt;
@@ -3622,33 +3604,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="87">
+      <c r="A87" t="n">
         <v>88</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>&lt;b&gt;Modais de Transporte&lt;/b&gt;: Dutoviário</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;largamente utilizado na indústria de Petróleo e seus derivados&lt;/li&gt;
@@ -3657,6 +3639,38 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>89</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Cabotagem&lt;/b&gt;
+&lt;i&gt;Conceito&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>transporte marítimo ou hidroviário de cargas e passageiros entre portos ou pontos dentro do mesmo país, mantendo a costa à vista, diferente da navegação de longo curso (internacional)</t>
+        </is>
+      </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
@@ -3666,7 +3680,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -3675,79 +3689,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Logística</t>
+          <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Cabotagem&lt;/b&gt;
-&lt;i&gt;Conceito&lt;/i&gt;</t>
+          <t>Subdivisão da Engenharia de Métodos</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
-        <is>
-          <t>transporte marítimo ou hidroviário de cargas e passageiros entre portos ou pontos dentro do mesmo país, mantendo a costa à vista, diferente da navegação de longo curso (internacional)</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>90</v>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Gestão de Estoques</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;VMI&lt;/b&gt;:
-&lt;i&gt;Conceito&lt;/i&gt;</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>modelo de reposição de estoques no qual o fornecedor assume a responsabilidade de monitorar e reabastecer o estoque do cliente com base na demanda real e nos níveis de estoque disponíveis.</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>7</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>91</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Engenharia de Métodos e Processos</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Subdivisão da Engenharia de Métodos</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Projeto de Métodos&lt;/li&gt;
@@ -3756,33 +3706,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="90">
+      <c r="A90" t="n">
         <v>92</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Etapas para o estudo de métodos</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Escolher o trabalho&lt;/li&gt;
@@ -3795,64 +3745,64 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="91">
+      <c r="A91" t="n">
         <v>93</v>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>Ortografia Oficial</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Grafias Corretas</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Paralizado; Exceção; Adivinhar; Cabeleireiro</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
         <v>94</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Quesitos a serem levados em consideração para análise de operações</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Materias&lt;/li&gt;
@@ -3864,33 +3814,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
         <v>95</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Perguntas fundamentais para a análise crítica de operações</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Qual é o objetivo?&lt;/li&gt;
@@ -3900,33 +3850,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
         <v>96</v>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>Estruturas Lógicas</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Ordem de precedência da negação e dos conectivos</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>1. Realizar a negação abrangendo o menor enunciado possível (~);
 2. Conjunção (∧) e disjunção inclusiva (∨), na ordem em que aparecerem;
@@ -3935,6 +3885,68 @@
 5. Bicondicional (&lt;-&gt;).</t>
         </is>
       </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>97</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Fundamentos De Engenharia</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Conceitos Básicos</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Área de um triângulo equilátero</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>A = (l^2√3)/4</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>98</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Fórmula do Tempo Normal</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Tempo Normal = 𝑡𝑒𝑚𝑝𝑜 𝑠𝑒𝑙𝑒𝑐𝑖𝑜𝑛𝑎𝑑𝑜 𝑥 (𝑟𝑖𝑡𝑚𝑜 𝑝𝑒𝑟𝑐𝑒𝑛𝑡𝑢𝑎𝑙)/100</t>
+        </is>
+      </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
@@ -3943,97 +3955,100 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>97</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fundamentos De Engenharia</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Conceitos Básicos</t>
+          <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Área de um triângulo equilátero</t>
+          <t>Fórmulas do Tempo Padrão</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
-        <is>
-          <t>A = (l^2√3)/4</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
-        <v>98</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Engenharia de Métodos e Processos</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Fórmula do Tempo Normal</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Tempo Normal = 𝑡𝑒𝑚𝑝𝑜 𝑠𝑒𝑙𝑒𝑐𝑖𝑜𝑛𝑎𝑑𝑜 𝑥 (𝑟𝑖𝑡𝑚𝑜 𝑝𝑒𝑟𝑐𝑒𝑛𝑡𝑢𝑎𝑙)/100</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Engenharia de Métodos e Processos</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Fórmulas do Tempo Padrão</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
         <is>
           <t>Tempo padrão = tempo normal x fator de tolerância.
 Tempo padrão = Tempo normal + Tolerâncias
 Tempo padrão = Tempo normal + (Tempo normal x tolerâncias, em %)</t>
         </is>
       </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>100</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Fórmula do Fator de Tolerância</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Fator de Tolerância = 1/(1-p)
+onde p é “tempo de intervalo/tempo de trabalho”</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento e Tecnologia</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Definição de Inovação</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>‘a criação, e a implementação de uma nova ideia, que pode estar relacionada a uma inovação tecnológica, de processo, ou administrativa’</t>
+        </is>
+      </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4041,7 +4056,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4050,78 +4065,15 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Engenharia de Métodos e Processos</t>
+          <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Fórmula do Fator de Tolerância</t>
+          <t>Modelo de Etapas da Inovação</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
-        <is>
-          <t>Fator de Tolerância = 1/(1-p)
-onde p é “tempo de intervalo/tempo de trabalho”</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
-        <v>101</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Definição de Inovação</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Inovação é definida como ‘a criação, e a implementação de uma nova ideia</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
-        <v>102</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Modelo de Etapas da Inovação</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
         <is>
           <t>1. Geração de Ideias:
 2. Avaliação:
@@ -4130,33 +4082,33 @@
 5. Acompanhamento:</t>
         </is>
       </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
+      <c r="F100" t="n">
+        <v>2</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
         <v>103</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>Inovação aberta</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>influência externa, com a ajuda de colaboradores externos e empresas externas.
 &lt;ul&gt;
@@ -4166,33 +4118,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="102">
+      <c r="A102" t="n">
         <v>104</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>Inovação Fechada</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;precede a inovação aberta&lt;/li&gt;
@@ -4200,33 +4152,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
         <v>105</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>Indicadores de Inovação</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Financeiros&lt;/li&gt;
@@ -4236,35 +4188,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>106</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>Tipos de Inovação Segundo o Manual de Oslo (2005)</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;de Produtos&lt;/li&gt;
@@ -4278,33 +4230,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
+      <c r="F104" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
         <v>107</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>três princípios basilares que definem e justificam um modelo de negócio</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criação de Valor&lt;/li&gt;
@@ -4313,6 +4265,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F105" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>108</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Análise Combinatória</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Fórmula da Permutação com Repetição</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>P&lt;sub&gt;n&lt;/sub&gt;&lt;sup&gt;k&lt;sub&gt;1&lt;/sub&gt;,k&lt;sub&gt;2&lt;/sub&gt;,...k&lt;sub&gt;i&lt;/sub&gt;&lt;/sup&gt; = n!/(k&lt;sub&gt;1&lt;/sub&gt;! x k&lt;sub&gt;2&lt;/sub&gt;! x ... x k&lt;sub&gt;i&lt;/sub&gt;!)</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>109</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Análise Combinatória</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Fórmula da Permutação Circular</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>PC&lt;sub&gt;n&lt;/sub&gt; = (n - 1)!</t>
+        </is>
+      </c>
       <c r="F107" t="n">
         <v>0</v>
       </c>
@@ -4321,8 +4335,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v>108</v>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -4336,12 +4352,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Fórmula da Permutação com Repetição</t>
+          <t>Fórmula da Combinhação com Repetiçao (ou Completa)</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>P&lt;sub&gt;n&lt;/sub&gt;&lt;sup&gt;k&lt;sub&gt;1&lt;/sub&gt;,k&lt;sub&gt;2&lt;/sub&gt;,...k&lt;sub&gt;i&lt;/sub&gt;&lt;/sup&gt; = n!/(k&lt;sub&gt;1&lt;/sub&gt;! x k&lt;sub&gt;2&lt;/sub&gt;! x ... x k&lt;sub&gt;i&lt;/sub&gt;!)</t>
+          <t>CR&lt;sup&gt;p&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = P&lt;sup&gt;n-1,p&lt;/sup&gt;&lt;sub&gt;n-1+p&lt;/sub&gt; = C&lt;sup&gt;n+p-1&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = [(n-1+p)!]/[(n-1)!xp!]</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4353,88 +4369,24 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Raciocínio Lógico</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Análise Combinatória</t>
+          <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Fórmula da Permutação Circular</t>
+          <t>quatro dimensões em que se pode inovar num modelo de negócios</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
-        <is>
-          <t>PC&lt;sub&gt;n&lt;/sub&gt; = (n - 1)!</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Raciocínio Lógico</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Análise Combinatória</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Fórmula da Combinhação com Repetiçao (ou Completa)</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>CR&lt;sup&gt;p&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = P&lt;sup&gt;n-1,p&lt;/sup&gt;&lt;sub&gt;n-1+p&lt;/sub&gt; = C&lt;sup&gt;n+p-1&lt;/sup&gt;&lt;sub&gt;n&lt;/sub&gt; = [(n-1+p)!]/[(n-1)!xp!]</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>111</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>quatro dimensões em que se pode inovar num modelo de negócios</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Oferta&lt;/li&gt;
@@ -4444,33 +4396,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
+      <c r="F109" t="n">
+        <v>2</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
         <v>112</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>fatores gerais que levam uma empresa a investir na inovação de Modelo de Negócios</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Reação&lt;/li&gt;
@@ -4480,70 +4432,72 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
-        <v>113</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
+      <c r="F110" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>guia para como inovar em modelo de negócios, ‘’Business Model Generation’’</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
 	&lt;li&gt;Mobilização&lt;/li&gt;
 	&lt;li&gt;Compreensão&lt;/li&gt;
 	&lt;li&gt;Design&lt;/li&gt;
 	&lt;li&gt;Implementação&lt;/li&gt;
 	&lt;li&gt;Gerenciamento&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
         <v>114</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento e Tecnologia</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>conceitos pilares para uma cultura inovadora</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E112" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Valores&lt;/li&gt;
@@ -4556,10 +4510,10 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
+      <c r="F112" t="n">
+        <v>2</v>
+      </c>
+      <c r="G112" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -855,8 +855,8 @@
 	&lt;li&gt;Sistema de duas gavetas;&lt;/li&gt;
 	&lt;li&gt;Sistema dos máximos-mínimos;
 &lt;ul&gt;
-	&lt;li&gt;Estoque mínimo = d*t, d = consumo médio do material e t = tempo de espera médio, em dias, para reposição do material.&lt;/li&gt;
-	&lt;li&gt;Estoque máximo = Emín + Lote de compra.&lt;/li&gt;
+	&lt;li&gt;E min = ER + dt &lt;ul&gt; &lt;li&gt;d = consumo médio&lt;/li&gt; &lt;li&gt;t = tempo de espera médio, em dias, para reposição do material&lt;/li&gt; &lt;li&gt;ER = estoque de reserva ou de segurança&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
+	&lt;li&gt;Emin = Emin + Lote de compra.&lt;/li&gt;
 	&lt;li&gt;ponto de ressuprimento ou ponto de pedido: &lt;ul&gt; &lt;li&gt;PR = (C X TR) + ES, onde &lt;ul&gt; &lt;li&gt;C = consumo médio do item&lt;/li&gt; &lt;li&gt;TR = tempo de reposição&lt;/li&gt; &lt;li&gt;ES = estoque mínimo ou de segurança&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;
 &lt;/li&gt;
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4055,8 +4055,10 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>102</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -4065,7 +4067,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4090,8 +4092,10 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>103</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4100,7 +4104,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4126,8 +4130,10 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>104</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -4136,7 +4142,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4153,15 +4159,17 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>105</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -4170,7 +4178,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4208,7 +4216,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4238,8 +4246,10 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>107</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -4248,7 +4258,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -4259,9 +4269,26 @@
       <c r="E105" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Criação de Valor&lt;/li&gt;
-	&lt;li&gt;Entrega de Valor&lt;/li&gt;
-	&lt;li&gt;Captura de valor&lt;/li&gt;
+	&lt;li&gt;Criação de Valor
+&lt;ul&gt;
+	&lt;li&gt;Atividades-chave&lt;/li&gt;
+	&lt;li&gt;Recursos-chave&lt;/li&gt;
+	&lt;li&gt;Parcerias-chave&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Entrega de Valor
+&lt;ul&gt;
+	&lt;li&gt;Canais&lt;/li&gt;
+	&lt;li&gt;Segmento de Clientes&lt;/li&gt;
+	&lt;li&gt;Relacionamento com o cliente&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Captura de valor
+&lt;ul&gt;
+	&lt;li&gt;Estrutura de Custos&lt;/li&gt;
+	&lt;li&gt;Fontes de Receita&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -4368,8 +4395,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>111</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -4378,7 +4407,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -4404,8 +4433,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>112</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -4414,7 +4445,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4452,7 +4483,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4479,8 +4510,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>114</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -4489,7 +4522,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento e Tecnologia</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Matemática Básica</t>
+          <t>Fundamentos De Engenharia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4550,6 +4550,115 @@
         <v>0</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>115</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>distinção entre dado, informação e conhecimento</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;dado é um elemento bruto, isolado, sem contexto&lt;/li&gt;
+	&lt;li&gt;informação é o dado interpretado, já inserido em uma realidade que lhe dá significado&lt;/li&gt;
+	&lt;li&gt;conhecimento &lt;ul&gt; &lt;li&gt;nível mais alto&lt;/li&gt; &lt;li&gt;envolve interpretação, experiência e capacidade de gerar ação a partir daquela informação.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>conhecimento tácito</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;reside nas pessoas&lt;/li&gt;
+	&lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt;
+	&lt;li&gt;dimensão técnica&lt;/li&gt;
+	&lt;li&gt;dimensão cognitiva&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>conhecimento explícito</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;pode ser formalizado&lt;/li&gt;
+	&lt;li&gt;é documentado, codificado e sistematizado&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4659,6 +4659,151 @@
         <v>0</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>118</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Abordagem Racional (Chun Wei Choo)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Dados Quantitativos&lt;/li&gt;
+	&lt;li&gt;lógica&lt;/li&gt;
+	&lt;li&gt;objetividade&lt;/li&gt;
+	&lt;li&gt;máquina&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>119</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Abordagem Interpretativa (Chun Wei Choo)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Dados Qualitativos&lt;/li&gt;
+	&lt;li&gt;Pessoas&lt;/li&gt;
+	&lt;li&gt;significados&lt;/li&gt;
+	&lt;li&gt;subjetividade&lt;/li&gt;
+	&lt;li&gt;cultura&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Processo de construção da Inteligência</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Dado&lt;/li&gt;
+	&lt;li&gt;Informação&lt;/li&gt;
+	&lt;li&gt;Conhecimento&lt;/li&gt;
+	&lt;li&gt;Inteligência&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>121</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Modelo SECI (Nonaka e Takeuchi)</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Socialização&lt;/li&gt;
+	&lt;li&gt;Externalização&lt;/li&gt;
+	&lt;li&gt;Combinação&lt;/li&gt;
+	&lt;li&gt;Internalização&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4804,6 +4804,301 @@
         <v>0</v>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>122</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Modelo Genérico: 7 Processos da Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Identificação&lt;/li&gt;
+	&lt;li&gt;Captura&lt;/li&gt;
+	&lt;li&gt;Aquisição&lt;/li&gt;
+	&lt;li&gt;Armazenamento&lt;/li&gt;
+	&lt;li&gt;Compartilhamento&lt;/li&gt;
+	&lt;li&gt;Aplicação&lt;/li&gt;
+	&lt;li&gt;Avaliação&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>123</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Barreiras à Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Organizacionais&lt;/li&gt;
+	&lt;li&gt;Culturais&lt;/li&gt;
+	&lt;li&gt;Tecnológicas&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>124</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ferramentas e Práticas da Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Comunidades de Prática (CoP)&lt;/li&gt;
+	&lt;li&gt;Lições Aprendidas, Storytelling e Repositórios de Conhecimento &lt;ul&gt; &lt;li&gt;mentoring, coaching e aprendizagem organizacional&lt;/li&gt; &lt;li&gt;circuitos de aprendizagem&lt;/li&gt; &lt;li&gt;cinco disciplinas essenciais que precisam estar integradas para que uma organização aprenda de verdade&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Mapas de Conhecimento&lt;/li&gt;
+	&lt;li&gt;Bases de Conhecimento e Sistemas de Informação&lt;/li&gt;
+	&lt;li&gt;Gestão de Competências&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>125</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>condições capacitadoras que sustentam "Ba" (espaço compartilhado onde ocorre a criação do conhecimento)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Intenção (Intentionality)&lt;/li&gt;
+	&lt;li&gt;Autonomia&lt;/li&gt;
+	&lt;li&gt;Flutuação e Caos Criativo&lt;/li&gt;
+	&lt;li&gt;Redundância&lt;/li&gt;
+	&lt;li&gt;Variedade de Requisitos (Variety of Requisite)&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>126</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sistemas de Gestão do Conhecimento (Knowledge Management Systems – KMS)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;infraestrutura tecnológica integrada, composta por diversas ferramentas e plataformas&lt;/li&gt;
+	&lt;li&gt;Um bom KMS permite que a organização: &lt;ul&gt; &lt;li&gt;Acesse rapidamente&lt;/li&gt; &lt;li&gt;Facilite a comunicação&lt;/li&gt; &lt;li&gt;Mapeie&lt;/li&gt; &lt;li&gt;Registre aprendizados&lt;/li&gt; &lt;li&gt;Crie ambientes colaborativos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Componentes típicos de um KMS</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;Repositórios de conhecimento&lt;/li&gt;
+	&lt;li&gt;Sistemas de workflow&lt;/li&gt;
+	&lt;li&gt;Ferramentas de colaboração&lt;/li&gt;
+	&lt;li&gt;Diretórios de especialistas&lt;/li&gt;
+	&lt;li&gt;Sistemas de BI e analytics&lt;/li&gt;
+	&lt;li&gt;Inteligência artificial&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Fatores críticos de sucesso para um KMS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Está alinhado&lt;/li&gt;
+	&lt;li&gt;É de fácil usabilidade&lt;/li&gt;
+	&lt;li&gt;Conta com conteúdo&lt;/li&gt;
+	&lt;li&gt;Recebe apoio&lt;/li&gt;
+	&lt;li&gt;É sustentado&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>tecnologias emergentes aplicadas à Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Big Data&lt;/li&gt;
+	&lt;li&gt;Business Intelligence (BI)&lt;/li&gt;
+	&lt;li&gt;Machine Learning (ML)&lt;/li&gt;
+	&lt;li&gt;Inteligência Artificial (IA)&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5099,6 +5099,292 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>130</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Processo para análise sintática</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;ache o verbo&lt;/li&gt;
+	&lt;li&gt;tente colocar a sentença na ordem direta&lt;/li&gt;
+	&lt;li&gt;procurar o sujeito de cada verbo&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>131</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>técnicas de indeterminação do sujeito</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;verbo na 3ª pessoa do plural, com omissão do agente que pratica a ação verbal&lt;/li&gt;
+	&lt;li&gt;uso da PIS&lt;/li&gt;
+	&lt;li&gt;uso do infinitivo impessoal&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>132</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Oração sem sujeito</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Fenômenos da natureza&lt;/li&gt;
+	&lt;li&gt;Verbos ser/estar/fazer/haver/parecer impessoais com sentido de fenômenos naturais, tempo ou estado&lt;/li&gt;
+	&lt;li&gt;verbo “haver” impessoal (com sentido de “existir”, “ocorrer” ou “tempo decorrido”)&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>133</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Casos de Objeto Direto Preposicionado</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Quando o objeto direto for um pronome oblíquo tônico ou “quem”&lt;/li&gt;
+	&lt;li&gt;Quando o objeto direto for verbo no infinitivo, com os verbos “ensinar” e “aprender”&lt;/li&gt;
+	&lt;li&gt;Quando houver dupla possibilidade de referente, ou seja, ambiguidade&lt;/li&gt;
+	&lt;li&gt;Quando o objeto indicar reciprocidade&lt;/li&gt;
+	&lt;li&gt;Com alguns pronomes indefinidos, sobretudo referentes a pessoas&lt;/li&gt;
+	&lt;li&gt;Quando o OD for um nome próprio&lt;/li&gt;
+	&lt;li&gt;Quando o objeto direto for a palavra “ambos”&lt;/li&gt;
+	&lt;li&gt;Quando houver reforço ou exaltação de um sentimento&lt;/li&gt;
+	&lt;li&gt;Em construções enfáticas, nas quais antecipamos o objeto direto para dar-lhe realce&lt;/li&gt;
+	&lt;li&gt;Em construções paralelas com pronomes oblíquos (átonos ou tônicos) do tipo&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>134</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Complemento Nominal</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;complemento de um nome que possua transitividade (substantivo, adjetivo ou advérbio), com preposição&lt;/li&gt;
+	&lt;li&gt;Parece um objeto indireto, com a diferença de que não completa o sentido de um verbo, mas sim de um nome.&lt;/li&gt;
+	&lt;li&gt;também pode ter forma de uma oração&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>135</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Adjunto Adnominal</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;acompanha substantivos concretos e abstratos para atribuir-lhes &lt;ul&gt; &lt;li&gt;características&lt;/li&gt; &lt;li&gt;qualidade ou&lt;/li&gt; &lt;li&gt;estado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;têm função adjetiva, ou seja, modificam termo substantivo&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>136</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Predicação Verbal</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Verbos de Ação/Movimento/Fenômeno &lt;ul&gt; &lt;li&gt;VI &lt;ul&gt; &lt;li&gt;É aquele que não precisa de complemento&lt;/li&gt; &lt;li&gt;Pode vir seguido de informações acessórias (Predicativo/Adj. Adverbial)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;VTD&lt;/li&gt; &lt;li&gt;VTI&lt;/li&gt; &lt;li&gt;VTDI&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Verbos de Estado/de Ligação&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>137</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Adjunto Adverbial</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Invariável&lt;/li&gt;
+	&lt;li&gt;Refere-se a verbo (Seta)&lt;/li&gt;
+	&lt;li&gt;Indica circunstância (Onde?/Quando?/Como?/...)&lt;/li&gt;
+	&lt;li&gt;Pode ser dispensado na frase&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4872,7 +4872,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -5316,8 +5316,10 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
-        <v>136</v>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -5338,7 +5340,7 @@
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Verbos de Ação/Movimento/Fenômeno &lt;ul&gt; &lt;li&gt;VI &lt;ul&gt; &lt;li&gt;É aquele que não precisa de complemento&lt;/li&gt; &lt;li&gt;Pode vir seguido de informações acessórias (Predicativo/Adj. Adverbial)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;VTD&lt;/li&gt; &lt;li&gt;VTI&lt;/li&gt; &lt;li&gt;VTDI&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Verbos de Estado/de Ligação&lt;/li&gt;
+	&lt;li&gt;Verbos de Estado/de Ligação &lt;ul&gt; &lt;li&gt;Vem sempre com Predicativo do Sujeito&lt;/li&gt; &lt;li&gt;Indica estado (e não ação)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -5385,6 +5387,290 @@
         <v>0</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Núcleo do sujeito</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Não é a ideia principal/ideia mais importante do sujeito&lt;/li&gt;
+	&lt;li&gt;É a paravra mais especificada do sujeito (tudo se refere a ele) (recebe setas)&lt;/li&gt;
+	&lt;li&gt;É um substantivo (pronome ou numeral)&lt;/li&gt;
+	&lt;li&gt;Não vem antecedido de preposição (preposição + substantivo = locução adjetiva)&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>139</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Passo a Passo - Classificação do Sujeito</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Vá ao verbo e pergunte pelo sujeito &lt;ul&gt; &lt;li&gt;Quem é que/O que é que + verbo?&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Procure o núcleo do sujeito&lt;/li&gt;
+	&lt;li&gt;Classifique o sujeito&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>140</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Tipos de Sujeito</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Simples&lt;/li&gt;
+	&lt;li&gt;Oculto&lt;/li&gt;
+	&lt;li&gt;Composto&lt;/li&gt;
+	&lt;li&gt;Indeterminado&lt;/li&gt;
+	&lt;li&gt;Inexistente&lt;/li&gt;
+	&lt;li&gt;Oracional&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>141</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Predicativo do sujeito</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Refere-se ao sujeito&lt;/li&gt;
+	&lt;li&gt;Indica estado (Semântica)&lt;/li&gt;
+	&lt;li&gt;Normalmente, é Adjetivo que vem no Predicado&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>142</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Passo a Passo - Predicação Verbal</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Vá ao verbo e pergunte pelo sujeito &lt;ul&gt; &lt;li&gt;Quem é que/O que é que + Verbo?&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Pergunte pelos complementos dos verbos &lt;ul&gt; &lt;li&gt;Mantra: na hora de classificar o verbo, não olhe para ele, olhe para o que vem depois dele! (Contexto)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>143</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Tipos de Predicado</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Predicado Nominal &lt;ul&gt; &lt;li&gt;O núcleo é um nome (predicativo do sujeito)&lt;/li&gt; &lt;li&gt;O verbo indica estado (verbo de ligação)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Predicado Verbal &lt;ul&gt; &lt;li&gt;O núcleo é um verbo que, em geral, indica ação, movimento.&lt;/li&gt; &lt;li&gt;&lt;b&gt;Não&lt;/b&gt; contém predicativo do sujeito.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Predicado verbo-nominal &lt;ul&gt; &lt;li&gt;há dois núcleos (um nome - predicativo - e um verbo que indica ação, movimento)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>144</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Indentificando o tipo de Predicado</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;A grande sacada é saber se o verbo é de ação ou estado &lt;ul&gt; &lt;li&gt;Macete: Primeiro pergunte se o verbo indica estado (Verbo de Estado + Predicativo = Predicado Nominal)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;O verbo só é de ligação se houver predicativo do sujeito na frase (Predicado Nominal). &lt;ul&gt; &lt;li&gt;Se houver Predicativo + Verbo de Ação, Será Predicado Verbo-Nominal&lt;/li&gt;&lt;li&gt;Predicativo pode vir com Verbo de Ligação ou de Ação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>145</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Passo a Passo - Classificação do Predicado</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Ir ao verbo e perguntar pelo sujeito&lt;/li&gt;
+	&lt;li&gt;Extraíndo-se o sujeito, o que sobra é o predicado (Predicado é tudo menos o Sujeito)&lt;/li&gt;
+	&lt;li&gt;Para classificar o Predicado, verificar se o Verbo é de estado (VL) ou de ação. &lt;ul&gt; &lt;li&gt;Se o Verbo for de ligação, o predicado é nominal&lt;/li&gt; &lt;li&gt;Se o Verbo for de ação, pode ser &lt;ul&gt; &lt;li&gt;PV (Sem Predicativo)&lt;/li&gt; &lt;li&gt;PVN (Com Predicativo)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5671,6 +5671,519 @@
         <v>0</v>
       </c>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>146</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Como reconhecer o Agente da Passiva?</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Pela preposição (por/de)&lt;/li&gt;
+	&lt;li&gt;Pela presença de Locução Verbal de Voz Passiva (Ser + Particípio)&lt;/li&gt;
+	&lt;li&gt;O Agente da Passiva vira Sujeito na Voz Ativa&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Tabela para identificar os termos da Oração</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>&lt;div style="margin:0;padding:0;font-family:sans-serif;font-size:14px;color:#333;"&gt;&lt;ul style="margin:0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Objeto Direto&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completam VERBO&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;VERBO&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Facultativa (OD preposicionado)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João leu &lt;span style="color:#d32f2f;text-decoration:underline"&gt;o livro&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Objeto Indireto&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completam VERBO&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;VERBO&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João gosta &lt;span style="color:#d32f2f;text-decoration:underline"&gt;de suco&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Complemento Nominal&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa NOME (Subst./Adj./Adv.)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;NOME&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João tem saudade &lt;span style="color:#d32f2f;text-decoration:underline"&gt;da família&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Agente da Passiva&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Age na Voz Passiva (SER + Particípio)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;strong&gt;Ø&lt;/strong&gt; (Inexistente)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João foi elogiado &lt;span style="color:#d32f2f;text-decoration:underline"&gt;pela professora&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Termos da Oração</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Essenciais&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;Sujeito&lt;/li&gt;
+			&lt;li&gt;Predicado&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Integrantes (Obrigatórios)&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;Complementos Verbais (Objeto Direto e Objeto Indireto)&lt;/li&gt;
+			&lt;li&gt;Complementos Nominais&lt;/li&gt;
+			&lt;li&gt;Agente da Passiva&lt;/li&gt;
+			&lt;li&gt;Predicativo (do Sujeito e do Objeto)&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Acessórios&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;Adjunto Adnominal&lt;/li&gt;
+			&lt;li&gt;Adjunto Adverbial&lt;/li&gt;
+			&lt;li&gt;Aposto&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Termo Independente&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;Vocativo&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>149</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Objeto Direto</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Objeto Direto&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa o sentido de um VTD&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Pronomes Oblíquos&lt;/strong&gt;:
+				&lt;ul&gt;
+					&lt;li&gt;o/a/os/as: Sempre OD&lt;/li&gt;
+					&lt;li&gt;me/te/se/nos/vos: Podem ser OD ou OI&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Particularidades&lt;/strong&gt;: Objeto Direto Pleonástico e Objeto Direto Preposicionado (parece com o OI, mas não é)&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>150</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Objeto Indireto</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Objeto Indireto&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa o sentido de um VTI&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Obrigatoriamente vem precedido de preposição&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Pronomes Oblíquos&lt;/strong&gt;:
+				&lt;ul&gt;
+					&lt;li&gt;lhe/lhes: Sempre OI&lt;/li&gt;
+					&lt;li&gt;me/te/se/nos/vos: Podem ser OD ou OI&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Particularidade&lt;/strong&gt;: Objeto Indireto Pleonástico&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>151</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Complemento Nominal</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Complemento Nominal&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Informação que completa o sentido de um nome (Substantivo, Adjetivo ou Advérbio)&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Vem sempre preposicionado&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>152</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Agente da Passiva</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Agente da Passiva&lt;/strong&gt;:
+		&lt;ul&gt;
+			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Termo que indica quem ou o que pratica a ação verbal na voz passiva&lt;/li&gt;
+			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Normalmente introduzido pelas preposições por (pelo, pela) ou de&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>153</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Vocativo</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Termo que se usa para chamar alguém ou coisa personificada&lt;/li&gt;
+	&lt;li&gt;Ex: &lt;ul&gt; &lt;li&gt;&lt;b&gt;&lt;u&gt;Adriana&lt;/u&gt;&lt;/b&gt;, veja isto.&lt;/li&gt; &lt;li&gt;Eu te amo, &lt;b&gt;&lt;u&gt;Carnaval&lt;/u&gt;&lt;/b&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Núcleo do Vocativo: Substantivo&lt;/li&gt;
+	&lt;li&gt;Cuidado para não confundir Vocativo com Sujeito&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>154</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Aposto</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;Termo de natureza substantiva ou pronominal que se apresenta a outro substantivo ou pronome&lt;/li&gt;
+	&lt;li&gt;Os tipos de aposto são: &lt;ul&gt; &lt;li&gt;Explicativo: &lt;ul&gt; &lt;li&gt;Machado de Assis, &lt;b&gt;&lt;u&gt;um dos maiores nomes da literatura mundial&lt;/u&gt;&lt;/b&gt;, escreveu cerca de duzentos contos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Enumerativo: &lt;ul&gt; &lt;li&gt;Naquele instante, recorri adois amigos: &lt;b&gt;&lt;u&gt;Gilson e Itamar&lt;/u&gt;&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Distributivo: &lt;ul&gt; &lt;li&gt;Eram dois grandes nomes do esporte: &lt;b&gt;&lt;u&gt;um do automobilistmo, outro do tênis&lt;/u&gt;&lt;/b&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Resumitivo: &lt;ul&gt; &lt;li&gt;Empresários, trabalhadores, &lt;b&gt;&lt;u&gt;ninguém &lt;/u&gt;&lt;/b&gt;confia em nossos governantes&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Especificativo: &lt;ul&gt; &lt;li&gt;A cidade &lt;b&gt;&lt;u&gt;de Paris&lt;/u&gt;&lt;/b&gt; é encantadora/O rio &lt;b&gt;&lt;u&gt;Tietê&lt;/u&gt;&lt;/b&gt;/O poeta &lt;b&gt;&lt;u&gt;Carlos Drummond de Andrade&lt;/u&gt;&lt;/b&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Em referência a uma oração: &lt;ul&gt; &lt;li&gt;É preciso rediscutir o papel das forças armadas, &lt;b&gt;&lt;u&gt;coisa &lt;/u&gt;&lt;/b&gt;que não foi feita na Consctituição de 1988&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>155</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Circunstâncias</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;6CsFTP&lt;/b&gt;
+&lt;ul&gt;
+	&lt;li&gt;Causa&lt;/li&gt;
+	&lt;li&gt;Condição&lt;/li&gt;
+	&lt;li&gt;Conseção&lt;/li&gt;
+	&lt;li&gt;Comparação&lt;/li&gt;
+	&lt;li&gt;Consequência&lt;/li&gt;
+	&lt;li&gt;Conformidade&lt;/li&gt;
+	&lt;li&gt;Final&lt;/li&gt;
+	&lt;li&gt;Temporal&lt;/li&gt;
+	&lt;li&gt;Proporcional&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>156</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Adjunto Adverbial</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Vocábulo ou expressão que denota alguma circunstância (tempo, lugar, modo, ...) do fato expresso pelo verbo.&lt;/li&gt;
+	&lt;li&gt;Pode ainda modificar adjetivo ou o próprio advérbio.&lt;/li&gt;
+	&lt;li&gt;Na Morfologia é o equivalente a Advérbi/Locução Adverbial&lt;/li&gt;
+	&lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;Falavam &lt;b&gt;muito&lt;/b&gt; &lt;ul&gt; &lt;li&gt;(Verbo)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Homem &lt;b&gt;muito &lt;/b&gt;bom &lt;ul&gt; &lt;li&gt;(Adjetivo)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Saíram &lt;b&gt;muito &lt;/b&gt;cedo &lt;ul&gt; &lt;li&gt;(Advérbio)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>157</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Adjunto Adnominal</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;"Termo que limita, individualiza a significação de um substantivo."&lt;/li&gt;
+	&lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;&lt;b&gt;&lt;u&gt;Dois &lt;/u&gt;&lt;/b&gt;alunos; &lt;ul&gt; &lt;li&gt;(Numeral)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;O/&lt;b&gt;&lt;u&gt;Um &lt;/u&gt;&lt;/b&gt;aluno; &lt;ul&gt; &lt;li&gt;(Artigo)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Aluno &lt;b&gt;&lt;u&gt;inteligente&lt;/u&gt;&lt;/b&gt;/&lt;b&gt;&lt;u&gt;de inteligência&lt;/u&gt;&lt;/b&gt; &lt;ul&gt; &lt;li&gt;(Adjetivo/Locução Adjetiva)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;&lt;u&gt;Meu&lt;/u&gt;&lt;/b&gt; aluno; &lt;ul&gt; &lt;li&gt;(Pronome)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Invasão &lt;b&gt;&lt;u&gt;dos mosquitos&lt;/u&gt;&lt;/b&gt; &lt;ul&gt; &lt;li&gt;(Locução Adjetiva)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Classes gramaticais que, sintaticamente, podem exercer o papel de Adjunto Adnominal: &lt;ul&gt; &lt;li&gt;Numeral&lt;/li&gt; &lt;li&gt;Artigo&lt;/li&gt; &lt;li&gt;Pronome&lt;/li&gt; &lt;li&gt;Adjetivo&lt;/li&gt; &lt;li&gt;Locução Adjetiva&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>158</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Predicativo do Sujeito</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Vem sempre no predicado&lt;/li&gt;
+	&lt;li&gt;Atribui característica ao sujeito &lt;ul&gt; &lt;li&gt;Vem no predicado e "manda seta" para o sujeito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Não vem apenas com verbo de ligação &lt;ul&gt; &lt;li&gt;Pode vir com qualquer verbo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Não é apenas adjetivo que pode ser predicativo do sujeito &lt;ul&gt; &lt;li&gt;Predicativo do sujeito pode ser (Substantivo/Adjetivo/Pronome/Numeral)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6114,8 +6114,10 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
-        <v>157</v>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6136,6 +6138,7 @@
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;"Termo que limita, individualiza a significação de um substantivo."&lt;/li&gt;
+        &lt;li&gt;Termo acessório&lt;/li&gt;
 	&lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;&lt;b&gt;&lt;u&gt;Dois &lt;/u&gt;&lt;/b&gt;alunos; &lt;ul&gt; &lt;li&gt;(Numeral)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;O/&lt;b&gt;&lt;u&gt;Um &lt;/u&gt;&lt;/b&gt;aluno; &lt;ul&gt; &lt;li&gt;(Artigo)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Aluno &lt;b&gt;&lt;u&gt;inteligente&lt;/u&gt;&lt;/b&gt;/&lt;b&gt;&lt;u&gt;de inteligência&lt;/u&gt;&lt;/b&gt; &lt;ul&gt; &lt;li&gt;(Adjetivo/Locução Adjetiva)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;&lt;b&gt;&lt;u&gt;Meu&lt;/u&gt;&lt;/b&gt; aluno; &lt;ul&gt; &lt;li&gt;(Pronome)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Invasão &lt;b&gt;&lt;u&gt;dos mosquitos&lt;/u&gt;&lt;/b&gt; &lt;ul&gt; &lt;li&gt;(Locução Adjetiva)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 	&lt;li&gt;Classes gramaticais que, sintaticamente, podem exercer o papel de Adjunto Adnominal: &lt;ul&gt; &lt;li&gt;Numeral&lt;/li&gt; &lt;li&gt;Artigo&lt;/li&gt; &lt;li&gt;Pronome&lt;/li&gt; &lt;li&gt;Adjetivo&lt;/li&gt; &lt;li&gt;Locução Adjetiva&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -6149,8 +6152,10 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
-        <v>158</v>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6164,16 +6169,15 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Predicativo do Sujeito</t>
+          <t>Predicativos</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Vem sempre no predicado&lt;/li&gt;
-	&lt;li&gt;Atribui característica ao sujeito &lt;ul&gt; &lt;li&gt;Vem no predicado e "manda seta" para o sujeito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Não vem apenas com verbo de ligação &lt;ul&gt; &lt;li&gt;Pode vir com qualquer verbo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Não é apenas adjetivo que pode ser predicativo do sujeito &lt;ul&gt; &lt;li&gt;Predicativo do sujeito pode ser (Substantivo/Adjetivo/Pronome/Numeral)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Vem &lt;b&gt;sempre&lt;/b&gt; no predicado&lt;/li&gt;
+	&lt;li&gt;Predicativo do Sujeito &lt;ul&gt; &lt;li&gt;Atribui característica ao sujeito &lt;ul&gt; &lt;li&gt;Vem no predicado e "manda seta" para o sujeito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Não vem apenas com verbo de ligação &lt;ul&gt; &lt;li&gt;Pode vir com qualquer verbo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Não é apenas adjetivo que pode ser predicativo do sujeito &lt;ul&gt; &lt;li&gt;Predicativo do sujeito pode ser (Substantivo/Adjetivo/Pronome/Numeral)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Predicativo do Objeto &lt;ul&gt; &lt;li&gt;Refere-se ao Objeto Direto ou Indireto&lt;/li&gt; &lt;li&gt;Se retirado, prejudica o sentido do Verbo&lt;/li&gt; &lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;Achei-o &lt;b&gt;competente&lt;/b&gt;&lt;/li&gt; &lt;li&gt;Julguei as suas perguntas &lt;b&gt;tolas&lt;/b&gt;&lt;/li&gt; &lt;li&gt;Chamaram o delegado &lt;b&gt;de inquieto&lt;/b&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -6181,6 +6185,121 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>159</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Passo a passo - distinguir Adjunto Adnominal de Predicativo do Objeto</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Coloca a seta!&lt;/li&gt;
+	&lt;li&gt;Caso o termo se refira ao Objeto, poderá ser AA ou PO &lt;ul&gt; &lt;li&gt;Olhar para o Verbo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Caso o termo não puder ser retirado (por "prejudicar" o verbo), será PO.&lt;/li&gt;
+&lt;/ol&gt;
+Dica: Quando é PO, você poderá deslocá-lo para perto do Verbo &lt;ul&gt; &lt;li&gt;pois sua conversa é com o verbo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>160</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Período Composto</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;strong&gt;Coordenação&lt;/strong&gt;
+		&lt;ul&gt;
+			&lt;li&gt;Orações Coordenadas Assindéticas (sem conectivo)&lt;/li&gt;
+			&lt;li&gt;Orações Coordenadas Sindéticas (com conectivo):
+				&lt;ul&gt;
+					&lt;li&gt;Aditivas&lt;/li&gt;
+					&lt;li&gt;Adversativas&lt;/li&gt;
+					&lt;li&gt;Alternativas&lt;/li&gt;
+					&lt;li&gt;Conclusivas&lt;/li&gt;
+					&lt;li&gt;Explicativas&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+	&lt;li&gt;&lt;strong&gt;Subordinação&lt;/strong&gt;
+		&lt;ul&gt;
+			&lt;li&gt;Orações Subordinadas Substantivas:
+				&lt;ul&gt;
+					&lt;li&gt;Subjetivas&lt;/li&gt;
+					&lt;li&gt;Objetivas Diretas&lt;/li&gt;
+					&lt;li&gt;Objetivas Indiretas&lt;/li&gt;
+					&lt;li&gt;Completivas Nominais&lt;/li&gt;
+					&lt;li&gt;Predicativas&lt;/li&gt;
+					&lt;li&gt;Apositivas&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+			&lt;li&gt;Orações Subordinadas Adjetivas:
+				&lt;ul&gt;
+					&lt;li&gt;Restritivas&lt;/li&gt;
+					&lt;li&gt;Explicativas&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+			&lt;li&gt;Orações Subordinadas Adverbiais:
+				&lt;ul&gt;
+					&lt;li&gt;Causais&lt;/li&gt;
+					&lt;li&gt;Comparativas&lt;/li&gt;
+					&lt;li&gt;Concessivas&lt;/li&gt;
+					&lt;li&gt;Condicionais&lt;/li&gt;
+					&lt;li&gt;Conformativas&lt;/li&gt;
+					&lt;li&gt;Consecutivas&lt;/li&gt;
+					&lt;li&gt;Finais&lt;/li&gt;
+					&lt;li&gt;Proporcionais&lt;/li&gt;
+					&lt;li&gt;Temporais&lt;/li&gt;
+				&lt;/ul&gt;
+			&lt;/li&gt;
+		&lt;/ul&gt;
+	&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -5800,8 +5800,10 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
-        <v>149</v>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -5820,8 +5822,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;&lt;strong&gt;Objeto Direto&lt;/strong&gt;:
+          <t xml:space="preserve">
 		&lt;ul&gt;
 			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa o sentido de um VTD&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Pronomes Oblíquos&lt;/strong&gt;:
@@ -5831,9 +5832,7 @@
 				&lt;/ul&gt;
 			&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Particularidades&lt;/strong&gt;: Objeto Direto Pleonástico e Objeto Direto Preposicionado (parece com o OI, mas não é)&lt;/li&gt;
-		&lt;/ul&gt;
-	&lt;/li&gt;
-&lt;/ul&gt;</t>
+		&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -5844,8 +5843,10 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>150</v>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -5864,8 +5865,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;&lt;strong&gt;Objeto Indireto&lt;/strong&gt;:
+          <t xml:space="preserve">
 		&lt;ul&gt;
 			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa o sentido de um VTI&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Obrigatoriamente vem precedido de preposição&lt;/li&gt;
@@ -5876,9 +5876,7 @@
 				&lt;/ul&gt;
 			&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Particularidade&lt;/strong&gt;: Objeto Indireto Pleonástico&lt;/li&gt;
-		&lt;/ul&gt;
-	&lt;/li&gt;
-&lt;/ul&gt;</t>
+		&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -5889,8 +5887,10 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
-        <v>151</v>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -5909,14 +5909,11 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;&lt;strong&gt;Complemento Nominal&lt;/strong&gt;:
+          <t xml:space="preserve">
 		&lt;ul&gt;
 			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Informação que completa o sentido de um nome (Substantivo, Adjetivo ou Advérbio)&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Vem sempre preposicionado&lt;/li&gt;
-		&lt;/ul&gt;
-	&lt;/li&gt;
-&lt;/ul&gt;</t>
+		&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -5927,8 +5924,10 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
-        <v>152</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -5947,14 +5946,11 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;&lt;strong&gt;Agente da Passiva&lt;/strong&gt;:
+          <t xml:space="preserve">
 		&lt;ul&gt;
 			&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Termo que indica quem ou o que pratica a ação verbal na voz passiva&lt;/li&gt;
 			&lt;li&gt;&lt;strong&gt;Estrutura&lt;/strong&gt;: Normalmente introduzido pelas preposições por (pelo, pela) ou de&lt;/li&gt;
-		&lt;/ul&gt;
-	&lt;/li&gt;
-&lt;/ul&gt;</t>
+		&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F150" t="n">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G158"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6299,6 +6299,181 @@
         <v>0</v>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Equação Fundamental da Contabilidade</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Ativo = Passivo + PL &lt;ul&gt; &lt;li&gt;Toda aplicação de recursos possui uma origem de igual valor&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>162</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Termos Importantes</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Ativo: Bens e direitos
+Passivo: Obrigações
+Patrimônio: Líquido Capital próprio (dos sócios)
+Aplicação de recursos: Ativo
+Origem de recursos: Passivo e Patrimônio líquido
+Capital próprio: Patrimônio Líquido
+Capital de terceiros: Passivo
+Capital aplicado: Ativo</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>163</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Situação Líquida (Patrimônio Líquido) e Equação Fundamental do Patrimônio</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Ativo maior do que passivo &lt;ul&gt; &lt;li&gt;Ativo &gt; Passivo exigível&lt;/li&gt; &lt;li&gt;Situação líquida &gt; 0&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Ativo menor do que passivo &lt;ul&gt; &lt;li&gt;passivo a descoberto&lt;/li&gt; &lt;li&gt;patrimônio líquido negativo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Ativo igual ao passivo &lt;ul&gt; &lt;li&gt;não existe capital próprio&lt;/li&gt; &lt;li&gt;Ativo = Passivo&lt;/li&gt; &lt;li&gt;Patrimônio Líquido = Zero&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Ativo igual à situação líquida &lt;ul&gt; &lt;li&gt;constituição da sociedade&lt;/li&gt; &lt;li&gt;Pode ser o caso também de uma entidade que somente trabalhe com recursos próprios&lt;/li&gt; &lt;li&gt;Ativo = Patrimônio Líquido&lt;/li&gt; &lt;li&gt;Passivo = Zero&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>164</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Atos e Fatos Contábeis</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Atos contábeis ou Atos Administrativos &lt;ul&gt; &lt;li&gt;não provocam alterações do patrimônio&lt;/li&gt; &lt;li&gt;ou apenas irão alterar o Patrimônio no futuro&lt;/li&gt; &lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;admissão de empregados&lt;/li&gt; &lt;li&gt;assinatura de um contrato de compra&lt;/li&gt; &lt;li&gt;venda&lt;/li&gt; &lt;li&gt;o aval de um título de crédito&lt;/li&gt; &lt;li&gt;uma fiança prestada em favor de terceiros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Lei 6.404/76: Art. 176. (...) § 4º As demonstrações serão complementadas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Fatos contábeis ou Fatos Administrativos &lt;ul&gt; &lt;li&gt;provocam variações no patrimônio da entidade&lt;/li&gt; &lt;li&gt;são contabilizados através &lt;ul&gt; &lt;li&gt;das contas patrimoniais (ativo, passivo, patrimônio líquido)&lt;/li&gt; &lt;li&gt;e/ou das contas de resultado (receitas e despesas)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>165</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Variações de Elementos Patrimoniais</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Subscrição do Capital Social &lt;ul&gt; &lt;li&gt;Comprometimento&lt;/li&gt; &lt;li&gt;Promessa&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Integralização do Capital Social &lt;ul&gt; &lt;li&gt;os sócios efetivamente entregam os recursos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="F115" t="n">
+        <v>4</v>
+      </c>
+      <c r="G115" t="n">
         <v>2</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123">
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
@@ -5023,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -4611,13 +4611,27 @@
           <t>&lt;ul&gt;
 	&lt;li&gt;reside nas pessoas&lt;/li&gt;
 	&lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt;
-	&lt;li&gt;dimensão técnica&lt;/li&gt;
-	&lt;li&gt;dimensão cognitiva&lt;/li&gt;
+	&lt;li&gt;dimensão técnica
+&lt;ul&gt;
+	&lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt;
+	&lt;li&gt;habilidades motoras&lt;/li&gt;
+	&lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;dimensão cognitiva
+&lt;ul&gt;
+	&lt;li&gt;modelos mentais&lt;/li&gt;
+	&lt;li&gt;crenças&lt;/li&gt;
+	&lt;li&gt;crenças&lt;/li&gt;
+	&lt;li&gt;percepções&lt;/li&gt;
+	&lt;li&gt;intuições&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G114" t="n">
         <v>2</v>
@@ -4648,20 +4662,23 @@
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;pode ser formalizado&lt;/li&gt;
-	&lt;li&gt;é documentado, codificado e sistematizado&lt;/li&gt;
+	&lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt;
+&lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G115" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>118</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -4681,15 +4698,15 @@
       <c r="E116" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Dados Quantitativos&lt;/li&gt;
-	&lt;li&gt;lógica&lt;/li&gt;
-	&lt;li&gt;objetividade&lt;/li&gt;
-	&lt;li&gt;máquina&lt;/li&gt;
+	&lt;li&gt;As decisões são tomadas com base em regras, lógica e análise objetiva da informação disponível.&lt;/li&gt;
+	&lt;li&gt;A organização é vista como uma máquina de processar dados&lt;/li&gt;
+	&lt;li&gt;eficiência e previsibilidade dos processos&lt;/li&gt;
+	&lt;li&gt;melhor escolha racional possível&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -4733,8 +4750,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v>120</v>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -4754,23 +4773,44 @@
       <c r="E118" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
-	&lt;li&gt;Dado&lt;/li&gt;
-	&lt;li&gt;Informação&lt;/li&gt;
-	&lt;li&gt;Conhecimento&lt;/li&gt;
-	&lt;li&gt;Inteligência&lt;/li&gt;
+	&lt;li&gt;Dado
+ &lt;ul&gt;
+	&lt;li&gt;elemento isolado, desprovido de significado&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Informação
+&lt;ul&gt;
+	&lt;li&gt;dado que foi contextualizado, organizado e interpretado&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Conhecimento
+&lt;ul&gt;
+	&lt;li&gt;informação combinada com experiência, julgamento, intuição e valores&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Inteligência
+&lt;ul&gt;
+	&lt;li&gt;tomar decisões complexas,&lt;/li&gt;
+	&lt;li&gt;prever cenários futuros,&lt;/li&gt;
+	&lt;li&gt;inovar&lt;/li&gt;
+	&lt;li&gt;gerar vantagem competitiva&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ol&gt;</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>121</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -4789,24 +4829,42 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Socialização&lt;/li&gt;
-	&lt;li&gt;Externalização&lt;/li&gt;
-	&lt;li&gt;Combinação&lt;/li&gt;
+          <t>&lt;ol&gt;
+	&lt;li&gt;Socialização
+&lt;ul&gt;
+	&lt;li&gt;tácito → tácito&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Externalização
+&lt;ul&gt;
+	&lt;li&gt;tácito → explícito&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Combinação
+&lt;ul&gt;
+	&lt;li&gt;explícito → explícito
+&lt;ul&gt;
+	&lt;li&gt;explícito → tácito&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 	&lt;li&gt;Internalização&lt;/li&gt;
-&lt;/ul&gt;</t>
+&lt;/ol&gt;</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>122</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -4826,26 +4884,69 @@
       <c r="E120" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
-	&lt;li&gt;Identificação&lt;/li&gt;
-	&lt;li&gt;Captura&lt;/li&gt;
-	&lt;li&gt;Aquisição&lt;/li&gt;
-	&lt;li&gt;Armazenamento&lt;/li&gt;
-	&lt;li&gt;Compartilhamento&lt;/li&gt;
-	&lt;li&gt;Aplicação&lt;/li&gt;
-	&lt;li&gt;Avaliação&lt;/li&gt;
+	&lt;li&gt;Identificação
+&lt;ul&gt;
+	&lt;li&gt;Diagnóstico&lt;/li&gt;
+	&lt;li&gt;Mapeamento&lt;/li&gt;
+	&lt;li&gt;Localização&lt;/li&gt;
+	&lt;li&gt;Reconhecimento&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Captura
+&lt;ul&gt;
+	&lt;li&gt;Entrevistas&lt;/li&gt;
+	&lt;li&gt;Relatos&lt;/li&gt;
+	&lt;li&gt;Vídeos&lt;/li&gt;
+	&lt;li&gt;Sistematização&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Aquisição
+&lt;ul&gt;
+	&lt;li&gt;obtenção de conhecimento fora da organização&lt;/li&gt;
+	&lt;li&gt;é complementar à captura&lt;/li&gt;
+	&lt;li&gt;olha para fora&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Armazenamento
+&lt;ul&gt;
+	&lt;li&gt;Bases&lt;/li&gt;
+	&lt;li&gt;Sistemas&lt;/li&gt;
+	&lt;li&gt;Repositórios&lt;/li&gt;
+	&lt;li&gt;Documentação&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Compartilhamento
+Treinamentos
+Mentorias
+Comunidades
+Ferramentas
+&lt;/li&gt;
+	&lt;li&gt;Aplicação
+&lt;ul&gt;
+	&lt;li&gt;uso efetivo do conhecimento disponível&lt;/li&gt;
+	&lt;li&gt;O conhecimento aplicado precisa ser atualizado constantemente&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Avaliação
+&lt;ul&gt;
+	&lt;li&gt;Alguns indicadores possíveis: &lt;ul&gt; &lt;li&gt;Redução&lt;/li&gt; &lt;li&gt;Aumento&lt;/li&gt; &lt;li&gt;Nível&lt;/li&gt; &lt;li&gt;Quantidade&lt;/li&gt; &lt;li&gt;Tempo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ol&gt;</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
-        <v>123</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -4865,14 +4966,26 @@
       <c r="E121" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Organizacionais&lt;/li&gt;
-	&lt;li&gt;Culturais&lt;/li&gt;
-	&lt;li&gt;Tecnológicas&lt;/li&gt;
+	&lt;li&gt;Organizacionais
+&lt;ul&gt;
+	&lt;li&gt;Alguns exemplos: &lt;ul&gt; &lt;li&gt;Hierarquias rígidas&lt;/li&gt; &lt;li&gt;Falta de tempo e recursos&lt;/li&gt; &lt;li&gt;Falta de processos formais de GC&lt;/li&gt; &lt;li&gt;Fragmentação departamental&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Culturais
+&lt;ul&gt;
+	&lt;li&gt;mais frequentes: &lt;ul&gt; &lt;li&gt;Resistência à mudança&lt;/li&gt; &lt;li&gt;Medo da exposição ou da obsolescência&lt;/li&gt; &lt;li&gt;Falta de confiança&lt;/li&gt; &lt;li&gt;Individualismo&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Tecnológicas
+&lt;ul&gt;
+	&lt;li&gt;mais comuns: &lt;ul&gt; &lt;li&gt;Falta de sistemas integrados&lt;/li&gt; &lt;li&gt;Baixa usabilidade&lt;/li&gt; &lt;li&gt;Falta de treinamento&lt;/li&gt; &lt;li&gt;Problemas de segurança da informação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G121" t="n">
         <v>2</v>
@@ -4916,8 +5029,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
-        <v>125</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -4931,22 +5046,47 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>condições capacitadoras que sustentam "Ba" (espaço compartilhado onde ocorre a criação do conhecimento)</t>
+          <t>condições capacitadoras que sustentam o "Ba" (espaço compartilhado onde ocorre a criação do conhecimento)</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Intenção (Intentionality)&lt;/li&gt;
-	&lt;li&gt;Autonomia&lt;/li&gt;
-	&lt;li&gt;Flutuação e Caos Criativo&lt;/li&gt;
-	&lt;li&gt;Redundância&lt;/li&gt;
-	&lt;li&gt;Variedade de Requisitos (Variety of Requisite)&lt;/li&gt;
+	&lt;li&gt;Intenção (Intentionality)
+&lt;ul&gt;
+	&lt;li&gt;propósito organizacional claro e compartilhado&lt;/li&gt;
+	&lt;li&gt;orienta os esforços de geração e uso do conhecimento&lt;/li&gt;
+	&lt;li&gt;liderança tem papel central&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Autonomia
+&lt;ul&gt;
+	&lt;li&gt;permitir que os indivíduos se apropriem do conhecimento que produzem&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Flutuação e Caos Criativo
+&lt;ul&gt;
+	&lt;li&gt;certo grau de instabilidade, ambiguidade ou desafio pode estimular a criação de novas ideias&lt;/li&gt;
+	&lt;li&gt;Mudanças, crises ou dilemas geram oportunidades de inovação&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Redundância
+&lt;ul&gt;
+	&lt;li&gt;sobreposição de informações, funções e responsabilidades&lt;/li&gt;
+	&lt;li&gt;previne a perda de saberes em caso de desligamentos ou mudanças&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Variedade de Requisitos (Variety of Requisite)
+&lt;ul&gt;
+	&lt;li&gt;diversidade de perspectivas, linguagens e experiências&lt;/li&gt;
+	&lt;li&gt;Equipes multidisciplinares, com backgrounds diferentes, são mais propensas à inovação&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G123" t="n">
         <v>2</v>
@@ -5064,8 +5204,10 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
-        <v>129</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5085,15 +5227,37 @@
       <c r="E127" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Big Data&lt;/li&gt;
-	&lt;li&gt;Business Intelligence (BI)&lt;/li&gt;
-	&lt;li&gt;Machine Learning (ML)&lt;/li&gt;
-	&lt;li&gt;Inteligência Artificial (IA)&lt;/li&gt;
+	&lt;li&gt;Big Data
+&lt;ul&gt;
+	&lt;li&gt;grandes volumes de dados&lt;/li&gt;
+	&lt;li&gt;volume, variedade e velocidade&lt;/li&gt;
+	&lt;li&gt;No contexto da GC, o Big Data permite &lt;ul&gt; &lt;li&gt;Capturar&lt;/li&gt; &lt;li&gt;Detectar&lt;/li&gt; &lt;li&gt;Identificar&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Business Intelligence (BI)
+&lt;ul&gt;
+	&lt;li&gt;transformam dados brutos em informações úteis&lt;/li&gt;
+	&lt;li&gt;No contexto da GC, o BI: &lt;ul&gt; &lt;li&gt;Organiza&lt;/li&gt; &lt;li&gt;Apoia&lt;/li&gt; &lt;li&gt;Ajuda&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Machine Learning (ML)
+&lt;ul&gt;
+	&lt;li&gt;permite que os sistemas aprendam automaticamente com os dados&lt;/li&gt;
+	&lt;li&gt;Na GC, o ML pode: &lt;ul&gt; &lt;li&gt;Sugerir&lt;/li&gt; &lt;li&gt;Classificar&lt;/li&gt; &lt;li&gt;Detectar&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+	&lt;li&gt;Inteligência Artificial (IA)
+&lt;ul&gt;
+	&lt;li&gt;aplicação mais abrangente&lt;/li&gt;
+	&lt;li&gt;uso de algoritmos para simular processos cognitivos humanos&lt;/li&gt;
+	&lt;li&gt;Dentro da GC, a IA: &lt;ul&gt; &lt;li&gt;Alimenta&lt;/li&gt; &lt;li&gt;Automatiza&lt;/li&gt; &lt;li&gt;Suporta&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -855,9 +855,9 @@
 	&lt;li&gt;Sistema de duas gavetas;&lt;/li&gt;
 	&lt;li&gt;Sistema dos máximos-mínimos;
 &lt;ul&gt;
-	&lt;li&gt;E min = ER + dt &lt;ul&gt; &lt;li&gt;d = consumo médio&lt;/li&gt; &lt;li&gt;t = tempo de espera médio, em dias, para reposição do material&lt;/li&gt; &lt;li&gt;ER = estoque de reserva ou de segurança&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
-	&lt;li&gt;Emin = Emin + Lote de compra.&lt;/li&gt;
-	&lt;li&gt;ponto de ressuprimento ou ponto de pedido: &lt;ul&gt; &lt;li&gt;PR = (C X TR) + ES, onde &lt;ul&gt; &lt;li&gt;C = consumo médio do item&lt;/li&gt; &lt;li&gt;TR = tempo de reposição&lt;/li&gt; &lt;li&gt;ES = estoque mínimo ou de segurança&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;E&lt;sub&gt;min&lt;/sub&gt; = ER + dt &lt;ul&gt; &lt;li&gt;d = consumo médio&lt;/li&gt; &lt;li&gt;t = tempo de espera médio, em dias, para reposição do material&lt;/li&gt; &lt;li&gt;ER = estoque de reserva ou de segurança&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
+	&lt;li&gt;E&lt;sub&gt;max&lt;/sub&gt; = E&lt;sub&gt;min&lt;/sub&gt; + Lote de compra.&lt;/li&gt;
+	&lt;li&gt;ponto de ressuprimento ou ponto de pedido: &lt;ul&gt; &lt;li&gt;PR = (d X TR) + RS, onde &lt;ul&gt; &lt;li&gt;d = consumo médio do item&lt;/li&gt; &lt;li&gt;TR = tempo de reposição&lt;/li&gt; &lt;li&gt;ER = estoque mínimo ou de segurança&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;
 &lt;/li&gt;
 	&lt;li&gt;Sistema de reposições periódicas;
@@ -905,14 +905,13 @@
 	&lt;li&gt;FIFO&lt;/li&gt;
 	&lt;li&gt;Custo Médio&lt;/li&gt;
 	&lt;li&gt;Custo de Reposição.
+	CR= PU+ACR &lt;ul&gt; &lt;li&gt;onde:
 &lt;ul&gt;
-	&lt;li&gt;CR= PU+ACR onde:&lt;/li&gt;
-	&lt;li&gt;&lt;ul&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;li&gt;CR = Custo de Reposição;&lt;/li&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;li&gt;PU = Preço Unitário do material; e&lt;/li&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;li&gt;ACR = Acréscimo do Custo de Reposição em porcentagem (%).&lt;/li&gt;&lt;/li&gt;
-	&lt;li&gt;&lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CR = Custo de Reposição;&lt;/li&gt;
+	&lt;li&gt;PU = Preço Unitário do material; e&lt;/li&gt;
+	&lt;li&gt;ACR = Acréscimo do Custo de Reposição em porcentagem (%).&lt;/li&gt;
 &lt;/ul&gt;
+&lt;/li&gt; &lt;/ul&gt;
 &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6637,6 +6637,714 @@
         <v>0</v>
       </c>
     </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>166</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Dissertação</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;exposição, discussão ou interpretação de determinada ideia&lt;/li&gt;
+	&lt;li&gt;exame crítico do assunto sobre o qual se vai escrever, com &lt;ul&gt; &lt;li&gt;raciocínio&lt;/li&gt; &lt;li&gt;clareza&lt;/li&gt; &lt;li&gt;coerência e&lt;/li&gt; &lt;li&gt;objetividade de exposição.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>167</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Questões Discursivas</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Em regra, apresentam-se os tópicos questionadores sobre os quais o candidato deverá expor ou argumentar.&lt;/li&gt;
+	&lt;li&gt;Às vezes, a banca poderá apresentar textos motivadores, os quais não precisam ser abordados na resposta.&lt;/li&gt;
+	&lt;li&gt;Dispensa-se a utilização de parágrafos de introdução e de fechamento. Entretanto, se houver tema no comando da questão, um breve parágrafo introdutório poderá ser utilizado.&lt;/li&gt;
+	&lt;li&gt;Quando não utilizar um parágrafo de introdução, o texto iniciará com a resposta direta ao primeiro tópico questionador.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>168</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Estrutura Formal da Questão Discursiva</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;podem-se ignorar os parágrafos de introdução e de fechamento&lt;/li&gt;
+	&lt;li&gt;Estrutura Formal Moderna ou Simplificada do Texto Dissertativo &lt;ul&gt; &lt;li&gt;Desenvolvimento 1&lt;/li&gt; &lt;li&gt;Desenvolvimento 2&lt;/li&gt; &lt;li&gt;[...]&lt;/li&gt; &lt;li&gt;Desenvolvimento n&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>169</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Introdução Roteiro</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;além da TESE,&lt;/li&gt;
+	&lt;li&gt;enumeram-se os argumentos/tópicos ou as bases expositivas&lt;/li&gt;
+	&lt;li&gt;o roteiro do texto é apresentado ao leitor já na introdução.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>170</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Introdução Conceito</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>apresenta-se a definição de um conceito</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>172</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Introdução por citação de jurisprudência, de entendimento doutrinário ou de diplomas legais</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>baseia-se nesses elementos para dar substrato à afirmação ou à exposição elencada no início do texto</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>173</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Desenvolvimento por Causa/Consequência</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>expõem-se as causas e os efeitos da questão tratada, dividindo-se em parágrafos cada um deles.</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>174</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Desenvolvimento por Ordenação Cronológica</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;relação “passado, presente e futuro”&lt;/li&gt;
+	&lt;li&gt;desenvolvimento comparativo entre os momentos históricos acerca de determinado assunto&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>175</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fechamento Reforço/Retorno </t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;volta a algo que já tenha sido apresentado&lt;/li&gt;
+	&lt;li&gt;forma mais elementar de arrematar a redação&lt;/li&gt;
+	&lt;li&gt;Reforça o ponto de vista apresentado na introdução (dissertação argumentativa) ou sintetizam-se bases expositivas (dissertação expositiva).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>176</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Fechamento Avanço (proposta de solução)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;vai além do que está no texto&lt;/li&gt;
+	&lt;li&gt;Deve-se ter o cuidado com a conexão lógica&lt;/li&gt;
+	&lt;li&gt;bastante utilizado em pareceres, estudos de caso e dissertações argumentativas.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>177</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Fechamento Expansão</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;excelente para situações em que o seu desenvolvimento acabou ocupando uma quantidade de linhas superior àquela inicialmente planejada&lt;/li&gt;
+	&lt;li&gt;estabelecer conexão com o último parágrafo de desenvolvimento e promover o esgotamento da discussão.&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>178</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Tamanho dos períodos</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Se o seu período ultrapassar duas ou três linhas, releia-o e veja se é possível modificá-lo</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>179</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Tamanho dos parágrafos</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>5 a 10 linhas</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>180</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Indicação de parágrafos e Respeito às margens</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Distância regular e a menor possível em relação às margens&lt;/li&gt;
+	&lt;li&gt;não se aplica &lt;ul&gt; &lt;li&gt;à primeira linha dos parágrafos &lt;ul&gt; &lt;li&gt;deve respeitar o recuo obrigatório da margem esquerda&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;à última linha destes &lt;ul&gt; &lt;li&gt;pode terminar a qualquer distância da margem direita.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;abertura de parágrafo, é necessário incluir espaço (recuo) de 1,5cm a 2,5 cm &lt;ul&gt; &lt;li&gt;deve ser regular na abertura de todos os parágrafos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>181</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Translineação</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>asdg</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>182</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Rasuras</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>apenas fazer um traço simples na palavra</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>183</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Siglas e abreviaturas</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;mencionadas pela primeira vez &lt;ul&gt; &lt;li&gt;forma por extenso, seguida da sigla entre parênteses, ou separada por hífen.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;citar apenas siglas já existentes ou consagradas&lt;/li&gt;
+	&lt;li&gt;Não são colocados pontos intermediários e ponto final&lt;/li&gt;
+	&lt;li&gt;até três letras &lt;ul&gt; &lt;li&gt;todas maiúsculas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;quatro letras ou mais &lt;ul&gt; &lt;li&gt;todas maiúsculas &lt;ul&gt; &lt;li&gt;cada uma de suas letras ou parte delas é pronunciada separadamente&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;somente com a inicial maiúscula &lt;ul&gt; &lt;li&gt;formam uma palavra pronunciável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;manter com maiúsculas e minúsculas as siglas que originalmente foram criadas com essa estrutura para se diferenciarem de outras &lt;ul&gt; &lt;li&gt;independentemente de seu tamanho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;siglas de origem estrangeira &lt;ul&gt; &lt;li&gt;adotar a sigla e seu nome em português quando houver forma traduzida, ou&lt;/li&gt; &lt;li&gt;adotar a forma original da sigla estrangeira quando esta não tiver correspondente em português, mesmo que o seu nome por extenso em português não corresponda perfeitamente à sigla.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;adicionar a letra s (sempre minúscula) para indicar o plural das siglas &lt;ul&gt; &lt;li&gt;somente quando a concordância gramatical assim o exigir.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>184</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Posso pular linhas?</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>A resposta é, definitivamente, NÃO!</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>185</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Como Utilizar Números em Provas Discursivas</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;forma extensa &lt;ul&gt; &lt;li&gt;formar apenas uma palavra &lt;ul&gt; &lt;li&gt;será grafado apenas por extenso.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;doze,&lt;/li&gt; &lt;li&gt;vinte,&lt;/li&gt; &lt;li&gt;nove.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;formar duas ou mais palavras &lt;ul&gt; &lt;li&gt;deverá constar o número cardinal seguido do extenso entre parênteses.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;21 (vinte e um),&lt;/li&gt; &lt;li&gt;34 (trinta e quatro).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;números utilizados em datas &lt;ul&gt; &lt;li&gt;não serão precedidos de zero &lt;ul&gt; &lt;li&gt;Ex.: 3/4/2018, e não 03/04/2018&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;referências ao primeiro dia do mês &lt;ul&gt; &lt;li&gt;será utilizado número ordinal &lt;ul&gt; &lt;li&gt;Ex.: 1º/12/2018, e não 1/12/2018&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;indicação dos anos &lt;ul&gt; &lt;li&gt;será grafada sem o ponto entre as casas do milhar e da centena &lt;ul&gt; &lt;li&gt;Ex.: 27/11/1981, e não 27/11/1.981&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Equivalências e Negações Lógicas</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Equivalências lógicas</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Equivalência contrapositiva &lt;ul&gt; &lt;li&gt;p→q ≡ ~q→~p&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Transformação da condicional em disjunção inclusiva &lt;ul&gt; &lt;li&gt;p→q ≡ ~p∨q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Transformação disjunção inclusiva em condicional &lt;ul&gt; &lt;li&gt;p∨q ≡ ~p→q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>187</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Equivalências e Negações Lógicas</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Negações lógicas</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Negação da conjunção e da disjunção inclusiva (Leis de De Morgan) &lt;ul&gt; &lt;li&gt;~(p∧q) ≡ ~p∨~q&lt;/li&gt; &lt;li&gt;~(p∨q) ≡ ~p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Negação da condicional &lt;ul&gt; &lt;li&gt;~(p→q) ≡ p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,7 +745,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>&lt;ul&gt; &lt;li&gt;Estoque de Segurança ou estoque isolado &lt;ul&gt; &lt;li&gt;Compensa as incertezas entre fornecimento e demanda&lt;/li&gt; &lt;li&gt;é definido como uma % do estoque total&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque cíclico &lt;ul&gt; &lt;li&gt;empresas que possuem vários produtos e precisam produzir ciclos de produtos&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de desacoplamento &lt;ul&gt; &lt;li&gt;arranjo físico de processo&lt;/li&gt; &lt;li&gt;Promove uma independência entre os estágios do processo produtivo&lt;/li&gt; &lt;li&gt;o estoque fica aguardando uma fila em cada um dos estágios&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de antecipação &lt;ul&gt; &lt;li&gt;usado para lidar com a demanda sazonal&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoques no canal de distribuição &lt;ul&gt; &lt;li&gt;Também chamado de estoque em trânsito&lt;/li&gt; &lt;li&gt;sendo transportado ou mesmo aguardando em centros de distribuição&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;</t>
+          <t>&lt;ul&gt; &lt;li&gt;Estoque de Segurança ou estoque isolado &lt;ul&gt; &lt;li&gt;Compensa as incertezas entre fornecimento e demanda&lt;/li&gt; &lt;li&gt;é definido como uma % do estoque total&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque cíclico &lt;ul&gt; &lt;li&gt;empresas que possuem vários produtos e precisam produzir ciclos de produtos&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de desacoplamento &lt;ul&gt; &lt;li&gt;arranjo físico de processo&lt;/li&gt; &lt;li&gt;Promove uma independência entre os estágios do processo produtivo&lt;/li&gt; &lt;li&gt;o estoque fica aguardando uma fila em cada um dos estágios&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoque de antecipação &lt;ul&gt; &lt;li&gt;usado para lidar com a demanda sazonal&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;Estoques no canal de distribuição ou estoque em trânsito&lt;ul&gt; &lt;li&gt;sendo transportado ou mesmo aguardando em centros de distribuição&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -7345,6 +7345,272 @@
         <v>0</v>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Definição oficial de contabilidade</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;doutrina  (IPECAFI)&lt;ul&gt; &lt;li&gt;objetivamente, um sistema de informação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>189</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Escrituração</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>técnica contábil que reúne todos os documentos</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>190</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>objeto de estudo da contabilidade</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>patrimônio</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>campo de aplicação da Contabilidade</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Aziendas &lt;ul&gt; 
+&lt;li&gt;patrimônio de uma pessoa que é gerido de maneira organizada&lt;/li&gt;
+&lt;li&gt;azienda econômica&lt;/li&gt;
+&lt;li&gt;aziendas econômico-sociais&lt;/li&gt;
+&lt;li&gt;aziendas sociais&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>192</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>finalidade principal da ciência contábil ou objetivo</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>193</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>usuários das demonstrações contábeis externos ou internos</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>194</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Muitos investidores, credores por empréstimos e outros credores</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>195</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Gestão de Estoques</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
+	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -752,7 +752,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -7611,6 +7611,993 @@
         <v>0</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>196</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Gestão de Estoques</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Como determinar o estoque mínimo</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>197</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Constituição Federal de 1988, Art. 7º</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>198</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Consolidação das leis do Trabalho, Capítulo V</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;responsabilidades dos órgãos&lt;/li&gt;
+	&lt;li&gt;responsabilidades das Empresas e dos Trabalhadores&lt;/li&gt;
+	&lt;li&gt;na Seção IV, trata do Equipamento de proteção Individual &lt;ul&gt; &lt;li&gt;deverá ser entregue pelo Empregador&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Equipamento de Proteção Individual só poderá ser posto à venda ou utilizado com a indicação do Certificado de Aprovação do Ministério do Trabalho&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>199</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Autosserviço</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Acesso pelo cidadão a serviço público</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>200</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Base nacional de serviços públicos</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Base de dados que contém as informações</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>201</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Dados abertos</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Dados acessíveis ao público</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>202</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Dado acessível ao público</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Qualquer dado gerado ou acumulado</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>203</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Formato aberto</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Formato de arquivo não proprietário</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>204</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Governo como plataforma</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Infraestrutura tecnológica que facilite</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>205</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Laboratório de inovação</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Espaço aberto à participação</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>206</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Plataformas de governo digital</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>207</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Registros de referência</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Informação íntegra e precisa</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>208</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Transparência ativa</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Disponibilização de dados pela administração pública</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>209</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Governo Digital</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;a administração pública deve utilizar soluções digitais&lt;/li&gt;
+	&lt;li&gt;processos administrativos eletrônicos&lt;/li&gt;
+	&lt;li&gt;documentos e atos processuais praticados em meio digital&lt;/li&gt;
+	&lt;li&gt;realização dos atos processuais em meio eletrônico&lt;/li&gt;
+	&lt;li&gt;acesso do interessado ao processo administrativo&lt;/li&gt;
+	&lt;li&gt;formato e o armazenamento dos documentos digitais&lt;/li&gt;
+	&lt;li&gt;prestação digital dos serviços públicos&lt;/li&gt;
+	&lt;li&gt;Cada ente federado&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Redes de Conhecimento</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
+	&lt;li&gt;Objetivo: &lt;ul&gt; &lt;li&gt;fortalecer o trabalho colaborativo&lt;/li&gt; &lt;li&gt;gerar, compartilhar e disseminar conhecimentos e experiências&lt;/li&gt; &lt;li&gt;identificar e avaliar novas tecnologias&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Papeis &lt;ul&gt; &lt;li&gt;formular propostas relacionadas a padrões, políticas, guias e manuais&lt;/li&gt; &lt;li&gt;promover discussões sobre desafios e possibilidades de ação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;A participação é aberta a todos os órgãos e entidades&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Componentes do Governo Digital</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
+	&lt;li&gt;Plataformas de Governo Digital&lt;/li&gt;
+	&lt;li&gt;Prestação Digital dos Serviços Públicos&lt;/li&gt;
+	&lt;li&gt;Direitos dos Usuários da Prestação Digital de Serviços Públicos&lt;/li&gt;
+	&lt;li&gt;Cartas de Serviços ao Usuário (Lei nº 13.460/2017)&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>212</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Princípios do governo digital</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;acesso centralizado&lt;/li&gt;
+	&lt;li&gt;prestação de contas&lt;/li&gt;
+	&lt;li&gt;simplificação&lt;/li&gt;
+	&lt;li&gt;proteção de dados pessoais&lt;/li&gt;
+	&lt;li&gt;Apoio a entes federados&lt;/li&gt;
+	&lt;li&gt;Uso de assinatura eletrônicas&lt;/li&gt;
+	&lt;li&gt;atendimento aos idosos&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>213</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Base Nacional de Serviços Públicos</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
+	&lt;li&gt;Pode ser instutuido pelo Poder Executivo&lt;/li&gt;
+	&lt;li&gt;informações devem ser disponibilizadas em formato &lt;ul&gt; &lt;li&gt;aberto,&lt;/li&gt; &lt;li&gt;interoperável&lt;/li&gt; &lt;li&gt;e seguindo um padrão comum a todos os entes.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>214</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Plataformas de Governo Digital</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instrumentos para os entes federativos disponibilizem seus serviços públicos
+devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
+padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Prestação Digital dos Serviços Públicos</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>216</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Normas Regulamentadoras do Trabalho</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
+	&lt;li&gt;elaboração/revisão &lt;ul&gt; &lt;li&gt;Ministério do Trabalho&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;37 Normas Regulamentadoras&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NR 1</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+&lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
+	&lt;li&gt;base&lt;/li&gt;
+	&lt;li&gt;disposições gerais&lt;/li&gt;
+	&lt;li&gt;campo de aplicação&lt;/li&gt;
+	&lt;li&gt;definições&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>218</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NR 2</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Inspeção Prévia</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>219</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NR 3</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
+	&lt;li&gt;diretrizes de avaliação de riscos graves e iminentes&lt;/li&gt;
+	&lt;li&gt;Embargo: paralisação parcial ou total da obra.&lt;/li&gt;
+	&lt;li&gt;Interdição: paralisação parcial ou total da atividade, máquina, setor ou até estabelecimento&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>220</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>221</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NR 5</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>222</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>NR 6</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
+	&lt;li&gt;EPI: dispositivo ou produto, de uso individual utilizado pelo trabalhador&lt;/li&gt;
+	&lt;li&gt;Equipamento Conjugado de Proteção Individual: composto por vários dispositivos&lt;/li&gt;
+	&lt;li&gt;Compete ao SESMT, ouvida a CIPA e trabalhadores usuários, recomendar ao empregador o EPI&lt;/li&gt;
+	&lt;li&gt;O EPI, de fabricação nacional ou importado, só poderá ser posto à venda ou utilizado com a indicação do Certificado de Aprovação - CA&lt;/li&gt;
+	&lt;li&gt;Caberá ao órgão nacional competente &lt;ul&gt; &lt;li&gt;cadastrar&lt;/li&gt; &lt;li&gt;receber&lt;/li&gt; &lt;li&gt;estabelecer&lt;/li&gt; &lt;li&gt;emitir&lt;/li&gt; &lt;li&gt;fiscalizar&lt;/li&gt; &lt;li&gt;suspender&lt;/li&gt; &lt;li&gt;cancelar&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;responsabilidades quanto ao EPI &lt;ul&gt; &lt;li&gt;Empregador &lt;ul&gt; &lt;li&gt;adquirir&lt;/li&gt; &lt;li&gt;exigir&lt;/li&gt; &lt;li&gt;fornecer&lt;/li&gt; &lt;li&gt;orientar&lt;/li&gt; &lt;li&gt;substituir&lt;/li&gt; &lt;li&gt;responsabilizar-se&lt;/li&gt; &lt;li&gt;comunicar&lt;/li&gt; &lt;li&gt;registrar&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Empregado &lt;ul&gt; &lt;li&gt;usar&lt;/li&gt; &lt;li&gt;responsabilizar-se&lt;/li&gt; &lt;li&gt;comunicar&lt;/li&gt; &lt;li&gt;cumprir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>223</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>NR 7</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
+	&lt;li&gt;competência do Empregador: &lt;ul&gt; &lt;li&gt;garantir&lt;/li&gt; &lt;li&gt;custear&lt;/li&gt; &lt;li&gt;indicar&lt;/li&gt; &lt;li&gt;no caso de&lt;/li&gt; &lt;li&gt;inexistindo médico do trabalho&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NR 8</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
+	&lt;li&gt;requisitos mínimos que devem ser observados nas edificações &lt;ul&gt; &lt;li&gt;altura do piso ao teto de acordo com as posturas municipais&lt;/li&gt; &lt;li&gt;pisos o não devem apresentar saliências nem depressões&lt;/li&gt; &lt;li&gt;aberturas nos pisos e nas paredes devem ser protegidas&lt;/li&gt; &lt;li&gt;rampas e as escadas devem ser construídas de acordo com as normas&lt;/li&gt; &lt;li&gt;passagens dos locais de trabalho&lt;/li&gt; &lt;li&gt;andares acima do solo devem dispor de proteção adequada contra quedas&lt;/li&gt; &lt;li&gt;partes externas devem observar as normas técnicas&lt;/li&gt; &lt;li&gt;pisos e as paredes devem ser, sempre que necessário, impermeabilizados e protegidos contra a umidade.&lt;/li&gt; &lt;li&gt;coberturas devem assegurar proteção contra as chuvas.&lt;/li&gt; &lt;li&gt;edificações devem ser projetadas e construídas de modo a evitar insolação excessiva ou falta de insolação.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115">
@@ -4670,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -4708,7 +4708,7 @@
         <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -4802,7 +4802,7 @@
         <v>7</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -4987,7 +4987,7 @@
         <v>4</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
@@ -5088,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
@@ -5199,7 +5199,7 @@
         <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -5259,7 +5259,7 @@
         <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -8598,6 +8598,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>225</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>NR 9</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
+	&lt;li&gt;estabelece os requisitos para a avaliação&lt;/li&gt;
+	&lt;li&gt;A identificação deverá considerar: &lt;ul&gt; &lt;li&gt;descrição&lt;/li&gt; &lt;li&gt;identificação&lt;/li&gt; &lt;li&gt;possíveis&lt;/li&gt; &lt;li&gt;fatores&lt;/li&gt; &lt;li&gt;medidas&lt;/li&gt; &lt;li&gt;identificação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Avaliação das Exposições Ocupacionais &lt;ul&gt; &lt;li&gt;qualitativas&lt;/li&gt; &lt;li&gt;quantitativas &lt;ol type="a"&gt; &lt;li&gt;comprovar&lt;/li&gt; &lt;li&gt;dimensionar&lt;/li&gt; &lt;li&gt;subsidiar&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Medidas de Prevenção e Controle das Exposições Ocupacionais &lt;ul&gt; &lt;li&gt;integram os controles dos riscos do PGR e devem ser incorporados ao Plano de Ação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disposições Transitórias &lt;ul&gt; &lt;li&gt;Na ausência de limites de tolerância previstos na NR-15, devem ser utilizados como referência os da American Conference of Governmental Industrial Higyenists - ACGIH.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -4390,7 +4390,7 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -8636,6 +8636,293 @@
         <v>0</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>226</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Gestão da Produção e Operações</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>produção intermitente</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
+	&lt;li&gt;organizado por lotes ou encomendas, em vez de um fluxo contínuo.&lt;/li&gt;
+	&lt;li&gt;alta variedade e baixo volume&lt;/li&gt;
+	&lt;li&gt;Produção puxada&lt;/li&gt;
+	&lt;li&gt;setup&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>227</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Gestão da Produção e Operações</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>cable belt (correia de cabo)</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
+	&lt;li&gt;projetado para longas distâncias e terrenos difíceis&lt;/li&gt;
+	&lt;li&gt;separa a função de transporte da função de tração &lt;ul&gt; &lt;li&gt;cabos de aço laterais movem a correia&lt;/li&gt; &lt;li&gt;a correia apenas carrega o material&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Sinônimos/Termos Relacionados: &lt;ul&gt; &lt;li&gt;Correia transportadora de cabo&lt;/li&gt; &lt;li&gt;Cable Belt Conveyor&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>228</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
+	&lt;li&gt;KPIs tipicos &lt;ul&gt; &lt;li&gt;Uso da metodologia de gestão de projetos&lt;/li&gt; &lt;li&gt;Estabelecimento dos processos de controle&lt;/li&gt; &lt;li&gt;Uso de métricas intermediárias&lt;/li&gt; &lt;li&gt;Qualidade dos recursos atribuídos versus planejados&lt;/li&gt; &lt;li&gt;Envolvimento do cliente&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>229</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;modelos de planejamento &lt;ul&gt; &lt;li&gt;disponíveis para auxiliar na programação estratégica de recursos.&lt;/li&gt; &lt;li&gt;frequentemente chamados de modelos de planejamento agregado.&lt;/li&gt; &lt;li&gt;permitem que uma organização identifique o excesso de alocação de recursos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Outro problema &lt;ul&gt; &lt;li&gt;determinar quais projetos exigem os melhores recursos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Outro componente-chave &lt;ul&gt; &lt;li&gt;nível de tolerância ao risco da organização&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>230</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>BI (Business Intelligence)</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Dados estruturados&lt;/li&gt;
+	&lt;li&gt;Função: coletar, organizar, analisar e transformar dados em informações úteis para apoiar decisões estratégicas e operacionais.&lt;/li&gt;
+	&lt;li&gt;Exemplos: &lt;ul&gt; &lt;li&gt;Relatório de Vendas,&lt;/li&gt; &lt;li&gt;Dashboards de Desempenho,&lt;/li&gt; &lt;li&gt;Análise de Tendências de Mercado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>231</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>licenciamento de patentes</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;identificação de oportunidades de mercado&lt;/li&gt;
+	&lt;li&gt;licenciamento transforma pesquisa e desenvolvimento (P&amp;D) em ativos financeiros e parcerias estratégicas&lt;/li&gt;
+	&lt;li&gt;transferência de tecnologia&lt;/li&gt;
+	&lt;li&gt;mecanismo que coloca inovações desenvolvidas no mercado&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>232</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>233</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Gestão de Investimentos e Risco</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Índices Financeiros</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;ul&gt;
+	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;ÍNDICES DE ATIVIDADE &lt;ul&gt; &lt;li&gt;Giro do estoque = Custo das mercadorias vendidas/Estoque&lt;/li&gt; &lt;li&gt;Prazo médio de recebimento = Contas a receber de clientes/Valor diário médio das vendas&lt;/li&gt; &lt;li&gt;Prazo médio de recebimento = (Contas a receber de clientes x 360)/Vendas anuais&lt;/li&gt; &lt;li&gt;Prazo médio de pagamento = Fornecedores/Valor diário médio das compras&lt;/li&gt; &lt;li&gt;Prazo médio de pagamento = (Fornecedore x 360)/Compras anuais&lt;/li&gt; &lt;li&gt;Giro do ativo total = Vendas/Ativo total&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;ÍNDICES DE ENDIVIDAMENTO &lt;ul&gt; &lt;li&gt;Índice de endividamento geral = Passivo total/Ativo total&lt;/li&gt; &lt;li&gt;Índice de cobertura de juros = Lucro antes de juros e imposto de renda/Juros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;ÍNDICES DE RENTABILIDADE &lt;ul&gt; &lt;li&gt;Margem de lucro bruto = (Receita de vendas – Custo das mercadorias vendidas)/Receita de vendas = Lucro bruto/Receita de vendas&lt;/li&gt; &lt;li&gt;Margem de lucro operacional = Lucro operacional/Receita de vendas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7108,7 +7108,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Translineação</t>
+          <t>Rasuras</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>asdg</t>
+          <t>apenas fazer um traço simples na palavra</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -7139,7 +7139,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -7153,41 +7153,10 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Rasuras</t>
+          <t>Siglas e abreviaturas</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
-        <is>
-          <t>apenas fazer um traço simples na palavra</t>
-        </is>
-      </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>183</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>Siglas e abreviaturas</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;mencionadas pela primeira vez &lt;ul&gt; &lt;li&gt;forma por extenso, seguida da sigla entre parênteses, ou separada por hífen.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7201,8 +7170,39 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>184</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Posso pular linhas?</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>A resposta é, definitivamente, NÃO!</t>
+        </is>
+      </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -7210,7 +7210,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -7224,41 +7224,10 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Posso pular linhas?</t>
+          <t>Como Utilizar Números em Provas Discursivas</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
-        <is>
-          <t>A resposta é, definitivamente, NÃO!</t>
-        </is>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>185</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>Como Utilizar Números em Provas Discursivas</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;forma extensa &lt;ul&gt; &lt;li&gt;formar apenas uma palavra &lt;ul&gt; &lt;li&gt;será grafado apenas por extenso.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;doze,&lt;/li&gt; &lt;li&gt;vinte,&lt;/li&gt; &lt;li&gt;nove.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;formar duas ou mais palavras &lt;ul&gt; &lt;li&gt;deverá constar o número cardinal seguido do extenso entre parênteses.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;21 (vinte e um),&lt;/li&gt; &lt;li&gt;34 (trinta e quatro).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7267,35 +7236,35 @@
 </t>
         </is>
       </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Equivalências lógicas</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Equivalência contrapositiva &lt;ul&gt; &lt;li&gt;p→q ≡ ~q→~p&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7304,33 +7273,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F183" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
         <v>187</v>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Negações lógicas</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Negação da conjunção e da disjunção inclusiva (Leis de De Morgan) &lt;ul&gt; &lt;li&gt;~(p∧q) ≡ ~p∨~q&lt;/li&gt; &lt;li&gt;~(p∨q) ≡ ~p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7338,35 +7307,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F184" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D184" t="inlineStr">
         <is>
           <t>Definição oficial de contabilidade</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E184" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7374,6 +7343,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>189</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Escrituração</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>técnica contábil que reúne todos os documentos</t>
+        </is>
+      </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
@@ -7383,7 +7383,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -7397,12 +7397,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Escrituração</t>
+          <t>objeto de estudo da contabilidade</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>técnica contábil que reúne todos os documentos</t>
+          <t>patrimônio</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -7413,8 +7413,10 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
-        <v>190</v>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -7428,43 +7430,10 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>objeto de estudo da contabilidade</t>
+          <t>campo de aplicação da Contabilidade</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
-        <is>
-          <t>patrimônio</t>
-        </is>
-      </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Aspectos Introdutórios</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>campo de aplicação da Contabilidade</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
         <is>
           <t>Aziendas &lt;ul&gt; 
 &lt;li&gt;patrimônio de uma pessoa que é gerido de maneira organizada&lt;/li&gt;
@@ -7474,6 +7443,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>192</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>finalidade principal da ciência contábil ou objetivo</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+        </is>
+      </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -7497,12 +7497,15 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>finalidade principal da ciência contábil ou objetivo</t>
+          <t>usuários das demonstrações contábeis externos ou internos</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -7514,7 +7517,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -7528,15 +7531,12 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>usuários das demonstrações contábeis externos ou internos</t>
+          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Muitos investidores, credores por empréstimos e outros credores</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -7548,26 +7548,29 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Contabilidade Gerencial</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Gestão de Estoques</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
+          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Muitos investidores, credores por empréstimos e outros credores</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
+	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -7579,7 +7582,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -7593,14 +7596,14 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
+          <t>Como determinar o estoque mínimo</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
-	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -7613,7 +7616,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -7622,19 +7625,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Gestão de Estoques</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Como determinar o estoque mínimo</t>
+          <t>Constituição Federal de 1988, Art. 7º</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -7647,7 +7650,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -7661,44 +7664,10 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Constituição Federal de 1988, Art. 7º</t>
+          <t>Consolidação das leis do Trabalho, Capítulo V</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>198</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>Consolidação das leis do Trabalho, Capítulo V</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;responsabilidades dos órgãos&lt;/li&gt;
@@ -7708,6 +7677,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>199</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Autosserviço</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Acesso pelo cidadão a serviço público</t>
+        </is>
+      </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
@@ -7717,7 +7717,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -7731,12 +7731,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Autosserviço</t>
+          <t>Base nacional de serviços públicos</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Acesso pelo cidadão a serviço público</t>
+          <t>Base de dados que contém as informações</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7748,7 +7748,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -7762,12 +7762,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Base nacional de serviços públicos</t>
+          <t>Dados abertos</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Base de dados que contém as informações</t>
+          <t>Dados acessíveis ao público</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -7779,7 +7779,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dados abertos</t>
+          <t>Dado acessível ao público</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Dados acessíveis ao público</t>
+          <t>Qualquer dado gerado ou acumulado</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7810,7 +7810,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7824,12 +7824,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Dado acessível ao público</t>
+          <t>Formato aberto</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Qualquer dado gerado ou acumulado</t>
+          <t>Formato de arquivo não proprietário</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7841,7 +7841,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Formato aberto</t>
+          <t>Governo como plataforma</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Formato de arquivo não proprietário</t>
+          <t>Infraestrutura tecnológica que facilite</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -7872,7 +7872,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Governo como plataforma</t>
+          <t>Laboratório de inovação</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Infraestrutura tecnológica que facilite</t>
+          <t>Espaço aberto à participação</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -7903,7 +7903,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7917,12 +7917,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Laboratório de inovação</t>
+          <t>Plataformas de governo digital</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Espaço aberto à participação</t>
+          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -7934,7 +7934,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Plataformas de governo digital</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
+          <t>Informação íntegra e precisa</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -7965,7 +7965,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -7979,12 +7979,12 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Informação íntegra e precisa</t>
+          <t>Disponibilização de dados pela administração pública</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -7996,7 +7996,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -8010,41 +8010,10 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Transparência ativa</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública</t>
-        </is>
-      </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>209</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;a administração pública deve utilizar soluções digitais&lt;/li&gt;
@@ -8058,35 +8027,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -8096,35 +8065,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -8135,33 +8104,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
         <v>212</v>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -8174,33 +8143,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
         <v>213</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -8209,39 +8178,72 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
         <v>214</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B210" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C210" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Plataformas de Governo Digital</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t xml:space="preserve">instrumentos para os entes federativos disponibilizem seus serviços públicos
 devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
 padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
         </is>
       </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Prestação Digital dos Serviços Públicos</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
@@ -8250,58 +8252,25 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A212" t="n">
+        <v>216</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Prestação Digital dos Serviços Públicos</t>
+          <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
-        <is>
-          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>216</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Normas Regulamentadoras do Trabalho</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -8310,35 +8279,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -8349,6 +8318,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>218</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NR 2</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Inspeção Prévia</t>
+        </is>
+      </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
@@ -8358,7 +8358,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -8372,41 +8372,10 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NR 2</t>
+          <t>NR 3</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
-        <is>
-          <t>Inspeção Prévia</t>
-        </is>
-      </c>
-      <c r="F215" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>219</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>NR 3</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -8416,6 +8385,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>220</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F216" t="n">
         <v>0</v>
       </c>
@@ -8425,7 +8428,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -8439,15 +8442,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -8459,7 +8459,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -8473,41 +8473,10 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>222</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -8520,33 +8489,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>223</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -8554,35 +8523,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -8591,33 +8560,33 @@
 </t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
         <v>225</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -8629,33 +8598,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>226</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -8666,33 +8635,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="223">
+      <c r="A223" t="n">
         <v>227</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -8702,33 +8671,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="n">
+    <row r="224">
+      <c r="A224" t="n">
         <v>228</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -8737,33 +8706,33 @@
 </t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>229</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8773,33 +8742,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>230</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -8808,33 +8777,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
         <v>231</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8845,6 +8814,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>232</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F228" t="n">
         <v>0</v>
       </c>
@@ -8854,7 +8857,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -8863,49 +8866,15 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+          <t>Índices Financeiros</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
-        <v>233</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Índices Financeiros</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8916,10 +8885,10 @@
 </t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6496,8 +6496,10 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
-        <v>162</v>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -6518,7 +6520,7 @@
         <is>
           <t>Ativo: Bens e direitos
 Passivo: Obrigações
-Patrimônio: Líquido Capital próprio (dos sócios)
+Patrimônio Líquido: Capital próprio (dos sócios)
 Aplicação de recursos: Ativo
 Origem de recursos: Passivo e Patrimônio líquido
 Capital próprio: Patrimônio Líquido
@@ -8892,6 +8894,152 @@
         <v>0</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>234</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Gestão de Investimentos e Risco</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
+	&lt;li&gt;Menor Taxa de Cupom&lt;/li&gt;
+	&lt;li&gt;Expectativa de Inflação em Alta&lt;/li&gt;
+	&lt;li&gt;Baixa Liquidez&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Engenharia de Produto</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Processo de Desenvolvimento de Produto</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Pré-Desenvolvimento &lt;ol&gt; &lt;li&gt;Planejamento do Projeto &lt;ul&gt; &lt;li&gt;são realizadas &lt;ul&gt; &lt;li&gt;brainstorming&lt;/li&gt; &lt;li&gt;visitas a feiras técnicas&lt;/li&gt; &lt;li&gt;análise de produtos da concorrência&lt;/li&gt; &lt;li&gt;pesquisa de mercado&lt;/li&gt; &lt;li&gt;elaboração das especificações do projeto&lt;/li&gt; &lt;li&gt;dentre outros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
+	&lt;li&gt;Desenvolvimento &lt;ol&gt; &lt;li&gt;Projeto Informacional&lt;/li&gt; &lt;li&gt;Projeto Conceitual&lt;/li&gt; &lt;li&gt;Projeto Detalhado&lt;/li&gt; &lt;li&gt;Preparação da Produção&lt;/li&gt; &lt;li&gt;Lançamento do Produto&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
+	&lt;li&gt;Pós-Desenvolvimento &lt;ol&gt; &lt;li&gt;Acompanhar Produto/Processo&lt;/li&gt; &lt;li&gt;Descontinuar Produto&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Gestão da Produção e Operações</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>sistema ERP</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Único Banco de Dados Centralizado&lt;/li&gt;
+	&lt;li&gt;Relação com Tabelas&lt;/li&gt;
+	&lt;li&gt;Objetivo: Eliminar a redundância de dados e garantir que a informação seja a mesma (tempo real) para todos os departamentos.&lt;/li&gt;
+	&lt;li&gt;Relacionamentos Diretos &lt;ul&gt; &lt;li&gt;Finanças&lt;/li&gt; &lt;li&gt;Suprimentos&lt;/li&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;li&gt;Comercial/Vendas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Relacionamentos Indiretos &lt;ul&gt; &lt;li&gt;Marketing&lt;/li&gt; &lt;li&gt;Avaliação de Mercado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>237</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2245,7 +2245,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -2903,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G68" t="n">
         <v>1</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -4466,7 +4466,7 @@
         <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -8425,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217">
@@ -9040,6 +9040,399 @@
         <v>0</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>238</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
+	&lt;li&gt;2º Especificações Técnicas: Descrição da Engenharia/TI (como será feito tecnicamente).&lt;/li&gt;
+	&lt;li&gt;Alinhamento: A definição do negócio deve preceder a definição técnica para garantir que a tecnologia sirva ao processo.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>239</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>240</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
+	&lt;li&gt;SaaS (Software as a Service)&lt;/li&gt;
+	&lt;li&gt;Plataformas Móveis Digitais&lt;/li&gt;
+	&lt;li&gt;Impacto &lt;ul&gt; &lt;li&gt;agilidade&lt;/li&gt; &lt;li&gt;custos&lt;/li&gt; &lt;li&gt;modelo de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>241</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>EDI (Electronic Data Interchange)</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
+	&lt;li&gt;Automatiza o envio de pedidos, faturas e avisos de expedição.&lt;/li&gt;
+	&lt;li&gt;Impacto na Produção: &lt;ul&gt; &lt;li&gt;Ferramenta de integração da Cadeia de Suprimentos (SCM)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Permite orientar e monitorar o processo produtivo em relação aos pedidos, pois provê visibilidade e dados em tempo real entre os elos da cadeia.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>242</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Técnica Nominal de Grupo (TNG)</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
+	&lt;li&gt;Diferente do Brainstorming livre &lt;ul&gt; &lt;li&gt;tiliza votação/ranking silencioso para priorizar opções.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Quando usar &lt;ul&gt; &lt;li&gt;alguns membros dominam a discussão.&lt;/li&gt; &lt;li&gt;problemas complexos onde o conhecimento está fragmentado entre os membros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Objetivo: Potencializar a criatividade e garantir que todas as vozes sejam pesadas igualmente na decisão final.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>243</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
+	&lt;li&gt;&lt;b&gt;Brainstorming&lt;/b&gt;: Livre, foco em quantidade, pode ser caótico.&lt;/li&gt;
+	&lt;li&gt;&lt;b&gt;TNG&lt;/b&gt;: Estruturada, encontro presencial (geralmente), foco em priorização/votação.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>244</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Gestão Ambiental: Reativa vs. Proativa</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
+	&lt;li&gt;&lt;b&gt;Proativa (Gestão)&lt;/b&gt;: Foco na Prevenção na Fonte, Ecoeficiência e Análise de Ciclo de Vida.&lt;/li&gt;
+	&lt;li&gt;&lt;b&gt;Principal Diferença&lt;/b&gt;: A proativa busca eliminar a causa da poluição no projeto/processo, enquanto a reativa foca apenas em mitigar o dano já gerado.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>245</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Variável Ambiental no Negócio</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
+	&lt;li&gt;Base Normativa: ISO 14001 (Requisito de Liderança).&lt;/li&gt;
+	&lt;li&gt;Lógica: Sem o suporte estratégico do topo, as metas ecológicas não recebem recursos nem integração com os processos de negócio da firma.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>246</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
+	&lt;li&gt;Classe II-A (Não Inertes): Podem ter propriedades como biodegradabilidade ou solubilidade em água (não são perigosos, mas reagem).&lt;/li&gt;
+	&lt;li&gt;Classe II-B (Inertes): Não se degradam nem se solubilizam (ex: lama de minério de ferro pura, entulho).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>247</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Não geração.&lt;/li&gt;
+	&lt;li&gt;Redução.&lt;/li&gt;
+	&lt;li&gt;Reutilização.&lt;/li&gt;
+	&lt;li&gt;Reciclagem.&lt;/li&gt;
+	&lt;li&gt;Compostagem.&lt;/li&gt;
+	&lt;li&gt;Recuperação energética.&lt;/li&gt;
+	&lt;li&gt;Disposição final (Rejeitos).&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
+	&lt;li&gt;&lt;b&gt;Rejeito&lt;/b&gt;: Sobra do processo de beneficiamento (onde se separa o mineral de interesse da rocha). É o que ficava nas barragens de Mariana.&lt;/li&gt;
+	&lt;li&gt;Barragens/Diques de alteamento são o método mais comum no Brasil (baixo custo), mas são considerados menos adequados por serem mais instáveis comparados ao empilhamento a seco.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G244"/>
+  <dimension ref="A1:G245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9433,6 +9433,43 @@
         <v>0</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>249</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Cadeia de Valor (Michael Porter)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>D&lt;ul&gt;
+	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
+	&lt;li&gt;Foco: Identificar fontes de vantagem competitiva (custo ou diferenciação).&lt;/li&gt;
+	&lt;li&gt;Margem: Diferença entre o Valor Total (o que o cliente está disposto a pagar) e o Custo Coletivo das atividades executadas.&lt;/li&gt;
+	&lt;li&gt;Atividades Primárias &lt;ul&gt; &lt;li&gt;Logística Interna&lt;/li&gt; &lt;li&gt;Operações&lt;/li&gt; &lt;li&gt;Logística Externa&lt;/li&gt; &lt;li&gt;Marketing e Vendas&lt;/li&gt; &lt;li&gt;Serviços&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Atividades de Apoio &lt;ul&gt; &lt;li&gt;Aquisição (Compras)&lt;/li&gt; &lt;li&gt;Desenvolvimento de Tecnologia&lt;/li&gt; &lt;li&gt;Gerência de Recursos Humanos&lt;/li&gt; &lt;li&gt;Infraestrutura da Empresa&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G245"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9470,6 +9470,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>250</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9504,6 +9504,73 @@
         <v>0</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>251</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Relação entre TIR e VPL</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;São análises independentes.&lt;/li&gt;
+	&lt;li&gt;Um projeto pode ter a TIR maior que outro projeto e VPL menor.&lt;/li&gt;
+	&lt;li&gt;Assim como pode ter a TIR menor e o VPL maior.&lt;/li&gt;
+	&lt;li&gt;Logo, as diferenças da TIR dos dois projetos não dizem nada sobre o valor presente líquido, VPL.&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>252</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>método da TIR</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9571,6 +9571,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>253</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Valor Presente Líquido (VPL)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
+	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G249"/>
+  <dimension ref="A1:G251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -749,10 +749,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -785,10 +785,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -920,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -998,7 +998,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1032,7 +1032,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1706,10 +1706,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2046,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2799,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -2903,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3000,7 +3000,7 @@
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -3985,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
@@ -4050,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4087,7 +4087,7 @@
         <v>2</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -4125,7 +4125,7 @@
         <v>2</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -4199,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
@@ -4241,7 +4241,7 @@
         <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4295,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -4428,7 +4428,7 @@
         <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4466,7 +4466,7 @@
         <v>2</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111">
@@ -4505,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -4546,7 +4546,7 @@
         <v>2</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4633,7 +4633,7 @@
         <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -4670,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
@@ -4708,7 +4708,7 @@
         <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -4745,7 +4745,7 @@
         <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -4802,7 +4802,7 @@
         <v>7</v>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -4938,7 +4938,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
@@ -4987,7 +4987,7 @@
         <v>4</v>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
@@ -5024,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123">
@@ -5088,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124">
@@ -5123,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
@@ -5199,7 +5199,7 @@
         <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127">
@@ -5259,7 +5259,7 @@
         <v>6</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -7576,7 +7576,7 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -7647,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -7683,7 +7683,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195">
@@ -8285,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213">
@@ -8324,7 +8324,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -8355,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
@@ -8391,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216">
@@ -8425,7 +8425,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217">
@@ -8456,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -8495,7 +8495,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
@@ -8529,7 +8529,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220">
@@ -8566,7 +8566,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -8604,7 +8604,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -8641,7 +8641,7 @@
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223">
@@ -8677,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -8712,7 +8712,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -8748,7 +8748,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -8783,7 +8783,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -8927,7 +8927,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -8964,7 +8964,7 @@
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -9003,7 +9003,7 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -9037,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -9072,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235">
@@ -9106,7 +9106,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236">
@@ -9142,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -9178,7 +9178,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -9249,7 +9249,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240">
@@ -9281,10 +9281,10 @@
         </is>
       </c>
       <c r="F240" t="n">
+        <v>2</v>
+      </c>
+      <c r="G240" t="n">
         <v>1</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -9354,7 +9354,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -9393,7 +9393,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -9430,7 +9430,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -9467,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246">
@@ -9605,6 +9605,72 @@
         <v>0</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>254</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Relação VPL X TMA</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Inversamente proporcionais</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>255</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Relação VPL x TIR x TMA</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;𝑽𝑷𝑳 &gt; 0 -&gt; 𝑽𝑷𝑳 &gt; TMA&lt;/li&gt;
+	&lt;li&gt;Se 𝑽𝑷𝑳 &lt; 0 -&gt; 𝑇𝐼𝑅 &lt; 𝑇𝑀A&lt;/li&gt;
+	&lt;li&gt;Se 𝑽𝑷𝑳 = 0 -&gt; 𝑇𝐼𝑅 = 𝑇𝑀A&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G251"/>
+  <dimension ref="A1:G260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5294,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5329,7 +5329,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -5511,7 +5511,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -5585,7 +5585,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -5620,7 +5620,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -5658,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -5727,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -5762,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -5796,7 +5796,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -6002,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -6046,7 +6046,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6083,7 +6083,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
@@ -6120,7 +6120,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -6156,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
@@ -6233,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6269,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -6307,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -6344,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -6380,7 +6380,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -6459,7 +6459,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -9671,6 +9671,536 @@
         <v>0</v>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>256</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Princípio da Entidade</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Autonomia da pessoa jurídica</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>257</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Entradas e saídas de capital
+&lt;ul&gt;
+	&lt;li&gt;sócios&lt;/li&gt;
+&lt;/ul&gt;
+Resultado do período apurado
+&lt;ul&gt;
+	&lt;li&gt;PERFORMANCE &lt;ul&gt; &lt;li&gt;Receitas&lt;/li&gt; &lt;li&gt;e Despesas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+posição patrimonial
+&lt;ul&gt;
+	&lt;li&gt;ativos&lt;/li&gt;
+	&lt;li&gt;passivos&lt;/li&gt;
+	&lt;li&gt;e patrimônio líquido&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Receitas</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;aumento nos ativos
+    &lt;ul&gt;
+      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diminuição de passivo
+    &lt;ul&gt;
+      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta aumento do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>259</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Despesas</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;consumo de bens ou serviços
+    &lt;ul&gt;
+      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;representam
+    &lt;ul&gt;
+      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
+      &lt;li&gt;aumento no passivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam despesas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>260</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+    &lt;li&gt;Contas contábeis
+        &lt;ul&gt;
+            &lt;li&gt;componentes patrimoniais e de resultado&lt;/li&gt;
+            &lt;li&gt;tipos quanto aos elementos
+                &lt;ul&gt;
+                    &lt;li&gt;patrimoniais
+                        &lt;ul&gt;
+                            &lt;li&gt;representam bens, direitos, obrigações e PL&lt;/li&gt;
+                            &lt;li&gt;estática patrimonial&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                    &lt;li&gt;de resultado
+                        &lt;ul&gt;
+                            &lt;li&gt;receitas e despesas&lt;/li&gt;
+                            &lt;li&gt;apuração de lucro ou prejuízo&lt;/li&gt;
+                            &lt;li&gt;performance da entidade&lt;/li&gt;
+                            &lt;li&gt;zeradas ao final do exercício&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+            &lt;li&gt;natureza
+                &lt;ul&gt;
+                    &lt;li&gt;devedoras
+                        &lt;ul&gt;
+                            &lt;li&gt;aplicações de recursos&lt;/li&gt;
+                            &lt;li&gt;natureza de Ativo e Despesas&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                    &lt;li&gt;credoras
+                        &lt;ul&gt;
+                            &lt;li&gt;origem dos recursos&lt;/li&gt;
+                            &lt;li&gt;natureza de Passivo, PL e Receitas&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                    &lt;li&gt;mecânica de lançamento
+                        &lt;ul&gt;
+                            &lt;li&gt;débito
+                                &lt;ul&gt;
+                                    &lt;li&gt;aumenta contas devedoras&lt;/li&gt;
+                                    &lt;li&gt;diminui contas credoras&lt;/li&gt;
+                                &lt;/ul&gt;
+                            &lt;/li&gt;
+                            &lt;li&gt;crédito
+                                &lt;ul&gt;
+                                    &lt;li&gt;aumenta contas credoras&lt;/li&gt;
+                                    &lt;li&gt;diminui contas devedoras&lt;/li&gt;
+                                &lt;/ul&gt;
+                            &lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+            &lt;li&gt;contas retificadoras
+                &lt;ul&gt;
+                    &lt;li&gt;natureza contrária ao grupo&lt;/li&gt;
+                    &lt;li&gt;ajustam o saldo do grupo&lt;/li&gt;
+                    &lt;li&gt;apresentadas com saldo negativo&lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+            &lt;li&gt;agregação de saldos
+                &lt;ul&gt;
+                    &lt;li&gt;sintéticas
+                        &lt;ul&gt;
+                            &lt;li&gt;agrupam e resumem outras contas&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                    &lt;li&gt;analíticas
+                        &lt;ul&gt;
+                            &lt;li&gt;detalham os registros&lt;/li&gt;
+                        &lt;/ul&gt;
+                    &lt;/li&gt;
+                &lt;/ul&gt;
+            &lt;/li&gt;
+        &lt;/ul&gt;
+    &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>261</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Equivalências e Negações Lógicas</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Outras Equivalências e Negações</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Negações da conjunção (e) para a forma condicional
+    &lt;ul&gt;
+      &lt;li&gt;~(p ∧ q) ≡ p → ~q&lt;/li&gt;
+      &lt;li&gt;~(p ∧ q) ≡ q → ~p&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Conjunção de condicionais
+    &lt;ul&gt;
+      &lt;li&gt;(p → r) ∧ (q → r) ≡ (p ∨ q) → r&lt;/li&gt;
+      &lt;li&gt;(p → q) ∧ (p → r) ≡ p → (q ∧ r)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Equivalências da disjunção exclusiva (ou...ou)
+    &lt;ul&gt;
+      &lt;li&gt;p &lt;u&gt;∨&lt;/u&gt; q ≡ (~p) &lt;u&gt;∨&lt;/u&gt; (~q)&lt;/li&gt;
+      &lt;li&gt;p &lt;u&gt;∨&lt;/u&gt; q ≡ (~p) ↔ q&lt;/li&gt;
+      &lt;li&gt;p &lt;u&gt;∨&lt;/u&gt; q ≡ p ↔ (~q)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Negações da disjunção exclusiva (ou...ou)
+    &lt;ul&gt;
+      &lt;li&gt;~(p &lt;u&gt;∨&lt;/u&gt; q) ≡ p ↔ q&lt;/li&gt;
+      &lt;li&gt;~(p &lt;u&gt;∨&lt;/u&gt; q) ≡ (~p) &lt;u&gt;∨&lt;/u&gt; q&lt;/li&gt;
+      &lt;li&gt;~(p &lt;u&gt;∨&lt;/u&gt; q) ≡ p &lt;u&gt;∨&lt;/u&gt; (~q)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Equivalências da bicondicional (se e somente se)
+    &lt;ul&gt;
+      &lt;li&gt;p ↔ q ≡ (p → q) ∧ (q → p)&lt;/li&gt;
+      &lt;li&gt;p ↔ q ≡ (~p) ↔ (~q)&lt;/li&gt;
+      &lt;li&gt;p ↔ q ≡ (~p) &lt;u&gt;∨&lt;/u&gt; q&lt;/li&gt;
+      &lt;li&gt;p ↔ q ≡ p &lt;u&gt;∨&lt;/u&gt; (~q)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Negações da bicondicional (se e somente se)
+    &lt;ul&gt;
+      &lt;li&gt;~(p ↔ q) ≡ p &lt;u&gt;∨&lt;/u&gt; q&lt;/li&gt;
+      &lt;li&gt;~(p ↔ q) ≡ (~p) ↔ q&lt;/li&gt;
+      &lt;li&gt;~(p ↔ q) ≡ p ↔ (~q)&lt;/li&gt;
+      &lt;li&gt;~(p ↔ q) ≡ (p ∧ ~q) ∨ (q ∧ ~p)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>262</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Equivalências e Negações Lógicas</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Álgebra de proposições</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Propriedade Comutativa
+    &lt;ul&gt;
+      &lt;li&gt;p ∧ q ≡ q ∧ p&lt;/li&gt;
+      &lt;li&gt;p ∨ q ≡ q ∨ p&lt;/li&gt;
+      &lt;li&gt;p &lt;u&gt;∨&lt;/u&gt; q ≡ q &lt;u&gt;∨&lt;/u&gt; p&lt;/li&gt;
+      &lt;li&gt;p ↔ q ≡ q ↔ p&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Propriedade Associativa
+    &lt;ul&gt;
+      &lt;li&gt;(p ∧ q) ∧ r ≡ p ∧ (q ∧ r)&lt;/li&gt;
+      &lt;li&gt;(p ∨ q) ∨ r ≡ p ∨ (q ∨ r)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Propriedade Distributiva
+    &lt;ul&gt;
+      &lt;li&gt;p ∧ (q ∨ r) ≡ (p ∧ q) ∨ (p ∧ r)&lt;/li&gt;
+      &lt;li&gt;p ∨ (q ∧ r) ≡ (p ∨ q) ∧ (p ∨ r)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Propriedade da Identidade
+    &lt;ul&gt;
+      &lt;li&gt;p ∧ t ≡ p&lt;/li&gt;
+      &lt;li&gt;p ∧ c ≡ c&lt;/li&gt;
+      &lt;li&gt;p ∨ t ≡ t&lt;/li&gt;
+      &lt;li&gt;p ∨ c ≡ p&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Propriedade da Absorção
+    &lt;ul&gt;
+      &lt;li&gt;p ∨ (p ∧ q) ≡ p&lt;/li&gt;
+      &lt;li&gt;p ∧ (p ∨ q) ≡ p&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Propriedade da Idempotência
+    &lt;ul&gt;
+      &lt;li&gt;p ∧ p ≡ p&lt;/li&gt;
+      &lt;li&gt;p ∨ p ≡ p&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Bicondicional (X ↔ Y)
+    &lt;ul&gt;
+      &lt;li&gt;Tautologia: X ≡ Y&lt;/li&gt;
+      &lt;li&gt;Contradição: X ≡ ~Y&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>263</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Os Três Tipos de Discurso</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Discurso Direto
+&lt;ul&gt;
+	&lt;li&gt;A fala do personagem é reproduzida textualmente &lt;ul&gt; &lt;li&gt;sem interferência do narrador.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+Discurso Indireto
+&lt;ul&gt;
+	&lt;li&gt;O narrador relata a fala ou o pensamento do personagem &lt;ul&gt; &lt;li&gt;com suas próprias palavras.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+Discurso Indireto Livre
+&lt;ul&gt;
+	&lt;li&gt;uma fusão dos dois anteriores.&lt;/li&gt;
+	&lt;li&gt;voz do narrador e a do personagem se misturam &lt;ul&gt; &lt;li&gt;sem marcas formais de pontuação.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Ex: &lt;ul&gt; &lt;li&gt;"Ele caminhava em silêncio pela caverna. Onde estaria a luz verdadeira? Seus companheiros não entenderiam."&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>264</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Semântica</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Prescrever vs. Facultativo</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Prescrever
+&lt;ul&gt;
+	&lt;li&gt;Significa determinar, impor, ordenar. É uma regra obrigatória.&lt;/li&gt;
+	&lt;li&gt;Ex: &lt;ul&gt; &lt;li&gt;As regras do código penal prescrevem o isolamento do réu.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;
+Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G260"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
@@ -3985,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>2</v>
@@ -4670,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="G115" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -4708,12 +4708,14 @@
         <v>5</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>119</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -4733,16 +4735,15 @@
       <c r="E117" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Dados Qualitativos&lt;/li&gt;
-	&lt;li&gt;Pessoas&lt;/li&gt;
-	&lt;li&gt;significados&lt;/li&gt;
-	&lt;li&gt;subjetividade&lt;/li&gt;
-	&lt;li&gt;cultura&lt;/li&gt;
+	&lt;li&gt;organização como um sistema social e simbólico&lt;/li&gt;
+	&lt;li&gt;informação é interpretada por pessoas&lt;/li&gt;
+	&lt;li&gt;com base em seus &lt;ul&gt; &lt;li&gt;contextos, experiências e valores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;tomada de decisão considera múltiplos significados possíveis&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -4853,7 +4854,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
@@ -4938,7 +4939,7 @@
         <v>6</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -5088,7 +5089,7 @@
         <v>2</v>
       </c>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -5123,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
@@ -7711,10 +7712,10 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -7745,7 +7746,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -7776,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -7807,7 +7808,7 @@
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199">
@@ -7838,7 +7839,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200">
@@ -7866,10 +7867,10 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201">
@@ -7900,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -7931,7 +7932,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
@@ -7962,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
@@ -7993,12 +7994,14 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
-        <v>209</v>
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -8018,14 +8021,79 @@
       <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;a administração pública deve utilizar soluções digitais&lt;/li&gt;
-	&lt;li&gt;processos administrativos eletrônicos&lt;/li&gt;
-	&lt;li&gt;documentos e atos processuais praticados em meio digital&lt;/li&gt;
-	&lt;li&gt;realização dos atos processuais em meio eletrônico&lt;/li&gt;
-	&lt;li&gt;acesso do interessado ao processo administrativo&lt;/li&gt;
-	&lt;li&gt;formato e o armazenamento dos documentos digitais&lt;/li&gt;
-	&lt;li&gt;prestação digital dos serviços públicos&lt;/li&gt;
-	&lt;li&gt;Cada ente federado&lt;/li&gt;
+  &lt;li&gt;operação padrão digital
+    &lt;ul&gt;
+      &lt;li&gt;gestão de políticas e processos&lt;/li&gt;
+      &lt;li&gt;documentos com validade legal
+        &lt;ul&gt;
+          &lt;li&gt;assinados eletronicamente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;atos processuais
+    &lt;ul&gt;
+      &lt;li&gt;meio digital
+        &lt;ul&gt;
+          &lt;li&gt;exceções
+            &lt;ul&gt;
+              &lt;li&gt;solicitação do usuário&lt;/li&gt;
+              &lt;li&gt;inviabilidade técnica ou indisponibilidade&lt;/li&gt;
+              &lt;li&gt;risco à celeridade&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;validade
+        &lt;ul&gt;
+          &lt;li&gt;preservados parâmetros de segurança&lt;/li&gt;
+          &lt;li&gt;não se aplica ao anonimato&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;contagem de prazo
+        &lt;ul&gt;
+          &lt;li&gt;dia e hora do recebimento&lt;/li&gt;
+          &lt;li&gt;tempestivos até as 23h59 do último dia
+            &lt;ul&gt;
+              &lt;li&gt;horário de Brasília&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;acesso e arquivamento
+    &lt;ul&gt;
+      &lt;li&gt;sistemas informatizados ou cópias&lt;/li&gt;
+      &lt;li&gt;classificação conforme a LAI&lt;/li&gt;
+      &lt;li&gt;assegurar preservação e acesso
+        &lt;ul&gt;
+          &lt;li&gt;normas arquivísticas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;prestação digital de serviços
+    &lt;ul&gt;
+      &lt;li&gt;tecnologias acessíveis&lt;/li&gt;
+      &lt;li&gt;atendimento presencial
+        &lt;ul&gt;
+          &lt;li&gt;permanece como direito&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;preferência pelo autosserviço&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Estratégia de Governo Digital
+    &lt;ul&gt;
+      &lt;li&gt;atuação integrada e cooperativa&lt;/li&gt;
+      &lt;li&gt;entes federados podem elaborar a própria
+        &lt;ul&gt;
+          &lt;li&gt;alinhada à nacional&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -8033,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
@@ -8071,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
@@ -8110,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -8149,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -8184,7 +8252,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -8217,7 +8285,7 @@
         <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211">
@@ -8250,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
@@ -9501,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247">
@@ -10201,6 +10269,464 @@
         <v>0</v>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;interoperabilidade de dados
+    &lt;ul&gt;
+      &lt;li&gt;elemento central&lt;/li&gt;
+      &lt;li&gt;órgãos e entidades
+        &lt;ul&gt;
+          &lt;li&gt;administrar ferramentas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;observar
+        &lt;ul&gt;
+          &lt;li&gt;LGPD&lt;/li&gt;
+          &lt;li&gt;restrições legais&lt;/li&gt;
+          &lt;li&gt;requisitos de segurança&lt;/li&gt;
+          &lt;li&gt;limitações tecnológicas&lt;/li&gt;
+          &lt;li&gt;custo-benefício&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;otimização
+        &lt;ul&gt;
+          &lt;li&gt;custos de acesso&lt;/li&gt;
+          &lt;li&gt;infraestruturas existentes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;mecanismo de interoperabilidade
+    &lt;ul&gt;
+      &lt;li&gt;aprimorar gestão e fortalecer confiabilidade&lt;/li&gt;
+      &lt;li&gt;assegurar
+        &lt;ul&gt;
+          &lt;li&gt;integridade e segurança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;viabilizar
+        &lt;ul&gt;
+          &lt;li&gt;identificação unificada&lt;/li&gt;
+          &lt;li&gt;partilha de dados&lt;/li&gt;
+          &lt;li&gt;tratamento com base no CPF&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;registros de referência
+    &lt;ul&gt;
+      &lt;li&gt;órgãos responsáveis pela publicidade&lt;/li&gt;
+      &lt;li&gt;pessoas físicas e jurídicas
+        &lt;ul&gt;
+          &lt;li&gt;verificar dados&lt;/li&gt;
+          &lt;li&gt;monitorar acessos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;criação de novas bases
+    &lt;ul&gt;
+      &lt;li&gt;apenas em caso de impossibilidade de uso das existentes
+        &lt;ul&gt;
+          &lt;li&gt;evitar redundância e promover eficiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>266</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Domicílio Eletrônico</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;comunicações, notificações e intimações por meios digitais
+    &lt;ul&gt;
+      &lt;li&gt;opção do usuário
+        &lt;ul&gt;
+          &lt;li&gt;não constitui direito se indisponível&lt;/li&gt;
+          &lt;li&gt;pode encerrar recebimento a qualquer momento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;ente público pode utilizar ferramentas de outro ente&lt;/li&gt;
+  &lt;li&gt;requisitos das ferramentas
+    &lt;ul&gt;
+      &lt;li&gt;garantir segurança, transparência e confiabilidade&lt;/li&gt;
+      &lt;li&gt;comprovar autoria&lt;/li&gt;
+      &lt;li&gt;registrar emissão e recebimento&lt;/li&gt;
+      &lt;li&gt;passíveis de auditoria&lt;/li&gt;
+      &lt;li&gt;preservar dados
+        &lt;ul&gt;
+          &lt;li&gt;mínimo de cinco anos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;aplicabilidade
+    &lt;ul&gt;
+      &lt;li&gt;mesmo quando a legislação mencionar formas tradicionais&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>267</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Laboratórios de Inovação</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;instituídos pelos entes públicos
+    &lt;ul&gt;
+      &lt;li&gt;espaços voltados ao desenvolvimento e à experimentação
+        &lt;ul&gt;
+          &lt;li&gt;ideias, métodos e ferramentas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;abertos à participação e à colaboração
+        &lt;ul&gt;
+          &lt;li&gt;sociedade, especialistas e instituições&lt;/li&gt;
+          &lt;li&gt;contribuir para
+            &lt;ul&gt;
+              &lt;li&gt;melhoria dos serviços públicos&lt;/li&gt;
+              &lt;li&gt;aprimoramento do tratamento de dados&lt;/li&gt;
+              &lt;li&gt;fortalecimento do controle social&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diretrizes
+    &lt;ul&gt;
+      &lt;li&gt;colaboração institucional e social&lt;/li&gt;
+      &lt;li&gt;promoção e experimentação de tecnologias abertas e livres&lt;/li&gt;
+      &lt;li&gt;foco no cidadão e na sociedade&lt;/li&gt;
+      &lt;li&gt;incentivar
+        &lt;ul&gt;
+          &lt;li&gt;inovação&lt;/li&gt;
+          &lt;li&gt;apoio ao empreendedorismo inovador&lt;/li&gt;
+          &lt;li&gt;ecossistema tecnológico&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;políticas públicas orientadas por dados e evidências&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;práticas e métodos
+    &lt;ul&gt;
+      &lt;li&gt;desenvolvimento e prototipação de softwares&lt;/li&gt;
+      &lt;li&gt;métodos ágeis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;participação e potencial criativo
+    &lt;ul&gt;
+      &lt;li&gt;servidores, estagiários e colaboradores&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;difusão de conhecimento
+    &lt;ul&gt;
+      &lt;li&gt;modernização e disseminação de práticas inovadoras&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>268</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;governança, gestão de riscos, controle e auditoria
+    &lt;ul&gt;
+      &lt;li&gt;pilares essenciais&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Governança
+    &lt;ul&gt;
+      &lt;li&gt;autoridade competente deve implementar&lt;/li&gt;
+      &lt;li&gt;mecanismos devem assegurar
+        &lt;ul&gt;
+          &lt;li&gt;acompanhamento de resultados&lt;/li&gt;
+          &lt;li&gt;soluções de desempenho organizacional&lt;/li&gt;
+          &lt;li&gt;decisões fundamentadas em evidências&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Gestão de riscos e controle interno
+    &lt;ul&gt;
+      &lt;li&gt;estruturados, monitorados e aperfeiçoados&lt;/li&gt;
+      &lt;li&gt;integrados ao planejamento estratégico&lt;/li&gt;
+      &lt;li&gt;controles proporcionais aos riscos&lt;/li&gt;
+      &lt;li&gt;resultados devem apoiar
+        &lt;ul&gt;
+          &lt;li&gt;melhoria contínua&lt;/li&gt;
+          &lt;li&gt;fortalecimento da tomada de decisão&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;norteados pela proteção das liberdades civis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Auditoria interna
+    &lt;ul&gt;
+      &lt;li&gt;agregar valor e melhorar operações&lt;/li&gt;
+      &lt;li&gt;abordagem sistemática e disciplinada&lt;/li&gt;
+      &lt;li&gt;realização independente
+        &lt;ul&gt;
+          &lt;li&gt;avaliação e consultoria&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;planejamento baseado em riscos&lt;/li&gt;
+      &lt;li&gt;apoio na prevenção e investigação de fraudes&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>269</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Diretrizes da Lei 14.129/2021</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
+    &lt;ul&gt;
+      &lt;li&gt;respeito a normas existentes
+        &lt;ul&gt;
+          &lt;li&gt;LAI, LGPD e Código Tributário&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;desburocratização e modernização
+        &lt;ul&gt;
+          &lt;li&gt;serviços simples e acessíveis&lt;/li&gt;
+          &lt;li&gt;disponíveis em dispositivos móveis&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;plataforma única
+        &lt;ul&gt;
+          &lt;li&gt;acesso centralizado&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;transparência e monitoramento
+        &lt;ul&gt;
+          &lt;li&gt;controle e fiscalização social&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;linguagem clara e compreensível
+        &lt;ul&gt;
+          &lt;li&gt;dever de prestar contas à população&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;proteção de dados pessoais
+        &lt;ul&gt;
+          &lt;li&gt;diretriz obrigatória observando a LGPD&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;interoperabilidade e abertura de dados&lt;/li&gt;
+      &lt;li&gt;acessibilidade
+        &lt;ul&gt;
+          &lt;li&gt;pessoas com deficiência&lt;/li&gt;
+          &lt;li&gt;tratamento adequado aos idosos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;ações educativas
+        &lt;ul&gt;
+          &lt;li&gt;qualificação de servidores e inclusão digital&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;apoio técnico a outros entes federados&lt;/li&gt;
+      &lt;li&gt;assinaturas eletrônicas
+        &lt;ul&gt;
+          &lt;li&gt;estímulo ao uso nas interações&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;governo como plataforma
+        &lt;ul&gt;
+          &lt;li&gt;uso de dados para políticas e novos negócios&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;padrões e formatos abertos e livres
+        &lt;ul&gt;
+          &lt;li&gt;prioridade conforme o Marco Civil da Internet&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Diretrizes para Laboratórios de Inovação
+    &lt;ul&gt;
+      &lt;li&gt;colaboração institucional e com a sociedade&lt;/li&gt;
+      &lt;li&gt;promoção de tecnologias abertas e livres&lt;/li&gt;
+      &lt;li&gt;foco no cidadão e na sociedade&lt;/li&gt;
+      &lt;li&gt;incentivo à inovação e empreendedorismo inovador&lt;/li&gt;
+      &lt;li&gt;políticas públicas orientadas por dados e evidências&lt;/li&gt;
+      &lt;li&gt;participação de servidores e colaboradores&lt;/li&gt;
+      &lt;li&gt;difusão de conhecimento e modernização&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>270</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Taxa Interna de Retorno Modificada (TIRM)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;transformação do fluxo &lt;ul&gt; &lt;li&gt;torna o fluxo convencional&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;possibilidade de trabalhar com duas taxas diferentes&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10727,6 +10727,70 @@
         <v>0</v>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>271</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>272</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PAYBACK DESCONTADO</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G268"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10791,6 +10791,68 @@
         <v>0</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>273</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>274</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Índice de Lucratividade </t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,7 +637,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4587,7 +4587,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4602,99 +4602,10 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>conhecimento tácito</t>
+          <t>Abordagem Racional (Chun Wei Choo)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;reside nas pessoas&lt;/li&gt;
-	&lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt;
-	&lt;li&gt;dimensão técnica
-&lt;ul&gt;
-	&lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt;
-	&lt;li&gt;habilidades motoras&lt;/li&gt;
-	&lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-	&lt;li&gt;dimensão cognitiva
-&lt;ul&gt;
-	&lt;li&gt;modelos mentais&lt;/li&gt;
-	&lt;li&gt;crenças&lt;/li&gt;
-	&lt;li&gt;crenças&lt;/li&gt;
-	&lt;li&gt;percepções&lt;/li&gt;
-	&lt;li&gt;intuições&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>5</v>
-      </c>
-      <c r="G114" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>conhecimento explícito</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;pode ser formalizado&lt;/li&gt;
-	&lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt;
-&lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>5</v>
-      </c>
-      <c r="G115" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Abordagem Racional (Chun Wei Choo)</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;As decisões são tomadas com base em regras, lógica e análise objetiva da informação disponível.&lt;/li&gt;
@@ -4704,35 +4615,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F116" t="n">
+      <c r="F114" t="n">
         <v>5</v>
       </c>
-      <c r="G116" t="n">
+      <c r="G114" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>119</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>Abordagem Interpretativa (Chun Wei Choo)</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;organização como um sistema social e simbólico&lt;/li&gt;
@@ -4742,35 +4653,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F117" t="n">
+      <c r="F115" t="n">
         <v>7</v>
       </c>
-      <c r="G117" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>Processo de construção da Inteligência</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Dado
@@ -4799,35 +4710,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F118" t="n">
+      <c r="F116" t="n">
         <v>7</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G116" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Modelo SECI (Nonaka e Takeuchi)</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Socialização
@@ -4853,35 +4764,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F119" t="n">
+      <c r="F117" t="n">
         <v>11</v>
       </c>
-      <c r="G119" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Modelo Genérico: 7 Processos da Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Identificação
@@ -4935,35 +4846,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F120" t="n">
+      <c r="F118" t="n">
         <v>6</v>
       </c>
-      <c r="G120" t="n">
+      <c r="G118" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>Barreiras à Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Organizacionais
@@ -4984,33 +4895,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F121" t="n">
+      <c r="F119" t="n">
         <v>4</v>
       </c>
-      <c r="G121" t="n">
+      <c r="G119" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="120">
+      <c r="A120" t="n">
         <v>124</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t xml:space="preserve"> Ferramentas e Práticas da Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Comunidades de Prática (CoP)&lt;/li&gt;
@@ -5021,35 +4932,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="n">
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>condições capacitadoras que sustentam o "Ba" (espaço compartilhado onde ocorre a criação do conhecimento)</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Intenção (Intentionality)
@@ -5085,33 +4996,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F123" t="n">
+      <c r="F121" t="n">
         <v>2</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G121" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="122">
+      <c r="A122" t="n">
         <v>126</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Sistemas de Gestão do Conhecimento (Knowledge Management Systems – KMS)</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;infraestrutura tecnológica integrada, composta por diversas ferramentas e plataformas&lt;/li&gt;
@@ -5120,33 +5031,33 @@
 </t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="123">
+      <c r="A123" t="n">
         <v>127</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Componentes típicos de um KMS</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;Repositórios de conhecimento&lt;/li&gt;
@@ -5159,33 +5070,33 @@
 </t>
         </is>
       </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="n">
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="124">
+      <c r="A124" t="n">
         <v>128</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>Fatores críticos de sucesso para um KMS</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Está alinhado&lt;/li&gt;
@@ -5196,35 +5107,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F126" t="n">
+      <c r="F124" t="n">
         <v>2</v>
       </c>
-      <c r="G126" t="n">
+      <c r="G124" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>tecnologias emergentes aplicadas à Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Big Data
@@ -5256,33 +5167,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F127" t="n">
+      <c r="F125" t="n">
         <v>6</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G125" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
+    <row r="126">
+      <c r="A126" t="n">
         <v>130</v>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>Processo para análise sintática</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;ache o verbo&lt;/li&gt;
@@ -5291,33 +5202,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
         <v>131</v>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>técnicas de indeterminação do sujeito</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;verbo na 3ª pessoa do plural, com omissão do agente que pratica a ação verbal&lt;/li&gt;
@@ -5326,33 +5237,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
         <v>132</v>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Oração sem sujeito</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fenômenos da natureza&lt;/li&gt;
@@ -5361,33 +5272,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
         <v>133</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Casos de Objeto Direto Preposicionado</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Quando o objeto direto for um pronome oblíquo tônico ou “quem”&lt;/li&gt;
@@ -5403,33 +5314,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
         <v>134</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Complemento Nominal</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;complemento de um nome que possua transitividade (substantivo, adjetivo ou advérbio), com preposição&lt;/li&gt;
@@ -5438,6 +5349,76 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>135</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Adjunto Adnominal</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;acompanha substantivos concretos e abstratos para atribuir-lhes &lt;ul&gt; &lt;li&gt;características&lt;/li&gt; &lt;li&gt;qualidade ou&lt;/li&gt; &lt;li&gt;estado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;têm função adjetiva, ou seja, modificam termo substantivo&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Funções Sintáticas</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Predicação Verbal</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Verbos de Ação/Movimento/Fenômeno &lt;ul&gt; &lt;li&gt;VI &lt;ul&gt; &lt;li&gt;É aquele que não precisa de complemento&lt;/li&gt; &lt;li&gt;Pode vir seguido de informações acessórias (Predicativo/Adj. Adverbial)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;VTD&lt;/li&gt; &lt;li&gt;VTI&lt;/li&gt; &lt;li&gt;VTDI&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Verbos de Estado/de Ligação &lt;ul&gt; &lt;li&gt;Vem sempre com Predicativo do Sujeito&lt;/li&gt; &lt;li&gt;Indica estado (e não ação)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
@@ -5447,7 +5428,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -5461,80 +5442,10 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Adjunto Adnominal</t>
+          <t>Adjunto Adverbial</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;acompanha substantivos concretos e abstratos para atribuir-lhes &lt;ul&gt; &lt;li&gt;características&lt;/li&gt; &lt;li&gt;qualidade ou&lt;/li&gt; &lt;li&gt;estado&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;têm função adjetiva, ou seja, modificam termo substantivo&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Funções Sintáticas</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Predicação Verbal</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Verbos de Ação/Movimento/Fenômeno &lt;ul&gt; &lt;li&gt;VI &lt;ul&gt; &lt;li&gt;É aquele que não precisa de complemento&lt;/li&gt; &lt;li&gt;Pode vir seguido de informações acessórias (Predicativo/Adj. Adverbial)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;VTD&lt;/li&gt; &lt;li&gt;VTI&lt;/li&gt; &lt;li&gt;VTDI&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Verbos de Estado/de Ligação &lt;ul&gt; &lt;li&gt;Vem sempre com Predicativo do Sujeito&lt;/li&gt; &lt;li&gt;Indica estado (e não ação)&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>137</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Português</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Funções Sintáticas</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Adjunto Adverbial</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Invariável&lt;/li&gt;
@@ -5544,35 +5455,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>138</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Núcleo do sujeito</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Não é a ideia principal/ideia mais importante do sujeito&lt;/li&gt;
@@ -5582,33 +5493,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
         <v>139</v>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>Passo a Passo - Classificação do Sujeito</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Vá ao verbo e pergunte pelo sujeito &lt;ul&gt; &lt;li&gt;Quem é que/O que é que + verbo?&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -5617,33 +5528,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
         <v>140</v>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>Tipos de Sujeito</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Simples&lt;/li&gt;
@@ -5655,33 +5566,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
         <v>141</v>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="B137" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Predicativo do sujeito</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Refere-se ao sujeito&lt;/li&gt;
@@ -5690,33 +5601,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
         <v>142</v>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>Passo a Passo - Predicação Verbal</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Vá ao verbo e pergunte pelo sujeito &lt;ul&gt; &lt;li&gt;Quem é que/O que é que + Verbo?&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -5724,33 +5635,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
         <v>143</v>
       </c>
-      <c r="B141" t="inlineStr">
+      <c r="B139" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>Tipos de Predicado</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Predicado Nominal &lt;ul&gt; &lt;li&gt;O núcleo é um nome (predicativo do sujeito)&lt;/li&gt; &lt;li&gt;O verbo indica estado (verbo de ligação)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -5759,33 +5670,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
         <v>144</v>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>Indentificando o tipo de Predicado</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;A grande sacada é saber se o verbo é de ação ou estado &lt;ul&gt; &lt;li&gt;Macete: Primeiro pergunte se o verbo indica estado (Verbo de Estado + Predicativo = Predicado Nominal)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -5793,33 +5704,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
         <v>145</v>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B141" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C141" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>Passo a Passo - Classificação do Predicado</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Ir ao verbo e perguntar pelo sujeito&lt;/li&gt;
@@ -5828,33 +5739,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
         <v>146</v>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B142" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C142" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>Como reconhecer o Agente da Passiva?</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Pela preposição (por/de)&lt;/li&gt;
@@ -5863,68 +5774,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>Tabela para identificar os termos da Oração</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>&lt;div style="margin:0;padding:0;font-family:sans-serif;font-size:14px;color:#333;"&gt;&lt;ul style="margin:0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Objeto Direto&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completam VERBO&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;VERBO&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Facultativa (OD preposicionado)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João leu &lt;span style="color:#d32f2f;text-decoration:underline"&gt;o livro&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Objeto Indireto&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completam VERBO&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;VERBO&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João gosta &lt;span style="color:#d32f2f;text-decoration:underline"&gt;de suco&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Complemento Nominal&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Completa NOME (Subst./Adj./Adv.)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;span style="color:#1976d2;"&gt;NOME&lt;/span&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João tem saudade &lt;span style="color:#d32f2f;text-decoration:underline"&gt;da família&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Agente da Passiva&lt;/strong&gt;:&lt;ul style="margin:5px 0;padding-left:20px;"&gt;&lt;li&gt;&lt;strong&gt;Conceito&lt;/strong&gt;: Age na Voz Passiva (SER + Particípio)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Referente&lt;/strong&gt;: &lt;strong&gt;Ø&lt;/strong&gt; (Inexistente)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Preposição?&lt;/strong&gt;: Obrigatória&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Classe (Morfologia)&lt;/strong&gt;: Substantivo&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Exemplo&lt;/strong&gt;: João foi elogiado &lt;span style="color:#d32f2f;text-decoration:underline"&gt;pela professora&lt;/span&gt;.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/div&gt;</t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>Termos da Oração</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;strong&gt;Essenciais&lt;/strong&gt;:
@@ -5956,35 +5867,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B145" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Objeto Direto</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t xml:space="preserve">
 		&lt;ul&gt;
@@ -5999,35 +5910,35 @@
 		&lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Objeto Indireto</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t xml:space="preserve">
 		&lt;ul&gt;
@@ -6043,35 +5954,35 @@
 		&lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Complemento Nominal</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t xml:space="preserve">
 		&lt;ul&gt;
@@ -6080,35 +5991,35 @@
 		&lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>152</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Agente da Passiva</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t xml:space="preserve">
 		&lt;ul&gt;
@@ -6117,33 +6028,33 @@
 		&lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
         <v>153</v>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Vocativo</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Termo que se usa para chamar alguém ou coisa personificada&lt;/li&gt;
@@ -6153,33 +6064,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
         <v>154</v>
       </c>
-      <c r="B152" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
+      <c r="C150" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Aposto</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;Termo de natureza substantiva ou pronominal que se apresenta a outro substantivo ou pronome&lt;/li&gt;
@@ -6188,33 +6099,33 @@
 </t>
         </is>
       </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
         <v>155</v>
       </c>
-      <c r="B153" t="inlineStr">
+      <c r="B151" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Circunstâncias</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>&lt;b&gt;6CsFTP&lt;/b&gt;
 &lt;ul&gt;
@@ -6230,33 +6141,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
         <v>156</v>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
+      <c r="C152" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Adjunto Adverbial</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Vocábulo ou expressão que denota alguma circunstância (tempo, lugar, modo, ...) do fato expresso pelo verbo.&lt;/li&gt;
@@ -6266,35 +6177,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>157</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B153" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C153" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>Adjunto Adnominal</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;"Termo que limita, individualiza a significação de um substantivo."&lt;/li&gt;
@@ -6304,35 +6215,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>Predicativos</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E154" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Vem &lt;b&gt;sempre&lt;/b&gt; no predicado&lt;/li&gt;
@@ -6341,33 +6252,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
         <v>159</v>
       </c>
-      <c r="B157" t="inlineStr">
+      <c r="B155" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
+      <c r="C155" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D155" t="inlineStr">
         <is>
           <t>Passo a passo - distinguir Adjunto Adnominal de Predicativo do Objeto</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E155" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Coloca a seta!&lt;/li&gt;
@@ -6377,33 +6288,33 @@
 Dica: Quando é PO, você poderá deslocá-lo para perto do Verbo &lt;ul&gt; &lt;li&gt;pois sua conversa é com o verbo&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
         <v>160</v>
       </c>
-      <c r="B158" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
+      <c r="C156" t="inlineStr">
         <is>
           <t>Funções Sintáticas</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>Período Composto</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;strong&gt;Coordenação&lt;/strong&gt;
@@ -6456,68 +6367,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr">
+      <c r="B157" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
+      <c r="C157" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>Equação Fundamental da Contabilidade</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>Ativo = Passivo + PL &lt;ul&gt; &lt;li&gt;Toda aplicação de recursos possui uma origem de igual valor&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B158" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C158" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Termos Importantes</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>Ativo: Bens e direitos
 Passivo: Obrigações
@@ -6529,33 +6440,33 @@
 Capital aplicado: Ativo</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
         <v>163</v>
       </c>
-      <c r="B161" t="inlineStr">
+      <c r="B159" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C159" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Situação Líquida (Patrimônio Líquido) e Equação Fundamental do Patrimônio</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Ativo maior do que passivo &lt;ul&gt; &lt;li&gt;Ativo &gt; Passivo exigível&lt;/li&gt; &lt;li&gt;Situação líquida &gt; 0&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6565,6 +6476,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>164</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Atos e Fatos Contábeis</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Atos contábeis ou Atos Administrativos &lt;ul&gt; &lt;li&gt;não provocam alterações do patrimônio&lt;/li&gt; &lt;li&gt;ou apenas irão alterar o Patrimônio no futuro&lt;/li&gt; &lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;admissão de empregados&lt;/li&gt; &lt;li&gt;assinatura de um contrato de compra&lt;/li&gt; &lt;li&gt;venda&lt;/li&gt; &lt;li&gt;o aval de um título de crédito&lt;/li&gt; &lt;li&gt;uma fiança prestada em favor de terceiros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Lei 6.404/76: Art. 176. (...) § 4º As demonstrações serão complementadas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Fatos contábeis ou Fatos Administrativos &lt;ul&gt; &lt;li&gt;provocam variações no patrimônio da entidade&lt;/li&gt; &lt;li&gt;são contabilizados através &lt;ul&gt; &lt;li&gt;das contas patrimoniais (ativo, passivo, patrimônio líquido)&lt;/li&gt; &lt;li&gt;e/ou das contas de resultado (receitas e despesas)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>165</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Variações de Elementos Patrimoniais</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Subscrição do Capital Social &lt;ul&gt; &lt;li&gt;Comprometimento&lt;/li&gt; &lt;li&gt;Promessa&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Integralização do Capital Social &lt;ul&gt; &lt;li&gt;os sócios efetivamente entregam os recursos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F161" t="n">
         <v>0</v>
       </c>
@@ -6574,92 +6553,24 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Contabilidade Gerencial</t>
+          <t>Discursiva</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Contabilidade Básica</t>
+          <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Atos e Fatos Contábeis</t>
+          <t>Dissertação</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Atos contábeis ou Atos Administrativos &lt;ul&gt; &lt;li&gt;não provocam alterações do patrimônio&lt;/li&gt; &lt;li&gt;ou apenas irão alterar o Patrimônio no futuro&lt;/li&gt; &lt;li&gt;Ex.: &lt;ul&gt; &lt;li&gt;admissão de empregados&lt;/li&gt; &lt;li&gt;assinatura de um contrato de compra&lt;/li&gt; &lt;li&gt;venda&lt;/li&gt; &lt;li&gt;o aval de um título de crédito&lt;/li&gt; &lt;li&gt;uma fiança prestada em favor de terceiros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;Lei 6.404/76: Art. 176. (...) § 4º As demonstrações serão complementadas&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Fatos contábeis ou Fatos Administrativos &lt;ul&gt; &lt;li&gt;provocam variações no patrimônio da entidade&lt;/li&gt; &lt;li&gt;são contabilizados através &lt;ul&gt; &lt;li&gt;das contas patrimoniais (ativo, passivo, patrimônio líquido)&lt;/li&gt; &lt;li&gt;e/ou das contas de resultado (receitas e despesas)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>165</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Variações de Elementos Patrimoniais</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Subscrição do Capital Social &lt;ul&gt; &lt;li&gt;Comprometimento&lt;/li&gt; &lt;li&gt;Promessa&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Integralização do Capital Social &lt;ul&gt; &lt;li&gt;os sócios efetivamente entregam os recursos&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>166</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Dissertação</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;exposição, discussão ou interpretação de determinada ideia&lt;/li&gt;
@@ -6668,33 +6579,33 @@
 </t>
         </is>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
         <v>167</v>
       </c>
-      <c r="B165" t="inlineStr">
+      <c r="B163" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Questões Discursivas</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Em regra, apresentam-se os tópicos questionadores sobre os quais o candidato deverá expor ou argumentar.&lt;/li&gt;
@@ -6704,33 +6615,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
         <v>168</v>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B164" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Estrutura Formal da Questão Discursiva</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;podem-se ignorar os parágrafos de introdução e de fechamento&lt;/li&gt;
@@ -6738,33 +6649,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F166" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
         <v>169</v>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B165" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C165" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Introdução Roteiro</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;além da TESE,&lt;/li&gt;
@@ -6773,6 +6684,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>170</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Introdução Conceito</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>apresenta-se a definição de um conceito</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>172</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Introdução por citação de jurisprudência, de entendimento doutrinário ou de diplomas legais</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>baseia-se nesses elementos para dar substrato à afirmação ou à exposição elencada no início do texto</t>
+        </is>
+      </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
@@ -6782,7 +6755,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6796,12 +6769,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Introdução Conceito</t>
+          <t>Desenvolvimento por Causa/Consequência</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>apresenta-se a definição de um conceito</t>
+          <t>expõem-se as causas e os efeitos da questão tratada, dividindo-se em parágrafos cada um deles.</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6813,7 +6786,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -6827,12 +6800,15 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Introdução por citação de jurisprudência, de entendimento doutrinário ou de diplomas legais</t>
+          <t>Desenvolvimento por Ordenação Cronológica</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>baseia-se nesses elementos para dar substrato à afirmação ou à exposição elencada no início do texto</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;relação “passado, presente e futuro”&lt;/li&gt;
+	&lt;li&gt;desenvolvimento comparativo entre os momentos históricos acerca de determinado assunto&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6844,7 +6820,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -6858,75 +6834,10 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Desenvolvimento por Causa/Consequência</t>
+          <t xml:space="preserve">Fechamento Reforço/Retorno </t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
-        <is>
-          <t>expõem-se as causas e os efeitos da questão tratada, dividindo-se em parágrafos cada um deles.</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>174</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Desenvolvimento por Ordenação Cronológica</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;relação “passado, presente e futuro”&lt;/li&gt;
-	&lt;li&gt;desenvolvimento comparativo entre os momentos históricos acerca de determinado assunto&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>175</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fechamento Reforço/Retorno </t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;volta a algo que já tenha sido apresentado&lt;/li&gt;
@@ -6935,33 +6846,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
         <v>176</v>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>Fechamento Avanço (proposta de solução)</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;vai além do que está no texto&lt;/li&gt;
@@ -6970,33 +6881,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
         <v>177</v>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Fechamento Expansão</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;excelente para situações em que o seu desenvolvimento acabou ocupando uma quantidade de linhas superior àquela inicialmente planejada&lt;/li&gt;
@@ -7005,6 +6916,68 @@
 </t>
         </is>
       </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>178</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Tamanho dos períodos</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Se o seu período ultrapassar duas ou três linhas, releia-o e veja se é possível modificá-lo</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>179</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Discursiva</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Teoria Geral da Produção Textual</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Tamanho dos parágrafos</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>5 a 10 linhas</t>
+        </is>
+      </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
@@ -7014,7 +6987,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -7028,72 +7001,10 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Tamanho dos períodos</t>
+          <t>Indicação de parágrafos e Respeito às margens</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
-        <is>
-          <t>Se o seu período ultrapassar duas ou três linhas, releia-o e veja se é possível modificá-lo</t>
-        </is>
-      </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>179</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>Tamanho dos parágrafos</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>5 a 10 linhas</t>
-        </is>
-      </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>180</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Discursiva</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Teoria Geral da Produção Textual</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>Indicação de parágrafos e Respeito às margens</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Distância regular e a menor possível em relação às margens&lt;/li&gt;
@@ -7102,64 +7013,64 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
         <v>182</v>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Rasuras</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>apenas fazer um traço simples na palavra</t>
         </is>
       </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
         <v>183</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Siglas e abreviaturas</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;mencionadas pela primeira vez &lt;ul&gt; &lt;li&gt;forma por extenso, seguida da sigla entre parênteses, ou separada por hífen.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7173,64 +7084,64 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
         <v>184</v>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Posso pular linhas?</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>A resposta é, definitivamente, NÃO!</t>
         </is>
       </c>
-      <c r="F180" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
         <v>185</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Discursiva</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Teoria Geral da Produção Textual</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Como Utilizar Números em Provas Discursivas</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;forma extensa &lt;ul&gt; &lt;li&gt;formar apenas uma palavra &lt;ul&gt; &lt;li&gt;será grafado apenas por extenso.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;doze,&lt;/li&gt; &lt;li&gt;vinte,&lt;/li&gt; &lt;li&gt;nove.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;formar duas ou mais palavras &lt;ul&gt; &lt;li&gt;deverá constar o número cardinal seguido do extenso entre parênteses.&lt;/li&gt; &lt;li&gt;Exemplo: &lt;ul&gt; &lt;li&gt;21 (vinte e um),&lt;/li&gt; &lt;li&gt;34 (trinta e quatro).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7239,35 +7150,35 @@
 </t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Equivalências lógicas</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Equivalência contrapositiva &lt;ul&gt; &lt;li&gt;p→q ≡ ~q→~p&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7276,6 +7187,76 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>187</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Raciocínio Lógico</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Equivalências e Negações Lógicas</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Negações lógicas</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Negação da conjunção e da disjunção inclusiva (Leis de De Morgan) &lt;ul&gt; &lt;li&gt;~(p∧q) ≡ ~p∨~q&lt;/li&gt; &lt;li&gt;~(p∨q) ≡ ~p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Negação da condicional &lt;ul&gt; &lt;li&gt;~(p→q) ≡ p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Definição oficial de contabilidade</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;doutrina  (IPECAFI)&lt;ul&gt; &lt;li&gt;objetivamente, um sistema de informação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
@@ -7285,29 +7266,26 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Raciocínio Lógico</t>
+          <t>Contabilidade Gerencial</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Equivalências e Negações Lógicas</t>
+          <t>Aspectos Introdutórios</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Negações lógicas</t>
+          <t>Escrituração</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Negação da conjunção e da disjunção inclusiva (Leis de De Morgan) &lt;ul&gt; &lt;li&gt;~(p∧q) ≡ ~p∨~q&lt;/li&gt; &lt;li&gt;~(p∨q) ≡ ~p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Negação da condicional &lt;ul&gt; &lt;li&gt;~(p→q) ≡ p∧~q&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>técnica contábil que reúne todos os documentos</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -7318,10 +7296,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
+      <c r="A184" t="n">
+        <v>190</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -7335,15 +7311,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Definição oficial de contabilidade</t>
+          <t>objeto de estudo da contabilidade</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;doutrina  (IPECAFI)&lt;ul&gt; &lt;li&gt;objetivamente, um sistema de informação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>patrimônio</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -7354,8 +7327,10 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
-        <v>189</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7369,74 +7344,10 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Escrituração</t>
+          <t>campo de aplicação da Contabilidade</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
-        <is>
-          <t>técnica contábil que reúne todos os documentos</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>190</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Aspectos Introdutórios</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>objeto de estudo da contabilidade</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>patrimônio</t>
-        </is>
-      </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Aspectos Introdutórios</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>campo de aplicação da Contabilidade</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
         <is>
           <t>Aziendas &lt;ul&gt; 
 &lt;li&gt;patrimônio de uma pessoa que é gerido de maneira organizada&lt;/li&gt;
@@ -7446,6 +7357,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>192</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>finalidade principal da ciência contábil ou objetivo</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>193</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>usuários das demonstrações contábeis externos ou internos</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F187" t="n">
         <v>0</v>
       </c>
@@ -7455,7 +7431,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -7469,12 +7445,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>finalidade principal da ciência contábil ou objetivo</t>
+          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+          <t>Muitos investidores, credores por empréstimos e outros credores</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -7486,33 +7462,33 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Contabilidade Gerencial</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Gestão de Estoques</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>usuários das demonstrações contábeis externos ou internos</t>
+          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
+	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -7520,38 +7496,41 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Contabilidade Gerencial</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Gestão de Estoques</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
+          <t>Como determinar o estoque mínimo</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Muitos investidores, credores por empréstimos e outros credores</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -7560,32 +7539,32 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Gestão de Estoques</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
+          <t>Constituição Federal de 1988, Art. 7º</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
-	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -7594,83 +7573,15 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Gestão de Estoques</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Como determinar o estoque mínimo</t>
+          <t>Consolidação das leis do Trabalho, Capítulo V</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>197</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Constituição Federal de 1988, Art. 7º</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>198</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>Consolidação das leis do Trabalho, Capítulo V</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;responsabilidades dos órgãos&lt;/li&gt;
@@ -7680,6 +7591,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>199</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Autosserviço</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Acesso pelo cidadão a serviço público</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>200</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Base nacional de serviços públicos</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Base de dados que contém as informações</t>
+        </is>
+      </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
@@ -7689,7 +7662,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -7703,16 +7676,16 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Autosserviço</t>
+          <t>Dados abertos</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Acesso pelo cidadão a serviço público</t>
+          <t>Dados acessíveis ao público</t>
         </is>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>1</v>
@@ -7720,7 +7693,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -7734,12 +7707,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Base nacional de serviços públicos</t>
+          <t>Dado acessível ao público</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Base de dados que contém as informações</t>
+          <t>Qualquer dado gerado ou acumulado</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7751,7 +7724,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -7765,24 +7738,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Dados abertos</t>
+          <t>Formato aberto</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Dados acessíveis ao público</t>
+          <t>Formato de arquivo não proprietário</t>
         </is>
       </c>
       <c r="F197" t="n">
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -7796,24 +7769,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dado acessível ao público</t>
+          <t>Governo como plataforma</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Qualquer dado gerado ou acumulado</t>
+          <t>Infraestrutura tecnológica que facilite</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7827,12 +7800,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Formato aberto</t>
+          <t>Laboratório de inovação</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Formato de arquivo não proprietário</t>
+          <t>Espaço aberto à participação</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7844,7 +7817,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7858,24 +7831,24 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Governo como plataforma</t>
+          <t>Plataformas de governo digital</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Infraestrutura tecnológica que facilite</t>
+          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
         </is>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7889,12 +7862,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Laboratório de inovação</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Espaço aberto à participação</t>
+          <t>Informação íntegra e precisa</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -7906,7 +7879,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7920,12 +7893,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Plataformas de governo digital</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
+          <t>Disponibilização de dados pela administração pública</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -7936,8 +7909,10 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
-        <v>207</v>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -7951,74 +7926,10 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
-        <is>
-          <t>Informação íntegra e precisa</t>
-        </is>
-      </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>208</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>Transparência ativa</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública</t>
-        </is>
-      </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação padrão digital
@@ -8097,35 +8008,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -8135,35 +8046,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
+    <row r="205">
+      <c r="A205" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -8174,33 +8085,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="206">
+      <c r="A206" t="n">
         <v>212</v>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -8213,33 +8124,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" t="n">
+    <row r="207">
+      <c r="A207" t="n">
         <v>213</v>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C209" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -8248,99 +8159,99 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
         <v>214</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr">
+      <c r="C208" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Plataformas de Governo Digital</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t xml:space="preserve">instrumentos para os entes federativos disponibilizem seus serviços públicos
 devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
 padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
         </is>
       </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="209">
+      <c r="A209" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B209" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C211" t="inlineStr">
+      <c r="C209" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Prestação Digital dos Serviços Públicos</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="n">
+    <row r="210">
+      <c r="A210" t="n">
         <v>216</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -8349,35 +8260,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
+    <row r="211">
+      <c r="A211" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -8388,64 +8299,64 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="n">
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
+    <row r="212">
+      <c r="A212" t="n">
         <v>218</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>NR 2</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>Inspeção Prévia</t>
         </is>
       </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
         <v>219</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>NR 3</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -8455,6 +8366,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>220</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>221</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NR 5</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
+        </is>
+      </c>
       <c r="F215" t="n">
         <v>0</v>
       </c>
@@ -8464,7 +8440,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -8478,75 +8454,10 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>221</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>NR 5</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
-        <v>222</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -8559,33 +8470,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
         <v>223</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -8593,35 +8504,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -8630,33 +8541,33 @@
 </t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>225</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -8668,33 +8579,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
         <v>226</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -8705,33 +8616,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="n">
+    <row r="221">
+      <c r="A221" t="n">
         <v>227</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -8741,33 +8652,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="222">
+      <c r="A222" t="n">
         <v>228</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -8776,33 +8687,33 @@
 </t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>229</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8812,33 +8723,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
         <v>230</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -8847,33 +8758,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>231</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8884,33 +8795,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>232</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8918,33 +8829,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
         <v>233</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>Índices Financeiros</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8955,33 +8866,33 @@
 </t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
         <v>234</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -8991,35 +8902,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pré-Desenvolvimento &lt;ol&gt; &lt;li&gt;Planejamento do Projeto &lt;ul&gt; &lt;li&gt;são realizadas &lt;ul&gt; &lt;li&gt;brainstorming&lt;/li&gt; &lt;li&gt;visitas a feiras técnicas&lt;/li&gt; &lt;li&gt;análise de produtos da concorrência&lt;/li&gt; &lt;li&gt;pesquisa de mercado&lt;/li&gt; &lt;li&gt;elaboração das especificações do projeto&lt;/li&gt; &lt;li&gt;dentre outros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
@@ -9028,35 +8939,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Único Banco de Dados Centralizado&lt;/li&gt;
@@ -9067,33 +8978,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
         <v>237</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>Back-office vs. Front-office</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -9101,33 +9012,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
         <v>238</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -9136,33 +9047,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
         <v>239</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>Critérios de Decisão no AHP</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
@@ -9170,33 +9081,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="234">
+      <c r="A234" t="n">
         <v>240</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -9206,33 +9117,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
         <v>241</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -9242,33 +9153,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
         <v>242</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -9278,33 +9189,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
         <v>243</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -9313,33 +9224,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="238">
+      <c r="A238" t="n">
         <v>244</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -9348,33 +9259,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
+      <c r="F238" t="n">
         <v>2</v>
       </c>
-      <c r="G240" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
+      <c r="G238" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
         <v>245</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -9383,33 +9294,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
         <v>246</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -9418,33 +9329,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
         <v>247</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -9457,35 +9368,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -9494,33 +9405,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
         <v>249</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -9531,33 +9442,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F245" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" t="n">
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" t="n">
+    <row r="244">
+      <c r="A244" t="n">
         <v>250</v>
       </c>
-      <c r="B246" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C244" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>Número suficiente para identificação</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -9565,33 +9476,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="n">
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" t="n">
+    <row r="245">
+      <c r="A245" t="n">
         <v>251</v>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C245" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>Relação entre TIR e VPL</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;São análises independentes.&lt;/li&gt;
@@ -9601,6 +9512,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>252</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>método da TIR</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>253</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Valor Presente Líquido (VPL)</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
+	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F247" t="n">
         <v>0</v>
       </c>
@@ -9610,7 +9586,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -9624,12 +9600,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>método da TIR</t>
+          <t>Relação VPL X TMA</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+          <t>Inversamente proporcionais</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -9641,7 +9617,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -9655,75 +9631,10 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Valor Presente Líquido (VPL)</t>
+          <t>Relação VPL x TIR x TMA</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
-	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>254</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Relação VPL X TMA</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Inversamente proporcionais</t>
-        </is>
-      </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>255</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>Relação VPL x TIR x TMA</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;𝑽𝑷𝑳 &gt; 0 -&gt; 𝑽𝑷𝑳 &gt; TMA&lt;/li&gt;
@@ -9732,64 +9643,64 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
         <v>256</v>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C250" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>Princípio da Entidade</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>Autonomia da pessoa jurídica</t>
         </is>
       </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
         <v>257</v>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C251" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -9807,35 +9718,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C252" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>Receitas</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;aumento nos ativos
@@ -9865,33 +9776,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
         <v>259</v>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;consumo de bens ou serviços
@@ -9922,33 +9833,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>260</v>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -10030,33 +9941,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>261</v>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -10104,33 +10015,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>262</v>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -10182,33 +10093,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
         <v>263</v>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -10226,33 +10137,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
         <v>264</v>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -10262,35 +10173,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -10358,33 +10269,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
         <v>266</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -10419,33 +10330,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
         <v>267</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -10503,33 +10414,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
         <v>268</v>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
@@ -10579,33 +10490,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F264" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
         <v>269</v>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
@@ -10685,33 +10596,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F265" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
         <v>270</v>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -10720,6 +10631,70 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>271</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>272</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>PAYBACK DESCONTADO</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F266" t="n">
         <v>0</v>
       </c>
@@ -10729,7 +10704,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -10743,12 +10718,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>PAYBACK SIMPLES</t>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -10760,7 +10735,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -10774,14 +10749,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>PAYBACK DESCONTADO</t>
+          <t xml:space="preserve">Índice de Lucratividade </t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -10793,26 +10766,87 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Processo de gestão de riscos
+    &lt;ul&gt;
+      &lt;li&gt;aplicação sistemática&lt;/li&gt;
+      &lt;li&gt;parte integrante da gestão&lt;/li&gt;
+      &lt;li&gt;natureza iterativa&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Fluxo de atividades
+    &lt;ol&gt;
+      &lt;li&gt;Comunicação e consulta
+        &lt;ul&gt;
+          &lt;li&gt;promover conscientização e entendimento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Escopo, contexto e critérios
+        &lt;ul&gt;
+          &lt;li&gt;personalizar o processo&lt;/li&gt;
+          &lt;li&gt;compreender ambientes interno e externo&lt;/li&gt;
+          &lt;li&gt;definir critérios de significância&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Avaliação de riscos
+        &lt;ol&gt;
+          &lt;li&gt;Identificação
+            &lt;ul&gt;
+              &lt;li&gt;encontrar, reconhecer e descrever riscos&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Análise
+            &lt;ul&gt;
+              &lt;li&gt;compreender natureza, características e nível&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Avaliação
+            &lt;ul&gt;
+              &lt;li&gt;comparar análise com critérios para apoiar decisões&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Tratamento de riscos
+        &lt;ol&gt;
+          &lt;li&gt;Formular e selecionar opções&lt;/li&gt;
+          &lt;li&gt;Planejar e implementar&lt;/li&gt;
+          &lt;li&gt;Avaliar eficácia&lt;/li&gt;
+          &lt;li&gt;Decidir sobre aceitabilidade do risco remanescente&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Monitoramento e análise crítica
+        &lt;ul&gt;
+          &lt;li&gt;assegurar e melhorar qualidade e resultados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Registro e relato
+        &lt;ul&gt;
+          &lt;li&gt;documentar e comunicar para governança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -10824,32 +10858,276 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Índice de Lucratividade </t>
+          <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
+          <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
+Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
+</t>
         </is>
       </c>
       <c r="F270" t="n">
         <v>0</v>
       </c>
       <c r="G270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>277</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Níveis de Aprendizado Organizacional</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
+    &lt;ul&gt;
+      &lt;li&gt;foco na detecção e correção de erros&lt;/li&gt;
+      &lt;li&gt;atuação dentro das normas e políticas existentes&lt;/li&gt;
+      &lt;li&gt;objetivo: manter o sistema funcionando conforme o planejado&lt;/li&gt;
+      &lt;li&gt;pergunta fundamental: "Estamos fazendo as coisas da maneira certa?"&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Aprendizado de Círculo Duplo (Double-loop Learning)
+    &lt;ul&gt;
+      &lt;li&gt;questionamento das premissas e variáveis governantes&lt;/li&gt;
+      &lt;li&gt;reflexão sobre por que as normas existem&lt;/li&gt;
+      &lt;li&gt;objetivo: modificar a cultura, as políticas e as metas subjacentes&lt;/li&gt;
+      &lt;li&gt;pergunta fundamental: "Estamos fazendo as coisas certas?"&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Aprendizado de Círculo Triplo (Triple-loop Learning)
+    &lt;ul&gt;
+      &lt;li&gt;foco no "aprender a aprender"&lt;/li&gt;
+      &lt;li&gt;desenvolvimento da capacidade de evoluir o próprio processo de aprendizado&lt;/li&gt;
+      &lt;li&gt;objetivo: transformar a identidade, os valores e a visão da organização&lt;/li&gt;
+      &lt;li&gt;pergunta fundamental: "Como decidimos o que é certo?"&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+&lt;ol&gt;
+  &lt;li&gt;Círculo Simples
+    &lt;ul&gt;
+      &lt;li&gt;Identifica-se um desvio no resultado.&lt;/li&gt;
+      &lt;li&gt;Ajusta-se a ação para retornar ao padrão.&lt;/li&gt;
+      &lt;li&gt;As normas permanecem inalteradas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Círculo Duplo
+    &lt;ul&gt;
+      &lt;li&gt;Identifica-se um desvio ou falha recorrente.&lt;/li&gt;
+      &lt;li&gt;Questionam-se os modelos mentais e as premissas que geraram a ação.&lt;/li&gt;
+      &lt;li&gt;Alteram-se as normas e os objetivos para criar uma nova estratégia.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Círculo Triplo
+    &lt;ul&gt;
+      &lt;li&gt;Analisa-se como a organização aprende e lida com mudanças.&lt;/li&gt;
+      &lt;li&gt;Avalia-se o contexto e o propósito maior da instituição.&lt;/li&gt;
+      &lt;li&gt;Promove-se uma mudança sistêmica na forma como a organização se percebe e evolui.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>278</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>279</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;órgão ou entidade da administração pública direta ou indireta&lt;/li&gt;
+      &lt;li&gt;pessoa jurídica de direito privado sem fins lucrativos&lt;/li&gt;
+      &lt;li&gt;missão institucional
+        &lt;ul&gt;
+          &lt;li&gt;pesquisa básica ou aplicada de caráter científico ou tecnológico&lt;/li&gt;
+          &lt;li&gt;desenvolvimento de novos produtos, serviços ou processos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;marco legal&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Lei nº 10.973/2004 (Lei de Inovação)&lt;/li&gt;
+      &lt;li&gt;Lei nº 13.243/2016 (Novo Marco Legal de Ciência, Tecnologia e Inovação)&lt;/li&gt;
+      &lt;li&gt;Decreto nº 9.283/2018 (Regulamentação)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;atuações e prerrogativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;celebração de acordos de parceria
+        &lt;ul&gt;
+          &lt;li&gt;realização de atividades conjuntas de pesquisa e desenvolvimento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;transferência de tecnologia
+        &lt;ul&gt;
+          &lt;li&gt;licenciamento ou cessão de propriedade intelectual&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;compartilhamento de laboratórios e infraestrutura
+        &lt;ul&gt;
+          &lt;li&gt;permissão de uso para empresas e outras ICTs&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;prestação de serviços técnicos especializados&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Núcleo de Inovação Tecnológica (NIT)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;estrutura obrigatória para ICTs públicas&lt;/li&gt;
+      &lt;li&gt;competências
+        &lt;ol&gt;
+          &lt;li&gt;zelar pela manutenção da política institucional de proteção à propriedade intelectual&lt;/li&gt;
+          &lt;li&gt;avaliar e classificar resultados decorrentes de atividades e projetos de pesquisa&lt;/li&gt;
+          &lt;li&gt;opinar pela conveniência de divulgação das criações passíveis de proteção&lt;/li&gt;
+          &lt;li&gt;acompanhar o processamento de pedidos e a manutenção de títulos de propriedade intelectual&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;incentivos ao pesquisador&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;percepção de retribuição pecuniária
+        &lt;ul&gt;
+          &lt;li&gt;participação nos ganhos econômicos da exploração da criação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;licença para constituir empresa de base tecnológica (startup)&lt;/li&gt;
+      &lt;li&gt;prestação de serviços de consultoria&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>280</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Invenção x Inovação</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;invenção &lt;ul&gt; &lt;li&gt;solução tecnicamente viável&lt;/li&gt; &lt;li&gt;não considera a viabilidade econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Inovação &lt;ul&gt; &lt;li&gt;solução tecnicamente e economicamente viável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G274"/>
+  <dimension ref="A1:G296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>6</v>
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
         <v>4</v>
@@ -874,7 +874,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -920,7 +920,7 @@
         <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -959,7 +959,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>3</v>
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1355,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -1706,7 +1706,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
@@ -1740,7 +1740,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1806,7 +1806,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>3</v>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1911,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2046,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -2119,7 +2119,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
@@ -2424,7 +2424,7 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -2575,7 +2575,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -2617,7 +2617,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -2656,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -2688,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -2762,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>2</v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -2870,7 +2870,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>2</v>
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -2965,7 +2965,7 @@
         <v>2</v>
       </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -3034,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
@@ -3071,7 +3071,7 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -3175,7 +3175,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
@@ -3211,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -3251,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3360,7 +3360,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -3538,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>2</v>
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
@@ -3674,7 +3674,7 @@
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -3817,7 +3817,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -3947,7 +3947,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
         <v>4</v>
@@ -3985,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G98" t="n">
         <v>2</v>
@@ -4050,7 +4050,7 @@
         <v>2</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -4161,7 +4161,7 @@
         <v>4</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -4199,7 +4199,7 @@
         <v>2</v>
       </c>
       <c r="G103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -4241,7 +4241,7 @@
         <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -4428,7 +4428,7 @@
         <v>2</v>
       </c>
       <c r="G109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -4714,7 +4714,7 @@
         <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -4850,7 +4850,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
@@ -5000,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="G121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
@@ -5111,7 +5111,7 @@
         <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -7595,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="193">
@@ -7657,7 +7657,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
@@ -7719,7 +7719,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -7812,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201">
@@ -7905,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
@@ -8012,7 +8012,7 @@
         <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204">
@@ -8163,7 +8163,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208">
@@ -8196,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -8264,7 +8264,7 @@
         <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="211">
@@ -8303,7 +8303,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212">
@@ -8370,7 +8370,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214">
@@ -8474,7 +8474,7 @@
         <v>0</v>
       </c>
       <c r="G216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217">
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220">
@@ -8656,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224">
@@ -8799,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226">
@@ -8982,7 +8982,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -9085,7 +9085,7 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -9480,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245">
@@ -10273,7 +10273,7 @@
         <v>0</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -10334,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -10418,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -10853,7 +10853,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -11128,6 +11128,1630 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>281</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>&lt;ol&gt;
+	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
+	&lt;li&gt;Aprendizado Organizacional e Inovação&lt;/li&gt;
+	&lt;li&gt;Liderança Transformadora&lt;/li&gt;
+	&lt;li&gt;Compromisso com as Partes Interessadas&lt;/li&gt;
+	&lt;li&gt;Adaptabilidade&lt;/li&gt;
+	&lt;li&gt;Desenvolvimento Sustentável&lt;/li&gt;
+	&lt;li&gt;Orientação por Processos&lt;/li&gt;
+	&lt;li&gt;Geração de Valor&lt;/li&gt;
+&lt;/ol&gt;</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>282</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>283</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;gestão da qualidade no setor nuclear&lt;/li&gt;
+      &lt;li&gt;foco em segurança e confiabilidade&lt;/li&gt;
+      &lt;li&gt;aplicada à cadeia de suprimentos de energia nuclear&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ISO 26000&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;diretrizes de responsabilidade social&lt;/li&gt;
+      &lt;li&gt;foco em desenvolvimento sustentável e ética&lt;/li&gt;
+      &lt;li&gt;norma de orientação (não certificável)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ISO 45001&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;gestão de saúde e segurança ocupacional (SSO)&lt;/li&gt;
+      &lt;li&gt;foco na prevenção de lesões e doenças do trabalho&lt;/li&gt;
+      &lt;li&gt;promoção de ambientes laborais seguros&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>284</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Tipos de Benchmarking</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Interno&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;comparação entre unidades da mesma empresa&lt;/li&gt;
+      &lt;li&gt;foco em disseminar internamente o que já funciona&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Competitivo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;alvo: concorrentes diretos&lt;/li&gt;
+      &lt;li&gt;foco em &lt;strong&gt;desempenho&lt;/strong&gt; (indicadores/números)&lt;/li&gt;
+      &lt;li&gt;alta barreira de acesso e riscos legais&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Funcional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;alvo: empresas de setores diferentes com funções similares&lt;/li&gt;
+      &lt;li&gt;foco em &lt;strong&gt;práticas&lt;/strong&gt; (processos) e não apenas resultados
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;escolha dos parceiros&lt;/strong&gt; (colaboração)&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;estudo detalhado do próprio processo&lt;/strong&gt;&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;preparo da visita&lt;/strong&gt; técnica&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Genérico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;processos idênticos em áreas totalmente distintas&lt;/li&gt;
+      &lt;li&gt;busca por inovação disruptiva&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>285</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>286</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade Total (TQM)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
+&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;fundamentos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;foco no cliente
+        &lt;ul&gt;
+          &lt;li&gt;atendimento de requisitos&lt;/li&gt;
+          &lt;li&gt;superação de expectativas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;envolvimento total dos funcionários
+        &lt;ul&gt;
+          &lt;li&gt;comprometimento em todos os níveis&lt;/li&gt;
+          &lt;li&gt;treinamento e capacitação contínua&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;abordagem de processo
+        &lt;ul&gt;
+          &lt;li&gt;visão sistêmica da organização&lt;/li&gt;
+          &lt;li&gt;gerenciamento de entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;estratégias e práticas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;melhoria contínua (Kaizen)
+        &lt;ul&gt;
+          &lt;li&gt;pequenas mudanças incrementais&lt;/li&gt;
+          &lt;li&gt;foco na eliminação de resíduos (Muda)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;tomada de decisão baseada em fatos
+        &lt;ul&gt;
+          &lt;li&gt;uso de dados e estatísticas&lt;/li&gt;
+          &lt;li&gt;objetividade na análise de falhas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;gerenciamento de relacionamentos
+        &lt;ul&gt;
+          &lt;li&gt;parcerias com fornecedores&lt;/li&gt;
+          &lt;li&gt;comunicação integrada&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ciclo de aplicação&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;&lt;strong&gt;Plan&lt;/strong&gt; (Planejar)
+        &lt;ul&gt;
+          &lt;li&gt;definir metas e métodos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Do&lt;/strong&gt; (Executar)
+        &lt;ul&gt;
+          &lt;li&gt;implementar as ações e treinar&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Check&lt;/strong&gt; (Verificar)
+        &lt;ul&gt;
+          &lt;li&gt;monitorar e mensurar resultados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Act&lt;/strong&gt; (Agir)
+        &lt;ul&gt;
+          &lt;li&gt;padronizar o sucesso ou corrigir desvios&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ferramentas tradicionais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Existem 7
+        &lt;ul&gt;
+          &lt;li&gt;Fluxograma&lt;/li&gt;
+          &lt;li&gt;Diagrama de Ishikawa (Espinha de Peixe)&lt;/li&gt;
+          &lt;li&gt;Folha de Verificação&lt;/li&gt;
+          &lt;li&gt;Diagrama de Pareto&lt;/li&gt;
+          &lt;li&gt;Histograma&lt;/li&gt;
+          &lt;li&gt;Diagrama de Dispersão&lt;/li&gt;
+          &lt;li&gt;Carta de Controle&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>287</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Custos na TQM</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;investimento para garantir que o produto atenda aos requisitos&lt;/li&gt;
+      &lt;li&gt;prevenção
+        &lt;ul&gt;
+          &lt;li&gt;treinamento e capacitação&lt;/li&gt;
+          &lt;li&gt;planejamento da qualidade&lt;/li&gt;
+          &lt;li&gt;manutenção preventiva&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;avaliação
+        &lt;ul&gt;
+          &lt;li&gt;inspeção de matérias-primas&lt;/li&gt;
+          &lt;li&gt;testes e ensaios laboratoriais&lt;/li&gt;
+          &lt;li&gt;auditorias de processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;custos de não conformidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;perdas geradas pela falta de qualidade&lt;/li&gt;
+      &lt;li&gt;falhas internas
+        &lt;ul&gt;
+          &lt;li&gt;identificado antes da entrega ao cliente&lt;/li&gt;
+          &lt;li&gt;refugo (scrap) e retrabalho&lt;/li&gt;
+          &lt;li&gt;reteste e análise de falhas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;falhas externas
+        &lt;ul&gt;
+          &lt;li&gt;identificado após a entrega ao cliente&lt;/li&gt;
+          &lt;li&gt;assistência técnica e garantias&lt;/li&gt;
+          &lt;li&gt;devoluções e recalls&lt;/li&gt;
+          &lt;li&gt;perda de imagem e de clientes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;otimização econômica&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;relação inversamente proporcional
+        &lt;ul&gt;
+          &lt;li&gt;aumentar investimento em prevenção reduz drasticamente custos de falhas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;custo total da qualidade
+        &lt;ul&gt;
+          &lt;li&gt;soma de todos os custos acima citados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>288</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Gurus da Qualidade</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;controle estatístico de processo (CEP)&lt;/li&gt;
+      &lt;li&gt;criação do ciclo PDCA&lt;/li&gt;
+      &lt;li&gt;distinção entre causas comuns e causas especiais&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;W. Edwards Deming (Anos 50)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;popularização do ciclo PDCA&lt;/li&gt;
+      &lt;li&gt;14 pontos para a gestão&lt;/li&gt;
+      &lt;li&gt;foco na redução da variabilidade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Joseph M. Juran (Anos 50/60)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;trilogia da qualidade
+        &lt;ol&gt;
+          &lt;li&gt;planejamento&lt;/li&gt;
+          &lt;li&gt;controle&lt;/li&gt;
+          &lt;li&gt;melhoria&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;aplicação do princípio de Pareto na qualidade&lt;/li&gt;
+      &lt;li&gt;custos da qualidade (modelo PAF)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Armand Feigenbaum (Anos 50/60)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;controle da qualidade total (TQC)&lt;/li&gt;
+      &lt;li&gt;qualidade como ferramenta de negócios integrada&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Kaoru Ishikawa (Anos 60)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;diagrama de causa e efeito (espinha de peixe)&lt;/li&gt;
+      &lt;li&gt;círculos de controle da qualidade (CCQ)&lt;/li&gt;
+      &lt;li&gt;7 ferramentas básicas da qualidade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Philip Crosby (Anos 70/80)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conceito de "zero defeitos"&lt;/li&gt;
+      &lt;li&gt;prevenção como padrão de desempenho&lt;/li&gt;
+      &lt;li&gt;medida da qualidade pelo preço da não conformidade (PONC)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Genichi Taguchi (Anos 80)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;função perda da qualidade&lt;/li&gt;
+      &lt;li&gt;engenharia robusta&lt;/li&gt;
+      &lt;li&gt;planejamento de experimentos (DoE)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>289</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Waterfall (modelo cascata)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;modelo sequencial e linear
+    &lt;ul&gt;
+      &lt;li&gt;uma fase deve terminar para a próxima iniciar&lt;/li&gt;
+      &lt;li&gt;rigidez e formalidade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;fases do ciclo
+    &lt;ol&gt;
+      &lt;li&gt;levantamento de requisitos
+        &lt;ul&gt;
+          &lt;li&gt;definição completa das necessidades&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;projeto e design
+        &lt;ul&gt;
+          &lt;li&gt;arquitetura do sistema&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;implementação
+        &lt;ul&gt;
+          &lt;li&gt;codificação e construção&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;verificação
+        &lt;ul&gt;
+          &lt;li&gt;testes e garantia da qualidade&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;manutenção
+        &lt;ul&gt;
+          &lt;li&gt;correções e atualizações&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;características principais
+    &lt;ul&gt;
+      &lt;li&gt;documentação exaustiva em cada etapa&lt;/li&gt;
+      &lt;li&gt;marcos e entregas claramente definidos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;adequação
+    &lt;ul&gt;
+      &lt;li&gt;projetos com requisitos estáveis e previsíveis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;limitações
+    &lt;ul&gt;
+      &lt;li&gt;dificuldade em lidar com mudanças tardias&lt;/li&gt;
+      &lt;li&gt;risco de erros descobertos apenas no final&lt;/li&gt;
+      &lt;li&gt;entrega de valor apenas após a conclusão total&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>290</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Extreme Programming (XP)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;comunicação&lt;/li&gt;
+      &lt;li&gt;simplicidade&lt;/li&gt;
+      &lt;li&gt;feedback&lt;/li&gt;
+      &lt;li&gt;coragem&lt;/li&gt;
+      &lt;li&gt;respeito&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;práticas de engenharia (o diferencial)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;programação em par (pair programming)
+        &lt;ul&gt;
+          &lt;li&gt;dois desenvolvedores em uma única estação&lt;/li&gt;
+          &lt;li&gt;revisão de código em tempo real&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;desenvolvimento orientado a testes (TDD)
+        &lt;ul&gt;
+          &lt;li&gt;escrever o teste antes da funcionalidade&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;integração contínua (CI)
+        &lt;ul&gt;
+          &lt;li&gt;código integrado várias vezes ao dia&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;refatoração
+        &lt;ul&gt;
+          &lt;li&gt;melhoria constante do design do código sem alterar comportamento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;propriedade coletiva
+        &lt;ul&gt;
+          &lt;li&gt;qualquer membro pode alterar qualquer parte do código&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;design simples&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ciclo de desenvolvimento&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;planejamento
+        &lt;ul&gt;
+          &lt;li&gt;criação de histórias de usuário&lt;/li&gt;
+          &lt;li&gt;definição de prioridades com o cliente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;iterações
+        &lt;ul&gt;
+          &lt;li&gt;ciclos curtos de desenvolvimento (1 a 2 semanas)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;testes de aceitação
+        &lt;ul&gt;
+          &lt;li&gt;validação direta com o cliente presente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;pequenas liberações (small releases)
+        &lt;ul&gt;
+          &lt;li&gt;entrega frequente de software funcional&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;papel do cliente&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;cliente presente (on-site customer)&lt;/li&gt;
+      &lt;li&gt;disponibilidade total para tirar dúvidas e validar requisitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>291</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Feature-Driven Development (FDD)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;foco em resultados tangíveis e curtos&lt;/li&gt;
+      &lt;li&gt;desenvolvimento iterativo e incremental&lt;/li&gt;
+      &lt;li&gt;ênfase na qualidade do design e do código&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;o que é uma Feature&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;pequena unidade de valor para o cliente&lt;/li&gt;
+      &lt;li&gt;descrita na forma: "ação", "resultado", "objeto"&lt;/li&gt;
+      &lt;li&gt;prazo de implementação: máximo 2 semanas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;processo de desenvolvimento&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;desenvolver um modelo global
+        &lt;ul&gt;
+          &lt;li&gt;especialistas de domínio e arquitetos criam a visão do sistema&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;construir uma lista de funcionalidades
+        &lt;ul&gt;
+          &lt;li&gt;agrupamento de funções por áreas temáticas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;planejar por funcionalidade
+        &lt;ul&gt;
+          &lt;li&gt;definição da ordem de implementação&lt;/li&gt;
+          &lt;li&gt;atribuição de responsabilidades&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;detalhar por funcionalidade
+        &lt;ul&gt;
+          &lt;li&gt;pacote de design (diagramas de sequência e inspeção)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;construir por funcionalidade
+        &lt;ul&gt;
+          &lt;li&gt;codificação, teste unitário e integração&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;papéis e responsabilidades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Programador-Chefe (Chief Programmer)
+        &lt;ul&gt;
+          &lt;li&gt;coordena o design e a construção de um conjunto de features&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Proprietário de Classe (Class Owner)
+        &lt;ul&gt;
+          &lt;li&gt;desenvolvedor responsável por manter a integridade de uma classe específica&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Especialistas de Domínio&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;práticas principais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;modelagem de objetos do domínio&lt;/li&gt;
+      &lt;li&gt;inspeções de código&lt;/li&gt;
+      &lt;li&gt;gerenciamento de configuração e compilações regulares&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>292</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Lean Development (ou Lean Software Development - LSD)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;foco no valor para o cliente&lt;/li&gt;
+      &lt;li&gt;pensamento sistêmico (otimizar o todo)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;os 7 princípios básicos&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;eliminar desperdícios
+        &lt;ul&gt;
+          &lt;li&gt;remover qualquer atividade que não agrega valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;embutir a qualidade
+        &lt;ul&gt;
+          &lt;li&gt;prevenção de erros em vez de apenas detecção&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;criar conhecimento
+        &lt;ul&gt;
+          &lt;li&gt;aprendizado constante através de iterações e feedback&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;adiar o comprometimento
+        &lt;ul&gt;
+          &lt;li&gt;tomar decisões importantes o mais tarde possível&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;entregar rápido
+        &lt;ul&gt;
+          &lt;li&gt;ciclos curtos para retorno de investimento célere&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;respeitar as pessoas
+        &lt;ul&gt;
+          &lt;li&gt;empoderamento da equipe e confiança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;otimizar o todo
+        &lt;ul&gt;
+          &lt;li&gt;melhorar o fluxo de ponta a ponta, não apenas partes isoladas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;desperdícios no desenvolvimento (Muda)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;trabalho parcialmente pronto (estoque)&lt;/li&gt;
+      &lt;li&gt;funcionalidades extras (não solicitadas)&lt;/li&gt;
+      &lt;li&gt;processos extras (burocracia desnecessária)&lt;/li&gt;
+      &lt;li&gt;troca de tarefas (perda de contexto)&lt;/li&gt;
+      &lt;li&gt;espera (atrasos por aprovações)&lt;/li&gt;
+      &lt;li&gt;movimento (esforço para encontrar informações)&lt;/li&gt;
+      &lt;li&gt;defeitos (retrabalho)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>293</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;transparência&lt;/li&gt;
+      &lt;li&gt;inspeção&lt;/li&gt;
+      &lt;li&gt;adaptação&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;valores do Scrum&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;comprometimento&lt;/li&gt;
+      &lt;li&gt;foco&lt;/li&gt;
+      &lt;li&gt;abertura&lt;/li&gt;
+      &lt;li&gt;respeito&lt;/li&gt;
+      &lt;li&gt;coragem&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;papéis (Scrum Team)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Product Owner (PO)
+        &lt;ul&gt;
+          &lt;li&gt;focado no valor do produto e gerenciamento do Product Backlog&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Scrum Master (SM)
+        &lt;ul&gt;
+          &lt;li&gt;líder que serve ao time e à organização na aplicação do Scrum&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Desenvolvedores
+        &lt;ul&gt;
+          &lt;li&gt;profissionais que criam qualquer aspecto de um incremento utilizável em cada Sprint&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;artefatos e compromissos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Product Backlog
+        &lt;ul&gt;
+          &lt;li&gt;compromisso: Meta do Produto&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Sprint Backlog
+        &lt;ul&gt;
+          &lt;li&gt;compromisso: Meta da Sprint&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Incremento
+        &lt;ul&gt;
+          &lt;li&gt;compromisso: Definição de Pronto (Definition of Done)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;eventos do Scrum&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;Sprint
+        &lt;ul&gt;
+          &lt;li&gt;container para todos os outros eventos (máximo 1 mês)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Sprint Planning
+        &lt;ul&gt;
+          &lt;li&gt;planejamento do trabalho a ser realizado na Sprint&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Daily Scrum
+        &lt;ul&gt;
+          &lt;li&gt;inspeção do progresso em direção à Meta da Sprint (15 minutos)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Sprint Review
+        &lt;ul&gt;
+          &lt;li&gt;inspeção do resultado da Sprint e adaptação do Product Backlog&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Sprint Retrospective
+        &lt;ul&gt;
+          &lt;li&gt;planejamento de melhorias na qualidade e eficácia do time&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>294</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Gestão de Projetos</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Kanban</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;comece com o que você faz agora&lt;/li&gt;
+      &lt;li&gt;concorde em buscar mudanças evolutivas e incrementais&lt;/li&gt;
+      &lt;li&gt;respeite os processos, papéis e responsabilidades atuais&lt;/li&gt;
+      &lt;li&gt;incentive atos de liderança em todos os níveis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;práticas principais&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;visualizar o fluxo de trabalho
+        &lt;ul&gt;
+          &lt;li&gt;uso de cartões e colunas no quadro&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;limitar o trabalho em progresso (WIP)
+        &lt;ul&gt;
+          &lt;li&gt;evitar sobrecarga da equipe&lt;/li&gt;
+          &lt;li&gt;reduzir o tempo de espera e gargalos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;gerenciar o fluxo
+        &lt;ul&gt;
+          &lt;li&gt;foco na velocidade e suavidade da passagem das tarefas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;tornar as políticas explícitas
+        &lt;ul&gt;
+          &lt;li&gt;regras claras sobre quando uma tarefa muda de coluna&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;implementar ciclos de feedback
+        &lt;ul&gt;
+          &lt;li&gt;reuniões de revisão e coordenação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;melhorar colaborativamente
+        &lt;ul&gt;
+          &lt;li&gt;uso de modelos científicos e dados para evoluir&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;métricas de desempenho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Lead Time
+        &lt;ul&gt;
+          &lt;li&gt;tempo total desde o pedido do cliente até a entrega&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Cycle Time
+        &lt;ul&gt;
+          &lt;li&gt;tempo em que a equipe está trabalhando ativamente na tarefa&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Throughput
+        &lt;ul&gt;
+          &lt;li&gt;quantidade de itens entregues em um determinado período&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;estrutura do quadro (exemplo)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Backlog -&gt; Selecionado -&gt; Desenvolvimento -&gt; Teste -&gt; Pronto&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>295</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;toda alteração ou desenvolvimento no ambiente externo gera informações&lt;/li&gt;
+      &lt;li&gt;essas informações servem como indicadores para a gestão estratégica&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação dos sinais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;sinais fracos (weak signals)&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;informações precoces, vagas e fragmentadas&lt;/li&gt;
+          &lt;li&gt;indicam mudanças em estágio inicial de desenvolvimento&lt;/li&gt;
+          &lt;li&gt;possuem baixo nível de clareza sobre fonte e impacto&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;sinais fortes (strong signals)&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;informações concretas, visíveis e quantificáveis&lt;/li&gt;
+          &lt;li&gt;indicam tendências consolidadas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;processo de evolução da informação&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;identificação de um sinal vago&lt;/li&gt;
+      &lt;li&gt;reconhecimento da fonte e direção da mudança&lt;/li&gt;
+      &lt;li&gt;compreensão do impacto potencial na organização&lt;/li&gt;
+      &lt;li&gt;formulação de respostas estratégicas&lt;/li&gt;
+      &lt;li&gt;conversão em sinal forte&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;aplicação na gestão do conhecimento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;monitoramento constante do ambiente&lt;/li&gt;
+      &lt;li&gt;superação de filtros mentais que ignoram informações fracas&lt;/li&gt;
+      &lt;li&gt;foco na antecipação para garantir vantagem competitiva&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>296</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>SMED</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Single-Minute Exchange of Dies&lt;/li&gt;
+      &lt;li&gt;conhecido em português como TRF (Troca Rápida de Ferramentas)&lt;/li&gt;
+      &lt;li&gt;redução do tempo de troca para menos de 10 minutos&lt;/li&gt;
+      &lt;li&gt;foco na eliminação de desperdícios no setup&lt;/li&gt;
+      &lt;li&gt;metodologia de Shigeo Shingo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;categorização das atividades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;setup interno (máquina parada)&lt;/li&gt;
+      &lt;li&gt;setup externo (máquina operando)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;estágios de implementação&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;&lt;strong&gt;observação e análise&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;registro de todas as etapas do setup atual&lt;/li&gt;
+          &lt;li&gt;distinção entre atividades internas e externas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;conversão de setup interno em externo&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;preparação prévia de ferramentas&lt;/li&gt;
+          &lt;li&gt;organização do local de trabalho&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;otimização das operações internas&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;uso de fixadores de ação rápida&lt;/li&gt;
+          &lt;li&gt;eliminação de ajustes manuais&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;otimização das operações externas&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;melhoria no transporte e logística de ferramentas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;benefícios para a produção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;redução do tamanho de lote&lt;/li&gt;
+      &lt;li&gt;redução de estoques (WIP)&lt;/li&gt;
+      &lt;li&gt;maior flexibilidade produtiva&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>297</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>298</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;sugerir melhorias ao processo de fabricação ou serviço&lt;/li&gt;
+      &lt;li&gt;atuar na causa raiz dos problemas, não apenas no sintoma&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;distinção de atividades (o que o CCQ não é)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;não é inspeção de peças (identificar defeituosas)&lt;/li&gt;
+      &lt;li&gt;não é manutenção corretiva&lt;/li&gt;
+      &lt;li&gt;não é definição de padrões estatísticos (cartas de controle)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;forma de atuação&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;identificar oportunidades de melhoria no ambiente de trabalho&lt;/li&gt;
+      &lt;li&gt;analisar os métodos atuais de produção&lt;/li&gt;
+      &lt;li&gt;propor mudanças que aumentem a eficiência ou qualidade&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;natureza da contribuição&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;caráter consultivo e propositivo&lt;/li&gt;
+      &lt;li&gt;foco no aperfeiçoamento contínuo (Kaizen)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>299</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>300</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Seis Sigma</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;reduzir a variabilidade dos processos&lt;/li&gt;
+      &lt;li&gt;alcançar níveis de qualidade próximos à perfeição&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;métrica de desempenho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;nível 6 Sigma
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;3,4 PPM&lt;/strong&gt; (defeitos por milhão de oportunidades)&lt;/li&gt;
+          &lt;li&gt;corresponde a 99,99966% de conformidade&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;deslocamento da média (Sigma Shift)
+        &lt;ul&gt;
+          &lt;li&gt;considera variação de 1,5 sigma a longo prazo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;metodologia principal (DMAIC)&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;&lt;strong&gt;Define&lt;/strong&gt; (Definir)
+        &lt;ul&gt;
+          &lt;li&gt;escopo e metas do projeto&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Measure&lt;/strong&gt; (Medir)
+        &lt;ul&gt;
+          &lt;li&gt;coleta de dados e desempenho atual&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Analyze&lt;/strong&gt; (Analisar)
+        &lt;ul&gt;
+          &lt;li&gt;identificação das causas raízes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Improve&lt;/strong&gt; (Melhorar)
+        &lt;ul&gt;
+          &lt;li&gt;desenvolvimento e teste de soluções&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Control&lt;/strong&gt; (Controlar)
+        &lt;ul&gt;
+          &lt;li&gt;monitoramento e padronização dos ganhos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;estrutura de papéis (Belts)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Yellow Belt&lt;/li&gt;
+      &lt;li&gt;Green Belt&lt;/li&gt;
+      &lt;li&gt;Black Belt&lt;/li&gt;
+      &lt;li&gt;Master Black Belt&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;base estatística&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;foco no desvio padrão (sigma)&lt;/li&gt;
+      &lt;li&gt;redução drástica da probabilidade de erro&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>301</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>302</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
+    &lt;ul&gt;
+      &lt;li&gt;engloba o início do ciclo&lt;/li&gt;
+      &lt;li&gt;subetapas correlatas:
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Identificação&lt;/strong&gt; (mapear o saber)&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Captura&lt;/strong&gt; (extrair o tácito)&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (fontes externas)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Armazenamento&lt;/strong&gt; (Retenção)
+    &lt;ul&gt;
+      &lt;li&gt;foco na memória organizacional&lt;/li&gt;
+      &lt;li&gt;subetapas correlatas:
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Armazenamento&lt;/strong&gt; (repositórios e bancos de dados)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Distribuição&lt;/strong&gt; (Disseminação/Uso)
+    &lt;ul&gt;
+      &lt;li&gt;foco no fluxo e na geração de valor&lt;/li&gt;
+      &lt;li&gt;subetapas correlatas:
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Compartilhamento&lt;/strong&gt; (disseminação interna)&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Aplicação&lt;/strong&gt; (uso prático e tomada de decisão)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Avaliação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;medir o impacto e eficiência do ciclo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G296"/>
+  <dimension ref="A1:G300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12755,6 +12755,255 @@
         <v>0</v>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>303</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Gráficos de Controle por Variáveis e por Atributos</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;objetivo: monitorar média e variabilidade de dados contínuos&lt;/li&gt;
+      &lt;li&gt;principais tipos
+        &lt;ol&gt;
+          &lt;li&gt;Carta X-barra e R (Média e Amplitude)
+            &lt;ul&gt;
+              &lt;li&gt;indicada para subgrupos pequenos (n &lt; 10)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Carta X-barra e S (Média e Desvio Padrão)
+            &lt;ul&gt;
+              &lt;li&gt;indicada para subgrupos maiores (n &gt;= 10)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Carta I-mR (Indivíduos e Amplitude Móvel)&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;particularidades: maior sensibilidade estatística e amostras menores&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Atributos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;objetivo: monitorar conformidade (dados discretos)&lt;/li&gt;
+      &lt;li&gt;principais tipos
+        &lt;ul&gt;
+          &lt;li&gt;Foco na Unidade Defeituosa
+            &lt;ul&gt;
+              &lt;li&gt;Carta p (amostra variável)&lt;/li&gt;
+              &lt;li&gt;Carta np (amostra constante)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Foco no Número de Defeitos
+            &lt;ul&gt;
+              &lt;li&gt;Carta c (amostra constante)&lt;/li&gt;
+              &lt;li&gt;Carta u (amostra variável)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;particularidades: exige amostras grandes e possui custo de coleta menor&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>304</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Técnica de Moderação por Cartelas</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Técnica de Moderação por cartelas
+    &lt;ul&gt;
+      &lt;li&gt;facilitação de grupos&lt;/li&gt;
+      &lt;li&gt;uso de cartões coloridos
+        &lt;ul&gt;
+          &lt;li&gt;uma ideia por cartaz&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;processo
+        &lt;ol&gt;
+          &lt;li&gt;geração de ideias&lt;/li&gt;
+          &lt;li&gt;exposição no painel&lt;/li&gt;
+          &lt;li&gt;agrupamento por afinidade&lt;/li&gt;
+          &lt;li&gt;estruturação e discussão&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;garantir
+        &lt;ul&gt;
+          &lt;li&gt;participação igualitária&lt;/li&gt;
+          &lt;li&gt;visualização imediata&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>305</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>306</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;determinação de questões internas e externas&lt;/li&gt;
+      &lt;li&gt;foco em partes interessadas (stakeholders)&lt;/li&gt;
+      &lt;li&gt;mentalidade de risco: substitui as antigas ações preventivas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;informação documentada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;termo que substitui "Manual da Qualidade" e "Procedimentos"&lt;/li&gt;
+      &lt;li&gt;exigência de manter e reter documentos essenciais para o SGQ&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;operação e controle&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;monitoramento da percepção e satisfação do cliente&lt;/li&gt;
+      &lt;li&gt;validação de processos especiais (saídas não verificáveis)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliação de desempenho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;análise de indicadores e eficácia dos processos&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;auditoria interna:&lt;/strong&gt; requisito obrigatório para manter o sistema&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;auditoria externa:&lt;/strong&gt; OPCIONAL para a gestão (obrigatória apenas para certificação formal)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -874,7 +874,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1355,7 +1355,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1391,7 +1391,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1610,7 +1610,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>3</v>
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2046,7 +2046,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
         <v>2</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -4017,7 +4017,7 @@
         <v>2</v>
       </c>
       <c r="G98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -4295,7 +4295,7 @@
         <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -4505,7 +4505,7 @@
         <v>2</v>
       </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
         <v>5</v>
       </c>
       <c r="G114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115">
@@ -4657,7 +4657,7 @@
         <v>7</v>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116">
@@ -4714,7 +4714,7 @@
         <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
@@ -4765,7 +4765,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G117" t="n">
         <v>1</v>
@@ -4850,7 +4850,7 @@
         <v>6</v>
       </c>
       <c r="G118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
@@ -4899,7 +4899,7 @@
         <v>4</v>
       </c>
       <c r="G119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
@@ -4936,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
@@ -5000,7 +5000,7 @@
         <v>2</v>
       </c>
       <c r="G121" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
@@ -5032,10 +5032,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123">
@@ -5074,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
@@ -5111,7 +5111,7 @@
         <v>2</v>
       </c>
       <c r="G124" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
@@ -5171,7 +5171,7 @@
         <v>6</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -6444,7 +6444,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160">
@@ -6511,10 +6511,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -6548,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
@@ -7252,16 +7252,16 @@
       <c r="E182" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;caráter científico  (1º Congresso Brasileiro de Contabilidade/1924)&lt;ul&gt; &lt;li&gt;ciência que estuda e pratica as funções de orientação, de controle e de registro dos atos e fatos de uma administração econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 	&lt;li&gt;doutrina  (IPECAFI)&lt;ul&gt; &lt;li&gt;objetivamente, um sistema de informação&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -7292,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -7323,14 +7323,12 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
+      <c r="A185" t="n">
+        <v>192</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -7344,29 +7342,24 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>campo de aplicação da Contabilidade</t>
+          <t>finalidade principal da ciência contábil ou objetivo</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aziendas &lt;ul&gt; 
-&lt;li&gt;patrimônio de uma pessoa que é gerido de maneira organizada&lt;/li&gt;
-&lt;li&gt;azienda econômica&lt;/li&gt;
-&lt;li&gt;aziendas econômico-sociais&lt;/li&gt;
-&lt;li&gt;aziendas sociais&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>fornecer informações sobre a situação patrimonial e financeira</t>
         </is>
       </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -7380,24 +7373,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>finalidade principal da ciência contábil ou objetivo</t>
+          <t>usuários das demonstrações contábeis externos ou internos</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>fornecer informações sobre a situação patrimonial e financeira</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F186" t="n">
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -7411,50 +7407,50 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>usuários das demonstrações contábeis externos ou internos</t>
+          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Usuários internos (nível estratégico) &lt;ul&gt; &lt;li&gt;Alta e Média Gerência da empresa&lt;/li&gt; &lt;li&gt;Conselho de Administração&lt;/li&gt; &lt;li&gt;Acionistas Controladores&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Usuários externos &lt;ul&gt; &lt;li&gt;Empregados&lt;/li&gt; &lt;li&gt;Investidores&lt;/li&gt; &lt;li&gt;Credores por empréstimos&lt;/li&gt; &lt;li&gt;Fornecedores&lt;/li&gt; &lt;li&gt;Clientes&lt;/li&gt; &lt;li&gt;Governo e suas agências&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Muitos investidores, credores por empréstimos e outros credores</t>
         </is>
       </c>
       <c r="F187" t="n">
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Contabilidade Gerencial</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Gestão de Estoques</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>COMITÊ DE PRONUNCIAMENTOS CONTÁBEIS - 00, Item 1.5</t>
+          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Muitos investidores, credores por empréstimos e outros credores</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
+	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -7462,7 +7458,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -7476,27 +7472,27 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>índice de rotatividade mensal para os produtos acabados (ou giro de estoque)</t>
+          <t>Como determinar o estoque mínimo</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;mede a velocidade com que o estoque é vendido&lt;/li&gt;
-	&lt;li&gt;Fórmula: &lt;ul&gt; &lt;li&gt;Índice de Rotatividade = Custo de Produtos Vendidos/Custo Médio Mensal de Estoque&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
         <v>1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -7505,19 +7501,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Gestão de Estoques</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Como determinar o estoque mínimo</t>
+          <t>Constituição Federal de 1988, Art. 7º</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;Projeção mínima de consumo: &lt;ul&gt; &lt;li&gt;consumo histórico ou previsões de uso durante o período de reposição, considerando uma margem de segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Cálculo estatístico: &lt;ul&gt; &lt;li&gt;dados históricos, médias de consumo e variação de demanda, aplicando fórmulas estatísticas para definir o nível mínimo, conforme orientações de manuais de administração de materiais (vide Manuais do Ministério da Economia/Governo Federal e autores como Chiavenato).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -7530,7 +7526,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -7544,44 +7540,10 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Constituição Federal de 1988, Art. 7º</t>
+          <t>Consolidação das leis do Trabalho, Capítulo V</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;redução dos riscos inerentes ao trabalho, por meio de normas de &lt;ul&gt; &lt;li&gt;saúde&lt;/li&gt; &lt;li&gt;higiene&lt;/li&gt; &lt;li&gt;segurança.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Adicional de remuneração para as atividades penosas, insalubres ou perigosas, na forma da lei;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>198</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>Consolidação das leis do Trabalho, Capítulo V</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;responsabilidades dos órgãos&lt;/li&gt;
@@ -7591,16 +7553,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>199</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Autosserviço</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Acesso pelo cidadão a serviço público</t>
+        </is>
+      </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -7614,24 +7607,24 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Autosserviço</t>
+          <t>Base nacional de serviços públicos</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Acesso pelo cidadão a serviço público</t>
+          <t>Base de dados que contém as informações</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -7645,24 +7638,24 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Base nacional de serviços públicos</t>
+          <t>Dados abertos</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Base de dados que contém as informações</t>
+          <t>Dados acessíveis ao público</t>
         </is>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -7676,24 +7669,24 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Dados abertos</t>
+          <t>Dado acessível ao público</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Dados acessíveis ao público</t>
+          <t>Qualquer dado gerado ou acumulado</t>
         </is>
       </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -7707,24 +7700,24 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Dado acessível ao público</t>
+          <t>Formato aberto</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Qualquer dado gerado ou acumulado</t>
+          <t>Formato de arquivo não proprietário</t>
         </is>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -7738,24 +7731,24 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Formato aberto</t>
+          <t>Governo como plataforma</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Formato de arquivo não proprietário</t>
+          <t>Infraestrutura tecnológica que facilite</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -7769,24 +7762,24 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Governo como plataforma</t>
+          <t>Laboratório de inovação</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Infraestrutura tecnológica que facilite</t>
+          <t>Espaço aberto à participação</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -7800,12 +7793,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Laboratório de inovação</t>
+          <t>Plataformas de governo digital</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Espaço aberto à participação</t>
+          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7817,7 +7810,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -7831,24 +7824,24 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Plataformas de governo digital</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
+          <t>Informação íntegra e precisa</t>
         </is>
       </c>
       <c r="F200" t="n">
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -7862,24 +7855,26 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Informação íntegra e precisa</t>
+          <t>Disponibilização de dados pela administração pública</t>
         </is>
       </c>
       <c r="F201" t="n">
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
-        <v>208</v>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -7893,43 +7888,10 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Transparência ativa</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública</t>
-        </is>
-      </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação padrão digital
@@ -8008,35 +7970,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
+    <row r="203">
+      <c r="A203" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B203" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr">
+      <c r="C203" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -8046,35 +8008,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
+    <row r="204">
+      <c r="A204" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B204" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C205" t="inlineStr">
+      <c r="C204" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -8085,33 +8047,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="205">
+      <c r="A205" t="n">
         <v>212</v>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B205" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr">
+      <c r="C205" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -8124,33 +8086,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="206">
+      <c r="A206" t="n">
         <v>213</v>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B206" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C207" t="inlineStr">
+      <c r="C206" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -8159,99 +8121,99 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="207">
+      <c r="A207" t="n">
         <v>214</v>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B207" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C207" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Plataformas de Governo Digital</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t xml:space="preserve">instrumentos para os entes federativos disponibilizem seus serviços públicos
 devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
 padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
         </is>
       </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Prestação Digital dos Serviços Públicos</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A209" t="n">
+        <v>216</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Prestação Digital dos Serviços Públicos</t>
+          <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
-        <is>
-          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>216</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Normas Regulamentadoras do Trabalho</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -8260,35 +8222,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
+    <row r="210">
+      <c r="A210" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -8299,16 +8261,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>218</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NR 2</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Inspeção Prévia</t>
+        </is>
+      </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -8322,41 +8315,10 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NR 2</t>
+          <t>NR 3</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
-        <is>
-          <t>Inspeção Prévia</t>
-        </is>
-      </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>219</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NR 3</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -8366,16 +8328,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>220</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F213" t="n">
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -8389,27 +8385,24 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -8423,41 +8416,10 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F215" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>222</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -8470,6 +8432,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>223</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NR 7</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
+	&lt;li&gt;competência do Empregador: &lt;ul&gt; &lt;li&gt;garantir&lt;/li&gt; &lt;li&gt;custear&lt;/li&gt; &lt;li&gt;indicar&lt;/li&gt; &lt;li&gt;no caso de&lt;/li&gt; &lt;li&gt;inexistindo médico do trabalho&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F216" t="n">
         <v>0</v>
       </c>
@@ -8478,8 +8474,10 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
-        <v>223</v>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -8493,46 +8491,10 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NR 7</t>
+          <t>NR 8</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
-	&lt;li&gt;competência do Empregador: &lt;ul&gt; &lt;li&gt;garantir&lt;/li&gt; &lt;li&gt;custear&lt;/li&gt; &lt;li&gt;indicar&lt;/li&gt; &lt;li&gt;no caso de&lt;/li&gt; &lt;li&gt;inexistindo médico do trabalho&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>NR 8</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -8541,33 +8503,33 @@
 </t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="218">
+      <c r="A218" t="n">
         <v>225</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -8579,33 +8541,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="219">
+      <c r="A219" t="n">
         <v>226</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -8616,33 +8578,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="n">
+    <row r="220">
+      <c r="A220" t="n">
         <v>227</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -8652,33 +8614,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="n">
+    <row r="221">
+      <c r="A221" t="n">
         <v>228</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -8687,33 +8649,33 @@
 </t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>229</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8723,33 +8685,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>230</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -8758,33 +8720,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" t="n">
+    <row r="224">
+      <c r="A224" t="n">
         <v>231</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8795,16 +8757,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>232</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F225" t="n">
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -8813,49 +8809,15 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+          <t>Índices Financeiros</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
-        <v>233</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Índices Financeiros</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8866,33 +8828,33 @@
 </t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="n">
+    <row r="227">
+      <c r="A227" t="n">
         <v>234</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -8902,35 +8864,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pré-Desenvolvimento &lt;ol&gt; &lt;li&gt;Planejamento do Projeto &lt;ul&gt; &lt;li&gt;são realizadas &lt;ul&gt; &lt;li&gt;brainstorming&lt;/li&gt; &lt;li&gt;visitas a feiras técnicas&lt;/li&gt; &lt;li&gt;análise de produtos da concorrência&lt;/li&gt; &lt;li&gt;pesquisa de mercado&lt;/li&gt; &lt;li&gt;elaboração das especificações do projeto&lt;/li&gt; &lt;li&gt;dentre outros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
@@ -8939,35 +8901,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Único Banco de Dados Centralizado&lt;/li&gt;
@@ -8978,16 +8940,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>237</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F230" t="n">
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -8996,49 +8992,15 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Back-office vs. Front-office</t>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
-        <v>238</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Hierarquia na Aquisição de Tecnologia</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -9047,16 +9009,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>239</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -9065,49 +9061,15 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Processos Decisórios</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Critérios de Decisão no AHP</t>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
-	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
-        <v>240</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>Tendências e Tecnologias em Gestão da Informação</t>
-        </is>
-      </c>
-      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -9117,33 +9079,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="234">
+      <c r="A234" t="n">
         <v>241</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -9153,33 +9115,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="235">
+      <c r="A235" t="n">
         <v>242</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -9189,33 +9151,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="n">
+    <row r="236">
+      <c r="A236" t="n">
         <v>243</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -9224,33 +9186,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
         <v>244</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -9259,33 +9221,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
+      <c r="F237" t="n">
         <v>2</v>
       </c>
-      <c r="G238" t="n">
+      <c r="G237" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="238">
+      <c r="A238" t="n">
         <v>245</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -9294,33 +9256,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="239">
+      <c r="A239" t="n">
         <v>246</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -9329,33 +9291,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="n">
+    <row r="240">
+      <c r="A240" t="n">
         <v>247</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -9368,35 +9330,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -9405,33 +9367,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="n">
+    <row r="242">
+      <c r="A242" t="n">
         <v>249</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -9442,67 +9404,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>250</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F243" t="n">
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Financeira</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Análise de Investimentos</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Número suficiente para identificação</t>
+          <t>Relação entre TIR e VPL</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
-        <v>251</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>Relação entre TIR e VPL</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;São análises independentes.&lt;/li&gt;
@@ -9512,6 +9474,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>252</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>método da TIR</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+        </is>
+      </c>
       <c r="F245" t="n">
         <v>0</v>
       </c>
@@ -9521,7 +9514,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -9535,12 +9528,15 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>método da TIR</t>
+          <t>Valor Presente Líquido (VPL)</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
+	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -9552,7 +9548,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -9566,15 +9562,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Valor Presente Líquido (VPL)</t>
+          <t>Relação VPL X TMA</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
-	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Inversamente proporcionais</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -9586,7 +9579,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -9600,41 +9593,10 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Relação VPL X TMA</t>
+          <t>Relação VPL x TIR x TMA</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
-        <is>
-          <t>Inversamente proporcionais</t>
-        </is>
-      </c>
-      <c r="F248" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
-        <v>255</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Relação VPL x TIR x TMA</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;𝑽𝑷𝑳 &gt; 0 -&gt; 𝑽𝑷𝑳 &gt; TMA&lt;/li&gt;
@@ -9643,16 +9605,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>256</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Princípio da Entidade</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Autonomia da pessoa jurídica</t>
+        </is>
+      </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -9661,46 +9654,15 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Contabilidade Básica</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Princípio da Entidade</t>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
-        <is>
-          <t>Autonomia da pessoa jurídica</t>
-        </is>
-      </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
-        <v>257</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -9718,18 +9680,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Receitas</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;aumento nos ativos
+    &lt;ul&gt;
+      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diminuição de passivo
+    &lt;ul&gt;
+      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta aumento do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F251" t="n">
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A252" t="n">
+        <v>259</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -9743,34 +9761,35 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Receitas</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;aumento nos ativos
-    &lt;ul&gt;
-      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;diminuição de passivo
-    &lt;ul&gt;
-      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+  &lt;li&gt;consumo de bens ou serviços
+    &lt;ul&gt;
+      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;representam
+    &lt;ul&gt;
+      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
+      &lt;li&gt;aumento no passivo&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;reconhecimento
     &lt;ul&gt;
-      &lt;li&gt;acarreta aumento do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;transações com sócios
     &lt;ul&gt;
-      &lt;li&gt;não representam receitas&lt;/li&gt;
+      &lt;li&gt;não representam despesas&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -9780,12 +9799,12 @@
         <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -9799,67 +9818,10 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;consumo de bens ou serviços
-    &lt;ul&gt;
-      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;representam
-    &lt;ul&gt;
-      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
-      &lt;li&gt;aumento no passivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;reconhecimento
-    &lt;ul&gt;
-      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;transações com sócios
-    &lt;ul&gt;
-      &lt;li&gt;não representam despesas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
-        <v>260</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -9941,33 +9903,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>261</v>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -10015,33 +9977,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>262</v>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -10093,33 +10055,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>263</v>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -10137,33 +10099,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
         <v>264</v>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -10173,35 +10135,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -10269,33 +10231,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="n">
+    <row r="259">
+      <c r="A259" t="n">
         <v>266</v>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -10330,33 +10292,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="n">
+    <row r="260">
+      <c r="A260" t="n">
         <v>267</v>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -10414,33 +10376,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" t="n">
+    <row r="261">
+      <c r="A261" t="n">
         <v>268</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
@@ -10490,33 +10452,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
         <v>269</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
@@ -10596,33 +10558,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
         <v>270</v>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -10631,6 +10593,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>271</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F264" t="n">
         <v>0</v>
       </c>
@@ -10640,7 +10633,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -10654,12 +10647,14 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>PAYBACK SIMPLES</t>
+          <t>PAYBACK DESCONTADO</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -10671,7 +10666,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -10685,14 +10680,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>PAYBACK DESCONTADO</t>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -10704,7 +10697,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -10718,12 +10711,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
+          <t xml:space="preserve">Índice de Lucratividade </t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
+          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -10735,55 +10728,24 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Índice de Lucratividade </t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
-        <is>
-          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
-        </is>
-      </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
-        <v>275</v>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Processo de Gestão de Risco</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -10849,66 +10811,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="n">
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="n">
+    <row r="269">
+      <c r="A269" t="n">
         <v>276</v>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F270" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
         <v>277</v>
       </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E270" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -10961,16 +10923,50 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>278</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F271" t="n">
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -10979,49 +10975,15 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>teoria da organização e da gestão da informação</t>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
-	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
-        <v>279</v>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Gestão da Inovação</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
-        </is>
-      </c>
-      <c r="E273" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -11090,16 +11052,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>280</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Invenção x Inovação</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;invenção &lt;ul&gt; &lt;li&gt;solução tecnicamente viável&lt;/li&gt; &lt;li&gt;não considera a viabilidade econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Inovação &lt;ul&gt; &lt;li&gt;solução tecnicamente e economicamente viável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -11108,49 +11104,15 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão da Qualidade</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Invenção x Inovação</t>
+          <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;invenção &lt;ul&gt; &lt;li&gt;solução tecnicamente viável&lt;/li&gt; &lt;li&gt;não considera a viabilidade econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Inovação &lt;ul&gt; &lt;li&gt;solução tecnicamente e economicamente viável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="n">
-        <v>281</v>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
-        </is>
-      </c>
-      <c r="E275" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -11164,6 +11126,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>282</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F275" t="n">
         <v>0</v>
       </c>
@@ -11173,7 +11166,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -11187,41 +11180,10 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>índice de capacidade do processo (Cp)</t>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
-        <is>
-          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
-        <v>283</v>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>ISO 19443; ISO 26000; e ISO 45001</t>
-        </is>
-      </c>
-      <c r="E277" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -11248,33 +11210,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
         <v>284</v>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>Tipos de Benchmarking</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E277" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Interno&lt;/strong&gt;
@@ -11311,6 +11273,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>285</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F278" t="n">
         <v>0</v>
       </c>
@@ -11320,7 +11316,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -11334,44 +11330,10 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Ciclo PDCA</t>
+          <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
-        <v>286</v>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade Total (TQM)</t>
-        </is>
-      </c>
-      <c r="E280" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -11461,33 +11423,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
         <v>287</v>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -11546,33 +11508,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
         <v>288</v>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E281" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -11632,33 +11594,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F282" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
         <v>289</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E282" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -11717,33 +11679,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F283" t="n">
-        <v>0</v>
-      </c>
-      <c r="G283" t="n">
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="n">
+    <row r="283">
+      <c r="A283" t="n">
         <v>290</v>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -11820,33 +11782,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F284" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
         <v>291</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -11918,33 +11880,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F285" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
         <v>292</v>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E285" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -12006,33 +11968,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F286" t="n">
-        <v>0</v>
-      </c>
-      <c r="G286" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="n">
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
         <v>293</v>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D286" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E286" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -12121,33 +12083,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F287" t="n">
-        <v>0</v>
-      </c>
-      <c r="G287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
         <v>294</v>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E287" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -12220,33 +12182,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F288" t="n">
-        <v>0</v>
-      </c>
-      <c r="G288" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="n">
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
         <v>295</v>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E288" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -12291,33 +12253,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F289" t="n">
-        <v>0</v>
-      </c>
-      <c r="G289" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="n">
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
         <v>296</v>
       </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C290" t="inlineStr">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
+      <c r="D289" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
+      <c r="E289" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -12372,6 +12334,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>297</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F290" t="n">
         <v>0</v>
       </c>
@@ -12381,7 +12399,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -12395,66 +12413,10 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Dimensões da Qualidade em Serviços</t>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;instalações físicas
-        &lt;ul&gt;
-          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;materiais
-        &lt;ul&gt;
-          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços explícitos
-        &lt;ul&gt;
-          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços complementares
-        &lt;ul&gt;
-          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F291" t="n">
-        <v>0</v>
-      </c>
-      <c r="G291" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" t="n">
-        <v>298</v>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C292" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>CCQ – Círculos de Controle de Qualidade</t>
-        </is>
-      </c>
-      <c r="E292" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -12486,6 +12448,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>299</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F292" t="n">
         <v>0</v>
       </c>
@@ -12495,7 +12522,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -12509,75 +12536,10 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+          <t>Seis Sigma</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
-      &lt;li&gt;utilizadas como manobra para "promover para fora"
-        &lt;ul&gt;
-          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
-          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
-      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F293" t="n">
-        <v>0</v>
-      </c>
-      <c r="G293" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="n">
-        <v>300</v>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>Seis Sigma</t>
-        </is>
-      </c>
-      <c r="E294" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -12647,6 +12609,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>301</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
       <c r="F294" t="n">
         <v>0</v>
       </c>
@@ -12656,7 +12649,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -12665,46 +12658,15 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Capabilidade</t>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
-        <is>
-          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
-        </is>
-      </c>
-      <c r="F295" t="n">
-        <v>0</v>
-      </c>
-      <c r="G295" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="n">
-        <v>302</v>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>Macrofluxo da Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="E296" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -12748,33 +12710,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F296" t="n">
-        <v>0</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
         <v>303</v>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="E296" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -12823,33 +12785,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F297" t="n">
-        <v>0</v>
-      </c>
-      <c r="G297" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="n">
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
         <v>304</v>
       </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
+      <c r="D297" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
+      <c r="E297" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -12879,6 +12841,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F297" t="n">
+        <v>0</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>305</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F298" t="n">
         <v>0</v>
       </c>
@@ -12888,7 +12910,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -12902,70 +12924,10 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Diagrama de Interação do Processo</t>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diagrama de Interação do Processo
-    &lt;ul&gt;
-      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
-      &lt;li&gt;foco nas interfaces
-        &lt;ul&gt;
-          &lt;li&gt;entradas e saídas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;elementos
-        &lt;ul&gt;
-          &lt;li&gt;blocos de processos macro&lt;/li&gt;
-          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;objetivos
-        &lt;ul&gt;
-          &lt;li&gt;identificar dependências&lt;/li&gt;
-          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;distinção
-        &lt;ul&gt;
-          &lt;li&gt;foco externo ao processo&lt;/li&gt;
-          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F299" t="n">
-        <v>0</v>
-      </c>
-      <c r="G299" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="n">
-        <v>306</v>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>Requisitos e Rotinas da ISO 9001:2015</t>
-        </is>
-      </c>
-      <c r="E300" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -12997,10 +12959,321 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Débito na Contabilidade</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;lado esquerdo do razonete&lt;/li&gt;
+      &lt;li&gt;indica a aplicação de recursos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;abrangência de aplicação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;contas patrimoniais:&lt;/strong&gt; Ativo, Passivo e PL&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;contas de resultado:&lt;/strong&gt; Receitas e Despesas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;comportamento técnico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Ativo e Despesas:&lt;/strong&gt; débito aumenta o saldo&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Passivo, PL e Receitas:&lt;/strong&gt; débito diminui o saldo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;método das partidas dobradas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;exigência de equilíbrio entre débitos e créditos (D = C)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;exemplos de aplicação&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;aquisição de bens ou direitos&lt;/li&gt;
+      &lt;li&gt;liquidação de obrigações&lt;/li&gt;
+      &lt;li&gt;reconhecimento de gastos (consumo de riqueza)&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F300" t="n">
         <v>0</v>
       </c>
       <c r="G300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>308</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Tipos de Contas e Retificadoras</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ativo: Bens e direitos (Natureza devedora)&lt;/li&gt;
+      &lt;li&gt;Passivo: Obrigações com terceiros (Natureza credora)&lt;/li&gt;
+      &lt;li&gt;Patrimônio Líquido (PL): Recursos próprios (Natureza credora)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Contas de Resultado&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Despesas: Diminuem o PL (Natureza devedora)&lt;/li&gt;
+      &lt;li&gt;Receitas: Aumentam o PL (Natureza credora)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Contas Retificadoras (Redutoras)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Aparecem com sinal oposto para ajustar o saldo do grupo&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;No Ativo (Credoras):&lt;/strong&gt; Depreciação Acumulada, Amortização Acumulada, PCLD&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;No Passivo/PL (Devedoras):&lt;/strong&gt; Capital a Integralizar, Ações em Tesouraria, Prejuízos Acumulados&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>309</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Diferenças Tributárias</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Classificação:&lt;/strong&gt; Passivo Circulante (Obrigação)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Significado:&lt;/strong&gt; Dívida da empresa com o governo&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Uso comum:&lt;/strong&gt; Valores retidos de terceiros ou saldo devedor de impostos indiretos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Impostos a Recuperar / Compensar&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Classificação:&lt;/strong&gt; Ativo Circulante (Direito)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Significado:&lt;/strong&gt; Créditos tributários que a empresa possui&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Uso comum:&lt;/strong&gt; Créditos de não cumulatividade (entradas) ou pagamentos feitos a maior&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>310</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Teoria Patrimonialista e Despesas</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Contas Patrimoniais:&lt;/strong&gt; Ativo, Passivo e PL (representam a situação estática)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Contas de Resultado:&lt;/strong&gt; Receitas e Despesas (representam a situação dinâmica)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Impacto das Despesas no Patrimônio Líquido&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;As despesas são contas redutoras do resultado do exercício&lt;/li&gt;
+      &lt;li&gt;O resultado (lucro ou prejuízo) é incorporado ao Patrimônio Líquido ao final do período&lt;/li&gt;
+      &lt;li&gt;Portanto: &lt;strong&gt;Despesa = (-) Lucro = (-) Patrimônio Líquido&lt;/strong&gt;&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diferença Crucial: Lucro Bruto vs. Patrimônio Líquido&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Nem toda despesa afeta o Lucro Bruto (ex: despesas financeiras)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Toda&lt;/strong&gt; despesa afeta o Lucro Líquido e o Patrimônio Líquido&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>311</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>O Ativo ao Final do Exercício</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representa o saldo após todas as operações do ano.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Lucro já incluso:&lt;/strong&gt; O valor do lucro já está refletido nas contas de Ativo (caixa, estoques, etc.).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Não somar:&lt;/strong&gt; Nunca adicione o lucro ao Ativo Total se ele já for o saldo de fechamento.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Cálculo Direto&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;Identifique o Ativo Total final.&lt;/li&gt;
+      &lt;li&gt;Aplique o percentual do Capital Próprio (100% - % de terceiros).&lt;/li&gt;
+      &lt;li&gt;O resultado é o Patrimônio Líquido final.&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>312</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Azienda</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Objeto de estudo da contabilidade: Patrimônio + Gestão&lt;/li&gt;
+      &lt;li&gt;Origem: Escola Italiana de Contabilidade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Elementos Essenciais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Sujeito:&lt;/strong&gt; Elemento pessoal (administrador/proprietário)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Objeto:&lt;/strong&gt; Elemento material (patrimônio)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fim:&lt;/strong&gt; Objetivo a ser alcançado pela entidade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Classificação por Finalidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Sociais:&lt;/strong&gt; Sem fins lucrativos (Associações)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Econômicas:&lt;/strong&gt; Com fins lucrativos (Empresas)&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Sócio-Econômicas:&lt;/strong&gt; Fins sociais com necessidade de superávit (Cooperativas)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G305"/>
+  <dimension ref="A1:G315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13277,6 +13277,1245 @@
         <v>0</v>
       </c>
     </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>313</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NR 10</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Medidas de controle e sistemas preventivos
+        &lt;ul&gt;
+          &lt;li&gt;Geração, transmissão, distribuição e consumo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Intervenções em instalações
+        &lt;ul&gt;
+          &lt;li&gt;Análise de risco&lt;/li&gt;
+          &lt;li&gt;Esquemas unifilares atualizados&lt;/li&gt;
+          &lt;li&gt;Prontuário de Instalações Elétricas
+            &lt;ul&gt;
+              &lt;li&gt;Carga instalada superior a 75 kW&lt;/li&gt;
+              &lt;li&gt;Conteúdo mínimo
+                &lt;ul&gt;
+                  &lt;li&gt;procedimentos e instruções técnicas&lt;/li&gt;
+                  &lt;li&gt;inspeções e medições&lt;/li&gt;
+                  &lt;li&gt;especificação de EPI/EPC e ferramentas&lt;/li&gt;
+                  &lt;li&gt;comprovação de qualificação e autorização&lt;/li&gt;
+                  &lt;li&gt;testes de isolação elétrica&lt;/li&gt;
+                  &lt;li&gt;certificações em áreas classificadas&lt;/li&gt;
+                  &lt;li&gt;relatório técnico atualizado&lt;/li&gt;
+                &lt;/ul&gt;
+              &lt;/li&gt;
+              &lt;li&gt;Manutenção por profissional habilitado&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Medidas de Proteção
+        &lt;ul&gt;
+          &lt;li&gt;Coletiva (Prioritária)
+            &lt;ul&gt;
+              &lt;li&gt;Desenergização&lt;/li&gt;
+              &lt;li&gt;Tensão de segurança&lt;/li&gt;
+              &lt;li&gt;Medidas alternativas
+                &lt;ul&gt;
+                  &lt;li&gt;isolação, barreiras, sinalização e bloqueios&lt;/li&gt;
+                &lt;/ul&gt;
+              &lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Individual
+            &lt;ul&gt;
+              &lt;li&gt;EPIs específicos&lt;/li&gt;
+              &lt;li&gt;Proibição de adornos pessoais&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Segurança em Projetos
+        &lt;ul&gt;
+          &lt;li&gt;Dispositivos de desligamento&lt;/li&gt;
+          &lt;li&gt;Espaço seguro e influências externas&lt;/li&gt;
+          &lt;li&gt;Aterramento temporário e definitivo&lt;/li&gt;
+          &lt;li&gt;Memorial descritivo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Instalações Desenergizadas
+        &lt;ul&gt;
+          &lt;li&gt;Sequência para liberação
+            &lt;ol&gt;
+              &lt;li&gt;seccionamento&lt;/li&gt;
+              &lt;li&gt;impedimento de reenergização&lt;/li&gt;
+              &lt;li&gt;constatação da ausência de tensão&lt;/li&gt;
+              &lt;li&gt;aterramento temporário com equipotencialização&lt;/li&gt;
+              &lt;li&gt;proteção de elementos energizados&lt;/li&gt;
+              &lt;li&gt;sinalização de impedimento&lt;/li&gt;
+            &lt;/ol&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Sequência para reenergização
+            &lt;ol&gt;
+              &lt;li&gt;retirada de ferramentas e equipamentos&lt;/li&gt;
+              &lt;li&gt;retirada de trabalhadores não envolvidos&lt;/li&gt;
+              &lt;li&gt;remoção do aterramento e proteções&lt;/li&gt;
+              &lt;li&gt;remoção da sinalização&lt;/li&gt;
+              &lt;li&gt;destravamento e religação&lt;/li&gt;
+            &lt;/ol&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Trabalhadores
+        &lt;ul&gt;
+          &lt;li&gt;Classificação
+            &lt;ul&gt;
+              &lt;li&gt;Qualificado (curso oficial)&lt;/li&gt;
+              &lt;li&gt;Habilitado (registro em conselho)&lt;/li&gt;
+              &lt;li&gt;Capacitado (sob supervisão)&lt;/li&gt;
+              &lt;li&gt;Autorizado (anuência formal)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Treinamento
+            &lt;ul&gt;
+              &lt;li&gt;Básico (40h)&lt;/li&gt;
+              &lt;li&gt;Complementar SEP/Alta Tensão (40h)&lt;/li&gt;
+              &lt;li&gt;Reciclagem bienal&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Exame de saúde compatível&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Emergência e Sinalização
+        &lt;ul&gt;
+          &lt;li&gt;Plano de emergência e métodos de resgate&lt;/li&gt;
+          &lt;li&gt;Treinamento em primeiros socorros e combate a incêndio&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>314</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NR 11</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;resistência e segurança
+        &lt;ul&gt;
+          &lt;li&gt;indicação de carga máxima visível&lt;/li&gt;
+          &lt;li&gt;inspeção permanente
+            &lt;ul&gt;
+              &lt;li&gt;cabos, cordas, correntes e ganchos&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;operadores de equipamentos motorizados
+        &lt;ul&gt;
+          &lt;li&gt;treinamento específico&lt;/li&gt;
+          &lt;li&gt;cartão de identificação visível
+            &lt;ul&gt;
+              &lt;li&gt;validade: 1 ano&lt;/li&gt;
+              &lt;li&gt;revalidação mediante exame de saúde&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;segurança ambiental
+        &lt;ul&gt;
+          &lt;li&gt;sinal de advertência sonora (buzina)&lt;/li&gt;
+          &lt;li&gt;controle de gases tóxicos em locais fechados&lt;/li&gt;
+          &lt;li&gt;proibição de motores a combustão interna sem neutralizadores&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Transporte de sacas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;transporte manual
+        &lt;ul&gt;
+          &lt;li&gt;distância máxima: 60m&lt;/li&gt;
+          &lt;li&gt;auxílio de ajudante em veículos&lt;/li&gt;
+          &lt;li&gt;vedado
+            &lt;ul&gt;
+              &lt;li&gt;uso de pranchas sobre vãos &gt; 1,00m&lt;/li&gt;
+              &lt;li&gt;pisos escorregadios ou molhados&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;empilhamento
+        &lt;ul&gt;
+          &lt;li&gt;limitado à resistência do piso e estabilidade&lt;/li&gt;
+          &lt;li&gt;processo manual exige escada de madeira
+            &lt;ul&gt;
+              &lt;li&gt;largura mínima: 1,00m&lt;/li&gt;
+              &lt;li&gt;patamar final: 1,00m x 1,00m&lt;/li&gt;
+              &lt;li&gt;corrimão lateral a 1,00m de altura&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Armazenamento de materiais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;capacidade de carga do piso&lt;/li&gt;
+      &lt;li&gt;proibição de obstrução
+        &lt;ul&gt;
+          &lt;li&gt;portas e saídas de emergência&lt;/li&gt;
+          &lt;li&gt;equipamentos contra incêndio&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;afastamento de estruturas laterais
+        &lt;ul&gt;
+          &lt;li&gt;distância mínima: 0,50m&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Chapas de rochas ornamentais (Anexo I)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;inspeção e manutenção
+        &lt;ul&gt;
+          &lt;li&gt;registro em meio físico ou eletrônico&lt;/li&gt;
+          &lt;li&gt;relatório anual com ART&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;proteções e dispositivos
+        &lt;ul&gt;
+          &lt;li&gt;fueiros com sistema de trava&lt;/li&gt;
+          &lt;li&gt;ventosas
+            &lt;ul&gt;
+              &lt;li&gt;dispositivo contra ricocheteamento de mangueira&lt;/li&gt;
+              &lt;li&gt;alarme sonoro e visual para pressão&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;cavaletes
+            &lt;ul&gt;
+              &lt;li&gt;altura mínima: 1,50m&lt;/li&gt;
+              &lt;li&gt;afastamento das paredes: 0,50m&lt;/li&gt;
+              &lt;li&gt;sinalização de 0,80m entre laterais&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;operação segura
+        &lt;ul&gt;
+          &lt;li&gt;proibida permanência de pessoas entre chapas&lt;/li&gt;
+          &lt;li&gt;proibida retirada de um único lado do carro&lt;/li&gt;
+          &lt;li&gt;interrupção de circulação durante a movimentação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;capacitação
+        &lt;ol&gt;
+          &lt;li&gt;Módulo I: Saúde e Segurança (16h)&lt;/li&gt;
+          &lt;li&gt;Módulo II: Conteúdo do Anexo I (4h)&lt;/li&gt;
+          &lt;li&gt;Módulo III: Ponte Rolante (16h)&lt;/li&gt;
+        &lt;/ol&gt;
+        &lt;ul&gt;
+          &lt;li&gt;orientação em serviço: 30 dias&lt;/li&gt;
+          &lt;li&gt;reciclagem: trienal (16h)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>315</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>NR 12</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;resguardar a saúde e integridade física&lt;/li&gt;
+      &lt;li&gt;fases abrangidas: projeto, utilização, fabricação e comercialização&lt;/li&gt;
+      &lt;li&gt;ordem de prioridade das medidas
+        &lt;ol&gt;
+          &lt;li&gt;proteção coletiva&lt;/li&gt;
+          &lt;li&gt;administrativas ou organização do trabalho&lt;/li&gt;
+          &lt;li&gt;proteção individual&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;responsabilidades do trabalhador
+        &lt;ul&gt;
+          &lt;li&gt;cumprir procedimentos operacionais&lt;/li&gt;
+          &lt;li&gt;não alterar proteções&lt;/li&gt;
+          &lt;li&gt;comunicar danos em dispositivos de segurança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Arranjo Físico e Instalações&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;áreas de circulação demarcadas e desobstruídas&lt;/li&gt;
+      &lt;li&gt;distância mínima segura entre máquinas&lt;/li&gt;
+      &lt;li&gt;ferramentas organizadas em locais específicos&lt;/li&gt;
+      &lt;li&gt;estabilidade de máquinas estacionárias e móveis
+        &lt;ul&gt;
+          &lt;li&gt;rodízios com travas (no mínimo duas)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Instalações e Dispositivos Elétricos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;prevenção de choques, incêndio e explosão&lt;/li&gt;
+      &lt;li&gt;aterramento obrigatório de carcaças e invólucros&lt;/li&gt;
+      &lt;li&gt;condutores com resistência mecânica e proteção contra calor/lubrificantes&lt;/li&gt;
+      &lt;li&gt;quadros de comando
+        &lt;ul&gt;
+          &lt;li&gt;porta mantida fechada&lt;/li&gt;
+          &lt;li&gt;sinalização de perigo&lt;/li&gt;
+          &lt;li&gt;identificação de circuitos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Proibições
+        &lt;ul&gt;
+          &lt;li&gt;chave geral como dispositivo de partida/parada&lt;/li&gt;
+          &lt;li&gt;chaves tipo faca&lt;/li&gt;
+          &lt;li&gt;partes energizadas expostas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sistemas de Segurança&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;proteção de zonas de perigo
+        &lt;ul&gt;
+          &lt;li&gt;Proteção Fixa (removível apenas com ferramentas)&lt;/li&gt;
+          &lt;li&gt;Proteção Móvel (intertravada com a estrutura)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Requisitos
+        &lt;ul&gt;
+          &lt;li&gt;categoria de segurança conforme análise de risco&lt;/li&gt;
+          &lt;li&gt;dificultar burla&lt;/li&gt;
+          &lt;li&gt;paralisação de movimentos em caso de falha&lt;/li&gt;
+          &lt;li&gt;monitoramento automático&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Dispositivos de Acionamento Bimanual
+        &lt;ul&gt;
+          &lt;li&gt;atuação síncrona (retardo máximo de 0,5 s)&lt;/li&gt;
+          &lt;li&gt;sinal de saída cessa ao desacionar qualquer controle&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Parada de Emergência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;acesso fácil e visualização clara&lt;/li&gt;
+      &lt;li&gt;prevalece sobre todos os comandos&lt;/li&gt;
+      &lt;li&gt;retenção do acionador até desacionamento manual&lt;/li&gt;
+      &lt;li&gt;exige rearme (reset) manual após correção do evento&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Manutenção e Intervenções&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;registro em livro ou sistema informatizado&lt;/li&gt;
+      &lt;li&gt;Procedimentos LOTO (Lockout/Tagout)
+        &lt;ul&gt;
+          &lt;li&gt;isolamento e descarga de energia&lt;/li&gt;
+          &lt;li&gt;bloqueio mecânico e elétrico na posição "desligado"&lt;/li&gt;
+          &lt;li&gt;sinalização com cartão ou etiqueta&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;realizada antes do início da função e sem ônus&lt;/li&gt;
+      &lt;li&gt;conteúdo programático teórico e prático&lt;/li&gt;
+      &lt;li&gt;reciclagem obrigatória em modificações significativas&lt;/li&gt;
+      &lt;li&gt;operadores de máquinas autopropelidas devem portar identificação com foto&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sinalização e Manuais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;inscrições em língua portuguesa e legíveis&lt;/li&gt;
+      &lt;li&gt;informações indeléveis (razão social, CNPJ, modelo, peso)&lt;/li&gt;
+      &lt;li&gt;manual deve permanecer disponível no local de trabalho&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>316</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>NR 13</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Gestão da integridade estrutural
+    &lt;ul&gt;
+      &lt;li&gt;objetiva garantir a segurança e saúde&lt;/li&gt;
+      &lt;li&gt;responsabilidade do empregador&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Equipamentos abrangidos
+    &lt;ul&gt;
+      &lt;li&gt;caldeiras (&gt; 60 kPa)&lt;/li&gt;
+      &lt;li&gt;vasos de pressão
+        &lt;ul&gt;
+          &lt;li&gt;produto P.V &gt; 8 ou&lt;/li&gt;
+          &lt;li&gt;fluidos classe A&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;tubulações (fluidos classe A ou B)&lt;/li&gt;
+      &lt;li&gt;tanques metálicos (&gt; 20.000 L e Ø &gt; 3m)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Condições de risco grave e iminente
+    &lt;ul&gt;
+      &lt;li&gt;operação sem dispositivos de segurança&lt;/li&gt;
+      &lt;li&gt;atraso na inspeção de caldeiras&lt;/li&gt;
+      &lt;li&gt;falta de controle do nível de água&lt;/li&gt;
+      &lt;li&gt;inaptidão atestada em relatório&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Profissional Legalmente Habilitado (PLH)
+    &lt;ul&gt;
+      &lt;li&gt;engenheiro com competência legal&lt;/li&gt;
+      &lt;li&gt;responsável técnico por inspeções e projetos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Caldeiras
+    &lt;ul&gt;
+      &lt;li&gt;Categorias
+        &lt;ul&gt;
+          &lt;li&gt;A (pressão ≥ 1.960 kPa)&lt;/li&gt;
+          &lt;li&gt;B (60 kPa &lt; pressão &lt; 1.960 kPa)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Itens obrigatórios
+        &lt;ul&gt;
+          &lt;li&gt;válvula de segurança&lt;/li&gt;
+          &lt;li&gt;instrumento de pressão&lt;/li&gt;
+          &lt;li&gt;sistema de alimentação independente&lt;/li&gt;
+          &lt;li&gt;controle automático de nível&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Inspeção periódica
+        &lt;ul&gt;
+          &lt;li&gt;Prazos padrão
+            &lt;ul&gt;
+              &lt;li&gt;12 meses (Cat A e B)&lt;/li&gt;
+              &lt;li&gt;24 meses (Cat A com teste de válvulas)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;Prazos com SPIE
+            &lt;ul&gt;
+              &lt;li&gt;até 30 meses (Cat A)&lt;/li&gt;
+              &lt;li&gt;até 48 meses (Cat A com SIS)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Vasos de Pressão
+    &lt;ul&gt;
+      &lt;li&gt;Categorização
+        &lt;ul&gt;
+          &lt;li&gt;Classe de fluido (A, B, C, D)&lt;/li&gt;
+          &lt;li&gt;Potencial de risco (Grupo 1 a 5)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Inspeção periódica
+        &lt;ul&gt;
+          &lt;li&gt;conforme tabela de prazos (1 a 10 anos)&lt;/li&gt;
+          &lt;li&gt;ampliável com inspeção baseada em risco&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Documentação obrigatória
+    &lt;ul&gt;
+      &lt;li&gt;prontuário atualizado&lt;/li&gt;
+      &lt;li&gt;registro de segurança (livro ou sistema)&lt;/li&gt;
+      &lt;li&gt;projeto de instalação e alteração&lt;/li&gt;
+      &lt;li&gt;relatórios de inspeção&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;Capacitação
+    &lt;ul&gt;
+      &lt;li&gt;Operador de caldeira
+        &lt;ul&gt;
+          &lt;li&gt;pré-requisito: ensino médio&lt;/li&gt;
+          &lt;li&gt;curso (40h) e estágio supervisionado
+            &lt;ul&gt;
+              &lt;li&gt;Cat A (80h)&lt;/li&gt;
+              &lt;li&gt;Cat B (60h)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Unidades de processo
+        &lt;ul&gt;
+          &lt;li&gt;treinamento de segurança (40h)&lt;/li&gt;
+          &lt;li&gt;estágio (300h)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>317</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>NR 14</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;operação com segurança
+    &lt;ul&gt;
+      &lt;li&gt;construção sólida
+        &lt;ul&gt;
+          &lt;li&gt;revestimento refratário&lt;/li&gt;
+          &lt;li&gt;calor radiante dentro dos limites&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;instalação
+        &lt;ul&gt;
+          &lt;li&gt;normas técnicas oficiais&lt;/li&gt;
+          &lt;li&gt;segurança e conforto&lt;/li&gt;
+          &lt;li&gt;evitar
+            &lt;ul&gt;
+              &lt;li&gt;acúmulo de gases nocivos e&lt;/li&gt;
+              &lt;li&gt;altas temperaturas&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;escadas e plataformas
+            &lt;ul&gt;
+              &lt;li&gt;acesso e execução segura&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;combustíveis gasosos ou líquidos
+        &lt;ul&gt;
+          &lt;li&gt;sistemas de proteção contra
+            &lt;ul&gt;
+              &lt;li&gt;explosão&lt;/li&gt;
+              &lt;li&gt;retrocesso da chama&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;chaminé
+        &lt;ul&gt;
+          &lt;li&gt;saída dos gases de combustão&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>NR 15</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Classificação: Risco físico (cor verde)&lt;/li&gt;
+      &lt;li&gt;Limites de Tolerância:
+        &lt;ul&gt;
+          &lt;li&gt;85 dB(A) &amp;rarr; 8 horas&lt;/li&gt;
+          &lt;li&gt;90 dB(A) &amp;rarr; 4 horas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Cálculo de Dose:
+        &lt;ul&gt;
+          &lt;li&gt;Fórmula: (Exposição 1 / Limite 1) + (Exposição 2 / Limite 2)&lt;/li&gt;
+          &lt;li&gt;Se resultado &amp;gt; 1 &amp;rarr; Condição Insalubre&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Insalubridade vs. Periculosidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ruído gera &lt;strong&gt;Insalubridade&lt;/strong&gt; (danos graduais), nunca periculosidade (risco imediato).&lt;/li&gt;
+      &lt;li&gt;Adicional de Insalubridade por Ruído: 20% (Grau Médio).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Eliminação do Risco&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O EPI (abafador) tenta neutralizar o risco, mas a cessação do adicional depende de &lt;strong&gt;avaliação pericial&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>319</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>NR 16</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;valor: 30%&lt;/li&gt;
+      &lt;li&gt;incidência: salário base
+        &lt;ul&gt;
+          &lt;li&gt;sem acréscimos de prêmios ou gratificações&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;direito de opção pelo adicional de insalubridade&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Caracterização Jurídica&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;responsabilidade do empregador&lt;/li&gt;
+      &lt;li&gt;laudo técnico obrigatório
+        &lt;ul&gt;
+          &lt;li&gt;Médico do Trabalho ou Engenheiro de Segurança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;delimitação física das áreas de risco&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Explosivos (Anexo I)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;atividades abrangidas
+        &lt;ul&gt;
+          &lt;li&gt;armazenamento e transporte&lt;/li&gt;
+          &lt;li&gt;escorva e carregamento&lt;/li&gt;
+          &lt;li&gt;detonação e verificação de falhas&lt;/li&gt;
+          &lt;li&gt;queima de materiais deteriorados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;área de risco definida por tabelas de distância&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Inflamáveis (Anexo II)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;limites de exclusão para transporte
+        &lt;ul&gt;
+          &lt;li&gt;líquidos: até 200 litros&lt;/li&gt;
+          &lt;li&gt;gases liquefeitos: até 135 quilos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;tanques de consumo próprio não computados
+        &lt;ul&gt;
+          &lt;li&gt;originais de fábrica e suplementares certificados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;líquido combustível: ponto de fulgor &amp;gt; 60°C e &amp;le; 93°C&lt;/li&gt;
+      &lt;li&gt;operações em postos de serviço (abastecimento)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança Pessoal ou Patrimonial (Anexo III)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;exposição a roubos ou violência física&lt;/li&gt;
+      &lt;li&gt;atividades profissionais
+        &lt;ul&gt;
+          &lt;li&gt;vigilância patrimonial e de eventos&lt;/li&gt;
+          &lt;li&gt;transporte de valores e escolta armada&lt;/li&gt;
+          &lt;li&gt;telemonitoramento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Energia Elétrica (Anexo IV)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Alta Tensão (AT)&lt;/li&gt;
+      &lt;li&gt;Sistema Elétrico de Potência (SEP)&lt;/li&gt;
+      &lt;li&gt;Baixa Tensão
+        &lt;ul&gt;
+          &lt;li&gt;em caso de descumprimento das medidas de proteção da NR 10&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;exclusão: trabalho em extra-baixa tensão ou desenergizado&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Motocicleta (Anexo V)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;deslocamento em vias públicas&lt;/li&gt;
+      &lt;li&gt;exclusões
+        &lt;ul&gt;
+          &lt;li&gt;trajeto residência-trabalho&lt;/li&gt;
+          &lt;li&gt;vias privadas ou estradas lindeiras&lt;/li&gt;
+          &lt;li&gt;uso eventual ou por tempo reduzido&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Agentes de Trânsito (Anexo VI)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;risco de colisões e atropelamentos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Radiações Ionizantes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;atividades em minas, reatores e laboratórios&lt;/li&gt;
+      &lt;li&gt;exclusão: áreas com Raio X móvel para diagnóstico médico&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>320</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>NR 17</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conforto, segurança e saúde&lt;/li&gt;
+      &lt;li&gt;desempenho eficiente&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Avaliação das situações de trabalho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Avaliação ergonômica preliminar (obrigatória)
+        &lt;ul&gt;
+          &lt;li&gt;identificar perigos e planejar prevenção&lt;/li&gt;
+          &lt;li&gt;registrada e integrada ao PGR&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Análise Ergonômica do Trabalho - AET (específica)
+        &lt;ul&gt;
+          &lt;li&gt;situações complexas ou falha de medidas&lt;/li&gt;
+          &lt;li&gt;sugerida pelo PCMSO ou acidentes&lt;/li&gt;
+          &lt;li&gt;relatório mantido por 20 anos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Isenção de AET (salvo exceções)
+        &lt;ul&gt;
+          &lt;li&gt;MEI, ME e EPP (graus de risco 1 e 2)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Organização do trabalho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;considerar: normas, ritmo e aspectos cognitivos&lt;/li&gt;
+      &lt;li&gt;evitar sobrecarga muscular e posturas nocivas&lt;/li&gt;
+      &lt;li&gt;medidas de prevenção
+        &lt;ul&gt;
+          &lt;li&gt;pausas (tempo de trabalho efetivo)&lt;/li&gt;
+          &lt;li&gt;alternância de atividades&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;saída garantida para necessidades fisiológicas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Manuseio de cargas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;peso não pode comprometer a saúde&lt;/li&gt;
+      &lt;li&gt;redução para mulheres e menores&lt;/li&gt;
+      &lt;li&gt;alcance horizontal máximo: 60 cm&lt;/li&gt;
+      &lt;li&gt;medidas técnicas facilitadoras&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Mobiliário e Equipamentos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;regulagens adaptáveis à antropometria&lt;/li&gt;
+      &lt;li&gt;alternância entre pé e sentado&lt;/li&gt;
+      &lt;li&gt;assentos: altura ajustável, encosto lombar e borda arredondada&lt;/li&gt;
+      &lt;li&gt;terminais de vídeo: ajuste de tela e proteção contra reflexos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Conforto Ambiental&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Iluminação (NHO 11)
+        &lt;ul&gt;
+          &lt;li&gt;evitar ofuscamento e sombras&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Ambientes de solicitação intelectual
+        &lt;ul&gt;
+          &lt;li&gt;Ruído: até 65 dB(A)&lt;/li&gt;
+          &lt;li&gt;Temperatura: entre 18 e 25 &amp;deg;C (climatizados)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Teleatendimento (Anexo II)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;jornada máxima: 6h diárias (36h semanais)&lt;/li&gt;
+      &lt;li&gt;pausas obrigatórias
+        &lt;ul&gt;
+          &lt;li&gt;2 períodos de 10 min&lt;/li&gt;
+          &lt;li&gt;intervalo de refeição: 20 min&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;headsets individuais e higienizados&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>321</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NR 18</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;implementação de medidas de controle e sistemas preventivos&lt;/li&gt;
+      &lt;li&gt;abrange demolição, reparo, pintura, limpeza e manutenção&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;PGR (Programa de Gerenciamento de Riscos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;obrigatória elaboração por PLH
+        &lt;ul&gt;
+          &lt;li&gt;exceção para obras até 7m e com 10 trabalhadores&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;deve conter projetos
+        &lt;ul&gt;
+          &lt;li&gt;áreas de vivência&lt;/li&gt;
+          &lt;li&gt;instalações elétricas temporárias&lt;/li&gt;
+          &lt;li&gt;sistemas de proteção coletiva e SPIQ&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;atualizado conforme a etapa da obra&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Áreas de vivência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;condições de segurança, conforto e privacidade&lt;/li&gt;
+      &lt;li&gt;instalações sanitárias
+        &lt;ul&gt;
+          &lt;li&gt;1 conjunto (lavatório, bacia e mictório) para cada 20&lt;/li&gt;
+          &lt;li&gt;1 chuveiro para cada 10&lt;/li&gt;
+          &lt;li&gt;deslocamento máximo: 150m&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;água potável e filtrada
+        &lt;ul&gt;
+          &lt;li&gt;1 bebedouro para cada 25&lt;/li&gt;
+          &lt;li&gt;distância máxima horizontal: 100m&lt;/li&gt;
+          &lt;li&gt;distância máxima vertical: 15m&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Escavação e fundação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;escavação com profundidade superior a 1,25m
+        &lt;ul&gt;
+          &lt;li&gt;exige projeto e liberação de PLH&lt;/li&gt;
+          &lt;li&gt;protegida com taludes ou escoramentos&lt;/li&gt;
+          &lt;li&gt;faixa de proteção de 1m livre de cargas na borda&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;tubulão escavado manualmente
+        &lt;ul&gt;
+          &lt;li&gt;profundidade máxima: 15m&lt;/li&gt;
+          &lt;li&gt;diâmetro mínimo: 0,9m&lt;/li&gt;
+          &lt;li&gt;obrigatoriamente encamisado em toda extensão&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Proteção contra quedas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;obrigatória instalação onde houver risco&lt;/li&gt;
+      &lt;li&gt;proteção de periferia
+        &lt;ul&gt;
+          &lt;li&gt;anteparos rígidos com 1,2m de altura ou&lt;/li&gt;
+          &lt;li&gt;sistema de guarda-corpo e rodapé
+            &lt;ul&gt;
+              &lt;li&gt;travessão superior: 1,2m&lt;/li&gt;
+              &lt;li&gt;travessão intermediário: 0,7m&lt;/li&gt;
+              &lt;li&gt;rodapé: 0,15m&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Máquinas e Equipamentos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conformidade com NR 12&lt;/li&gt;
+      &lt;li&gt;serra circular projetada por PLH
+        &lt;ul&gt;
+          &lt;li&gt;estrutura metálica estável e coifa de proteção&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;máquinas autopropelidas acima de 4.500 kg
+        &lt;ul&gt;
+          &lt;li&gt;cabine climatizada&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Equipamentos de guindar&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;utilização conforme plano de carga&lt;/li&gt;
+      &lt;li&gt;dispositivos obrigatórios
+        &lt;ul&gt;
+          &lt;li&gt;limitador de carga e altura&lt;/li&gt;
+          &lt;li&gt;alarme sonoro&lt;/li&gt;
+          &lt;li&gt;anemômetro para indicar velocidade do vento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Andaimes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;projeto por PLH e fabricação por empresa habilitada&lt;/li&gt;
+      &lt;li&gt;montagem e desmontagem com uso de SPIQ&lt;/li&gt;
+      &lt;li&gt;torres de andaimes
+        &lt;ul&gt;
+          &lt;li&gt;altura máxima: 4 vezes a menor dimensão da base&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>322</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>NR 19</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;definição: substância que sofre decomposição rápida com calor e pressão&lt;/li&gt;
+      &lt;li&gt;conformidade obrigatória com o Exército Brasileiro (DFPC)&lt;/li&gt;
+      &lt;li&gt;proibida a fabricação em perímetro urbano&lt;/li&gt;
+      &lt;li&gt;PGR deve prever riscos específicos de incêndio e explosão&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fabricação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;exige Certificado de Conformidade do Exército&lt;/li&gt;
+      &lt;li&gt;monitoramento eletrônico permanente em áreas perigosas&lt;/li&gt;
+      &lt;li&gt;restrições de pessoal
+        &lt;ul&gt;
+          &lt;li&gt;máximo de 4 trabalhadores em locais de encartuchamento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;infraestrutura física
+        &lt;ul&gt;
+          &lt;li&gt;paredes e tetos incombustíveis&lt;/li&gt;
+          &lt;li&gt;pisos antiestáticos e aterramento de equipamentos&lt;/li&gt;
+          &lt;li&gt;ventilação adequada&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;proibições no manuseio
+        &lt;ul&gt;
+          &lt;li&gt;ferramentas que gerem centelha ou calor por atrito&lt;/li&gt;
+          &lt;li&gt;calçados com pregos ou peças metálicas externas&lt;/li&gt;
+          &lt;li&gt;fumo ou prática de fogo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;matérias-primas no local
+        &lt;ul&gt;
+          &lt;li&gt;quantidade máxima para 4 horas de trabalho&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Armazenamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;depósitos e paióis
+        &lt;ul&gt;
+          &lt;li&gt;paredes duplas com intervalo de 0,50 m (paióis permanentes)&lt;/li&gt;
+          &lt;li&gt;materiais incombustíveis e maus condutores de calor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;gestão do espaço
+        &lt;ul&gt;
+          &lt;li&gt;ocupação máxima de 60% da área&lt;/li&gt;
+          &lt;li&gt;distância mínima de 0,70 m entre o teto e o empilhamento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;segregação e compatibilidade
+        &lt;ul&gt;
+          &lt;li&gt;proibido armazenar explosivos com iniciadores ou pólvoras&lt;/li&gt;
+          &lt;li&gt;seguir grupos de incompatibilidade (Anexo III)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distâncias mínimas
+        &lt;ul&gt;
+          &lt;li&gt;respeitar Tabela de Quantidades-Distâncias (Anexo II)&lt;/li&gt;
+          &lt;li&gt;distâncias podem ser reduzidas à metade em depósitos barricados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Transporte&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conformidade com agências reguladoras (ANTT, ANTAQ, ANAC)&lt;/li&gt;
+      &lt;li&gt;requisitos do veículo
+        &lt;ul&gt;
+          &lt;li&gt;carroceria fechada (tipo baú) ou contêiner&lt;/li&gt;
+          &lt;li&gt;sistema de rastreamento em tempo real (GPS)&lt;/li&gt;
+          &lt;li&gt;botão de pânico e bloqueio remoto de portas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;segurança na operação
+        &lt;ul&gt;
+          &lt;li&gt;sinalização de "Explosivo" visível&lt;/li&gt;
+          &lt;li&gt;supervisão por trabalhador capacitado&lt;/li&gt;
+          &lt;li&gt;proteção contra umidade e raios solares&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fogos de Artifício (Anexo I)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;vestimentas de algodão ou material antiestático&lt;/li&gt;
+      &lt;li&gt;manipulação de pólvora branca exige lâmina d'água de 0,10 m&lt;/li&gt;
+      &lt;li&gt;proibida a remuneração por produtividade&lt;/li&gt;
+      &lt;li&gt;proibida a mão de obra de menores de 18 anos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G315"/>
+  <dimension ref="A1:G319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14516,6 +14516,478 @@
         <v>0</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>323</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>NR 20</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;extração, produção, armazenamento e transferência&lt;/li&gt;
+      &lt;li&gt;manuseio e manipulação&lt;/li&gt;
+      &lt;li&gt;abrange etapas desde o projeto até a desativação&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Definições técnicas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;líquidos inflamáveis: ponto de fulgor &amp;le; 60&amp;deg;C&lt;/li&gt;
+      &lt;li&gt;líquidos combustíveis: ponto de fulgor &amp;gt; 60&amp;deg;C e &amp;le; 93&amp;deg;C&lt;/li&gt;
+      &lt;li&gt;gases inflamáveis: inflamam a 20&amp;deg;C e 101,3 kPa&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Classificação das instalações&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Classe I
+        &lt;ul&gt;
+          &lt;li&gt;postos de serviço&lt;/li&gt;
+          &lt;li&gt;gases: &amp;gt; 2t até 60t&lt;/li&gt;
+          &lt;li&gt;líquidos: &amp;gt; 10 m&amp;sup3; até 5.000 m&amp;sup3;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Classe II
+        &lt;ul&gt;
+          &lt;li&gt;engarrafadoras e transporte dutoviário&lt;/li&gt;
+          &lt;li&gt;gases: &amp;gt; 60t até 600t&lt;/li&gt;
+          &lt;li&gt;líquidos: &amp;gt; 5.000 m&amp;sup3; até 50.000 m&amp;sup3;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Classe III
+        &lt;ul&gt;
+          &lt;li&gt;refinarias, petroquímicas e usinas de etanol&lt;/li&gt;
+          &lt;li&gt;gases: &amp;gt; 600t&lt;/li&gt;
+          &lt;li&gt;líquidos: &amp;gt; 50.000 m&amp;sup3;&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Documentação e Projetos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Prontuário da Instalação
+        &lt;ul&gt;
+          &lt;li&gt;projeto e plano de inspeção/manutenção&lt;/li&gt;
+          &lt;li&gt;análise de riscos e plano de emergência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Análise de Riscos
+        &lt;ul&gt;
+          &lt;li&gt;Classe I: APP/APR (Análise Preliminar)&lt;/li&gt;
+          &lt;li&gt;Classe II e III: metodologias definidas por profissional habilitado&lt;/li&gt;
+          &lt;li&gt;revisão periódica ou em caso de modificações&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança Operacional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;procedimentos escritos para todas as fases
+        &lt;ul&gt;
+          &lt;li&gt;pré-operação, operação normal e emergência&lt;/li&gt;
+          &lt;li&gt;parada e pós-emergência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;controle de fontes de ignição
+        &lt;ul&gt;
+          &lt;li&gt;aterramento e controle de eletricidade estática&lt;/li&gt;
+          &lt;li&gt;permissão de trabalho para atividades a quente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação (Cursos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Iniciação: trabalhadores que apenas adentram a área&lt;/li&gt;
+      &lt;li&gt;Básico, Intermediário, Avançado I e II
+        &lt;ul&gt;
+          &lt;li&gt;definidos pela classe da instalação e função&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Atualização periódica
+        &lt;ul&gt;
+          &lt;li&gt;bienal ou trienal conforme a carga horária&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Emergência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Resposta a Emergências (PRE)&lt;/li&gt;
+      &lt;li&gt;exercícios simulados anuais obrigatórios&lt;/li&gt;
+      &lt;li&gt;comunicação de ocorrências em até 2 dias úteis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>324</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>NR 21</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;abrigos contra intempéries&lt;/li&gt;
+      &lt;li&gt;medidas contra
+        &lt;ul&gt;
+          &lt;li&gt;insolação excessiva e calor&lt;/li&gt;
+          &lt;li&gt;frio e umidade&lt;/li&gt;
+          &lt;li&gt;ventos inconvenientes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;profilaxia de endemias
+        &lt;ul&gt;
+          &lt;li&gt;em regiões pantanosas ou alagadiças&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Alojamento e moradia&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;condições sanitárias adequadas&lt;/li&gt;
+      &lt;li&gt;moradia familiar
+        &lt;ul&gt;
+          &lt;li&gt;vedada a modalidade coletiva&lt;/li&gt;
+          &lt;li&gt;capacidade dimensionada&lt;/li&gt;
+          &lt;li&gt;ventilação e luz direta&lt;/li&gt;
+          &lt;li&gt;estrutural
+            &lt;ul&gt;
+              &lt;li&gt;paredes caiadas&lt;/li&gt;
+              &lt;li&gt;pisos impermeáveis&lt;/li&gt;
+              &lt;li&gt;cobertura impermeável e não combustível&lt;/li&gt;
+              &lt;li&gt;portas e janelas com dispositivos de fechamento&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;compartimentos mínimos
+            &lt;ul&gt;
+              &lt;li&gt;dormitório&lt;/li&gt;
+              &lt;li&gt;cozinha&lt;/li&gt;
+              &lt;li&gt;compartimento sanitário&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;localização
+        &lt;ul&gt;
+          &lt;li&gt;local arejado e livre de vegetação&lt;/li&gt;
+          &lt;li&gt;afastamento mínimo de 50m de
+            &lt;ul&gt;
+              &lt;li&gt;depósitos de feno ou estercos&lt;/li&gt;
+              &lt;li&gt;currais, estábulos e pocilgas&lt;/li&gt;
+              &lt;li&gt;viveiros de criação&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Saneamento e Higiene&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;poço de água protegido&lt;/li&gt;
+      &lt;li&gt;fossas negras
+        &lt;ul&gt;
+          &lt;li&gt;distância do poço: 15m&lt;/li&gt;
+          &lt;li&gt;distância da casa: 10m&lt;/li&gt;
+          &lt;li&gt;posicionada à jusante do poço&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;instalações sanitárias
+        &lt;ul&gt;
+          &lt;li&gt;ventilação abundante&lt;/li&gt;
+          &lt;li&gt;proteção contra pragas e animais&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>325</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>NR 22</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;planejamento e desenvolvimento compatíveis com segurança&lt;/li&gt;
+      &lt;li&gt;supervisão técnica por profissional legalmente habilitado (PLH)
+        &lt;ul&gt;
+          &lt;li&gt;registro obrigatório de intervenções e ocorrências&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;interrupção de atividades em risco grave e iminente&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gerenciamento de Riscos (GRO/PGR)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;identificação de perigos específicos
+        &lt;ul&gt;
+          &lt;li&gt;atmosferas explosivas e deficiência de oxigênio&lt;/li&gt;
+          &lt;li&gt;estabilidade de maciços e ventilação mecânica&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;ações integradas entre contratante e contratada&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Organização e Equipes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;equipes mínimas de dois trabalhadores para atividades críticas
+        &lt;ul&gt;
+          &lt;li&gt;abatimento de choco e contenção de maciço&lt;/li&gt;
+          &lt;li&gt;perfuração e manuseio de explosivos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;exceção: atividades mecanizadas com análise de risco&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Circulação e Transporte&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Trânsito obrigatório&lt;/li&gt;
+      &lt;li&gt;transporte de trabalhadores
+        &lt;ul&gt;
+          &lt;li&gt;obrigatório para trajetos superiores a 1.000 m&lt;/li&gt;
+          &lt;li&gt;veículos projetados ou adaptados com segurança&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;vias de trânsito a céu aberto
+        &lt;ul&gt;
+          &lt;li&gt;largura: 2x a do maior veículo (pista simples) ou 3x (pista dupla)&lt;/li&gt;
+          &lt;li&gt;construção de leiras (altura = 1/2 do pneu)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;transporte vertical
+        &lt;ul&gt;
+          &lt;li&gt;dispositivos de intertravamento e frenagem de segurança&lt;/li&gt;
+          &lt;li&gt;comunicação permanente com o operador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Equipamentos e Máquinas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;transportadores contínuos
+        &lt;ul&gt;
+          &lt;li&gt;parada de emergência e sensores de segurança&lt;/li&gt;
+          &lt;li&gt;sinal sonoro 20 segundos antes da partida&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;máquinas autopropelidas
+        &lt;ul&gt;
+          &lt;li&gt;cabine climatizada para massa superior a 4.500 kg&lt;/li&gt;
+          &lt;li&gt;proteção contra queda de objetos e raios solares&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Mineração Subterrânea (Subsolo)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ventilação Mecânica
+        &lt;ul&gt;
+          &lt;li&gt;suprir oxigênio (mínimo 19% em volume)&lt;/li&gt;
+          &lt;li&gt;diluir gases inflamáveis e poeiras&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;monitoramento de Metano
+        &lt;ul&gt;
+          &lt;li&gt;suspensão de atividades: &gt; 1%&lt;/li&gt;
+          &lt;li&gt;proibição de desmonte: &gt; 0,8%&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;câmaras de refúgio
+        &lt;ul&gt;
+          &lt;li&gt;distância máxima das frentes: 750 m&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estabilidade e Maciços&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;monitoramento geomecânico e hidrogeológico&lt;/li&gt;
+      &lt;li&gt;abatimento imediato de chocos&lt;/li&gt;
+      &lt;li&gt;isolamento de áreas com blocos instáveis&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Explosivos e Desmonte&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Fogo elaborado por PLH&lt;/li&gt;
+      &lt;li&gt;atividades supervisionadas por Blaster&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança em Barragens e Depósitos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Ação de Emergência (PAEBM)&lt;/li&gt;
+      &lt;li&gt;restrição na Zona de Autossalvamento&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Condições Sanitárias&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações sanitárias nas frentes de trabalho
+        &lt;ul&gt;
+          &lt;li&gt;distância máxima: 250 m&lt;/li&gt;
+          &lt;li&gt;proporção: 1 bacia/lavatório para cada 20 trabalhadores&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>326</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NR 23</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Quinta-feira, 16 de abril de 2026, 17:52:43 (Fuso horário local).
+---
+### Resumo com lista em cascata
+· **Medidas de prevenção contra incêndios**
+    o estabelecidas para ambientes de trabalho
+    o conformidade com
+        § legislação estadual
+        § normas técnicas oficiais (complementar)
+· **Informações aos trabalhadores**
+    o utilização de equipamentos de combate
+    o procedimentos de resposta e evacuação
+    o funcionamento de dispositivos de alarme
+· **Saídas e vias de passagem**
+    o número suficiente para abandono rápido
+    o requisitos de segurança
+        § sinalização indicando a direção da saída
+        § manutenção permanente de desobstrução
+        § proibição de trancamento durante a jornada
+        § permissão de dispositivos de fácil abertura interna
+---
+### Estrutura em HTML
+```html
+&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;estabelecidas para ambientes de trabalho&lt;/li&gt;
+      &lt;li&gt;conformidade com
+        &lt;ul&gt;
+          &lt;li&gt;legislação estadual&lt;/li&gt;
+          &lt;li&gt;normas técnicas oficiais (complementar)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Informações aos trabalhadores&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;utilização de equipamentos de combate&lt;/li&gt;
+      &lt;li&gt;procedimentos de resposta e evacuação&lt;/li&gt;
+      &lt;li&gt;funcionamento de dispositivos de alarme&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Saídas e vias de passagem&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;número suficiente para abandono rápido&lt;/li&gt;
+      &lt;li&gt;requisitos de segurança
+        &lt;ul&gt;
+          &lt;li&gt;sinalização indicando a direção da saída&lt;/li&gt;
+          &lt;li&gt;manutenção permanente de desobstrução&lt;/li&gt;
+          &lt;li&gt;proibição de trancamento durante a jornada&lt;/li&gt;
+          &lt;li&gt;permissão de dispositivos de fácil abertura interna&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;
+```</t>
+        </is>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G319"/>
+  <dimension ref="A1:G331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8270,7 +8270,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -8284,41 +8284,10 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NR 2</t>
+          <t>NR 3</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
-        <is>
-          <t>Inspeção Prévia</t>
-        </is>
-      </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>219</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>NR 3</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -8328,6 +8297,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>220</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F212" t="n">
         <v>0</v>
       </c>
@@ -8337,7 +8340,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -8351,27 +8354,24 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F213" t="n">
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -8385,41 +8385,10 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>222</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -8432,33 +8401,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F215" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" t="n">
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="n">
+    <row r="215">
+      <c r="A215" t="n">
         <v>223</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -8466,35 +8435,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -8503,33 +8472,33 @@
 </t>
         </is>
       </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="n">
+    <row r="217">
+      <c r="A217" t="n">
         <v>225</v>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -8541,33 +8510,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="218">
+      <c r="A218" t="n">
         <v>226</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -8578,33 +8547,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="219">
+      <c r="A219" t="n">
         <v>227</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -8614,33 +8583,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="n">
+    <row r="220">
+      <c r="A220" t="n">
         <v>228</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -8649,33 +8618,33 @@
 </t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" t="n">
+    <row r="221">
+      <c r="A221" t="n">
         <v>229</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8685,33 +8654,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="n">
+    <row r="222">
+      <c r="A222" t="n">
         <v>230</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -8720,33 +8689,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="n">
+    <row r="223">
+      <c r="A223" t="n">
         <v>231</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8757,16 +8726,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>232</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F224" t="n">
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -8775,49 +8778,15 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Diferença entre modelos tradicionais e modelos modernos de inovação</t>
+          <t>Índices Financeiros</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Modelos Lineares (Antigos): &lt;ul&gt; &lt;li&gt;Fundamentados em uma sequência lógica e rígida de etapas sucessivas.&lt;/li&gt; &lt;li&gt;Focam no fluxo unidirecional (ex: P&amp;D -&gt; Vendas).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Modelos Não Lineares (Recentes): &lt;ul&gt; &lt;li&gt;Processo interativo e dinâmico com sobreposição de fases.&lt;/li&gt; &lt;li&gt;Envolvem ciclos de feedback e colaboração entre múltiplos atores (internos e externos).&lt;/li&gt; &lt;li&gt;Referência: Manual de Oslo (OCDE).&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
-        <v>233</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Índices Financeiros</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8828,33 +8797,33 @@
 </t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" t="n">
+    <row r="226">
+      <c r="A226" t="n">
         <v>234</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -8864,35 +8833,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pré-Desenvolvimento &lt;ol&gt; &lt;li&gt;Planejamento do Projeto &lt;ul&gt; &lt;li&gt;são realizadas &lt;ul&gt; &lt;li&gt;brainstorming&lt;/li&gt; &lt;li&gt;visitas a feiras técnicas&lt;/li&gt; &lt;li&gt;análise de produtos da concorrência&lt;/li&gt; &lt;li&gt;pesquisa de mercado&lt;/li&gt; &lt;li&gt;elaboração das especificações do projeto&lt;/li&gt; &lt;li&gt;dentre outros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
@@ -8901,35 +8870,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Único Banco de Dados Centralizado&lt;/li&gt;
@@ -8940,16 +8909,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>237</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F229" t="n">
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -8958,49 +8961,15 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Back-office vs. Front-office</t>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
-        <v>238</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Hierarquia na Aquisição de Tecnologia</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -9009,16 +8978,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>239</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F231" t="n">
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -9027,49 +9030,15 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Processos Decisórios</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Critérios de Decisão no AHP</t>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
-	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
-        <v>240</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Tendências e Tecnologias em Gestão da Informação</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -9079,33 +9048,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" t="n">
+    <row r="233">
+      <c r="A233" t="n">
         <v>241</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -9115,33 +9084,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" t="n">
+    <row r="234">
+      <c r="A234" t="n">
         <v>242</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -9151,33 +9120,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" t="n">
+    <row r="235">
+      <c r="A235" t="n">
         <v>243</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -9186,33 +9155,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" t="n">
+    <row r="236">
+      <c r="A236" t="n">
         <v>244</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -9221,33 +9190,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
+      <c r="F236" t="n">
         <v>2</v>
       </c>
-      <c r="G237" t="n">
+      <c r="G236" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" t="n">
+    <row r="237">
+      <c r="A237" t="n">
         <v>245</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -9256,33 +9225,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" t="n">
+    <row r="238">
+      <c r="A238" t="n">
         <v>246</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -9291,33 +9260,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" t="n">
+    <row r="239">
+      <c r="A239" t="n">
         <v>247</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -9330,35 +9299,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -9367,33 +9336,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" t="n">
+    <row r="241">
+      <c r="A241" t="n">
         <v>249</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -9404,67 +9373,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>250</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F242" t="n">
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Financeira</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Análise de Investimentos</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Número suficiente para identificação</t>
+          <t>Relação entre TIR e VPL</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
-        <v>251</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>Relação entre TIR e VPL</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;São análises independentes.&lt;/li&gt;
@@ -9474,6 +9443,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>252</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>método da TIR</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+        </is>
+      </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -9497,12 +9497,15 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>método da TIR</t>
+          <t>Valor Presente Líquido (VPL)</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
+	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -9514,7 +9517,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -9528,15 +9531,12 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Valor Presente Líquido (VPL)</t>
+          <t>Relação VPL X TMA</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
-	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Inversamente proporcionais</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -9548,7 +9548,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -9562,41 +9562,10 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Relação VPL X TMA</t>
+          <t>Relação VPL x TIR x TMA</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
-        <is>
-          <t>Inversamente proporcionais</t>
-        </is>
-      </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
-        <v>255</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Relação VPL x TIR x TMA</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;𝑽𝑷𝑳 &gt; 0 -&gt; 𝑽𝑷𝑳 &gt; TMA&lt;/li&gt;
@@ -9605,16 +9574,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>256</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Princípio da Entidade</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Autonomia da pessoa jurídica</t>
+        </is>
+      </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -9623,46 +9623,15 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Contabilidade Básica</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Princípio da Entidade</t>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
-        <is>
-          <t>Autonomia da pessoa jurídica</t>
-        </is>
-      </c>
-      <c r="F249" t="n">
-        <v>1</v>
-      </c>
-      <c r="G249" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
-        <v>257</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -9680,18 +9649,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Receitas</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;aumento nos ativos
+    &lt;ul&gt;
+      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diminuição de passivo
+    &lt;ul&gt;
+      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta aumento do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F250" t="n">
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A251" t="n">
+        <v>259</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -9705,34 +9730,35 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Receitas</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;aumento nos ativos
-    &lt;ul&gt;
-      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;diminuição de passivo
-    &lt;ul&gt;
-      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+  &lt;li&gt;consumo de bens ou serviços
+    &lt;ul&gt;
+      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;representam
+    &lt;ul&gt;
+      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
+      &lt;li&gt;aumento no passivo&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;reconhecimento
     &lt;ul&gt;
-      &lt;li&gt;acarreta aumento do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;transações com sócios
     &lt;ul&gt;
-      &lt;li&gt;não representam receitas&lt;/li&gt;
+      &lt;li&gt;não representam despesas&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -9747,7 +9773,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -9761,67 +9787,10 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;consumo de bens ou serviços
-    &lt;ul&gt;
-      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;representam
-    &lt;ul&gt;
-      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
-      &lt;li&gt;aumento no passivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;reconhecimento
-    &lt;ul&gt;
-      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;transações com sócios
-    &lt;ul&gt;
-      &lt;li&gt;não representam despesas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
-        <v>260</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -9903,33 +9872,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="254">
-      <c r="A254" t="n">
+    <row r="253">
+      <c r="A253" t="n">
         <v>261</v>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C253" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -9977,33 +9946,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>262</v>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C254" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -10055,33 +10024,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>263</v>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C255" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -10099,33 +10068,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>264</v>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B256" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C256" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -10135,35 +10104,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C257" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -10231,33 +10200,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
+    <row r="258">
+      <c r="A258" t="n">
         <v>266</v>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C258" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -10292,33 +10261,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" t="n">
+    <row r="259">
+      <c r="A259" t="n">
         <v>267</v>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C259" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -10376,33 +10345,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="261">
-      <c r="A261" t="n">
+    <row r="260">
+      <c r="A260" t="n">
         <v>268</v>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C260" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
@@ -10452,33 +10421,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
         <v>269</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
@@ -10558,33 +10527,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
         <v>270</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -10593,6 +10562,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>271</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F263" t="n">
         <v>0</v>
       </c>
@@ -10602,7 +10602,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -10616,12 +10616,14 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>PAYBACK SIMPLES</t>
+          <t>PAYBACK DESCONTADO</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -10633,7 +10635,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -10647,14 +10649,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>PAYBACK DESCONTADO</t>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -10666,7 +10666,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -10680,12 +10680,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
+          <t xml:space="preserve">Índice de Lucratividade </t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
+          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -10697,55 +10697,24 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Índice de Lucratividade </t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
-        <is>
-          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>275</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Processo de Gestão de Risco</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -10811,66 +10780,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" t="n">
+    <row r="268">
+      <c r="A268" t="n">
         <v>276</v>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="n">
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" t="n">
+    <row r="269">
+      <c r="A269" t="n">
         <v>277</v>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -10923,6 +10892,40 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>278</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F270" t="n">
         <v>0</v>
       </c>
@@ -10932,7 +10935,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -10941,49 +10944,15 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>teoria da organização e da gestão da informação</t>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
-	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F271" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>279</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Gestão da Inovação</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -11052,8 +11021,42 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>280</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Gestão da Inovação</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Invenção x Inovação</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;invenção &lt;ul&gt; &lt;li&gt;solução tecnicamente viável&lt;/li&gt; &lt;li&gt;não considera a viabilidade econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Inovação &lt;ul&gt; &lt;li&gt;solução tecnicamente e economicamente viável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
@@ -11061,7 +11064,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -11070,49 +11073,15 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Gestão da Inovação</t>
+          <t>Gestão da Qualidade</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Invenção x Inovação</t>
+          <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;invenção &lt;ul&gt; &lt;li&gt;solução tecnicamente viável&lt;/li&gt; &lt;li&gt;não considera a viabilidade econômica&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Inovação &lt;ul&gt; &lt;li&gt;solução tecnicamente e economicamente viável&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F273" t="n">
-        <v>1</v>
-      </c>
-      <c r="G273" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
-        <v>281</v>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -11126,6 +11095,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>282</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F274" t="n">
         <v>0</v>
       </c>
@@ -11135,7 +11135,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -11149,41 +11149,10 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>índice de capacidade do processo (Cp)</t>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
-        <is>
-          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>283</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>ISO 19443; ISO 26000; e ISO 45001</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -11210,33 +11179,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
         <v>284</v>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>Tipos de Benchmarking</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="E276" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Interno&lt;/strong&gt;
@@ -11273,6 +11242,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>285</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F277" t="n">
         <v>0</v>
       </c>
@@ -11282,7 +11285,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -11296,44 +11299,10 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Ciclo PDCA</t>
+          <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
-        <v>286</v>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade Total (TQM)</t>
-        </is>
-      </c>
-      <c r="E279" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -11423,33 +11392,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
         <v>287</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -11508,33 +11477,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
         <v>288</v>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -11594,33 +11563,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="n">
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="282">
-      <c r="A282" t="n">
+    <row r="281">
+      <c r="A281" t="n">
         <v>289</v>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E281" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -11679,33 +11648,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F282" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" t="n">
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="283">
-      <c r="A283" t="n">
+    <row r="282">
+      <c r="A282" t="n">
         <v>290</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D282" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E282" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -11782,33 +11751,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F283" t="n">
-        <v>0</v>
-      </c>
-      <c r="G283" t="n">
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="284">
-      <c r="A284" t="n">
+    <row r="283">
+      <c r="A283" t="n">
         <v>291</v>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D283" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E283" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -11880,33 +11849,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F284" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
         <v>292</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -11968,33 +11937,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F285" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
         <v>293</v>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E285" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -12083,33 +12052,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F286" t="n">
-        <v>0</v>
-      </c>
-      <c r="G286" t="n">
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" t="n">
+    <row r="286">
+      <c r="A286" t="n">
         <v>294</v>
       </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C287" t="inlineStr">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
+      <c r="D286" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
+      <c r="E286" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -12182,33 +12151,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F287" t="n">
-        <v>0</v>
-      </c>
-      <c r="G287" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="n">
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
         <v>295</v>
       </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
+      <c r="D287" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
+      <c r="E287" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -12253,33 +12222,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F288" t="n">
-        <v>0</v>
-      </c>
-      <c r="G288" t="n">
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="289">
-      <c r="A289" t="n">
+    <row r="288">
+      <c r="A288" t="n">
         <v>296</v>
       </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
+      <c r="D288" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
+      <c r="E288" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -12334,6 +12303,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>297</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F289" t="n">
         <v>0</v>
       </c>
@@ -12343,7 +12368,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -12357,66 +12382,10 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Dimensões da Qualidade em Serviços</t>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;instalações físicas
-        &lt;ul&gt;
-          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;materiais
-        &lt;ul&gt;
-          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços explícitos
-        &lt;ul&gt;
-          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços complementares
-        &lt;ul&gt;
-          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F290" t="n">
-        <v>0</v>
-      </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" t="n">
-        <v>298</v>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>CCQ – Círculos de Controle de Qualidade</t>
-        </is>
-      </c>
-      <c r="E291" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -12448,6 +12417,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>299</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F291" t="n">
         <v>0</v>
       </c>
@@ -12457,7 +12491,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -12471,75 +12505,10 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+          <t>Seis Sigma</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
-      &lt;li&gt;utilizadas como manobra para "promover para fora"
-        &lt;ul&gt;
-          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
-          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
-      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F292" t="n">
-        <v>0</v>
-      </c>
-      <c r="G292" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="n">
-        <v>300</v>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>Seis Sigma</t>
-        </is>
-      </c>
-      <c r="E293" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -12609,6 +12578,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F292" t="n">
+        <v>0</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>301</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
       <c r="F293" t="n">
         <v>0</v>
       </c>
@@ -12618,7 +12618,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -12627,46 +12627,15 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Capabilidade</t>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
-        <is>
-          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
-        </is>
-      </c>
-      <c r="F294" t="n">
-        <v>0</v>
-      </c>
-      <c r="G294" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="n">
-        <v>302</v>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>Macrofluxo da Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="E295" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -12710,33 +12679,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F295" t="n">
-        <v>0</v>
-      </c>
-      <c r="G295" t="n">
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="296">
-      <c r="A296" t="n">
+    <row r="295">
+      <c r="A295" t="n">
         <v>303</v>
       </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
+      <c r="D295" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
+      <c r="E295" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -12785,33 +12754,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F296" t="n">
-        <v>0</v>
-      </c>
-      <c r="G296" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="n">
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
         <v>304</v>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
+      <c r="D296" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
+      <c r="E296" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -12841,6 +12810,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F296" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>305</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F297" t="n">
         <v>0</v>
       </c>
@@ -12850,7 +12879,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -12864,70 +12893,10 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Diagrama de Interação do Processo</t>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diagrama de Interação do Processo
-    &lt;ul&gt;
-      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
-      &lt;li&gt;foco nas interfaces
-        &lt;ul&gt;
-          &lt;li&gt;entradas e saídas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;elementos
-        &lt;ul&gt;
-          &lt;li&gt;blocos de processos macro&lt;/li&gt;
-          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;objetivos
-        &lt;ul&gt;
-          &lt;li&gt;identificar dependências&lt;/li&gt;
-          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;distinção
-        &lt;ul&gt;
-          &lt;li&gt;foco externo ao processo&lt;/li&gt;
-          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F298" t="n">
-        <v>0</v>
-      </c>
-      <c r="G298" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="n">
-        <v>306</v>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Requisitos e Rotinas da ISO 9001:2015</t>
-        </is>
-      </c>
-      <c r="E299" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -12959,35 +12928,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F299" t="n">
-        <v>0</v>
-      </c>
-      <c r="G299" t="n">
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
+    <row r="299">
+      <c r="A299" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
+      <c r="C299" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
+      <c r="D299" t="inlineStr">
         <is>
           <t>Débito na Contabilidade</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
+      <c r="E299" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -13023,33 +12992,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F300" t="n">
-        <v>0</v>
-      </c>
-      <c r="G300" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="n">
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
         <v>308</v>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C300" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
+      <c r="D300" t="inlineStr">
         <is>
           <t>Tipos de Contas e Retificadoras</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
+      <c r="E300" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
@@ -13075,33 +13044,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F301" t="n">
-        <v>0</v>
-      </c>
-      <c r="G301" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="n">
+      <c r="F300" t="n">
+        <v>0</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
         <v>309</v>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr">
+      <c r="C301" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
+      <c r="D301" t="inlineStr">
         <is>
           <t>Diferenças Tributárias</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
+      <c r="E301" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
@@ -13121,33 +13090,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F302" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="n">
+      <c r="F301" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
         <v>310</v>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr">
+      <c r="C302" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
+      <c r="D302" t="inlineStr">
         <is>
           <t>Teoria Patrimonialista e Despesas</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
+      <c r="E302" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
@@ -13172,33 +13141,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F303" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="n">
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
         <v>311</v>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr">
+      <c r="C303" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
+      <c r="D303" t="inlineStr">
         <is>
           <t>O Ativo ao Final do Exercício</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
+      <c r="E303" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
@@ -13218,33 +13187,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F304" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="n">
+      <c r="F303" t="n">
+        <v>0</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
         <v>312</v>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr">
+      <c r="C304" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
+      <c r="D304" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
+      <c r="E304" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
@@ -13270,33 +13239,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F305" t="n">
-        <v>0</v>
-      </c>
-      <c r="G305" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="n">
+      <c r="F304" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
         <v>313</v>
       </c>
-      <c r="B306" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
+      <c r="D305" t="inlineStr">
         <is>
           <t>NR 10</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
+      <c r="E305" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
@@ -13412,33 +13381,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F306" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="n">
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
         <v>314</v>
       </c>
-      <c r="B307" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C307" t="inlineStr">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
+      <c r="D306" t="inlineStr">
         <is>
           <t>NR 11</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
+      <c r="E306" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
@@ -13566,33 +13535,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F307" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="n">
+      <c r="F306" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
         <v>315</v>
       </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C308" t="inlineStr">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
+      <c r="D307" t="inlineStr">
         <is>
           <t>NR 12</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
+      <c r="E307" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
@@ -13710,33 +13679,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F308" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="n">
+      <c r="F307" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
         <v>316</v>
       </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C309" t="inlineStr">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
+      <c r="D308" t="inlineStr">
         <is>
           <t>NR 13</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
+      <c r="E308" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Gestão da integridade estrutural
@@ -13854,33 +13823,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F309" t="n">
-        <v>0</v>
-      </c>
-      <c r="G309" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="n">
+      <c r="F308" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
         <v>317</v>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D309" t="inlineStr">
         <is>
           <t>NR 14</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
+      <c r="E309" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação com segurança
@@ -13928,35 +13897,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F310" t="n">
-        <v>0</v>
-      </c>
-      <c r="G310" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+      <c r="F309" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C311" t="inlineStr">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
+      <c r="D310" t="inlineStr">
         <is>
           <t>NR 15</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
+      <c r="E310" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
@@ -13990,33 +13959,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F311" t="n">
-        <v>0</v>
-      </c>
-      <c r="G311" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" t="n">
+      <c r="F310" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
         <v>319</v>
       </c>
-      <c r="B312" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C312" t="inlineStr">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
+      <c r="D311" t="inlineStr">
         <is>
           <t>NR 16</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
+      <c r="E311" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
@@ -14121,33 +14090,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F312" t="n">
-        <v>0</v>
-      </c>
-      <c r="G312" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="n">
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
         <v>320</v>
       </c>
-      <c r="B313" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
+      <c r="E312" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
@@ -14237,33 +14206,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F313" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="n">
+      <c r="F312" t="n">
+        <v>0</v>
+      </c>
+      <c r="G312" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
         <v>321</v>
       </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
+      <c r="D313" t="inlineStr">
         <is>
           <t>NR 18</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
+      <c r="E313" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
@@ -14384,33 +14353,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F314" t="n">
-        <v>0</v>
-      </c>
-      <c r="G314" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="n">
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
         <v>322</v>
       </c>
-      <c r="B315" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
+      <c r="D314" t="inlineStr">
         <is>
           <t>NR 19</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
+      <c r="E314" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
@@ -14509,33 +14478,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F315" t="n">
-        <v>0</v>
-      </c>
-      <c r="G315" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="n">
+      <c r="F314" t="n">
+        <v>0</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
         <v>323</v>
       </c>
-      <c r="B316" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
+      <c r="D315" t="inlineStr">
         <is>
           <t>NR 20</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
+      <c r="E315" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
@@ -14635,33 +14604,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F316" t="n">
-        <v>0</v>
-      </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="n">
+      <c r="F315" t="n">
+        <v>0</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
         <v>324</v>
       </c>
-      <c r="B317" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
+      <c r="D316" t="inlineStr">
         <is>
           <t>NR 21</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
+      <c r="E316" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
@@ -14741,33 +14710,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F317" t="n">
-        <v>0</v>
-      </c>
-      <c r="G317" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="n">
+      <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
         <v>325</v>
       </c>
-      <c r="B318" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
+      <c r="D317" t="inlineStr">
         <is>
           <t>NR 22</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
+      <c r="E317" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
@@ -14895,57 +14864,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F318" t="n">
-        <v>0</v>
-      </c>
-      <c r="G318" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" t="n">
-        <v>326</v>
-      </c>
-      <c r="B319" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
+      <c r="F317" t="n">
+        <v>0</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
+      <c r="D318" t="inlineStr">
         <is>
           <t>NR 23</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>Quinta-feira, 16 de abril de 2026, 17:52:43 (Fuso horário local).
----
-### Resumo com lista em cascata
-· **Medidas de prevenção contra incêndios**
-    o estabelecidas para ambientes de trabalho
-    o conformidade com
-        § legislação estadual
-        § normas técnicas oficiais (complementar)
-· **Informações aos trabalhadores**
-    o utilização de equipamentos de combate
-    o procedimentos de resposta e evacuação
-    o funcionamento de dispositivos de alarme
-· **Saídas e vias de passagem**
-    o número suficiente para abandono rápido
-    o requisitos de segurança
-        § sinalização indicando a direção da saída
-        § manutenção permanente de desobstrução
-        § proibição de trancamento durante a jornada
-        § permissão de dispositivos de fácil abertura interna
----
-### Estrutura em HTML
-```html
-&lt;ul&gt;
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
     &lt;ul&gt;
       &lt;li&gt;estabelecidas para ambientes de trabalho&lt;/li&gt;
@@ -14977,14 +14926,1656 @@
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
-&lt;/ul&gt;
-```</t>
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F318" t="n">
+        <v>0</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>NR 24</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensionamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;baseado no turno com maior contingente&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Instalações Sanitárias&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;composição: bacia sanitária sifonada e lavatório&lt;/li&gt;
+      &lt;li&gt;proporção: 1 conjunto para cada 20 trabalhadores&lt;/li&gt;
+      &lt;li&gt;mictórios
+        &lt;ul&gt;
+          &lt;li&gt;obrigatórios em sanitários masculinos (exceto individuais)&lt;/li&gt;
+          &lt;li&gt;1 para cada 20 (até 100 trabalhadores)&lt;/li&gt;
+          &lt;li&gt;1 para cada 50 (no que exceder)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;lavatórios
+        &lt;ul&gt;
+          &lt;li&gt;1 para cada 10 em atividades com material infectante ou tóxico&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;chuveiros
+        &lt;ul&gt;
+          &lt;li&gt;1 para cada 10 (material infectante/tóxico)&lt;/li&gt;
+          &lt;li&gt;1 para cada 20 (poeira/esforço físico/calor intenso)&lt;/li&gt;
+          &lt;li&gt;individuais com água quente e fria&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;requisitos estruturais
+        &lt;ul&gt;
+          &lt;li&gt;piso e parede impermeáveis e laváveis&lt;/li&gt;
+          &lt;li&gt;ventilação para o exterior ou exaustão forçada&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Vestiários&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;obrigatórios quando houver troca de roupa ou chuveiro&lt;/li&gt;
+      &lt;li&gt;armários
+        &lt;ul&gt;
+          &lt;li&gt;individuais com sistema de trancamento&lt;/li&gt;
+          &lt;li&gt;duplos para atividades com exposição a agentes nocivos ou poeira&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Locais para Refeições&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;até 30 trabalhadores
+        &lt;ul&gt;
+          &lt;li&gt;espaço adaptado, arejado e com assentos&lt;/li&gt;
+          &lt;li&gt;proximidade de água potável e meios para aquecimento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mais de 30 trabalhadores
+        &lt;ul&gt;
+          &lt;li&gt;fora da área de trabalho&lt;/li&gt;
+          &lt;li&gt;lavatórios próprios ou próximos&lt;/li&gt;
+          &lt;li&gt;recipientes com tampa para descarte de restos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Alojamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;quartos
+        &lt;ul&gt;
+          &lt;li&gt;capacidade máxima de 8 trabalhadores&lt;/li&gt;
+          &lt;li&gt;proibido uso de 3 ou mais camas na mesma vertical&lt;/li&gt;
+          &lt;li&gt;relação de área: 3,00 m² (cama simples) ou 4,50 m² (beliche)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;sanitários
+        &lt;ul&gt;
+          &lt;li&gt;1 conjunto com chuveiro para cada 10 hospedados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Vestimenta de Trabalho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;fornecimento gratuito&lt;/li&gt;
+      &lt;li&gt;higienização sob responsabilidade do empregador se houver risco de contaminação&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;água potável: 1 bebedouro para cada 50 trabalhadores&lt;/li&gt;
+      &lt;li&gt;pé-direito mínimo: 2,50 m (3,00 m se houver beliche)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F319" t="n">
         <v>0</v>
       </c>
       <c r="G319" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Engenharia de Produto</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>NR 25</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gerenciamento de resíduos industriais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;provenientes de processos industriais&lt;/li&gt;
+      &lt;li&gt;formas: sólida, líquida, gasosa ou combinação&lt;/li&gt;
+      &lt;li&gt;não assemelhados a resíduos domésticos
+        &lt;ul&gt;
+          &lt;li&gt;cinzas, lodos e óleos&lt;/li&gt;
+          &lt;li&gt;materiais alcalinos ou ácidos&lt;/li&gt;
+          &lt;li&gt;escórias, poeiras e borras&lt;/li&gt;
+          &lt;li&gt;efluentes líquidos e emissões gasosas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diretrizes de segurança e saúde&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;redução da exposição ocupacional
+        &lt;ul&gt;
+          &lt;li&gt;adoção das melhores práticas tecnológicas disponíveis&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;proibição de lançamento no ambiente de trabalho
+        &lt;ul&gt;
+          &lt;li&gt;quando comprometer a segurança e saúde&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;aprovação de dispositivos de controle
+        &lt;ul&gt;
+          &lt;li&gt;submetidos aos órgãos competentes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ciclo de gestão (com medidas de prevenção em cada etapa)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;coleta e acondicionamento&lt;/li&gt;
+      &lt;li&gt;armazenamento e transporte&lt;/li&gt;
+      &lt;li&gt;tratamento&lt;/li&gt;
+      &lt;li&gt;disposição final&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Resíduos específicos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;radioativos
+        &lt;ul&gt;
+          &lt;li&gt;conforme normas da Autoridade Nacional de Segurança Nuclear (ANSN)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;risco biológico
+        &lt;ul&gt;
+          &lt;li&gt;conforme legislações sanitária e ambiental&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;treinamento continuado para trabalhadores envolvidos&lt;/li&gt;
+      &lt;li&gt;temas obrigatórios
+        &lt;ul&gt;
+          &lt;li&gt;riscos ocupacionais&lt;/li&gt;
+          &lt;li&gt;medidas de prevenção adequadas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>329</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>NR 26</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Sinalização e identificação de segurança&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;indicação e advertência de perigos e riscos&lt;/li&gt;
+      &lt;li&gt;uso de cores
+        &lt;ul&gt;
+          &lt;li&gt;identificar equipamentos de segurança&lt;/li&gt;
+          &lt;li&gt;delimitar áreas&lt;/li&gt;
+          &lt;li&gt;identificar tubulações de líquidos e gases&lt;/li&gt;
+          &lt;li&gt;seguir normas técnicas oficiais&lt;/li&gt;
+          &lt;li&gt;uso reduzido para evitar distração e fadiga&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Identificação de produto químico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;classificação pelo GHS
+        &lt;ul&gt;
+          &lt;li&gt;baseada em lista harmonizada ou ensaios&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;rotulagem preventiva
+        &lt;ul&gt;
+          &lt;li&gt;obrigatória na embalagem&lt;/li&gt;
+          &lt;li&gt;elementos GHS
+            &lt;ul&gt;
+              &lt;li&gt;identificação e composição&lt;/li&gt;
+              &lt;li&gt;pictogramas de perigo&lt;/li&gt;
+              &lt;li&gt;palavra de advertência&lt;/li&gt;
+              &lt;li&gt;frases de perigo e precaução&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;simplificada para produtos não perigosos
+            &lt;ul&gt;
+              &lt;li&gt;nome e recomendações de precaução&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ficha com dados de segurança (FDS)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;fornecida pelo fabricante ou fornecedor&lt;/li&gt;
+      &lt;li&gt;obrigatória para
+        &lt;ul&gt;
+          &lt;li&gt;produtos classificados como perigosos&lt;/li&gt;
+          &lt;li&gt;produtos cujos usos deem origem a riscos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;formato e conteúdo conforme GHS&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Informação e treinamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;acesso garantido dos trabalhadores às fichas&lt;/li&gt;
+      &lt;li&gt;temas do treinamento
+        &lt;ul&gt;
+          &lt;li&gt;compreensão da rotulagem e da ficha&lt;/li&gt;
+          &lt;li&gt;perigos e riscos&lt;/li&gt;
+          &lt;li&gt;medidas preventivas e procedimentos de emergência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F321" t="n">
+        <v>0</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>NR 28</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Fiscalização do Trabalho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;agentes de inspeção do trabalho
+        &lt;ul&gt;
+          &lt;li&gt;verificam cumprimento das disposições legais e regulamentares&lt;/li&gt;
+          &lt;li&gt;utilizam meios comprobatórios (inclusive audiovisuais)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;critério da dupla visita
+        &lt;ul&gt;
+          &lt;li&gt;aplicado conforme legislação vigente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;termo de notificação
+        &lt;ul&gt;
+          &lt;li&gt;prazo para correção: máximo 60 dias&lt;/li&gt;
+          &lt;li&gt;prorrogação: até 120 dias (mediante solicitação em 10 dias)&lt;/li&gt;
+          &lt;li&gt;prazos superiores: exigem negociação com o sindicato&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Embargo e Interdição&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;caracterizados por risco grave e iminente&lt;/li&gt;
+      &lt;li&gt;modalidades
+        &lt;ul&gt;
+          &lt;li&gt;interdição: estabelecimento, setor, máquina ou equipamento&lt;/li&gt;
+          &lt;li&gt;embargo: parcial ou total da obra&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;suspensão condicionada a novo laudo técnico&lt;/li&gt;
+      &lt;li&gt;descumprimento reiterado
+        &lt;ul&gt;
+          &lt;li&gt;lavratura de auto de infração por 3 vezes no mesmo item&lt;/li&gt;
+          &lt;li&gt;negligência do empregador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Penalidades e Multas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;classificação das infrações (Anexo II)
+        &lt;ul&gt;
+          &lt;li&gt;Segurança do Trabalho (S)&lt;/li&gt;
+          &lt;li&gt;Medicina do Trabalho (M)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;gradação das multas (Anexo I)
+        &lt;ul&gt;
+          &lt;li&gt;baseada no número de empregados&lt;/li&gt;
+          &lt;li&gt;níveis de infração de 1 a 4 (I1 a I4)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;reincidência e resistência
+        &lt;ul&gt;
+          &lt;li&gt;multas com valores fixados em UFIR (Segurança: 6.304 / Medicina: 3.782)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;atividades rurais
+        &lt;ul&gt;
+          &lt;li&gt;sanções conforme Lei nº 5.889/73&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;reajuste anual dos valores conforme a CLT&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F322" t="n">
+        <v>0</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>NR 29</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Operadores Portuários e Tomadores de Serviço
+        &lt;ul&gt;
+          &lt;li&gt;asseguram que as operações ocorram após medidas de prevenção&lt;/li&gt;
+          &lt;li&gt;garantem o uso correto de EPIs (NR-06)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;OGMO (Órgão Gestor de Mão de Obra)
+        &lt;ul&gt;
+          &lt;li&gt;escala apenas trabalhadores capacitados&lt;/li&gt;
+          &lt;li&gt;constitui o SESSTP (Serviço Especializado)&lt;/li&gt;
+          &lt;li&gt;implementa o PCMSO&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;PGR (Programa de Gerenciamento de Riscos)
+        &lt;ul&gt;
+          &lt;li&gt;intercâmbio obrigatório de informações entre Operador, OGMO e Administração&lt;/li&gt;
+          &lt;li&gt;contém procedimentos para acesso seguro, porões e espaços confinados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas de Segurança&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;SESSTP (Serviço Especializado)
+        &lt;ul&gt;
+          &lt;li&gt;realiza inspeção prévia na atracação e a bordo&lt;/li&gt;
+          &lt;li&gt;identifica condições impeditivas e sinaliza riscos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;CPATP (Comissão de Prevenção de Acidentes)
+        &lt;ul&gt;
+          &lt;li&gt;constituída de forma paritária (trabalhadores avulsos e operadores)&lt;/li&gt;
+          &lt;li&gt;mandato de dois anos, permitida uma reeleição&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Operações a Bordo e Acessos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Acesso a embarcações
+        &lt;ul&gt;
+          &lt;li&gt;proibido escada tipo quebra-peito&lt;/li&gt;
+          &lt;li&gt;fora do alcance do raio da lança do guindaste&lt;/li&gt;
+          &lt;li&gt;rede de segurança obrigatória se houver risco de queda n'água&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Trabalho em Porões e Conveses
+        &lt;ul&gt;
+          &lt;li&gt;vedada atividade em cobertas distintas do mesmo porão simultaneamente&lt;/li&gt;
+          &lt;li&gt;passagem sobre cargas estivadas exige passarelas de no mínimo 0,60 m&lt;/li&gt;
+          &lt;li&gt;iluminação mínima de 50 lux (operação) e 10 lux (circulação)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Equipamentos e Cargas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Máquinas e Acessórios
+        &lt;ul&gt;
+          &lt;li&gt;indicação legível de capacidade máxima e peso bruto&lt;/li&gt;
+          &lt;li&gt;sinalização sonora e luminosa de marcha-a-ré&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Operações com Contêineres
+        &lt;ul&gt;
+          &lt;li&gt;quadro posicionador com travas automáticas e indicador visual&lt;/li&gt;
+          &lt;li&gt;gaiola de transporte para pessoal se altura &gt; 5 m ou 2 contêineres&lt;/li&gt;
+          &lt;li&gt;proibida permanência de trabalhador sobre contêiner em movimento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Cargas Perigosas (Anexo IV)
+        &lt;ul&gt;
+          &lt;li&gt;treinamento específico de 20 horas&lt;/li&gt;
+          &lt;li&gt;segregação rigorosa conforme Anexo V&lt;/li&gt;
+          &lt;li&gt;ficha de informações de segurança disponível no local&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Saúde e Emergência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Locais Frigorificados
+        &lt;ul&gt;
+          &lt;li&gt;regime de recuperação térmica fora do ambiente frio (Anexo III)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Primeiros Socorros
+        &lt;ul&gt;
+          &lt;li&gt;presença obrigatória de integrante do serviço de urgência no berço&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;PCE e PAM
+        &lt;ul&gt;
+          &lt;li&gt;Plano de Controle de Emergência e Ajuda Mútua&lt;/li&gt;
+          &lt;li&gt;realização de 3 simulados anuais por tipo de risco&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>333</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>NR 30</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Riscos e Saúde&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;PGRTA (Programa de Gerenciamento de Riscos no Trabalho Aquaviário)
+        &lt;ul&gt;
+          &lt;li&gt;elaborado por embarcação&lt;/li&gt;
+          &lt;li&gt;revisado a cada 3 anos&lt;/li&gt;
+          &lt;li&gt;contém procedimentos operacionais específicos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Proteção à saúde
+        &lt;ul&gt;
+          &lt;li&gt;PCMSO com padrões STCW para marítimos&lt;/li&gt;
+          &lt;li&gt;Cópia do ASO mantida na embarcação&lt;/li&gt;
+          &lt;li&gt;Enfermaria obrigatória em certas classes
+            &lt;ul&gt;
+              &lt;li&gt;uso exclusivo para doentes&lt;/li&gt;
+              &lt;li&gt;instalações de água quente e fria&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Organização de Bordo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;GSSTB (Grupo de Segurança e Saúde no Trabalho a Bordo)
+        &lt;ul&gt;
+          &lt;li&gt;obrigatório para embarcações &amp;ge; 500 AB&lt;/li&gt;
+          &lt;li&gt;reunião mensal obrigatória&lt;/li&gt;
+          &lt;li&gt;composto por tripulantes de convés, máquinas e saúde&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;CIPA (Comissão Interna de Prevenção de Acidentes e Assédio)
+        &lt;ul&gt;
+          &lt;li&gt;representação proporcional ao número de embarcações&lt;/li&gt;
+          &lt;li&gt;participação permitida via meios eletrônicos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Condições de Vivência (Habitabilidade)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Acomodações e Camarotes
+        &lt;ul&gt;
+          &lt;li&gt;camas individuais com dimensões mínimas (1,98 m x 0,80 m)&lt;/li&gt;
+          &lt;li&gt;máximo de 2 camas sobrepostas&lt;/li&gt;
+          &lt;li&gt;proibido sobreposição que impeça ventilação natural&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Alimentação e Higiene
+        &lt;ul&gt;
+          &lt;li&gt;provisão de víveres e água potável&lt;/li&gt;
+          &lt;li&gt;cozinha com sistema de exaustão&lt;/li&gt;
+          &lt;li&gt;lavanderia obrigatória para embarcações &amp;ge; 500 AB&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança Operacional e Acessos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Manutenção em operação
+        &lt;ul&gt;
+          &lt;li&gt;exige Análise de Risco (AR)&lt;/li&gt;
+          &lt;li&gt;emissão de Permissão de Trabalho (PT) válida por 24h&lt;/li&gt;
+          &lt;li&gt;interrupção imediata em condições meteorológicas adversas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Movimentação de Carga
+        &lt;ul&gt;
+          &lt;li&gt;equipamentos e acessórios certificados&lt;/li&gt;
+          &lt;li&gt;inspeção diária pelo operador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Acesso à embarcação
+        &lt;ul&gt;
+          &lt;li&gt;escada de portaló com ângulo máximo de 55&amp;deg;&lt;/li&gt;
+          &lt;li&gt;uso obrigatório de rede de segurança&lt;/li&gt;
+          &lt;li&gt;proibido uso de escada tipo quebra-peito para acesso habitual&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Pesca Comercial (Anexo I)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;aplicável a barcos &amp;ge; 12 m ou &amp;ge; 10 AB&lt;/li&gt;
+      &lt;li&gt;estabilidade deve ser mantida em todas as fases da pesca&lt;/li&gt;
+      &lt;li&gt;equipamentos de tração
+        &lt;ul&gt;
+          &lt;li&gt;dispositivo de parada de emergência&lt;/li&gt;
+          &lt;li&gt;visão clara da faina pelo operador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;segurança nas áreas de vivência
+        &lt;ul&gt;
+          &lt;li&gt;nível de ruído máximo nos dormitórios: 65 dB(A)&lt;/li&gt;
+          &lt;li&gt;isolamento térmico e acústico obrigatórios&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>334</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>NR 31</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Campo de Aplicação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Atividades abrangidas
+        &lt;ul&gt;
+          &lt;li&gt;agricultura, pecuária, silvicultura, exploração florestal e aquicultura&lt;/li&gt;
+          &lt;li&gt;exploração industrial desenvolvida em estabelecimento rural&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Exceções (aplica-se outras NRs nestes casos)
+        &lt;ul&gt;
+          &lt;li&gt;NR-03: Embargo e interdição&lt;/li&gt;
+          &lt;li&gt;NR-13: Caldeiras e vasos de pressão&lt;/li&gt;
+          &lt;li&gt;NR-15: Insalubridade&lt;/li&gt;
+          &lt;li&gt;NR-16: Periculosidade&lt;/li&gt;
+          &lt;li&gt;NR-20: Inflamáveis e combustíveis&lt;/li&gt;
+          &lt;li&gt;NR-28: Fiscalização e penalidades&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Riscos (PGRTR)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Elaboração e Custeio
+        &lt;ul&gt;
+          &lt;li&gt;responsabilidade do empregador&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Revisão
+        &lt;ul&gt;
+          &lt;li&gt;a cada 3 (três) anos&lt;/li&gt;
+          &lt;li&gt;quando houver inovações tecnológicas ou mudanças de processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Abrangência de riscos
+        &lt;ul&gt;
+          &lt;li&gt;químicos, físicos, biológicos, de acidentes e ergonômicos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Fator climáticos
+        &lt;ul&gt;
+          &lt;li&gt;orientação obrigatória sobre condições extremas e interrupção de atividades&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Serviços Especializados (SESTR)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Obrigatoriedade (Individual)
+        &lt;ul&gt;
+          &lt;li&gt;estabelecimentos com 51 ou mais trabalhadores (prazo indeterminado)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Modalidade Coletiva (Permitida se)
+        &lt;ul&gt;
+          &lt;li&gt;estabelecimentos do mesmo grupo distantes até 200 km&lt;/li&gt;
+          &lt;li&gt;consórcio de empregadores ou cooperativas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Estabelecimentos de 11 a 50 empregados
+        &lt;ul&gt;
+          &lt;li&gt;dispensado de SESTR se empregador/preposto tiver capacitação em prevenção&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Comissão de Prevenção (CIPATR)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Obrigatoriedade
+        &lt;ul&gt;
+          &lt;li&gt;estabelecimentos com 20 ou mais empregados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Composição e Mandato
+        &lt;ul&gt;
+          &lt;li&gt;paritária (eleitos e indicados)&lt;/li&gt;
+          &lt;li&gt;mandato de 2 anos (permitida uma reeleição)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Funcionamento
+        &lt;ul&gt;
+          &lt;li&gt;reuniões ordinárias: bimestrais&lt;/li&gt;
+          &lt;li&gt;reuniões extraordinárias: em até 5 dias úteis após acidente grave/fatal&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Agrotóxicos e Produtos Afins&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Proibições de manipulação
+        &lt;ul&gt;
+          &lt;li&gt;menores de 18 anos&lt;/li&gt;
+          &lt;li&gt;maiores de 60 anos&lt;/li&gt;
+          &lt;li&gt;gestantes e lactantes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Capacitação (Exposição Direta)
+        &lt;ul&gt;
+          &lt;li&gt;carga horária mínima: 20 horas&lt;/li&gt;
+          &lt;li&gt;conteúdo: teórico e prático&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Higiene Ocupacional
+        &lt;ul&gt;
+          &lt;li&gt;banho obrigatório após o término da jornada de trabalho&lt;/li&gt;
+          &lt;li&gt;vedado levar vestimentas contaminadas para fora do ambiente (exceto para lavanderia especializada)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Armazenamento
+        &lt;ul&gt;
+          &lt;li&gt;distância mínima de habitações/alimentos: 15 metros&lt;/li&gt;
+          &lt;li&gt;armários (limite de 100L ou 100kg): permitidos se trancados e fora de moradias&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Máquinas e Equipamentos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Transporte de pessoas
+        &lt;ul&gt;
+          &lt;li&gt;proibido em máquinas autopropelidas e implementos&lt;/li&gt;
+          &lt;li&gt;exceto se houver posto de trabalho projetado para esse fim&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Capacitação de operadores
+        &lt;ul&gt;
+          &lt;li&gt;máquinas autopropelidas: 24 horas (mínimo 12h práticas)&lt;/li&gt;
+          &lt;li&gt;motosserras e motopodas: 16 horas&lt;/li&gt;
+          &lt;li&gt;roçadeiras costais: 4 horas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Dispositivos de segurança
+        &lt;ul&gt;
+          &lt;li&gt;EPC (Estrutura de Proteção na Capotagem): obrigatória em tratores&lt;/li&gt;
+          &lt;li&gt;Tomada de Potência (TDP): proteção obrigatória nas partes superior e laterais&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Silos e Espaços Confinados&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Acesso ao interior
+        &lt;ul&gt;
+          &lt;li&gt;mínimo de 2 trabalhadores (um sempre no exterior)&lt;/li&gt;
+          &lt;li&gt;proibido durante operação de carga/descarga&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Capacitação (Espaço Confinado)
+        &lt;ul&gt;
+          &lt;li&gt;supervisor de entrada: 40 horas&lt;/li&gt;
+          &lt;li&gt;vigia e trabalhador autorizado: 16 horas&lt;/li&gt;
+          &lt;li&gt;reciclagem: a cada 12 meses (mínimo 8 horas)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Transporte de Trabalhadores&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Requisitos do veículo
+        &lt;ul&gt;
+          &lt;li&gt;tacógrafo obrigatório (se capacidade &amp;gt; 10 lugares)&lt;/li&gt;
+          &lt;li&gt;ferramentas e materiais: compartimento resistente e separado dos passageiros&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Condições Sanitárias e Conforto&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Instalações nas frentes de trabalho
+        &lt;ul&gt;
+          &lt;li&gt;proporção: 1 vaso e 1 lavatório para cada 40 trabalhadores ou fração&lt;/li&gt;
+          &lt;li&gt;distância máxima do posto de trabalho: 250 metros&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Alojamentos
+        &lt;ul&gt;
+          &lt;li&gt;capacidade máxima: 8 trabalhadores por quarto&lt;/li&gt;
+          &lt;li&gt;área mínima: 3,00 m² (cama simples) ou 4,50 m² (beliche)&lt;/li&gt;
+          &lt;li&gt;pé-direito (beliche): mínimo 3,00 metros&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Moradias Familiares
+        &lt;ul&gt;
+          &lt;li&gt;distância mínima de currais/depósitos de esterco: 30 metros&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F325" t="n">
+        <v>0</v>
+      </c>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>335</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>NR 32</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Segurança e Saúde em Serviços de Saúde (NR 32)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;objetivo: medidas de proteção para trabalhadores da saúde e assistência geral&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos Biológicos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;definição: microrganismos, parasitas, toxinas e príons&lt;/li&gt;
+      &lt;li&gt;gestão de riscos (PGR)
+        &lt;ul&gt;
+          &lt;li&gt;identificar fontes, vias de transmissão e virulência&lt;/li&gt;
+          &lt;li&gt;reavaliar em mudanças de condições ou após acidentes&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;medidas de proteção
+        &lt;ul&gt;
+          &lt;li&gt;lavatório exclusivo com acionamento sem mãos&lt;/li&gt;
+          &lt;li&gt;vedado
+            &lt;ul&gt;
+              &lt;li&gt;uso de calçados abertos&lt;/li&gt;
+              &lt;li&gt;ato de fumar e uso de adornos&lt;/li&gt;
+              &lt;li&gt;consumo de alimentos nos postos de trabalho&lt;/li&gt;
+              &lt;li&gt;reencape e desconexão manual de agulhas&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;vestimentas: fornecidas sem ônus, higienização sob responsabilidade do empregador em áreas críticas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;vacinação: gratuita contra tétano, difteria e hepatite B&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos Químicos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;rotulagem original e fichas descritivas em português&lt;/li&gt;
+      &lt;li&gt;quimioterápicos antineoplásicos
+        &lt;ul&gt;
+          &lt;li&gt;preparo em sala exclusiva com Cabine de Segurança Biológica Classe II B2&lt;/li&gt;
+          &lt;li&gt;afastamento de gestantes e nutrizes&lt;/li&gt;
+          &lt;li&gt;proibição de iniciar atividades sem Kit de Derramamento e EPIs&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;gases medicinais: cilindros fixados, na vertical e com capacete&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Radiações Ionizantes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;exige Plano de Proteção Radiológica (PPR) aprovado (CNEN/ANVISA)&lt;/li&gt;
+      &lt;li&gt;monitoração individual mensal via dosímetro&lt;/li&gt;
+      &lt;li&gt;gestantes: afastamento imediato das atividades com radiação&lt;/li&gt;
+      &lt;li&gt;registros de dose e prontuário: conservados por 30 anos&lt;/li&gt;
+      &lt;li&gt;áreas sinalizadas com o símbolo internacional de radiação&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Resíduos de Saúde&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;capacitação continuada sobre segregação na fonte&lt;/li&gt;
+      &lt;li&gt;sacos plásticos: preenchimento até 2/3 da capacidade&lt;/li&gt;
+      &lt;li&gt;perfurocortantes: descarte pelo usuário, limite 5 cm abaixo do bocal&lt;/li&gt;
+      &lt;li&gt;armazenamento temporário: piso e paredes laváveis, ralo sifonado e ventilado&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Manutenção e Limpeza&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;proibida varrição seca em áreas internas&lt;/li&gt;
+      &lt;li&gt;equipamentos: descontaminação prévia obrigatória para manutenção&lt;/li&gt;
+      &lt;li&gt;lavanderia: barreira física separando área suja da área limpa&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>336</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NR 33</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Espaço Confinado&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;não projetado para ocupação humana contínua&lt;/li&gt;
+      &lt;li&gt;meios limitados de entrada e saída&lt;/li&gt;
+      &lt;li&gt;atmosfera perigosa ou risco de engolfamento/afogamento&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Responsabilidades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Organização
+        &lt;ul&gt;
+          &lt;li&gt;indicar Responsável Técnico (RT) formalmente&lt;/li&gt;
+          &lt;li&gt;garantir sinalização, bloqueio e equipamentos&lt;/li&gt;
+          &lt;li&gt;assegurar serviços de emergência e salvamento&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Responsável Técnico
+        &lt;ul&gt;
+          &lt;li&gt;elaborar cadastro e procedimentos de segurança&lt;/li&gt;
+          &lt;li&gt;adaptar modelo de PET e plano de resgate&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Supervisor de Entrada
+        &lt;ul&gt;
+          &lt;li&gt;emitir PET antes das atividades&lt;/li&gt;
+          &lt;li&gt;executar testes e conferir equipamentos&lt;/li&gt;
+          &lt;li&gt;assegurar vigia operante&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Vigia
+        &lt;ul&gt;
+          &lt;li&gt;permanecer fora do espaço, junto à entrada&lt;/li&gt;
+          &lt;li&gt;manter contagem de trabalhadores autorizados&lt;/li&gt;
+          &lt;li&gt;ordenar abandono em caso de perigo ou alarme&lt;/li&gt;
+          &lt;li&gt;proibido realizar outras tarefas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Trabalhadores Autorizados
+        &lt;ul&gt;
+          &lt;li&gt;cumprir procedimentos da PET&lt;/li&gt;
+          &lt;li&gt;usar equipamentos adequados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Medidas de Prevenção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Permissão de Entrada e Trabalho (PET)
+        &lt;ul&gt;
+          &lt;li&gt;validade limitada à jornada (máximo 24h)&lt;/li&gt;
+          &lt;li&gt;arquivamento por 5 (cinco) anos&lt;/li&gt;
+          &lt;li&gt;rastreável e acessível&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Atmosfera
+        &lt;ul&gt;
+          &lt;li&gt;Oxigênio: entre 19,5% e 23,0%&lt;/li&gt;
+          &lt;li&gt;monitoramento contínuo durante a permanência&lt;/li&gt;
+          &lt;li&gt;proibida ventilação com oxigênio puro&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Controle de Energias Perigosas
+        &lt;ul&gt;
+          &lt;li&gt;isolamento, bloqueio e etiquetagem (LOTO)&lt;/li&gt;
+          &lt;li&gt;proibido interromper apenas circuito de controle&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Supervisor de entrada: 40 horas inicial&lt;/li&gt;
+      &lt;li&gt;Vigia e trabalhador autorizado: 16 horas inicial&lt;/li&gt;
+      &lt;li&gt;Equipe de salvamento: 24 ou 32 horas inicial&lt;/li&gt;
+      &lt;li&gt;Reciclagem: periódica (anual ou bianual)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Emergência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Resgate obrigatório&lt;/li&gt;
+      &lt;li&gt;simulado anual de salvamento&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>337</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NR 34</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;implementação obrigatória
+        &lt;ul&gt;
+          &lt;li&gt;designar responsável formal&lt;/li&gt;
+          &lt;li&gt;APR (Análise Preliminar de Risco)&lt;/li&gt;
+          &lt;li&gt;PT (Permissão de Trabalho)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;DDS (Diálogo Diário de Segurança)
+        &lt;ul&gt;
+          &lt;li&gt;realizado antes das atividades operacionais&lt;/li&gt;
+          &lt;li&gt;registro com tema e lista de presença&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;interrupção imediata em caso de perigo ambiental&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação e Treinamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Admissional
+        &lt;ul&gt;
+          &lt;li&gt;mínimo de 6 horas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Periódico
+        &lt;ul&gt;
+          &lt;li&gt;mínimo de 4 horas (anual ou retorno após &amp;gt; 90 dias)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Trabalho a Quente&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Inspeção preliminar
+        &lt;ul&gt;
+          &lt;li&gt;local limpo, seco e isento de combustíveis&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Proteção contra incêndio
+        &lt;ul&gt;
+          &lt;li&gt;instalação de proteção física (calor/fagulhas)&lt;/li&gt;
+          &lt;li&gt;sistema de combate desimpedido e próximo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Observador (Vigilância especial)
+        &lt;ul&gt;
+          &lt;li&gt;permanência até a conclusão do serviço&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Cilindros de gás
+        &lt;ul&gt;
+          &lt;li&gt;posição vertical e devidamente fixados&lt;/li&gt;
+          &lt;li&gt;proibidos em ambientes confinados&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Trabalho em Altura&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Conformidade com NR-35&lt;/li&gt;
+      &lt;li&gt;Condições climáticas
+        &lt;ul&gt;
+          &lt;li&gt;interrupção imediata com ventos &amp;gt; 40 km/h&lt;/li&gt;
+          &lt;li&gt;trabalho assistido entre 40 km/h e 46 km/h (acesso por corda)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Acesso por corda
+        &lt;ul&gt;
+          &lt;li&gt;equipe mínima de 3 pessoas (1 supervisor)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Movimentação de Cargas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Prontuário dos equipamentos
+        &lt;ul&gt;
+          &lt;li&gt;manual em português e registros de inspeção&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Segurança operacional
+        &lt;ul&gt;
+          &lt;li&gt;proibido uso de cabos de fibras naturais&lt;/li&gt;
+          &lt;li&gt;interrupção com iluminação deficiente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Sinalização
+        &lt;ul&gt;
+          &lt;li&gt;orientação obrigatória por sinaleiro identificado&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Ventos (Gruas)
+        &lt;ul&gt;
+          &lt;li&gt;assistido se &amp;gt; 42 km/h; proibido se &amp;gt; 72 km/h&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Processos Específicos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Jateamento e Hidrojateamento
+        &lt;ul&gt;
+          &lt;li&gt;proibido uso de areia/sílica acima do permitido&lt;/li&gt;
+          &lt;li&gt;despressurização fora de uso ou em limpeza&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Pintura
+        &lt;ul&gt;
+          &lt;li&gt;interrupção se concentração &amp;ge; 10% do LIE (Limite de Explosividade)&lt;/li&gt;
+          &lt;li&gt;proibido consumo de alimentos na área&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas Flutuantes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Escala Beaufort
+        &lt;ul&gt;
+          &lt;li&gt;interrupção na Força 3 (12 a 19 km/h)&lt;/li&gt;
+          &lt;li&gt;evacuação na Força 5 (29 a 38 km/h)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Higiene
+        &lt;ul&gt;
+          &lt;li&gt;banheiro a no máximo 50 metros do posto&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Emergência&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;PRE (Plano de Resposta a Emergências)
+        &lt;ul&gt;
+          &lt;li&gt;exercícios simulados anuais&lt;/li&gt;
+          &lt;li&gt;revisão a cada 2 anos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F328" t="n">
+        <v>0</v>
+      </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>338</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>NR 35</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Objetivo e Campo de Aplicação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;requisitos e medidas de prevenção
+        &lt;ul&gt;
+          &lt;li&gt;planejamento, organização e execução&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;aplicação: diferença de nível acima de 2,0 m
+        &lt;ul&gt;
+          &lt;li&gt;onde haja risco de queda&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Responsabilidades&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;da Organização (Empregador)
+        &lt;ul&gt;
+          &lt;li&gt;implementar medidas de prevenção&lt;/li&gt;
+          &lt;li&gt;assegurar Análise de Risco (AR) e Permissão de Trabalho (PT)&lt;/li&gt;
+          &lt;li&gt;autorizar formalmente os trabalhadores&lt;/li&gt;
+          &lt;li&gt;arquivar documentação por no mínimo 5 anos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;do Trabalhador
+        &lt;ul&gt;
+          &lt;li&gt;cumprir normas e procedimentos operacionais&lt;/li&gt;
+          &lt;li&gt;interromper atividades em caso de risco grave e iminente&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação e Autorização&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;treinamento inicial (mínimo 8 horas)
+        &lt;ul&gt;
+          &lt;li&gt;realizado antes de iniciar a atividade&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;treinamento periódico (a cada 2 anos)
+        &lt;ul&gt;
+          &lt;li&gt;carga horária mínima de 8 horas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;aptidão clínica
+        &lt;ul&gt;
+          &lt;li&gt;avaliada conforme a NR-07 (PCMSO)&lt;/li&gt;
+          &lt;li&gt;consignada no Atestado de Saúde Ocupacional (ASO)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Planejamento e Organização&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;evitar o trabalho em altura (meio alternativo)&lt;/li&gt;
+      &lt;li&gt;eliminar o risco de queda&lt;/li&gt;
+      &lt;li&gt;minimizar as consequências da queda&lt;/li&gt;
+    &lt;/ol&gt;
+    &lt;ul&gt;
+      &lt;li&gt;supervisão definida pela Análise de Risco (AR)&lt;/li&gt;
+      &lt;li&gt;Permissão de Trabalho (PT)
+        &lt;ul&gt;
+          &lt;li&gt;obrigatória para atividades não rotineiras&lt;/li&gt;
+          &lt;li&gt;validade limitada à jornada de trabalho&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sistemas de Proteção Contra Quedas (SPQ)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;uso obrigatório se o trabalho não puder ser evitado&lt;/li&gt;
+      &lt;li&gt;prioridade: Proteção Coletiva (SPCQ) sobre Individual (SPIQ)&lt;/li&gt;
+      &lt;li&gt;componentes do SPIQ
+        &lt;ul&gt;
+          &lt;li&gt;sistema de ancoragem&lt;/li&gt;
+          &lt;li&gt;elemento de ligação (talabarte, trava-queda)&lt;/li&gt;
+          &lt;li&gt;cinturão de segurança tipo paraquedista&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;requisitos técnicos
+        &lt;ul&gt;
+          &lt;li&gt;força de impacto máxima transmitida: 6 kN&lt;/li&gt;
+          &lt;li&gt;inspeção periódica obrigatória (mínimo a cada 12 meses)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Escadas (Anexo III)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;escolha por hierarquia
+        &lt;ol&gt;
+          &lt;li&gt;rampa ou escada de uso coletivo&lt;/li&gt;
+          &lt;li&gt;escada de inclinação elevada&lt;/li&gt;
+          &lt;li&gt;escada fixa vertical&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+      &lt;li&gt;requisitos de uso individual
+        &lt;ul&gt;
+          &lt;li&gt;contato de 3 pontos obrigatório na subida/descida&lt;/li&gt;
+          &lt;li&gt;escada de mão: extensão máxima de 7 m&lt;/li&gt;
+          &lt;li&gt;escada autossustentável (abrir): máximo 6 m&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;escada fixa vertical
+        &lt;ul&gt;
+          &lt;li&gt;gaiola protetora acima de 3,5 m&lt;/li&gt;
+          &lt;li&gt;plataforma de descanso a cada 6 m (se altura &amp;gt; 10 m)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Emergência e Salvamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Plano de Resgate obrigatório (integrado ao PGR)&lt;/li&gt;
+      &lt;li&gt;foco: reduzir o tempo de suspensão inerte do trabalhador&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>339</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>NR 36</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Objetivo e Aplicação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;requisitos para avaliação, controle e monitoramento de riscos&lt;/li&gt;
+      &lt;li&gt;aplicável a indústrias de abate e processamento de carnes para consumo humano&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Mobiliário e Postos de Trabalho&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;alternância entre posição sentada e em pé
+        &lt;ul&gt;
+          &lt;li&gt;mínimo de um assento para cada três trabalhadores&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;requisitos das bancadas e mesas
+        &lt;ul&gt;
+          &lt;li&gt;proporcionar boa postura e visualização&lt;/li&gt;
+          &lt;li&gt;ausência de quinas vivas ou rebarbas&lt;/li&gt;
+          &lt;li&gt;apoio para os pés&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;trabalho exclusivamente em pé
+        &lt;ul&gt;
+          &lt;li&gt;assentos para pausas atendendo a 50% do efetivo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Manuseio e Transporte de Produtos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;redução de esforços musculares excessivos
+        &lt;ul&gt;
+          &lt;li&gt;elementos dentro da área de alcance principal&lt;/li&gt;
+          &lt;li&gt;vedado levantamento não eventual com alcance horizontal &gt; 60 cm&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;prevenção de repetitividade e impactos
+        &lt;ul&gt;
+          &lt;li&gt;uso de ajudas mecânicas e sistemas de transporte&lt;/li&gt;
+          &lt;li&gt;evitar contato permanente das mãos com água&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Condições Ambientais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ruído: priorizar eliminação ou redução na fonte&lt;/li&gt;
+      &lt;li&gt;Qualidade do Ar (ambientes climatizados)
+        &lt;ul&gt;
+          &lt;li&gt;concentração de CO2 inferior a 1.000 ppm&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Agentes Químicos (Amônia)
+        &lt;ul&gt;
+          &lt;li&gt;detecção precoce de vazamentos e sistema de alarme&lt;/li&gt;
+          &lt;li&gt;Plano de Resposta a Emergências e simulados anuais&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Agentes Biológicos: medidas de biossegurança e limpeza/desinfecção&lt;/li&gt;
+      &lt;li&gt;Conforto Térmico: sistema de aquecimento das mãos em ambientes frios&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Organização Temporal (Pausas)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ambientes artificialmente frios
+        &lt;ul&gt;
+          &lt;li&gt;1 hora e 40 minutos de trabalho / 20 minutos de repouso&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Processo produtivo (repetitividade/sobrecarga)
+        &lt;ul&gt;
+          &lt;li&gt;até 6h de jornada: 20 min de pausa&lt;/li&gt;
+          &lt;li&gt;até 7h20 de jornada: 45 min de pausa&lt;/li&gt;
+          &lt;li&gt;até 8h48 de jornada: 60 min de pausa&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;pausas computadas como tempo de trabalho efetivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Máquinas, Equipamentos e Ferramentas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;conformidade com a NR-12&lt;/li&gt;
+      &lt;li&gt;parada de emergência por segmentos curtos em esteiras e nórias&lt;/li&gt;
+      &lt;li&gt;Facas: sistema de controle de afiação e reposição constante&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;EPIs e Vestimentas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;fornecimento gratuito e higienização sob responsabilidade da empresa&lt;/li&gt;
+      &lt;li&gt;troca diária das vestimentas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Capacitação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Treinamento inicial: mínimo 4 horas (antes de assumir a função)&lt;/li&gt;
+      &lt;li&gt;Treinamento periódico: mínimo 2 horas (anual)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F330" t="n">
+        <v>0</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>340</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>NR 37</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>&lt;li&gt;segurança operacional
+    &lt;ul&gt;
+      &lt;li&gt;movimentação de cargas
+        &lt;ul&gt;
+          &lt;li&gt;exige sinaleiro e operador capacitado&lt;/li&gt;
+          &lt;li&gt;limites de vento
+            &lt;ul&gt;
+              &lt;li&gt;alarme e interrupção ordinária: 39 a 49 km/h&lt;/li&gt;
+              &lt;li&gt;interrupção total: &gt; 61 km/h&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;radiações ionizantes
+        &lt;ul&gt;
+          &lt;li&gt;Plano de Proteção Radiológica (CNEN)&lt;/li&gt;
+          &lt;li&gt;controle de materiais de ocorrência natural (NORM)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;emergência e incidentes
+    &lt;ul&gt;
+      &lt;li&gt;PRE (Plano de Resposta a Emergências)
+        &lt;ul&gt;
+          &lt;li&gt;equipe de resposta: mínimo 20% do POB&lt;/li&gt;
+          &lt;li&gt;simulados anuais obrigatórios&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;comunicação de incidentes
+        &lt;ul&gt;
+          &lt;li&gt;até o 2º dia útil para inspeção do trabalho&lt;/li&gt;
+          &lt;li&gt;até 72 horas para o sindicato (casos graves/fatais)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F331" t="n">
+        <v>0</v>
+      </c>
+      <c r="G331" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G331"/>
+  <dimension ref="A1:G334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16579,6 +16579,202 @@
         <v>0</v>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>341</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Engenharia de Métodos e Processos</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Fluxograma</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Fluxograma&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representação gráfica de processos&lt;/li&gt;
+      &lt;li&gt;Sequenciamento de etapas e decisões&lt;/li&gt;
+      &lt;li&gt;Tipos principais
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Diagrama de blocos&lt;/strong&gt;
+            &lt;ul&gt;
+              &lt;li&gt;sequência linear e simplificada&lt;/li&gt;
+              &lt;li&gt;utiliza apenas blocos e setas&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Fluxograma de processos simples&lt;/strong&gt;
+            &lt;ul&gt;
+              &lt;li&gt;foco na rotina operacional&lt;/li&gt;
+              &lt;li&gt;utiliza simbologia padrão (início, processo, decisão)&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Fluxograma funcional&lt;/strong&gt;
+            &lt;ul&gt;
+              &lt;li&gt;divide etapas por departamentos ou responsáveis&lt;/li&gt;
+              &lt;li&gt;também chamado de "fluxograma de raias"&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Fluxograma vertical&lt;/strong&gt;
+            &lt;ul&gt;
+              &lt;li&gt;representação em colunas e listas&lt;/li&gt;
+              &lt;li&gt;comum em rotinas administrativas e operacionais&lt;/li&gt;
+              &lt;li&gt;facilita a visualização de transportes, esperas e inspeções&lt;/li&gt;
+            &lt;/ul&gt;
+          &lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F332" t="n">
+        <v>0</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>342</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Histograma</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Objetivos e Diagnóstico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Padrão de variação
+        &lt;ul&gt;
+          &lt;li&gt;revela a forma da distribuição (Normal, Bimodal, Assimétrica ou Chata)&lt;/li&gt;
+          &lt;li&gt;indica a tendência central (média) e a dispersão&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Comparação com padrões
+        &lt;ul&gt;
+          &lt;li&gt;permite sobrepor os Limites de Especificação (LSE e LIE)&lt;/li&gt;
+          &lt;li&gt;identifica se o processo é capaz de atender aos requisitos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Utilidade no Controle da Qualidade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ferramenta essencial para entender a "voz do processo" em um dado período&lt;/li&gt;
+      &lt;li&gt;ajuda a identificar erros de medição ou misturas de populações&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Limitação: Ação Corretiva vs. Monitoramento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Natureza Estática
+        &lt;ul&gt;
+          &lt;li&gt;não apresenta a ordem cronológica dos dados&lt;/li&gt;
+          &lt;li&gt;não diferencia causas comuns de causas especiais de variação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;Inadequação para gatilhos de ação
+        &lt;ul&gt;
+          &lt;li&gt;o histograma não rastreia o momento da ocorrência da falha&lt;/li&gt;
+          &lt;li&gt;não indica se o processo é estatisticamente estável&lt;/li&gt;
+          &lt;li&gt;o Gráfico de Controle é a ferramenta superior para esta finalidade&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F333" t="n">
+        <v>0</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>343</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Diagrama de Causa e Efeito</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Diagrama de Causa e Efeito&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Ferramenta visual de análise de processos&lt;/li&gt;
+          &lt;li&gt;Foca na relação entre um efeito (problema) e suas causas potenciais&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Sinônimos Comuns&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Diagrama de Ishikawa:&lt;/strong&gt; Nome em homenagem ao seu criador&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Diagrama Espinha de Peixe:&lt;/strong&gt; Devido ao formato gráfico&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Método dos 6 Ms (Categorias das Causas)&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Método:&lt;/strong&gt; Procedimentos e técnicas de execução&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Máquina:&lt;/strong&gt; Equipamentos e ferramentas envolvidos&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Material:&lt;/strong&gt; Matéria-prima e insumos&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Medida:&lt;/strong&gt; Dados e métricas de controle&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Meio Ambiente:&lt;/strong&gt; Condições externas e local de trabalho&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Mão de obra:&lt;/strong&gt; Pessoas e competências humanas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F334" t="n">
+        <v>0</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G334"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8863,11 +8863,35 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>&lt;ol&gt;
-	&lt;li&gt;Pré-Desenvolvimento &lt;ol&gt; &lt;li&gt;Planejamento do Projeto &lt;ul&gt; &lt;li&gt;são realizadas &lt;ul&gt; &lt;li&gt;brainstorming&lt;/li&gt; &lt;li&gt;visitas a feiras técnicas&lt;/li&gt; &lt;li&gt;análise de produtos da concorrência&lt;/li&gt; &lt;li&gt;pesquisa de mercado&lt;/li&gt; &lt;li&gt;elaboração das especificações do projeto&lt;/li&gt; &lt;li&gt;dentre outros&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
-	&lt;li&gt;Desenvolvimento &lt;ol&gt; &lt;li&gt;Projeto Informacional&lt;/li&gt; &lt;li&gt;Projeto Conceitual&lt;/li&gt; &lt;li&gt;Projeto Detalhado&lt;/li&gt; &lt;li&gt;Preparação da Produção&lt;/li&gt; &lt;li&gt;Lançamento do Produto&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
-	&lt;li&gt;Pós-Desenvolvimento &lt;ol&gt; &lt;li&gt;Acompanhar Produto/Processo&lt;/li&gt; &lt;li&gt;Descontinuar Produto&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
-&lt;/ol&gt;</t>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;I. PRÉ-DESENVOLVIMENTO&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Planejamento Estratégico (Portfólio)&lt;/li&gt;
+      &lt;li&gt;Planejamento do Projeto (Briefing e Equipe)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;II. DESENVOLVIMENTO (Foco Técnico)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Informacional:&lt;/strong&gt; Tradução de requisitos em especificações.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Conceitual:&lt;/strong&gt; Geração de &lt;u&gt;Princípios de Solução&lt;/u&gt; (Abstração).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Detalhado - Configuração:&lt;/strong&gt; Definição de &lt;u&gt;Arranjo Físico&lt;/u&gt; e Arquitetura.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Detalhado - Precisão:&lt;/strong&gt; Definição de &lt;u&gt;Tolerâncias&lt;/u&gt; e Ajustes (Paramétrico).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Preparação da Produção:&lt;/strong&gt; Ferramentais e Lote Piloto.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Lançamento:&lt;/strong&gt; Vendas e Suporte.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;III. PÓS-DESENVOLVIMENTO&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Acompanhamento (Pós-venda) e Descontinuidade.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;SISTEMA DE GATES (Sinalização)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;span style="color:red;"&gt;●&lt;/span&gt; &lt;strong&gt;Vermelho (Gate):&lt;/strong&gt; Decisão Gerencial/Negócio (Go / No-Go).&lt;/li&gt;
+      &lt;li&gt;&lt;span style="color:blue;"&gt;●&lt;/span&gt; &lt;strong&gt;Azul (Revisão):&lt;/strong&gt; Verificação Técnica/Qualidade.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -11187,8 +11211,10 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
-        <v>284</v>
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -11197,46 +11223,39 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Tipos de Benchmarking</t>
+          <t>Benchmarking</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Interno&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;comparação entre unidades da mesma empresa&lt;/li&gt;
-      &lt;li&gt;foco em disseminar internamente o que já funciona&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Competitivo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;alvo: concorrentes diretos&lt;/li&gt;
-      &lt;li&gt;foco em &lt;strong&gt;desempenho&lt;/strong&gt; (indicadores/números)&lt;/li&gt;
-      &lt;li&gt;alta barreira de acesso e riscos legais&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Funcional&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;alvo: empresas de setores diferentes com funções similares&lt;/li&gt;
-      &lt;li&gt;foco em &lt;strong&gt;práticas&lt;/strong&gt; (processos) e não apenas resultados
-        &lt;ul&gt;
-          &lt;li&gt;&lt;strong&gt;escolha dos parceiros&lt;/strong&gt; (colaboração)&lt;/li&gt;
-          &lt;li&gt;&lt;strong&gt;estudo detalhado do próprio processo&lt;/strong&gt;&lt;/li&gt;
-          &lt;li&gt;&lt;strong&gt;preparo da visita&lt;/strong&gt; técnica&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Genérico&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;processos idênticos em áreas totalmente distintas&lt;/li&gt;
-      &lt;li&gt;busca por inovação disruptiva&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Benchmarking&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Processo de aprendizado e adaptação de melhores práticas de mercado.&lt;/li&gt;
+      &lt;li&gt;Não é uma simples "cópia", mas uma análise de desempenho e adaptação à realidade local.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Categorias Principais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Interno:&lt;/strong&gt; Comparação entre unidades da mesma organização.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Competitivo:&lt;/strong&gt; Foco em concorrentes diretos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Funcional/Genérico:&lt;/strong&gt; Foco em processos excelentes, independente do setor de atuação.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Vantagens do Benchmarking Multissetorial&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Maior facilidade na troca de informações (não há conflito de interesses).&lt;/li&gt;
+      &lt;li&gt;Possibilidade de saltos de produtividade ao adotar soluções de indústrias mais avançadas em certas áreas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para a Prova:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Palavras como "exclusivamente", "fundamentalmente" ou "apenas no mesmo setor" costumam tornar itens de benchmarking &lt;strong&gt;errados&lt;/strong&gt;.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -15075,7 +15094,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Engenharia de Produto</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -16775,6 +16794,738 @@
         <v>0</v>
       </c>
     </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>344</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Sustentabilidade</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ações de Gestão Ambiental Organizacional</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Resíduos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Segregação na fonte geradora&lt;/li&gt;
+      &lt;li&gt;Implementação de logística reversa&lt;/li&gt;
+      &lt;li&gt;Destinação para co-processamento ou reciclagem&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Eficiência Energética e Hídrica&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Sistemas de reuso de água industrial&lt;/li&gt;
+      &lt;li&gt;Uso de fontes de energia renováveis (solar, eólica)&lt;/li&gt;
+      &lt;li&gt;Substituição de equipamentos obsoletos por modelos de alta eficiência&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estratégias de Operação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Aplicação de Produção Mais Limpa (P+L)&lt;/li&gt;
+      &lt;li&gt;Análise do Ciclo de Vida do produto (ACV)&lt;/li&gt;
+      &lt;li&gt;Controle de emissões atmosféricas e efluentes&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Políticas Organizacionais&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Treinamento e capacitação em educação ambiental&lt;/li&gt;
+      &lt;li&gt;Gestão de transporte coletivo para redução de emissões&lt;/li&gt;
+      &lt;li&gt;Seleção de fornecedores com critérios de sustentabilidade (Compras Verdes)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Compliance e Melhoria Contínua&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Auditorias internas de conformidade legal&lt;/li&gt;
+      &lt;li&gt;Monitoramento de indicadores de desempenho ambiental (KPIs)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>345</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>principais termos técnicos de tipos e mudanças nas estruturas organizacionais</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Processos de Reestruturação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; Redução do quadro de funcionários para corte de custos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Rightsizing:&lt;/strong&gt; Redesign estratégico para o tamanho ideal da operação.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Delayering (Achatamento):&lt;/strong&gt; Eliminação de níveis hierárquicos intermediários.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dinâmicas de Autoridade&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Span of Control (Amplitude):&lt;/strong&gt; Quantidade de pessoas sob o comando de um líder.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Unity of Command (Unidade de Comando):&lt;/strong&gt; Princípio de ter apenas um superior direto.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Delegação de autoridade para a base (ligado à descentralização).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Modelos de Estrutura&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Functional (Funcional):&lt;/strong&gt; Foco na especialização técnica de cada setor.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Divisional (Divisional):&lt;/strong&gt; Foco em resultados por unidades (produto/mercado).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Estrutura híbrida com reporte duplo (funcional e projeto).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Pouca hierarquia e grande autonomia dos colaboradores.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>346</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Mentalidade de Risco e Prevenção</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F337" t="n">
+        <v>0</v>
+      </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>347</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>ARL (Average Run Length)</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Curva OC (Operating Characteristic)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Gráfico que relaciona a magnitude de um desvio (k) com a probabilidade de não detectá-lo (&amp;beta;).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Leitura:&lt;/strong&gt; Se o processo se desloca em 1&amp;sigma; (k=1) e o gráfico aponta 0,7 no eixo Y, isso significa que há 70% de chance de NÃO perceber o erro na primeira amostra.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;ARL (Average Run Length)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Conceito:&lt;/strong&gt; Número médio de amostras até o ponto sair dos limites de controle.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula Vital:&lt;/strong&gt; $ARL = \frac{1}{1 - \beta}$&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplo da Questão:&lt;/strong&gt; Se &amp;beta; = 0,7, então $ARL = \frac{1}{0,3} = 3,33$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/Cebraspe:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se o ARL for alto, o gráfico é ruim para detectar aquele desvio específico.&lt;/li&gt;
+      &lt;li&gt;Sempre verifique se a curva no gráfico representa &amp;beta; (prob. de aceitar o erro) ou $1-\beta$ (poder de detecção). A curva OC padrão sempre plota o &amp;beta; (começa em 1 no k=0 e cai conforme k aumenta).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>348</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Gestão da tecnologia</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Gestão da Tecnologia&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Aplicação prática de métodos científicos para resolução de problemas.&lt;/li&gt;
+      &lt;li&gt;Integração entre ciência, engenharia e administração.&lt;/li&gt;
+      &lt;li&gt;Foco na criação de valor e alcance de metas estratégicas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Principais Objetivos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Geração de &lt;strong&gt;Vantagem Competitiva&lt;/strong&gt; sustentável.&lt;/li&gt;
+      &lt;li&gt;Otimização do Ciclo de Vida da Tecnologia (Curva S).&lt;/li&gt;
+      &lt;li&gt;Redução de riscos associados à adoção de novas tecnologias.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Tipos de Inovação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Incremental:&lt;/strong&gt; Melhorias contínuas em processos existentes.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Radical:&lt;/strong&gt; Ruptura com o modelo atual e criação de novos padrões.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Transferência Tecnológica:&lt;/strong&gt; Aplicação comercial de pesquisas científicas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/Cebraspe:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A GT não é um fim em si mesma, mas um &lt;strong&gt;meio&lt;/strong&gt; para a organização ser mais eficiente e competitiva.&lt;/li&gt;
+      &lt;li&gt;Fique atento ao termo &lt;i&gt;"Método Científico"&lt;/i&gt;: se a questão associar gestão tecnológica a empirismo puro ou sorte, geralmente estará incorreta.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F339" t="n">
+        <v>0</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>349</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>QFD - Modelo de 4 Matrizes</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ferramenta para traduzir a "Voz do Cliente" em especificações técnicas.&lt;/li&gt;
+      &lt;li&gt;Reduz mudanças de projeto de última hora e aumenta a satisfação.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;O Modelo de 4 Matrizes (Sequência Lógica)&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;&lt;strong&gt;Matriz 1: Planejamento do Produto (House of Quality)&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Foco: Requisitos do Cliente vs. Requisitos de Projeto (Engenharia).&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Matriz 2: Desdobramento de Partes&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Foco: Requisitos de Projeto vs. Características dos Componentes.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Matriz 3: Planejamento do Processo&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Foco: Características dos Componentes vs. Operações de Produção.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Matriz 4: Planejamento da Produção&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Foco: Operações de Produção vs. Controles de Qualidade/Instruções.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Componentes da Matriz 1 (HOQ)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;O quê:&lt;/strong&gt; Necessidades do cliente.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Como:&lt;/strong&gt; Atributos técnicos do produto.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Matriz de Relações:&lt;/strong&gt; Impacto do "Como" no "O quê".&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Telhado (Roof):&lt;/strong&gt; Correlação entre os requisitos técnicos (conflitos ou sinergias).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>350</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Logística</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Sistemas de Codificação de Materiais</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Numeração Arbitrária (Sequencial)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Atribuição de números por ordem de entrada (1, 2, 3...).&lt;/li&gt;
+      &lt;li&gt;Não possui relação com as características físicas do item.&lt;/li&gt;
+      &lt;li&gt;Dificulta a comunicação técnica e o agrupamento de materiais similares.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Codificação por Grupos e Classes (Sistema Decimal)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O código é estruturado de forma lógica e hierárquica.&lt;/li&gt;
+      &lt;li&gt;Cada bloco de números representa uma categoria (ex: Grupo -&gt; Classe -&gt; Item).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Facilita a comunicação interna&lt;/strong&gt;, pois o código "fala" o que o material é.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Concursos:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se a questão associar &lt;u&gt;Arbitrário&lt;/u&gt; a &lt;u&gt;Facilidade de Comunicação&lt;/u&gt; ou &lt;u&gt;Lógica de Classes&lt;/u&gt;, o item estará &lt;strong&gt;ERRADO&lt;/strong&gt;.&lt;/li&gt;
+      &lt;li&gt;O sistema arbitrário é simples de implementar, mas pobre em informação.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F341" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>351</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BSC (Perspectivas)</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
+      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
+      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F342" t="n">
+        <v>0</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>352</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Gestão de Investimentos e Risco</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>modelo CAPM (Capital Asset Pricing Model)</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Modelo que determina o retorno esperado de um investimento com base no risco sistêmico.&lt;/li&gt;
+      &lt;li&gt;Fórmula: $E[R] = R_f + \beta \cdot (R_m - R_f)$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Cálculo para Carteiras (Portfólio)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O Beta da carteira é a média ponderada dos Betas individuais.&lt;/li&gt;
+      &lt;li&gt;$\beta_{carteira} = (\% \text{Ativo A} \cdot \beta_A) + (\% \text{Ativo B} \cdot \beta_B)$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Premissas Importantes&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Taxa Livre de Risco ($R_f$):&lt;/strong&gt; Retorno de ativos sem risco de crédito.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Beta ($\beta$):&lt;/strong&gt; Se &gt; 1, o ativo é mais volátil que o mercado; se &lt; 1, é mais defensivo.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Prêmio de Risco:&lt;/strong&gt; A diferença $(R_m - R_f)$ representa a compensação por correr risco de mercado.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Concursos:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Cuidado para não confundir "Retorno de Mercado" ($R_m$) com "Prêmio de Risco" ($R_m - R_f$). A questão já deu a diferença (o prêmio) de 10%, facilitando o cálculo.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>353</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Gestão da Manutenção e Confiabilidade</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Relação entre MTTF e R(t)</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;MTTF de Sistemas (Tempo Esperado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição Matemática:&lt;/strong&gt; O MTTF é a área sob a curva de confiabilidade $R(t)$.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Sistema em Série:&lt;/strong&gt; $MTTF_{serie} = \frac{1}{\sum \lambda_i}$ (Soma as taxas de falha).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Sistema em Paralelo (Ativos Idênticos):&lt;/strong&gt; 
+        &lt;ul&gt;
+          &lt;li&gt;Fórmula: $MTTF = \frac{1}{\lambda} \cdot (1 + \frac{1}{2} + \frac{1}{3} + ... + \frac{1}{n})$.&lt;/li&gt;
+          &lt;li&gt;Exemplo n=3: $\frac{1}{\lambda} \cdot \frac{11}{6}$.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica de Prova:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se a questão der a função $F(t) = 1 - e^{-t}$ e pedir o tempo esperado de um sistema &lt;strong&gt;paralelo&lt;/strong&gt; de 3 unidades, a resposta sempre será $11/6$ anos (se $\lambda = 1$).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F344" t="n">
+        <v>0</v>
+      </c>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>354</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Verbos</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Presente Histórico e Paralelismo Temporal</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Pretérito Perfeito do Subjuntivo (Tenha Prevalecido):&lt;/strong&gt; Expressa um fato passado concluído em relação a um momento presente.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Presente do Indicativo (É):&lt;/strong&gt; Utilizado aqui para expressar uma definição conceitual e permanente (Presente Atemporal).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Desconstruindo a Pegadinha&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Presente Histórico:&lt;/strong&gt; &lt;u&gt;Não ocorre&lt;/u&gt; neste texto. Ele serve para "trazer o passado para o presente" em narrações, o que não é o caso de um manual técnico.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Paralelismo Temporal:&lt;/strong&gt; Não exige que todos os verbos estejam no mesmo tempo, mas sim que a relação entre eles seja lógica. No texto, a relação é: "Embora algo tenha ocorrido (passado), o fato é (presente)...".&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica de Ouro:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Sempre que a banca afirmar que um verbo é "Presente Histórico", verifique se o texto está contando uma história antiga. Se for um texto dissertativo/informativo como este, quase nunca será presente histórico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F345" t="n">
+        <v>0</v>
+      </c>
+      <c r="G345" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Compreensão e Interpretação de Textos</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Iterpretação x Inferência textual</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Compreensão (Literal)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Comandos:&lt;/strong&gt; "Segundo o texto...", "De acordo com o texto...", "O autor afirma que...", "Na linha X, o texto diz...".&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Informação explícita. A resposta está &lt;u&gt;escrita&lt;/u&gt; (mesmo que com outras palavras).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Inferência / Depreensão (Lógica)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Comandos:&lt;/strong&gt; "Infere-se...", "Depreende-se...", "Conclui-se...", "O texto permite concluir que...".&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Informação implícita. É o que &lt;u&gt;nasce&lt;/u&gt; do papel através da lógica do autor.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Extrapolação (ERRO de Interpretação)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Identificação:&lt;/strong&gt; Itens que inserem causas, consequências ou opiniões que &lt;u&gt;não estão&lt;/u&gt; no texto.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Alerta:&lt;/strong&gt; Cuidado com o "bom senso" ou conhecimentos externos que o autor não mencionou.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;O "Pulo do Gato":&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se o comando é &lt;i&gt;"Segundo o texto"&lt;/i&gt; e a alternativa exige uma conclusão lógica (inferência), o item costuma estar &lt;strong&gt;Errado&lt;/strong&gt; por não ser literal.&lt;/li&gt;
+      &lt;li&gt;Se o comando é &lt;i&gt;"Infere-se"&lt;/i&gt; e a alternativa traz um fato externo, o item é &lt;strong&gt;Extrapolação&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F346" t="n">
+        <v>0</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>356</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Dados</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>DAMA-DMBOK</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Governança de Dados (DAMA-DMBOK)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Autoridade, Planejamento e Controle sobre os ativos de dados.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Responsabilidades:&lt;/strong&gt; Definir políticas, normas, métricas e fiscalizar a conformidade.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Não faz:&lt;/strong&gt; Não realiza a execução técnica direta das atividades operacionais.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gerenciamento de Dados&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Operacionalização e &lt;u&gt;execução direta&lt;/u&gt; das tarefas.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Responsabilidades:&lt;/strong&gt; Implementar as políticas de qualidade, segurança e arquitetura no ambiente técnico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica de Ouro para a Prova:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Governança:&lt;/strong&gt; "Garante" que as coisas sejam feitas conforme a lei (Fiscal).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Gerenciamento:&lt;/strong&gt; "Faz" as coisas acontecerem (Executor).&lt;/li&gt;
+      &lt;li&gt;Leu "Execução Direta" vinculada à Governança? O item está &lt;strong&gt;ERRADO&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17526,6 +17526,182 @@
         <v>0</v>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>357</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Português</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Mecanismos de Coesão Textual</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Paralelismo</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Paralelismo Sintático&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Substantivo com Substantivo:&lt;/strong&gt; "Temos fé &lt;u&gt;na&lt;/u&gt; vitória e &lt;u&gt;na&lt;/u&gt; aprovação."&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Verbo com Verbo:&lt;/strong&gt; "É necessário &lt;u&gt;estudar&lt;/u&gt; teoria e &lt;u&gt;praticar&lt;/u&gt; exercícios."&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Omissão de preposição no segundo termo quebra o paralelismo (Ex: "Gosto de café e chocolate" está OK, mas "Gosto &lt;u&gt;do&lt;/u&gt; café e chocolate" é erro, deve ser "&lt;u&gt;do&lt;/u&gt; café e &lt;u&gt;do&lt;/u&gt; chocolate").&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Paralelismo Semântico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Manutenção da lógica e do campo de ideias.&lt;/li&gt;
+      &lt;li&gt;Evita o "efeito lista de supermercado" com itens que não se conversam.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Impacto nas Reescritas (Cebraspe)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Muitas reescritas que parecem corretas falham porque trocam um substantivo simples por uma oração (Ex: "...buscando &lt;u&gt;agilidade&lt;/u&gt; e &lt;u&gt;que os processos sejam rápidos&lt;/u&gt;"). Isso quebra a simetria.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Taxas</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Inflação Acumulada</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
+      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
+      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F349" t="n">
+        <v>0</v>
+      </c>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Proteção contra vírus</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Aplicativos Antivírus</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;1ª Geração (Assinatura / Escaneamento Simples)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em identificar o que já é conhecido.&lt;/li&gt;
+      &lt;li&gt;Técnica: Comparação de &lt;u&gt;assinaturas&lt;/u&gt; (strings de bits específicas).&lt;/li&gt;
+      &lt;li&gt;Limitação: Inútil contra vírus novos ou modificados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;2ª Geração (Proativa / Escaneamento Avançado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em prever ameaças novas (Zero-Day).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Técnica Principal: Heurística&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;Não busca o código exato, mas &lt;u&gt;padrões e regras de similaridade&lt;/u&gt;.&lt;/li&gt;
+          &lt;li&gt;Identifica variações de famílias de vírus conhecidos.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Outras Técnicas desta Geração:&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Análise Comportamental:&lt;/strong&gt; Bloqueia ações suspeitas durante a execução.&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Sandboxing:&lt;/strong&gt; Emulação em ambiente isolado.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diferença de Ouro para a Prova:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se a questão diz que o antivírus detecta vírus &lt;u&gt;por semelhança&lt;/u&gt; ou &lt;u&gt;por padrões de código&lt;/u&gt;, ela está falando de &lt;strong&gt;HEURÍSTICA&lt;/strong&gt; (2ª Geração).&lt;/li&gt;
+      &lt;li&gt;Se diz que detecta pela &lt;u&gt;ação&lt;/u&gt; do arquivo no sistema, está falando de &lt;strong&gt;COMPORTAMENTO&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
         <v>1</v>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142" t="n">
         <v>1</v>
@@ -5886,7 +5886,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
         <v>1</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
         <v>1</v>
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -7545,7 +7545,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -7576,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
@@ -7731,7 +7731,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -8588,7 +8588,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219">
@@ -8625,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
@@ -8901,7 +8901,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227">
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229">
@@ -9330,7 +9330,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="239">
@@ -10184,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -16972,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229">
@@ -16972,7 +16972,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="336">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15142,8 +15142,10 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
-        <v>360</v>
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -15175,7 +15177,12 @@
     &lt;ul&gt;
       &lt;li&gt;&lt;strong&gt;Entrada (Input):&lt;/strong&gt; Coleta de dados brutos de dentro ou fora da organização.&lt;/li&gt;
       &lt;li&gt;&lt;strong&gt;Processamento:&lt;/strong&gt; Conversão dos dados em forma significativa.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Saída (Output):&lt;/strong&gt; Transferência da informação processada às pessoas ou atividades.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Saída (Output / &lt;u&gt;Produto Informacional&lt;/u&gt;):&lt;/strong&gt; 
+        &lt;ul&gt;
+          &lt;li&gt;Transferência da informação processada às pessoas ou atividades.&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Relatórios, Dashboards, Telas de consulta, Notas Fiscais.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
       &lt;li&gt;&lt;strong&gt;Feedback:&lt;/strong&gt; Saída que retorna a membros da organização para ajudar a avaliar ou corrigir a etapa de entrada.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
@@ -15242,8 +15249,9 @@
   &lt;/li&gt;
   &lt;li&gt;&lt;strong&gt;Levantamento de Requisitos&lt;/strong&gt;
     &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Processo:&lt;/strong&gt; Identificação das necessidades de informação e funcionalidades junto aos usuários e stakeholders.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Processo:&lt;/strong&gt; Identificação das necessidades de informação e funcionalidades junto aos usuários e stakeholders (público interno e externo).&lt;/li&gt;
       &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Definir o "quê" o sistema deve fazer antes de decidir "como" ele será construído tecnicamente.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Orientação por Necessidade:&lt;/strong&gt; Entender os requisitos é o passo fundamental para desenvolver &lt;strong&gt;Produtos Informacionais&lt;/strong&gt; (saídas do sistema) orientados especificamente para cada grupo e necessidade.&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -15570,6 +15578,201 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>368</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>axonomia de Software (Sistema vs. Aplicativo)</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Atua como intermediário entre o hardware e o usuário/aplicativo. Coordena as operações básicas do computador.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; &lt;u&gt;Sistemas Operacionais&lt;/u&gt; (Windows, Linux), Drivers de dispositivo e utilitários de sistema (desfragmentadores, compiladores).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Software Aplicativo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Programas projetados para permitir que o usuário realize tarefas específicas, profissionais ou pessoais.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Planilhas eletrônicas, processadores de texto, navegadores, ERPs, CRMs e bancos de dados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>369</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Aquisição de Software (Prateleira vs. Customizado)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Software de Prateleira (Off-the-shelf)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Soluções genéricas e padronizadas produzidas para o mercado de massa.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Uso:&lt;/strong&gt; Atende a necessidades comuns a muitas empresas (contabilidade padrão, e-mail, automação de escritório).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Vantagens:&lt;/strong&gt; Menor custo inicial, atualizações frequentes pelo fabricante e confiabilidade testada por muitos usuários.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Software Personalizado ou Customizado (Custom Software)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Desenvolvido sob medida (in-house ou por terceiros) para uma organização.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Uso:&lt;/strong&gt; Atende a uma &lt;strong&gt;necessidade empresarial específica e única&lt;/strong&gt; que não é suprida por soluções padrão.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Nuance "Proprietário":&lt;/strong&gt; Em provas de gestão, o termo pode ser usado para indicar que o software é exclusivo e de propriedade da empresa que o encomendou (solução dedicada).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Vantagens:&lt;/strong&gt; Alinhamento total aos processos exclusivos; pode gerar vantagem competitiva sustentável.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>370</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Indústria 4.0 (Conceitos e Paradigmas)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Origem e Definição&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Cunhagem:&lt;/strong&gt; Termo surgido em 2011 na Feira de Hannover (Alemanha).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Conceito Central:&lt;/strong&gt; Fábricas Inteligentes (*Smart Factories*) baseadas na fusão dos mundos físico e virtual.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Sistemas Ciber-Físicos (CPS)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Integração entre computação, redes e processos físicos. Sensores e softwares monitoram e controlam os componentes físicos em tempo real.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Características de Valor&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Descentralização:&lt;/strong&gt; Capacidade dos sistemas tomarem decisões de forma autônoma.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Interoperabilidade:&lt;/strong&gt; Comunicação global entre máquinas, dispositivos, sensores e pessoas.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Virtualização:&lt;/strong&gt; Criação de uma cópia virtual da fábrica (ligado ao conceito de Gêmeos Digitais).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Orientação a Serviços:&lt;/strong&gt; Oferta das funcionalidades do SI via computação em nuvem.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>371</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Tecnologias Habilitadoras (Os 9 Pilares da Indústria 4.0)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Pilares de Processamento e Dados&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;1. Big Data e Analytics:&lt;/strong&gt; Coleta e avaliação massiva de dados para identificar falhas e otimizar a produção em tempo real.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;2. Computação na Nuvem (Cloud Computing):&lt;/strong&gt; Infraestrutura que permite o acesso e o compartilhamento de dados entre diferentes locais e sistemas.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;3. Cibersegurança (Cybersecurity):&lt;/strong&gt; Proteção de sistemas industriais e linhas de produção contra ameaças e invasões digitais.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Pilares de Integração e Simulação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;4. Integração de Sistemas (Vertical e Horizontal):&lt;/strong&gt; Conexão de todos os elos da cadeia de valor (fornecedores aos clientes) e dos níveis da fábrica (chão de fábrica à gestão).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;5. Simulação (Digital Twins):&lt;/strong&gt; Uso de modelos virtuais para espelhar o mundo físico em simulações 3D, permitindo testes antes da execução real.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;6. Internet das Coisas (IoT):&lt;/strong&gt; Rede de objetos físicos com sensores e conectividade para trocar dados entre si e com o centro de controle.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Pilares de Execução Física&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;7. Robôs Autônomos:&lt;/strong&gt; Máquinas que interagem entre si, trabalham lado a lado com humanos e aprendem com novas tarefas.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;8. Manufatura Aditiva:&lt;/strong&gt; Produção de peças via impressão 3D, reduzindo estoques de peças complexas e facilitando prototipagem rápida.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;9. Realidade Aumentada (AR):&lt;/strong&gt; Sistemas que sobrepõem informações digitais ao campo de visão real (ex: instruções de manutenção projetadas em uma peça).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>0</v>
+      </c>
+      <c r="G286" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -1199,12 +1199,14 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>37</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1234,12 +1236,14 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>40</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1253,7 +1257,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>etapas do FMEA</t>
+          <t>etapas do FMEA (Análise de Modo e Efeitos de Falha)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1274,7 +1278,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1316,8 +1320,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>42</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1331,7 +1337,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3 fases da FTA</t>
+          <t>3 fases da FTA (Fault Tree Analysis) - Análise da Árvore de Falhas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1347,7 +1353,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -3267,31 +3273,15 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
-	&lt;li&gt;Socialização
-&lt;ul&gt;
-	&lt;li&gt;tácito → tácito&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-	&lt;li&gt;Externalização
-&lt;ul&gt;
-	&lt;li&gt;tácito → explícito&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-	&lt;li&gt;Combinação
-&lt;ul&gt;
-	&lt;li&gt;explícito → explícito
-&lt;ul&gt;
-	&lt;li&gt;explícito → tácito&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-&lt;/ul&gt;
-&lt;/li&gt;
-	&lt;li&gt;Internalização&lt;/li&gt;
+	&lt;li&gt;Socialização &lt;ul&gt; &lt;li&gt;tácito → tácito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Externalização &lt;ul&gt; &lt;li&gt;tácito → explícito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Combinação &lt;ul&gt; &lt;li&gt;explícito → explícito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Internalização &lt;ul&gt; &lt;li&gt;explícito → tácito&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
 &lt;/ol&gt;</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -8334,8 +8324,10 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
-        <v>276</v>
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -8354,7 +8346,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
+          <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;valores&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
@@ -8363,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G286"/>
+  <dimension ref="A1:G285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2639,8 +2639,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>96</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2654,16 +2656,33 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ordem de precedência da negação e dos conectivos</t>
+          <t>Ordem de Precedência e Pontuação Lógica</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1. Realizar a negação abrangendo o menor enunciado possível (~);
-2. Conjunção (∧) e disjunção inclusiva (∨), na ordem em que aparecerem;
-3. Disjunção exclusiva (∨);
-4. Condicional (→);
-5. Bicondicional (&lt;-&gt;).</t>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Regra Suprema: A Pontuação (O "Parêntese" Oculto)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Vírgulas, pontos e vírgulas ou pontos finais funcionam como parênteses. Eles definem o escopo dos blocos antes da hierarquia técnica.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplo (ID 3198):&lt;/strong&gt; "Estou doente &lt;u&gt;e ,&lt;/u&gt; se o médico permite então viajo" $\rightarrow d \wedge (m \rightarrow v)$. A vírgula isolou a condicional em um bloco.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Ordem de Precedência da Negação e dos Conectivos&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;&lt;strong&gt;Realizar a negação&lt;/strong&gt; abrangendo o menor enunciado possível ($\sim$);&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Conjunção ($\wedge$) e disjunção inclusiva ($\vee$)&lt;/strong&gt;, na ordem em que aparecerem;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Disjunção exclusiva ($\underline{\vee}$)&lt;/strong&gt;;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Condicional ($\rightarrow$)&lt;/strong&gt;;&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Bicondicional ($\leftrightarrow$)&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Provas (Sintaxe vs. Semântica):&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Sempre olhe a vírgula primeiro. Se houver uma vírgula após um conectivo, ela "empurra" o restante da proposição para dentro de um parêntese invisível.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -4778,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
@@ -4809,7 +4828,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -6983,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -7014,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
@@ -7048,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -7079,12 +7098,14 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
-        <v>255</v>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -7104,9 +7125,9 @@
       <c r="E173" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;𝑽𝑷𝑳 &gt; 0 -&gt; 𝑽𝑷𝑳 &gt; TMA&lt;/li&gt;
-	&lt;li&gt;Se 𝑽𝑷𝑳 &lt; 0 -&gt; 𝑇𝐼𝑅 &lt; 𝑇𝑀A&lt;/li&gt;
-	&lt;li&gt;Se 𝑽𝑷𝑳 = 0 -&gt; 𝑇𝐼𝑅 = 𝑇𝑀A&lt;/li&gt;
+    &lt;li&gt;$$\text{VPL} &gt; 0 \implies \text{TIR} &gt; \text{TMA}$$&lt;/li&gt;
+    &lt;li&gt;$$\text{VPL} &lt; 0 \implies \text{TIR} &lt; \text{TMA}$$&lt;/li&gt;
+    &lt;li&gt;$$\text{VPL} = 0 \implies \text{TIR} = \text{TMA}$$&lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -7114,7 +7135,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
@@ -7490,8 +7511,10 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
-        <v>262</v>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -7533,10 +7556,10 @@
   &lt;/li&gt;
   &lt;li&gt;Propriedade da Identidade
     &lt;ul&gt;
-      &lt;li&gt;p ∧ t ≡ p&lt;/li&gt;
-      &lt;li&gt;p ∧ c ≡ c&lt;/li&gt;
-      &lt;li&gt;p ∨ t ≡ t&lt;/li&gt;
-      &lt;li&gt;p ∨ c ≡ p&lt;/li&gt;
+      &lt;li&gt;p ∧ V ≡ p&lt;/li&gt;
+      &lt;li&gt;p ∧ F ≡ F&lt;/li&gt;
+      &lt;li&gt;p ∨ V ≡ V&lt;/li&gt;
+      &lt;li&gt;p ∨ F ≡ p&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;Propriedade da Absorção
@@ -8102,7 +8125,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189">
@@ -8133,7 +8156,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190">
@@ -8163,15 +8186,17 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
-        <v>273</v>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -8190,11 +8215,11 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Taxa de Rentabilidade = 𝑉𝑃𝐿/Inv. Inicial</t>
+          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -8202,55 +8227,24 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Índice de Lucratividade </t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
-        <is>
-          <t>𝐼𝐿 = 1 + 𝑉𝑃𝐿/Inv. Inicial</t>
-        </is>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>275</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>Processo de Gestão de Risco</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -8316,68 +8310,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;valores&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="194">
+      <c r="A194" t="n">
         <v>277</v>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -8430,6 +8424,40 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>278</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
@@ -8439,7 +8467,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -8448,49 +8476,15 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>teoria da organização e da gestão da informação</t>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
-	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>279</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Gestão da Inovação</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -8559,33 +8553,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
+    <row r="197">
+      <c r="A197" t="n">
         <v>281</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -8599,6 +8593,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>282</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F198" t="n">
         <v>0</v>
       </c>
@@ -8608,7 +8633,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -8622,41 +8647,10 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>índice de capacidade do processo (Cp)</t>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
-        <is>
-          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>283</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>ISO 19443; ISO 26000; e ISO 45001</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -8683,35 +8677,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Benchmarking</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Benchmarking&lt;/strong&gt;
@@ -8741,6 +8735,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>285</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F201" t="n">
         <v>0</v>
       </c>
@@ -8750,7 +8778,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -8764,44 +8792,10 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Ciclo PDCA</t>
+          <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>286</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade Total (TQM)</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -8891,33 +8885,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
         <v>287</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -8976,33 +8970,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
         <v>288</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -9062,33 +9056,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="205">
+      <c r="A205" t="n">
         <v>289</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -9147,33 +9141,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="206">
+      <c r="A206" t="n">
         <v>290</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -9250,33 +9244,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" t="n">
+    <row r="207">
+      <c r="A207" t="n">
         <v>291</v>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -9348,33 +9342,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
         <v>292</v>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -9436,33 +9430,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
         <v>293</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -9551,33 +9545,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" t="n">
+    <row r="210">
+      <c r="A210" t="n">
         <v>294</v>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -9650,33 +9644,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
         <v>295</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -9721,33 +9715,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="n">
+    <row r="212">
+      <c r="A212" t="n">
         <v>296</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -9802,6 +9796,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>297</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F213" t="n">
         <v>0</v>
       </c>
@@ -9811,7 +9861,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -9825,66 +9875,10 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Dimensões da Qualidade em Serviços</t>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;instalações físicas
-        &lt;ul&gt;
-          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;materiais
-        &lt;ul&gt;
-          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços explícitos
-        &lt;ul&gt;
-          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços complementares
-        &lt;ul&gt;
-          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>298</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>CCQ – Círculos de Controle de Qualidade</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -9916,6 +9910,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>299</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F215" t="n">
         <v>0</v>
       </c>
@@ -9925,7 +9984,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -9939,75 +9998,10 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+          <t>Seis Sigma</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
-      &lt;li&gt;utilizadas como manobra para "promover para fora"
-        &lt;ul&gt;
-          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
-          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
-      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>300</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Seis Sigma</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -10077,6 +10071,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>301</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
       <c r="F217" t="n">
         <v>0</v>
       </c>
@@ -10086,7 +10111,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -10095,46 +10120,15 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Capabilidade</t>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
-        <is>
-          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
-        </is>
-      </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
-        <v>302</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Macrofluxo da Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -10178,33 +10172,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" t="n">
+    <row r="219">
+      <c r="A219" t="n">
         <v>303</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -10253,33 +10247,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
         <v>304</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -10309,6 +10303,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>305</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F221" t="n">
         <v>0</v>
       </c>
@@ -10318,7 +10372,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -10332,70 +10386,10 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Diagrama de Interação do Processo</t>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diagrama de Interação do Processo
-    &lt;ul&gt;
-      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
-      &lt;li&gt;foco nas interfaces
-        &lt;ul&gt;
-          &lt;li&gt;entradas e saídas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;elementos
-        &lt;ul&gt;
-          &lt;li&gt;blocos de processos macro&lt;/li&gt;
-          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;objetivos
-        &lt;ul&gt;
-          &lt;li&gt;identificar dependências&lt;/li&gt;
-          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;distinção
-        &lt;ul&gt;
-          &lt;li&gt;foco externo ao processo&lt;/li&gt;
-          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
-        <v>306</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>Requisitos e Rotinas da ISO 9001:2015</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -10427,35 +10421,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
+    <row r="223">
+      <c r="A223" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Débito na Contabilidade</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -10491,33 +10485,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
         <v>308</v>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C224" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>Tipos de Contas e Retificadoras</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
@@ -10543,33 +10537,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>309</v>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B225" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C225" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>Diferenças Tributárias</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
@@ -10589,33 +10583,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>310</v>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B226" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C226" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>Teoria Patrimonialista e Despesas</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
@@ -10640,33 +10634,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
         <v>311</v>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B227" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C227" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>O Ativo ao Final do Exercício</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
@@ -10686,33 +10680,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
         <v>312</v>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C229" t="inlineStr">
+      <c r="C228" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
@@ -10738,33 +10732,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
         <v>313</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>NR 10</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
@@ -10880,33 +10874,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
         <v>314</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>NR 11</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
@@ -11034,33 +11028,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
         <v>315</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>NR 12</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
@@ -11178,33 +11172,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
         <v>316</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>NR 13</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Gestão da integridade estrutural
@@ -11322,33 +11316,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
         <v>317</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>NR 14</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação com segurança
@@ -11396,35 +11390,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>NR 15</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
@@ -11458,33 +11452,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
         <v>319</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>NR 16</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
@@ -11589,33 +11583,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
         <v>320</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
@@ -11705,33 +11699,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
         <v>321</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>NR 18</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
@@ -11852,33 +11846,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
         <v>322</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>NR 19</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
@@ -11977,33 +11971,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
         <v>323</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>NR 20</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
@@ -12103,33 +12097,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
         <v>324</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>NR 21</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
@@ -12209,33 +12203,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
         <v>325</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>NR 22</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
@@ -12363,35 +12357,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>326</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>NR 23</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
@@ -12428,35 +12422,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
         <is>
           <t>327</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>NR 24</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Dimensionamento&lt;/strong&gt;
@@ -12554,35 +12548,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>NR 25</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gerenciamento de resíduos industriais&lt;/strong&gt;
@@ -12654,33 +12648,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F245" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
         <v>329</v>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>NR 26</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Sinalização e identificação de segurança&lt;/strong&gt;
@@ -12751,35 +12745,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>NR 28</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fiscalização do Trabalho&lt;/strong&gt;
@@ -12852,35 +12846,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>NR 29</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -12987,33 +12981,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F248" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
         <v>333</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>NR 30</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Riscos e Saúde&lt;/strong&gt;
@@ -13119,33 +13113,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
         <v>334</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>NR 31</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Campo de Aplicação&lt;/strong&gt;
@@ -13338,33 +13332,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
         <v>335</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>NR 32</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança e Saúde em Serviços de Saúde (NR 32)&lt;/strong&gt;
@@ -13438,33 +13432,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
         <v>336</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>NR 33</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Espaço Confinado&lt;/strong&gt;
@@ -13553,33 +13547,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
         <v>337</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>NR 34</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -13725,33 +13719,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
         <v>338</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>NR 35</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Campo de Aplicação&lt;/strong&gt;
@@ -13874,33 +13868,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>339</v>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>NR 36</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Aplicação&lt;/strong&gt;
@@ -14003,33 +13997,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>340</v>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>NR 37</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>&lt;li&gt;segurança operacional
     &lt;ul&gt;
@@ -14071,33 +14065,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>341</v>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Fluxograma</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fluxograma&lt;/strong&gt;
@@ -14138,33 +14132,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
         <v>342</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Histograma</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivos e Diagnóstico&lt;/strong&gt;
@@ -14209,33 +14203,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
         <v>343</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Diagrama de Causa e Efeito</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Diagrama de Causa e Efeito&lt;/strong&gt;
@@ -14267,33 +14261,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
         <v>344</v>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>ações de Gestão Ambiental Organizacional</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Resíduos&lt;/strong&gt;
@@ -14333,33 +14327,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
         <v>345</v>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>principais termos técnicos de tipos e mudanças nas estruturas organizacionais</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Processos de Reestruturação&lt;/strong&gt;
@@ -14387,6 +14381,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>346</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Mentalidade de Risco e Prevenção</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F261" t="n">
         <v>0</v>
       </c>
@@ -14396,7 +14446,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -14410,66 +14460,10 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Mentalidade de Risco e Prevenção</t>
+          <t>ARL (Average Run Length)</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
-        <v>347</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>ARL (Average Run Length)</t>
-        </is>
-      </c>
-      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Curva OC (Operating Characteristic)&lt;/strong&gt;
@@ -14494,33 +14488,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
         <v>348</v>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Gestão da tecnologia</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Gestão da Tecnologia&lt;/strong&gt;
@@ -14553,33 +14547,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F264" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" t="n">
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" t="n">
+    <row r="264">
+      <c r="A264" t="n">
         <v>349</v>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>QFD - Modelo de 4 Matrizes</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
@@ -14623,33 +14617,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F265" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
         <v>350</v>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>Sistemas de Codificação de Materiais</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Numeração Arbitrária (Sequencial)&lt;/strong&gt;
@@ -14675,6 +14669,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>351</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>BSC (Perspectivas)</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
+      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
+      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F266" t="n">
         <v>0</v>
       </c>
@@ -14684,7 +14738,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -14693,75 +14747,15 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>BSC (Perspectivas)</t>
+          <t>modelo CAPM (Capital Asset Pricing Model)</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
-      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
-      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
-        <v>352</v>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>modelo CAPM (Capital Asset Pricing Model)</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
@@ -14791,33 +14785,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="n">
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
         <v>354</v>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Presente Histórico e Paralelismo Temporal</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
@@ -14840,35 +14834,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B269" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C269" t="inlineStr">
         <is>
           <t>Compreensão e Interpretação de Textos</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Iterpretação x Inferência textual</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Compreensão (Literal)&lt;/strong&gt;
@@ -14898,33 +14892,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F270" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
         <v>356</v>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B270" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C270" t="inlineStr">
         <is>
           <t>Dados</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>DAMA-DMBOK</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E270" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Governança de Dados (DAMA-DMBOK)&lt;/strong&gt;
@@ -14950,33 +14944,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F271" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
         <v>357</v>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B271" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C271" t="inlineStr">
         <is>
           <t>Mecanismos de Coesão Textual</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>Paralelismo</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Paralelismo Sintático&lt;/strong&gt;
@@ -15000,97 +14994,97 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Taxas</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Inflação Acumulada</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
+      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
+      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F272" t="n">
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Informática</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Taxas</t>
+          <t>Proteção contra vírus</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Inflação Acumulada</t>
+          <t>Aplicativos Antivírus</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
-      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
-      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Proteção contra vírus</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>Aplicativos Antivírus</t>
-        </is>
-      </c>
-      <c r="E274" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;1ª Geração (Assinatura / Escaneamento Simples)&lt;/strong&gt;
@@ -15126,35 +15120,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>Sistemas de Informação (SI)</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E274" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito e Dimensões do SI&lt;/strong&gt;
@@ -15202,35 +15196,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D275" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos e Planejamento de SI</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="E275" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Planejamento&lt;/strong&gt;
@@ -15249,6 +15243,61 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>362</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Representação abstrata e global dos dados da organização. Foca no negócio e ignora detalhes de implementação.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; DER (Diagrama Entidade-Relacionamento).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Lógico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Tradução do modelo conceitual para uma estrutura que o SGBD compreenda (tabelas e relações).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; Modelo Relacional (Chaves Primárias e Estrangeiras).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Físico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Descrição técnica de como os dados são armazenados no hardware.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Elementos:&lt;/strong&gt; Tipos de arquivos, ordenação de registros, métodos de acesso e criação de &lt;u&gt;índices&lt;/u&gt; para performance.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Independência de Dados&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Capacidade de alterar um nível (ex: mudar o hardware no nível físico) sem impactar os níveis superiores (conceitual e lógico).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F276" t="n">
         <v>0</v>
       </c>
@@ -15258,7 +15307,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -15272,65 +15321,10 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
+          <t>Abordagem Orientada a Dados (Data-Driven) vs. Processos</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Representação abstrata e global dos dados da organização. Foca no negócio e ignora detalhes de implementação.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; DER (Diagrama Entidade-Relacionamento).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Lógico&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Tradução do modelo conceitual para uma estrutura que o SGBD compreenda (tabelas e relações).&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; Modelo Relacional (Chaves Primárias e Estrangeiras).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Físico&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Descrição técnica de como os dados são armazenados no hardware.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Elementos:&lt;/strong&gt; Tipos de arquivos, ordenação de registros, métodos de acesso e criação de &lt;u&gt;índices&lt;/u&gt; para performance.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Independência de Dados&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Capacidade de alterar um nível (ex: mudar o hardware no nível físico) sem impactar os níveis superiores (conceitual e lógico).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>363</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Abordagem Orientada a Dados (Data-Driven) vs. Processos</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Filosofia Data-Driven&lt;/strong&gt;
@@ -15349,33 +15343,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
         <v>364</v>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>Indicadores de Disponibilidade e Manutenção (Conceitos)</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Principais Indicadores de Tempo&lt;/strong&gt;
@@ -15402,33 +15396,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
         <v>365</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>Engenharia de Confiabilidade (Modelagem Matemática)</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Distribuição Exponencial (Regime de Falhas Constantes)&lt;/strong&gt;
@@ -15463,6 +15457,59 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>366</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>BPM e BPMS</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;BPM (Business Process Management)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Natureza:&lt;/strong&gt; Disciplina de gestão (metodologia) e não apenas um software.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Gestão ponta a ponta. Ele é &lt;u&gt;transversal&lt;/u&gt;, atravessando silos departamentais e múltiplos sistemas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;O Ciclo de Vida BPM&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Planejamento -&gt; Modelagem -&gt; Simulação -&gt; Execução -&gt; Monitoramento -&gt; Otimização.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;BPMS (O Suporte Tecnológico)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ferramenta que automatiza a lógica do BPM. Pode ser um sistema independente que se "conecta" ao ERP para buscar ou inserir dados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diferença de Hierarquia:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O ERP é focado na &lt;u&gt;transação e registro&lt;/u&gt;. O BPM é focado no &lt;u&gt;fluxo e desempenho&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F280" t="n">
         <v>0</v>
       </c>
@@ -15472,7 +15519,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -15486,63 +15533,10 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>BPM e BPMS</t>
+          <t>CRM (Customer Relationship Management)</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;BPM (Business Process Management)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Natureza:&lt;/strong&gt; Disciplina de gestão (metodologia) e não apenas um software.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Gestão ponta a ponta. Ele é &lt;u&gt;transversal&lt;/u&gt;, atravessando silos departamentais e múltiplos sistemas.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;O Ciclo de Vida BPM&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Planejamento -&gt; Modelagem -&gt; Simulação -&gt; Execução -&gt; Monitoramento -&gt; Otimização.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;BPMS (O Suporte Tecnológico)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Ferramenta que automatiza a lógica do BPM. Pode ser um sistema independente que se "conecta" ao ERP para buscar ou inserir dados.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Diferença de Hierarquia:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;O ERP é focado na &lt;u&gt;transação e registro&lt;/u&gt;. O BPM é focado no &lt;u&gt;fluxo e desempenho&lt;/u&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
-        <v>367</v>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>CRM (Customer Relationship Management)</t>
-        </is>
-      </c>
-      <c r="E282" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Definição e Foco&lt;/strong&gt;
@@ -15566,6 +15560,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>368</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>axonomia de Software (Sistema vs. Aplicativo)</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Atua como intermediário entre o hardware e o usuário/aplicativo. Coordena as operações básicas do computador.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; &lt;u&gt;Sistemas Operacionais&lt;/u&gt; (Windows, Linux), Drivers de dispositivo e utilitários de sistema (desfragmentadores, compiladores).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Software Aplicativo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Programas projetados para permitir que o usuário realize tarefas específicas, profissionais ou pessoais.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Planilhas eletrônicas, processadores de texto, navegadores, ERPs, CRMs e bancos de dados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F282" t="n">
         <v>0</v>
       </c>
@@ -15575,7 +15613,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -15589,54 +15627,10 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>axonomia de Software (Sistema vs. Aplicativo)</t>
+          <t>Aquisição de Software (Prateleira vs. Customizado)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Atua como intermediário entre o hardware e o usuário/aplicativo. Coordena as operações básicas do computador.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; &lt;u&gt;Sistemas Operacionais&lt;/u&gt; (Windows, Linux), Drivers de dispositivo e utilitários de sistema (desfragmentadores, compiladores).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Software Aplicativo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Programas projetados para permitir que o usuário realize tarefas específicas, profissionais ou pessoais.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Planilhas eletrônicas, processadores de texto, navegadores, ERPs, CRMs e bancos de dados.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F283" t="n">
-        <v>0</v>
-      </c>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
-        <v>369</v>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>Aquisição de Software (Prateleira vs. Customizado)</t>
-        </is>
-      </c>
-      <c r="E284" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Software de Prateleira (Off-the-shelf)&lt;/strong&gt;
@@ -15657,33 +15651,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F284" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
+      <c r="F283" t="n">
+        <v>0</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
         <v>370</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D284" t="inlineStr">
         <is>
           <t>Indústria 4.0 (Conceitos e Paradigmas)</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E284" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Origem e Definição&lt;/strong&gt;
@@ -15708,33 +15702,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F285" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" t="n">
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
         <v>371</v>
       </c>
-      <c r="B286" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C286" t="inlineStr">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
+      <c r="D285" t="inlineStr">
         <is>
           <t>Tecnologias Habilitadoras (Os 9 Pilares da Indústria 4.0)</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr">
+      <c r="E285" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Processamento e Dados&lt;/strong&gt;
@@ -15761,10 +15755,10 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F286" t="n">
-        <v>0</v>
-      </c>
-      <c r="G286" t="n">
+      <c r="F285" t="n">
+        <v>0</v>
+      </c>
+      <c r="G285" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G285"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5317,7 +5317,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5331,12 +5331,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Plataformas de governo digital</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Ferramentas digitais e serviços comuns aos órgãos</t>
+          <t>Informação íntegra e precisa</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -5348,7 +5348,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5362,12 +5362,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Informação íntegra e precisa</t>
+          <t>Disponibilização de dados pela administração pública</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -5378,8 +5378,10 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>208</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -5393,43 +5395,10 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Transparência ativa</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação padrão digital
@@ -5508,35 +5477,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -5546,35 +5515,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -5585,33 +5554,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="n">
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="131">
+      <c r="A131" t="n">
         <v>212</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -5624,33 +5593,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="G132" t="n">
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="132">
+      <c r="A132" t="n">
         <v>213</v>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B132" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -5659,99 +5628,101 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G132" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>214</v>
-      </c>
-      <c r="B134" t="inlineStr">
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Plataformas de Governo Digital</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">instrumentos para os entes federativos disponibilizem seus serviços públicos
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instrumentos para que os entes federativos disponibilizem seus serviços públicos
 devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
 padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
         </is>
       </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Prestação Digital dos Serviços Públicos</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F134" t="n">
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A135" t="n">
+        <v>216</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Prestação Digital dos Serviços Públicos</t>
+          <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
-        <is>
-          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>216</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Normas Regulamentadoras do Trabalho</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -5760,35 +5731,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="n">
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -5799,33 +5770,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F137" t="n">
-        <v>0</v>
-      </c>
-      <c r="G137" t="n">
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="137">
+      <c r="A137" t="n">
         <v>219</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>NR 3</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -5835,6 +5806,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>220</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F138" t="n">
         <v>0</v>
       </c>
@@ -5844,7 +5849,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5858,27 +5863,24 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F139" t="n">
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -5892,41 +5894,10 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>222</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -5939,33 +5910,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="141">
+      <c r="A141" t="n">
         <v>223</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -5973,35 +5944,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+    <row r="142">
+      <c r="A142" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -6010,33 +5981,33 @@
 </t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="143">
+      <c r="A143" t="n">
         <v>225</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -6048,33 +6019,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="144">
+      <c r="A144" t="n">
         <v>226</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -6085,33 +6056,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="145">
+      <c r="A145" t="n">
         <v>227</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -6121,33 +6092,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="n">
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="146">
+      <c r="A146" t="n">
         <v>228</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -6156,33 +6127,33 @@
 </t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="147">
+      <c r="A147" t="n">
         <v>229</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6192,33 +6163,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="n">
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="148">
+      <c r="A148" t="n">
         <v>230</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -6227,33 +6198,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="149">
+      <c r="A149" t="n">
         <v>231</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6264,33 +6235,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="150">
+      <c r="A150" t="n">
         <v>233</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Índices Financeiros</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6301,33 +6272,33 @@
 </t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="151">
+      <c r="A151" t="n">
         <v>234</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -6337,35 +6308,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;I. PRÉ-DESENVOLVIMENTO&lt;/strong&gt;
@@ -6398,35 +6369,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="n">
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
+    <row r="153">
+      <c r="A153" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
+      <c r="D153" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E153" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Arquitetura Técnica&lt;/strong&gt;
@@ -6464,16 +6435,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>237</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6482,49 +6487,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Back-office vs. Front-office</t>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>238</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Hierarquia na Aquisição de Tecnologia</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -6533,16 +6504,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>239</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -6551,49 +6556,15 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Processos Decisórios</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Critérios de Decisão no AHP</t>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
-	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>240</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Tendências e Tecnologias em Gestão da Informação</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -6603,33 +6574,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="158">
+      <c r="A158" t="n">
         <v>241</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -6639,33 +6610,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="159">
+      <c r="A159" t="n">
         <v>242</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -6675,33 +6646,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="n">
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
+    <row r="160">
+      <c r="A160" t="n">
         <v>243</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -6710,33 +6681,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" t="n">
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="n">
+    <row r="161">
+      <c r="A161" t="n">
         <v>244</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -6745,33 +6716,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F162" t="n">
+      <c r="F161" t="n">
         <v>2</v>
       </c>
-      <c r="G162" t="n">
+      <c r="G161" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="162">
+      <c r="A162" t="n">
         <v>245</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -6780,33 +6751,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="n">
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="n">
+    <row r="163">
+      <c r="A163" t="n">
         <v>246</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -6815,33 +6786,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="n">
+    <row r="164">
+      <c r="A164" t="n">
         <v>247</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -6854,35 +6825,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
+    <row r="165">
+      <c r="A165" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -6891,33 +6862,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F166" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" t="n">
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="n">
+    <row r="166">
+      <c r="A166" t="n">
         <v>249</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
+      <c r="D166" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="E166" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -6928,37 +6899,95 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>250</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F167" t="n">
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Financeira</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Análise de Investimentos</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Número suficiente para identificação</t>
+          <t>Critérios de Viabilidade e Relações (VPL, TIR e TMA)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Premissas de Reinvestimento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Método da TIR:&lt;/strong&gt; Pressupõe que os fluxos de caixa intermediários sejam reinvestidos com base na &lt;u&gt;própria Taxa Interna de Retorno&lt;/u&gt;.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Método do VPL:&lt;/strong&gt; Pressupõe que os valores sejam reinvestidos com base na &lt;u&gt;própria TMA&lt;/u&gt; (Taxa Mínima de Atratividade).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Sinônimos de TMA:&lt;/strong&gt; Custo de Oportunidade ou Custo de Capital.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Lógica de Decisão e Comparação (Relação Matemático-Lógica)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;$$\text{VPL} &gt; 0 \implies \text{TIR} &gt; \text{TMA}$$ (Projeto Viável)&lt;/li&gt;
+      &lt;li&gt;$$\text{VPL} &lt; 0 \implies \text{TIR} &lt; \text{TMA}$$ (Projeto Inviável)&lt;/li&gt;
+      &lt;li&gt;$$\text{VPL} = 0 \implies \text{TIR} = \text{TMA}$$ (Ponto de Indiferença)&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Interdependência e Comportamento&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;VPL x TMA:&lt;/strong&gt; São &lt;u&gt;inversamente proporcionais&lt;/u&gt; (quanto maior a taxa de desconto/TMA, menor o Valor Presente Líquido).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Conflitos de Ranking:&lt;/strong&gt; VPL e TIR são análises &lt;u&gt;independentes&lt;/u&gt;.
+        &lt;ul&gt;
+          &lt;li&gt;Um projeto pode ter TIR maior que outro e, ainda assim, possuir um VPL menor.&lt;/li&gt;
+          &lt;li&gt;Inversamente, um projeto pode ter TIR menor e VPL maior.&lt;/li&gt;
+          &lt;li&gt;&lt;strong&gt;Conclusão:&lt;/strong&gt; As diferenças entre as TIRs de dois projetos não determinam a hierarquia do VPL entre eles.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -6966,40 +6995,35 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Contabilidade Gerencial</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Aspectos Introdutórios</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Relação entre TIR e VPL</t>
+          <t>Princípio da Entidade</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;São análises independentes.&lt;/li&gt;
-	&lt;li&gt;Um projeto pode ter a TIR maior que outro projeto e VPL menor.&lt;/li&gt;
-	&lt;li&gt;Assim como pode ter a TIR menor e o VPL maior.&lt;/li&gt;
-	&lt;li&gt;Logo, as diferenças da TIR dos dois projetos não dizem nada sobre o valor presente líquido, VPL.&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>Autonomia da pessoa jurídica</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G169" t="n">
         <v>1</v>
@@ -7007,188 +7031,24 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Contabilidade Gerencial</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Contabilidade Básica</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>método da TIR</t>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
-        <is>
-          <t>pressupõe que o fluxo de caixa seja reinvestido com base na própria Taxa Interna de Retorno.</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>253</v>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>Valor Presente Líquido (VPL)</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;pressupõe que os valores são reinvestidos com base na própria TMA.&lt;/li&gt;
-	&lt;li&gt;TMA &lt;ul&gt; &lt;li&gt;pode ser chamada de &lt;b&gt;Custo de Oportunidade&lt;/b&gt; ou &lt;b&gt;Custo de Capital&lt;/b&gt;.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>254</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>Relação VPL X TMA</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Inversamente proporcionais</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>Relação VPL x TIR x TMA</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-    &lt;li&gt;$$\text{VPL} &gt; 0 \implies \text{TIR} &gt; \text{TMA}$$&lt;/li&gt;
-    &lt;li&gt;$$\text{VPL} &lt; 0 \implies \text{TIR} &lt; \text{TMA}$$&lt;/li&gt;
-    &lt;li&gt;$$\text{VPL} = 0 \implies \text{TIR} = \text{TMA}$$&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>256</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Aspectos Introdutórios</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>Princípio da Entidade</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Autonomia da pessoa jurídica</t>
-        </is>
-      </c>
-      <c r="F174" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>257</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -7206,35 +7066,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="n">
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
+    <row r="171">
+      <c r="A171" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B171" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C171" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D171" t="inlineStr">
         <is>
           <t>Receitas</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E171" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;aumento nos ativos
@@ -7264,33 +7124,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="n">
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="n">
+    <row r="172">
+      <c r="A172" t="n">
         <v>259</v>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Despesas</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;consumo de bens ou serviços
@@ -7321,33 +7181,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="n">
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
+    <row r="173">
+      <c r="A173" t="n">
         <v>260</v>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -7429,33 +7289,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="n">
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="174">
+      <c r="A174" t="n">
         <v>261</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -7503,35 +7363,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -7583,33 +7443,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
         <v>263</v>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -7627,33 +7487,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
         <v>264</v>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -7663,35 +7523,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -7759,33 +7619,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F183" t="n">
-        <v>0</v>
-      </c>
-      <c r="G183" t="n">
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="n">
+    <row r="179">
+      <c r="A179" t="n">
         <v>266</v>
       </c>
-      <c r="B184" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -7820,33 +7680,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F184" t="n">
-        <v>0</v>
-      </c>
-      <c r="G184" t="n">
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="n">
+    <row r="180">
+      <c r="A180" t="n">
         <v>267</v>
       </c>
-      <c r="B185" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -7904,33 +7764,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F185" t="n">
-        <v>0</v>
-      </c>
-      <c r="G185" t="n">
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="n">
+    <row r="181">
+      <c r="A181" t="n">
         <v>268</v>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
@@ -7980,33 +7840,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
         <v>269</v>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
@@ -8086,33 +7946,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
         <v>270</v>
       </c>
-      <c r="B188" t="inlineStr">
+      <c r="B183" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
+      <c r="C183" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D183" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E183" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8121,130 +7981,130 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="n">
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>271</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>272</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PAYBACK DESCONTADO</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>271</v>
-      </c>
-      <c r="B189" t="inlineStr">
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
+      <c r="C186" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>PAYBACK SIMPLES</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>0</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>272</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>PAYBACK DESCONTADO</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
         <v>1</v>
       </c>
-      <c r="G190" t="n">
+      <c r="G186" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
-        </is>
-      </c>
-      <c r="F191" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
+    <row r="187">
+      <c r="A187" t="n">
         <v>275</v>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Processo de Gestão de Risco</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -8310,68 +8170,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
+    <row r="188">
+      <c r="A188" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;valores&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="n">
+    <row r="189">
+      <c r="A189" t="n">
         <v>277</v>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D189" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E189" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -8424,33 +8284,33 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="190">
+      <c r="A190" t="n">
         <v>278</v>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>teoria da organização e da gestão da informação</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
@@ -8458,33 +8318,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" t="n">
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="n">
+    <row r="191">
+      <c r="A191" t="n">
         <v>279</v>
       </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -8553,33 +8413,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="n">
+    <row r="192">
+      <c r="A192" t="n">
         <v>281</v>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D192" t="inlineStr">
         <is>
           <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E192" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -8593,64 +8453,64 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" t="n">
+    <row r="193">
+      <c r="A193" t="n">
         <v>282</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>índice de capacidade do processo (Cp)</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="194">
+      <c r="A194" t="n">
         <v>283</v>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -8677,35 +8537,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D195" t="inlineStr">
         <is>
           <t>Benchmarking</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E195" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Benchmarking&lt;/strong&gt;
@@ -8735,33 +8595,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
         <v>285</v>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>Ciclo PDCA</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -8769,33 +8629,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
         <v>286</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -8885,33 +8745,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
         <v>287</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -8970,33 +8830,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
         <v>288</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -9056,33 +8916,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="n">
+    <row r="200">
+      <c r="A200" t="n">
         <v>289</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -9141,33 +9001,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="201">
+      <c r="A201" t="n">
         <v>290</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -9244,33 +9104,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="202">
+      <c r="A202" t="n">
         <v>291</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -9342,33 +9202,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
         <v>292</v>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -9430,33 +9290,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
         <v>293</v>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -9545,33 +9405,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" t="n">
+    <row r="205">
+      <c r="A205" t="n">
         <v>294</v>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -9644,33 +9504,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
         <v>295</v>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -9715,33 +9575,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" t="n">
+    <row r="207">
+      <c r="A207" t="n">
         <v>296</v>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D207" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E207" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -9796,33 +9656,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
         <v>297</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>Dimensões da Qualidade em Serviços</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
@@ -9852,33 +9712,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
         <v>298</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D209" t="inlineStr">
         <is>
           <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E209" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -9910,33 +9770,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
         <v>299</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>A Visão de Deming sobre Avaliações de Desempenho</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
@@ -9975,33 +9835,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F215" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
         <v>300</v>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>Seis Sigma</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E211" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -10071,64 +9931,64 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
         <v>301</v>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Capabilidade</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
         </is>
       </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
         <v>302</v>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -10172,33 +10032,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" t="n">
+    <row r="214">
+      <c r="A214" t="n">
         <v>303</v>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -10247,33 +10107,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
         <v>304</v>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -10303,33 +10163,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
         <v>305</v>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>Diagrama de Interação do Processo</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Diagrama de Interação do Processo
@@ -10363,33 +10223,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
         <v>306</v>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -10421,35 +10281,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
+    <row r="218">
+      <c r="A218" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>Débito na Contabilidade</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -10485,33 +10345,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>308</v>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Tipos de Contas e Retificadoras</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
@@ -10537,33 +10397,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
         <v>309</v>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Diferenças Tributárias</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
@@ -10583,33 +10443,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
         <v>310</v>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Teoria Patrimonialista e Despesas</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
@@ -10634,33 +10494,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>311</v>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>O Ativo ao Final do Exercício</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
@@ -10680,33 +10540,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>312</v>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B223" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
+      <c r="C223" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
@@ -10732,33 +10592,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
         <v>313</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>NR 10</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
@@ -10874,33 +10734,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>314</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>NR 11</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
@@ -11028,33 +10888,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>315</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>NR 12</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
@@ -11172,33 +11032,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
         <v>316</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>NR 13</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Gestão da integridade estrutural
@@ -11316,33 +11176,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
         <v>317</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>NR 14</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação com segurança
@@ -11390,35 +11250,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>NR 15</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
@@ -11452,33 +11312,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
         <v>319</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>NR 16</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
@@ -11583,33 +11443,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
         <v>320</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
@@ -11699,33 +11559,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="n">
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
         <v>321</v>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>NR 18</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
@@ -11846,33 +11706,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
         <v>322</v>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>NR 19</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
@@ -11971,33 +11831,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
         <v>323</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>NR 20</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
@@ -12097,33 +11957,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
         <v>324</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>NR 21</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
@@ -12203,33 +12063,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="n">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
         <v>325</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>NR 22</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
@@ -12357,35 +12217,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>326</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>NR 23</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
@@ -12422,35 +12282,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>327</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>NR 24</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Dimensionamento&lt;/strong&gt;
@@ -12548,35 +12408,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>NR 25</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gerenciamento de resíduos industriais&lt;/strong&gt;
@@ -12648,33 +12508,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
         <v>329</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>NR 26</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Sinalização e identificação de segurança&lt;/strong&gt;
@@ -12745,35 +12605,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F245" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>NR 28</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fiscalização do Trabalho&lt;/strong&gt;
@@ -12846,35 +12706,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>NR 29</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -12981,33 +12841,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
         <v>333</v>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>NR 30</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Riscos e Saúde&lt;/strong&gt;
@@ -13113,33 +12973,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F248" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
         <v>334</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>NR 31</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Campo de Aplicação&lt;/strong&gt;
@@ -13332,33 +13192,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
         <v>335</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>NR 32</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança e Saúde em Serviços de Saúde (NR 32)&lt;/strong&gt;
@@ -13432,33 +13292,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
         <v>336</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>NR 33</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Espaço Confinado&lt;/strong&gt;
@@ -13547,33 +13407,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
         <v>337</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>NR 34</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -13719,33 +13579,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
         <v>338</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>NR 35</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Campo de Aplicação&lt;/strong&gt;
@@ -13868,33 +13728,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
         <v>339</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>NR 36</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Aplicação&lt;/strong&gt;
@@ -13997,33 +13857,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
         <v>340</v>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>NR 37</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>&lt;li&gt;segurança operacional
     &lt;ul&gt;
@@ -14065,33 +13925,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
         <v>341</v>
       </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>Fluxograma</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fluxograma&lt;/strong&gt;
@@ -14132,33 +13992,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
         <v>342</v>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>Histograma</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivos e Diagnóstico&lt;/strong&gt;
@@ -14203,33 +14063,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
         <v>343</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>Diagrama de Causa e Efeito</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Diagrama de Causa e Efeito&lt;/strong&gt;
@@ -14261,33 +14121,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>344</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>ações de Gestão Ambiental Organizacional</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Resíduos&lt;/strong&gt;
@@ -14327,33 +14187,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
         <v>345</v>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D255" t="inlineStr">
         <is>
           <t>principais termos técnicos de tipos e mudanças nas estruturas organizacionais</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E255" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Processos de Reestruturação&lt;/strong&gt;
@@ -14381,33 +14241,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>346</v>
       </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Mentalidade de Risco e Prevenção</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
@@ -14437,33 +14297,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
         <v>347</v>
       </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>ARL (Average Run Length)</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Curva OC (Operating Characteristic)&lt;/strong&gt;
@@ -14488,33 +14348,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
         <v>348</v>
       </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Gestão da tecnologia</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Gestão da Tecnologia&lt;/strong&gt;
@@ -14547,33 +14407,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" t="n">
+    <row r="259">
+      <c r="A259" t="n">
         <v>349</v>
       </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>QFD - Modelo de 4 Matrizes</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
@@ -14617,33 +14477,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F264" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
         <v>350</v>
       </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D260" t="inlineStr">
         <is>
           <t>Sistemas de Codificação de Materiais</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E260" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Numeração Arbitrária (Sequencial)&lt;/strong&gt;
@@ -14669,33 +14529,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F265" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
         <v>351</v>
       </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>BSC (Perspectivas)</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
@@ -14729,33 +14589,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F266" t="n">
-        <v>0</v>
-      </c>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="n">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
         <v>352</v>
       </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>modelo CAPM (Capital Asset Pricing Model)</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
@@ -14785,33 +14645,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F267" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="n">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
         <v>354</v>
       </c>
-      <c r="B268" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C268" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Presente Histórico e Paralelismo Temporal</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
@@ -14834,35 +14694,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C269" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>Compreensão e Interpretação de Textos</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>Iterpretação x Inferência textual</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Compreensão (Literal)&lt;/strong&gt;
@@ -14892,33 +14752,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="n">
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
         <v>356</v>
       </c>
-      <c r="B270" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>Dados</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>DAMA-DMBOK</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Governança de Dados (DAMA-DMBOK)&lt;/strong&gt;
@@ -14944,33 +14804,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F270" t="n">
-        <v>0</v>
-      </c>
-      <c r="G270" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="n">
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
         <v>357</v>
       </c>
-      <c r="B271" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C271" t="inlineStr">
+      <c r="C266" t="inlineStr">
         <is>
           <t>Mecanismos de Coesão Textual</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
+      <c r="D266" t="inlineStr">
         <is>
           <t>Paralelismo</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E266" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Paralelismo Sintático&lt;/strong&gt;
@@ -14994,35 +14854,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F271" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>358</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
+      <c r="C267" t="inlineStr">
         <is>
           <t>Taxas</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
+      <c r="D267" t="inlineStr">
         <is>
           <t>Inflação Acumulada</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
@@ -15056,35 +14916,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="n">
+      <c r="F267" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>359</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B268" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C268" t="inlineStr">
         <is>
           <t>Proteção contra vírus</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Aplicativos Antivírus</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;1ª Geração (Assinatura / Escaneamento Simples)&lt;/strong&gt;
@@ -15120,35 +14980,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Sistemas de Informação (SI)</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito e Dimensões do SI&lt;/strong&gt;
@@ -15196,35 +15056,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F274" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
+      <c r="D270" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos e Planejamento de SI</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr">
+      <c r="E270" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Planejamento&lt;/strong&gt;
@@ -15243,33 +15103,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
         <v>362</v>
       </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
+      <c r="D271" t="inlineStr">
         <is>
           <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr">
+      <c r="E271" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
@@ -15298,33 +15158,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F276" t="n">
-        <v>0</v>
-      </c>
-      <c r="G276" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="n">
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
         <v>363</v>
       </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>Abordagem Orientada a Dados (Data-Driven) vs. Processos</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr">
+      <c r="E272" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Filosofia Data-Driven&lt;/strong&gt;
@@ -15343,33 +15203,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
         <v>364</v>
       </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>Indicadores de Disponibilidade e Manutenção (Conceitos)</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr">
+      <c r="E273" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Principais Indicadores de Tempo&lt;/strong&gt;
@@ -15396,33 +15256,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
         <v>365</v>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D274" t="inlineStr">
         <is>
           <t>Engenharia de Confiabilidade (Modelagem Matemática)</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E274" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Distribuição Exponencial (Regime de Falhas Constantes)&lt;/strong&gt;
@@ -15457,33 +15317,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
+      <c r="F274" t="n">
+        <v>0</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
         <v>366</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D275" t="inlineStr">
         <is>
           <t>BPM e BPMS</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E275" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;BPM (Business Process Management)&lt;/strong&gt;
@@ -15510,33 +15370,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
         <v>367</v>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D276" t="inlineStr">
         <is>
           <t>CRM (Customer Relationship Management)</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E276" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Definição e Foco&lt;/strong&gt;
@@ -15560,33 +15420,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
+      <c r="F276" t="n">
+        <v>0</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
         <v>368</v>
       </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D277" t="inlineStr">
         <is>
           <t>axonomia de Software (Sistema vs. Aplicativo)</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E277" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
@@ -15604,33 +15464,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F282" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="n">
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
         <v>369</v>
       </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>Aquisição de Software (Prateleira vs. Customizado)</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Software de Prateleira (Off-the-shelf)&lt;/strong&gt;
@@ -15651,33 +15511,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F283" t="n">
-        <v>0</v>
-      </c>
-      <c r="G283" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="n">
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
         <v>370</v>
       </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>Indústria 4.0 (Conceitos e Paradigmas)</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Origem e Definição&lt;/strong&gt;
@@ -15702,33 +15562,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F284" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="n">
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
         <v>371</v>
       </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>Tecnologias Habilitadoras (Os 9 Pilares da Indústria 4.0)</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Processamento e Dados&lt;/strong&gt;
@@ -15755,10 +15615,133 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F285" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" t="n">
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>372</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Taxas</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Taxas Reais, Nominais e Impacto do IR (Equação de Fisher)</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceitos de Base&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Taxa Nominal (Bruta):&lt;/strong&gt; A taxa anunciada pelo investimento (antes de impostos e inflação).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Taxa Líquida ($i_{liq}$):&lt;/strong&gt; Taxa nominal após o desconto do Imposto de Renda (IR).
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Importante:&lt;/strong&gt; O IR incide apenas sobre o &lt;u&gt;lucro nominal&lt;/u&gt; (Rendimento), não sobre o capital total.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Taxa Real ($i_r$):&lt;/strong&gt; O ganho efetivo de poder de compra.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;A Equação de Fisher (Relação de Taxas)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Garante que a inflação seja "expurgada" do ganho líquido:
+          $$(1 + i_{liq}) = (1 + i_r) \cdot (1 + i_{inf})$$
+      &lt;/li&gt;
+      &lt;li&gt;Para isolar a Taxa Real:
+          $$i_r = \frac{1 + i_{liq}}{1 + i_{inf}} - 1$$
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Algoritmo de Resolução (Passo a Passo)&lt;/strong&gt;
+    &lt;ol&gt;
+      &lt;li&gt;Calcule o Montante Bruto ($M = C \cdot (1+i_{bruta})$).&lt;/li&gt;
+      &lt;li&gt;Ache o Ganho Nominal ($M - C$) e aplique a alíquota de IR sobre ele.&lt;/li&gt;
+      &lt;li&gt;Calcule o Montante Líquido ($M_{liq} = M - IR$).&lt;/li&gt;
+      &lt;li&gt;Ache a Taxa Líquida ($i_{liq} = \frac{M_{liq}}{C} - 1$).&lt;/li&gt;
+      &lt;li&gt;Aplique a Equação de Fisher para achar a Taxa Real ($i_r$).&lt;/li&gt;
+    &lt;/ol&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;A Pegadinha do Cebraspe&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A banca vai sugerir que você faça: $\text{Taxa Real} = \text{Taxa Nominal} - \text{Inflação}$. 
+      &lt;strong&gt;ERRADO!&lt;/strong&gt; Essa é apenas uma aproximação linear. Para cálculos exatos, use sempre a divisão de fatores.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>373</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Contabilidade De Custos</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Equivalentes de Produção</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Equivalente de Produção e Custeio por Processo</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Equivalente de Produção (EP)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;É a tradução do estoque em processamento (WIP) em unidades acabadas.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Fórmula:&lt;/strong&gt; $$EP = Qtd.\ Acabada + (Qtd.\ em\ Processo \cdot \%Acabamento)$$&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Lógica PEPS (FIFO) no Custeio por Processo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O custo do período deve ser dividido apenas pelo &lt;u&gt;esforço realizado no período&lt;/u&gt;.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cálculo do EP (PEPS):&lt;/strong&gt;
+        &lt;ol&gt;
+          &lt;li&gt;Esforço para terminar o estoque inicial (Ex: se iniciou 75% pronto, falta 25%).&lt;/li&gt;
+          &lt;li&gt;Unidades iniciadas e terminadas no próprio mês.&lt;/li&gt;
+          &lt;li&gt;Esforço realizado no estoque final (Ex: 80 unidades a 75% = 60 EP).&lt;/li&gt;
+        &lt;/ol&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Regra de Ouro (CPA - Custo da Produção Acabada)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O custo total das unidades que saíram da fábrica é a soma do custo que elas já traziam do mês anterior + o custo adicionado para finalizá-las no mês atual.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F282" t="n">
+        <v>0</v>
+      </c>
+      <c r="G282" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G282"/>
+  <dimension ref="A1:G281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5099,8 +5099,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>199</v>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -5119,7 +5121,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Acesso pelo cidadão a serviço público</t>
+          <t>Acesso pelo cidadão a serviço público prestado por meio digital, sem necessidade de mediação humana;</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -5130,8 +5132,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>200</v>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -5145,24 +5149,24 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Base nacional de serviços públicos</t>
+          <t>Dados abertos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Base de dados que contém as informações</t>
+          <t>Dados acessíveis ao público, representados em meio digital, estruturados em formato aberto, processáveis por máquina, referenciados na internet e disponibilizados sob licença aberta que permita sua livre utilização, consumo ou tratamento por qualquer pessoa, física ou jurídica;</t>
         </is>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5176,24 +5180,26 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Dados abertos</t>
+          <t>Dado acessível ao público</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dados acessíveis ao público</t>
+          <t>Qualquer dado gerado ou acumulado</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v>202</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -5207,24 +5213,26 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Dado acessível ao público</t>
+          <t>Formato aberto</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Qualquer dado gerado ou acumulado</t>
+          <t>Formato de arquivo não proprietário, cuja especificação esteja documentada publicamente e seja de livre conhecimento e implementação, livre de patentes ou de qualquer outra restrição legal quanto à sua utilização;</t>
         </is>
       </c>
       <c r="F122" t="n">
         <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
-        <v>203</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -5238,24 +5246,26 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Formato aberto</t>
+          <t>Governo como plataforma</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Formato de arquivo não proprietário</t>
+          <t>Infraestrutura tecnológica que facilite o uso de dados de acesso público e promova a interação entre diversos agentes, de forma segura, eficiente e responsável, para estímulo à inovação, à exploração de atividade econômica e à prestação de serviços à população;</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>204</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -5269,24 +5279,26 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Governo como plataforma</t>
+          <t>Laboratório de inovação</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Infraestrutura tecnológica que facilite</t>
+          <t>Espaço aberto à participação e à colaboração da sociedade para o desenvolvimento de ideias, de ferramentas e de métodos inovadores para a gestão pública, a prestação de serviços públicos e a participação do cidadão para o exercício do controle sobre a administração pública;</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>205</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -5300,12 +5312,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Laboratório de inovação</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Espaço aberto à participação</t>
+          <t>Informação íntegra e precisa oriunda de uma ou mais fontes de dados, centralizadas ou descentralizadas, sobre elementos fundamentais para a prestação de serviços e para a gestão de políticas públicas;</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -5316,8 +5328,10 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>207</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -5331,24 +5345,26 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Informação íntegra e precisa</t>
+          <t>Disponibilização de dados pela administração pública independentemente de solicitações.</t>
         </is>
       </c>
       <c r="F126" t="n">
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
-        <v>208</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -5362,43 +5378,10 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Transparência ativa</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação padrão digital
@@ -5477,35 +5460,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -5515,35 +5498,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -5554,33 +5537,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="130">
+      <c r="A130" t="n">
         <v>212</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -5593,33 +5576,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="G131" t="n">
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="131">
+      <c r="A131" t="n">
         <v>213</v>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B131" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -5628,17 +5611,51 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Plataformas de Governo Digital</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instrumentos para que os entes federativos disponibilizem seus serviços públicos
+devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt; padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
+        </is>
+      </c>
       <c r="F132" t="n">
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5653,14 +5670,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Plataformas de Governo Digital</t>
+          <t>Prestação Digital dos Serviços Públicos</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">instrumentos para que os entes federativos disponibilizem seus serviços públicos
-devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt;
-padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -5671,58 +5686,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A134" t="n">
+        <v>216</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Prestação Digital dos Serviços Públicos</t>
+          <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
-        <is>
-          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>216</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Normas Regulamentadoras do Trabalho</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -5731,35 +5713,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -5770,33 +5752,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F136" t="n">
-        <v>0</v>
-      </c>
-      <c r="G136" t="n">
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" t="n">
+    <row r="136">
+      <c r="A136" t="n">
         <v>219</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>NR 3</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="E136" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -5806,6 +5788,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>220</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
@@ -5815,7 +5831,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5829,27 +5845,24 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F138" t="n">
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -5863,41 +5876,10 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>222</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -5910,33 +5892,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="n">
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="n">
+    <row r="140">
+      <c r="A140" t="n">
         <v>223</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -5944,35 +5926,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+    <row r="141">
+      <c r="A141" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -5981,33 +5963,33 @@
 </t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="142">
+      <c r="A142" t="n">
         <v>225</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -6019,33 +6001,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="143">
+      <c r="A143" t="n">
         <v>226</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -6056,33 +6038,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="144">
+      <c r="A144" t="n">
         <v>227</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -6092,33 +6074,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="145">
+      <c r="A145" t="n">
         <v>228</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -6127,33 +6109,33 @@
 </t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="n">
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="146">
+      <c r="A146" t="n">
         <v>229</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6163,33 +6145,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="147">
+      <c r="A147" t="n">
         <v>230</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -6198,33 +6180,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="n">
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="148">
+      <c r="A148" t="n">
         <v>231</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6235,33 +6217,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="149">
+      <c r="A149" t="n">
         <v>233</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Índices Financeiros</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6272,33 +6254,33 @@
 </t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="150">
+      <c r="A150" t="n">
         <v>234</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -6308,35 +6290,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;I. PRÉ-DESENVOLVIMENTO&lt;/strong&gt;
@@ -6369,35 +6351,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="G152" t="n">
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Arquitetura Técnica&lt;/strong&gt;
@@ -6435,16 +6417,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>237</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -6453,49 +6469,15 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Back-office vs. Front-office</t>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>238</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Hierarquia na Aquisição de Tecnologia</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -6504,16 +6486,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>239</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F155" t="n">
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -6522,49 +6538,15 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Processos Decisórios</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Critérios de Decisão no AHP</t>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
-	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>240</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Tendências e Tecnologias em Gestão da Informação</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -6574,33 +6556,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="157">
+      <c r="A157" t="n">
         <v>241</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -6610,33 +6592,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="158">
+      <c r="A158" t="n">
         <v>242</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -6646,33 +6628,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="159">
+      <c r="A159" t="n">
         <v>243</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -6681,33 +6663,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F160" t="n">
-        <v>0</v>
-      </c>
-      <c r="G160" t="n">
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
+    <row r="160">
+      <c r="A160" t="n">
         <v>244</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -6716,33 +6698,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F161" t="n">
+      <c r="F160" t="n">
         <v>2</v>
       </c>
-      <c r="G161" t="n">
+      <c r="G160" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="n">
+    <row r="161">
+      <c r="A161" t="n">
         <v>245</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -6751,33 +6733,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="162">
+      <c r="A162" t="n">
         <v>246</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -6786,33 +6768,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="n">
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="n">
+    <row r="163">
+      <c r="A163" t="n">
         <v>247</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -6825,35 +6807,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -6862,33 +6844,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" t="n">
+    <row r="165">
+      <c r="A165" t="n">
         <v>249</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
+      <c r="D165" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E165" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -6899,67 +6881,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>250</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F166" t="n">
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Financeira</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Análise de Investimentos</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Número suficiente para identificação</t>
+          <t>Critérios de Viabilidade e Relações (VPL, TIR e TMA)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F167" t="n">
-        <v>0</v>
-      </c>
-      <c r="G167" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>251</v>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Critérios de Viabilidade e Relações (VPL, TIR e TMA)</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Reinvestimento&lt;/strong&gt;
@@ -6991,16 +6973,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>256</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Princípio da Entidade</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Autonomia da pessoa jurídica</t>
+        </is>
+      </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -7009,46 +7022,15 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Contabilidade Básica</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Princípio da Entidade</t>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
-        <is>
-          <t>Autonomia da pessoa jurídica</t>
-        </is>
-      </c>
-      <c r="F169" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>257</v>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -7066,18 +7048,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Receitas</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;aumento nos ativos
+    &lt;ul&gt;
+      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diminuição de passivo
+    &lt;ul&gt;
+      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta aumento do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F170" t="n">
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A171" t="n">
+        <v>259</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -7091,34 +7129,35 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Receitas</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;aumento nos ativos
-    &lt;ul&gt;
-      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;diminuição de passivo
-    &lt;ul&gt;
-      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+  &lt;li&gt;consumo de bens ou serviços
+    &lt;ul&gt;
+      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;representam
+    &lt;ul&gt;
+      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
+      &lt;li&gt;aumento no passivo&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;reconhecimento
     &lt;ul&gt;
-      &lt;li&gt;acarreta aumento do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;transações com sócios
     &lt;ul&gt;
-      &lt;li&gt;não representam receitas&lt;/li&gt;
+      &lt;li&gt;não representam despesas&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -7133,7 +7172,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -7147,67 +7186,10 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;consumo de bens ou serviços
-    &lt;ul&gt;
-      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;representam
-    &lt;ul&gt;
-      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
-      &lt;li&gt;aumento no passivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;reconhecimento
-    &lt;ul&gt;
-      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;transações com sócios
-    &lt;ul&gt;
-      &lt;li&gt;não representam despesas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>260</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -7289,33 +7271,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" t="n">
+    <row r="173">
+      <c r="A173" t="n">
         <v>261</v>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -7363,35 +7345,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -7443,33 +7425,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
         <v>263</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -7487,33 +7469,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
         <v>264</v>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -7523,35 +7505,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -7619,33 +7601,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="n">
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="178">
+      <c r="A178" t="n">
         <v>266</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -7680,33 +7662,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="n">
+    <row r="179">
+      <c r="A179" t="n">
         <v>267</v>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -7764,38 +7746,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="n">
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>268</v>
-      </c>
-      <c r="B181" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
     &lt;ul&gt;
-      &lt;li&gt;pilares essenciais&lt;/li&gt;
+      &lt;li&gt;pilares essenciais para garantir que a administração pública digital funcione de forma responsável, transparente e orientada a resultados&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;Governança
@@ -7840,37 +7824,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>269</v>
-      </c>
-      <c r="B182" t="inlineStr">
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diretrizes Gerais (Princípios e Orientações)
-    &lt;ul&gt;
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
       &lt;li&gt;respeito a normas existentes
         &lt;ul&gt;
           &lt;li&gt;LAI, LGPD e Código Tributário&lt;/li&gt;
@@ -7941,38 +7925,36 @@
       &lt;li&gt;políticas públicas orientadas por dados e evidências&lt;/li&gt;
       &lt;li&gt;participação de servidores e colaboradores&lt;/li&gt;
       &lt;li&gt;difusão de conhecimento e modernização&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F182" t="n">
-        <v>0</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
         <v>270</v>
       </c>
-      <c r="B183" t="inlineStr">
+      <c r="B182" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
+      <c r="C182" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
+      <c r="D182" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E182" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7981,6 +7963,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>271</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F183" t="n">
         <v>0</v>
       </c>
@@ -7990,7 +8003,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -8004,24 +8017,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PAYBACK SIMPLES</t>
+          <t>PAYBACK DESCONTADO</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
-        <v>272</v>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -8035,76 +8052,41 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>PAYBACK DESCONTADO</t>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+      <c r="A186" t="n">
+        <v>275</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
-        <is>
-          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
-        </is>
-      </c>
-      <c r="F186" t="n">
-        <v>1</v>
-      </c>
-      <c r="G186" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>275</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>Processo de Gestão de Risco</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -8170,68 +8152,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="n">
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
+    <row r="187">
+      <c r="A187" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;valores&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F188" t="n">
-        <v>0</v>
-      </c>
-      <c r="G188" t="n">
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" t="n">
+    <row r="188">
+      <c r="A188" t="n">
         <v>277</v>
       </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -8284,6 +8266,40 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>278</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F189" t="n">
         <v>0</v>
       </c>
@@ -8293,7 +8309,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -8302,49 +8318,15 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>teoria da organização e da gestão da informação</t>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
-	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>279</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Gestão da Inovação</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -8413,33 +8395,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="n">
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="n">
+    <row r="191">
+      <c r="A191" t="n">
         <v>281</v>
       </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D191" t="inlineStr">
         <is>
           <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E191" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -8453,6 +8435,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>282</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
@@ -8462,7 +8475,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -8476,41 +8489,10 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>índice de capacidade do processo (Cp)</t>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
-        <is>
-          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>283</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>ISO 19443; ISO 26000; e ISO 45001</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -8537,35 +8519,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D194" t="inlineStr">
         <is>
           <t>Benchmarking</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E194" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Benchmarking&lt;/strong&gt;
@@ -8595,6 +8577,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>285</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
@@ -8604,7 +8620,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -8618,44 +8634,10 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Ciclo PDCA</t>
+          <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>286</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade Total (TQM)</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -8745,33 +8727,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
         <v>287</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -8830,33 +8812,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
         <v>288</v>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -8916,33 +8898,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="199">
+      <c r="A199" t="n">
         <v>289</v>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -9001,33 +8983,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="200">
+      <c r="A200" t="n">
         <v>290</v>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -9104,33 +9086,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="n">
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" t="n">
+    <row r="201">
+      <c r="A201" t="n">
         <v>291</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -9202,33 +9184,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
         <v>292</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -9290,33 +9272,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
         <v>293</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -9405,33 +9387,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" t="n">
+    <row r="204">
+      <c r="A204" t="n">
         <v>294</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -9504,33 +9486,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
         <v>295</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -9575,33 +9557,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F206" t="n">
-        <v>0</v>
-      </c>
-      <c r="G206" t="n">
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" t="n">
+    <row r="206">
+      <c r="A206" t="n">
         <v>296</v>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D206" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E206" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -9656,6 +9638,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>297</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F207" t="n">
         <v>0</v>
       </c>
@@ -9665,7 +9703,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -9679,66 +9717,10 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Dimensões da Qualidade em Serviços</t>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;instalações físicas
-        &lt;ul&gt;
-          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;materiais
-        &lt;ul&gt;
-          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços explícitos
-        &lt;ul&gt;
-          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços complementares
-        &lt;ul&gt;
-          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>298</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>CCQ – Círculos de Controle de Qualidade</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -9770,6 +9752,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>299</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F209" t="n">
         <v>0</v>
       </c>
@@ -9779,7 +9826,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -9793,75 +9840,10 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+          <t>Seis Sigma</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
-      &lt;li&gt;utilizadas como manobra para "promover para fora"
-        &lt;ul&gt;
-          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
-          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
-      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F210" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>300</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>Seis Sigma</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -9931,6 +9913,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>301</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
@@ -9940,7 +9953,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -9949,46 +9962,15 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Capabilidade</t>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
-        <is>
-          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
-        </is>
-      </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>302</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>Macrofluxo da Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -10032,33 +10014,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="n">
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" t="n">
+    <row r="213">
+      <c r="A213" t="n">
         <v>303</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -10107,33 +10089,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F214" t="n">
-        <v>0</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
         <v>304</v>
       </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D214" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E214" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -10163,6 +10145,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>305</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F215" t="n">
         <v>0</v>
       </c>
@@ -10172,7 +10214,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -10186,70 +10228,10 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Diagrama de Interação do Processo</t>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diagrama de Interação do Processo
-    &lt;ul&gt;
-      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
-      &lt;li&gt;foco nas interfaces
-        &lt;ul&gt;
-          &lt;li&gt;entradas e saídas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;elementos
-        &lt;ul&gt;
-          &lt;li&gt;blocos de processos macro&lt;/li&gt;
-          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;objetivos
-        &lt;ul&gt;
-          &lt;li&gt;identificar dependências&lt;/li&gt;
-          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;distinção
-        &lt;ul&gt;
-          &lt;li&gt;foco externo ao processo&lt;/li&gt;
-          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>306</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Requisitos e Rotinas da ISO 9001:2015</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -10281,35 +10263,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
+    <row r="217">
+      <c r="A217" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>Débito na Contabilidade</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -10345,33 +10327,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
         <v>308</v>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>Tipos de Contas e Retificadoras</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
@@ -10397,33 +10379,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>309</v>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Diferenças Tributárias</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
@@ -10443,33 +10425,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
         <v>310</v>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>Teoria Patrimonialista e Despesas</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
@@ -10494,33 +10476,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
         <v>311</v>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>O Ativo ao Final do Exercício</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
@@ -10540,33 +10522,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>312</v>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B222" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
+      <c r="C222" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
@@ -10592,33 +10574,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>313</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>NR 10</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
@@ -10734,33 +10716,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
         <v>314</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>NR 11</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
@@ -10888,33 +10870,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>315</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>NR 12</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
@@ -11032,33 +11014,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>316</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>NR 13</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Gestão da integridade estrutural
@@ -11176,33 +11158,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="n">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
         <v>317</v>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>NR 14</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação com segurança
@@ -11250,35 +11232,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>NR 15</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
@@ -11312,33 +11294,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
         <v>319</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>NR 16</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
@@ -11443,33 +11425,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
         <v>320</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
@@ -11559,33 +11541,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
         <v>321</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>NR 18</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
@@ -11706,33 +11688,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
         <v>322</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>NR 19</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
@@ -11831,33 +11813,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
         <v>323</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>NR 20</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
@@ -11957,33 +11939,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
         <v>324</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>NR 21</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
@@ -12063,33 +12045,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="n">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
         <v>325</v>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>NR 22</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
@@ -12217,35 +12199,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>326</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>NR 23</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
@@ -12282,35 +12264,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>327</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>NR 24</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Dimensionamento&lt;/strong&gt;
@@ -12408,35 +12390,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>NR 25</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gerenciamento de resíduos industriais&lt;/strong&gt;
@@ -12508,33 +12490,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="n">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
         <v>329</v>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>NR 26</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Sinalização e identificação de segurança&lt;/strong&gt;
@@ -12605,35 +12587,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>NR 28</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fiscalização do Trabalho&lt;/strong&gt;
@@ -12706,35 +12688,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>NR 29</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -12841,33 +12823,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
         <v>333</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>NR 30</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Riscos e Saúde&lt;/strong&gt;
@@ -12973,33 +12955,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
         <v>334</v>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>NR 31</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Campo de Aplicação&lt;/strong&gt;
@@ -13192,33 +13174,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
         <v>335</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>NR 32</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança e Saúde em Serviços de Saúde (NR 32)&lt;/strong&gt;
@@ -13292,33 +13274,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F245" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
         <v>336</v>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>NR 33</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Espaço Confinado&lt;/strong&gt;
@@ -13407,33 +13389,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
         <v>337</v>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>NR 34</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -13579,33 +13561,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
         <v>338</v>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>NR 35</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Campo de Aplicação&lt;/strong&gt;
@@ -13728,33 +13710,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F248" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
         <v>339</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>NR 36</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Aplicação&lt;/strong&gt;
@@ -13857,33 +13839,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
         <v>340</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>NR 37</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>&lt;li&gt;segurança operacional
     &lt;ul&gt;
@@ -13925,33 +13907,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
         <v>341</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>Fluxograma</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fluxograma&lt;/strong&gt;
@@ -13992,33 +13974,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
         <v>342</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>Histograma</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivos e Diagnóstico&lt;/strong&gt;
@@ -14063,33 +14045,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
         <v>343</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>Diagrama de Causa e Efeito</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Diagrama de Causa e Efeito&lt;/strong&gt;
@@ -14121,33 +14103,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
         <v>344</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>ações de Gestão Ambiental Organizacional</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Resíduos&lt;/strong&gt;
@@ -14187,33 +14169,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F254" t="n">
-        <v>0</v>
-      </c>
-      <c r="G254" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="n">
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
         <v>345</v>
       </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D254" t="inlineStr">
         <is>
           <t>principais termos técnicos de tipos e mudanças nas estruturas organizacionais</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E254" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Processos de Reestruturação&lt;/strong&gt;
@@ -14241,6 +14223,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F254" t="n">
+        <v>0</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>346</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Mentalidade de Risco e Prevenção</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F255" t="n">
         <v>0</v>
       </c>
@@ -14250,7 +14288,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -14264,66 +14302,10 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Mentalidade de Risco e Prevenção</t>
+          <t>ARL (Average Run Length)</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
-        <v>347</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>ARL (Average Run Length)</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Curva OC (Operating Characteristic)&lt;/strong&gt;
@@ -14348,33 +14330,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
         <v>348</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>Gestão da tecnologia</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Gestão da Tecnologia&lt;/strong&gt;
@@ -14407,33 +14389,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" t="n">
+    <row r="258">
+      <c r="A258" t="n">
         <v>349</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>QFD - Modelo de 4 Matrizes</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
@@ -14477,33 +14459,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F259" t="n">
-        <v>0</v>
-      </c>
-      <c r="G259" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="n">
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
         <v>350</v>
       </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D259" t="inlineStr">
         <is>
           <t>Sistemas de Codificação de Materiais</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E259" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Numeração Arbitrária (Sequencial)&lt;/strong&gt;
@@ -14529,6 +14511,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F259" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>351</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>BSC (Perspectivas)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
+      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
+      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F260" t="n">
         <v>0</v>
       </c>
@@ -14538,7 +14580,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -14547,75 +14589,15 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>BSC (Perspectivas)</t>
+          <t>modelo CAPM (Capital Asset Pricing Model)</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
-      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
-      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
-        <v>352</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>modelo CAPM (Capital Asset Pricing Model)</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
@@ -14645,33 +14627,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="n">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
         <v>354</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Presente Histórico e Paralelismo Temporal</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
@@ -14694,35 +14676,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Compreensão e Interpretação de Textos</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>Iterpretação x Inferência textual</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Compreensão (Literal)&lt;/strong&gt;
@@ -14752,33 +14734,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F264" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
         <v>356</v>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>Dados</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>DAMA-DMBOK</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Governança de Dados (DAMA-DMBOK)&lt;/strong&gt;
@@ -14804,33 +14786,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F265" t="n">
-        <v>0</v>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="n">
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
         <v>357</v>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr">
+      <c r="C265" t="inlineStr">
         <is>
           <t>Mecanismos de Coesão Textual</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D265" t="inlineStr">
         <is>
           <t>Paralelismo</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E265" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Paralelismo Sintático&lt;/strong&gt;
@@ -14854,97 +14836,97 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Taxas</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Inflação Acumulada</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
+      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
+      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Informática</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Taxas</t>
+          <t>Proteção contra vírus</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Inflação Acumulada</t>
+          <t>Aplicativos Antivírus</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
-      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
-      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F267" t="n">
-        <v>1</v>
-      </c>
-      <c r="G267" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Proteção contra vírus</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Aplicativos Antivírus</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;1ª Geração (Assinatura / Escaneamento Simples)&lt;/strong&gt;
@@ -14980,35 +14962,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Sistemas de Informação (SI)</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito e Dimensões do SI&lt;/strong&gt;
@@ -15056,35 +15038,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F269" t="n">
-        <v>0</v>
-      </c>
-      <c r="G269" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
+      <c r="D269" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos e Planejamento de SI</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E269" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Planejamento&lt;/strong&gt;
@@ -15103,6 +15085,61 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>362</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Representação abstrata e global dos dados da organização. Foca no negócio e ignora detalhes de implementação.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; DER (Diagrama Entidade-Relacionamento).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Lógico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Tradução do modelo conceitual para uma estrutura que o SGBD compreenda (tabelas e relações).&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; Modelo Relacional (Chaves Primárias e Estrangeiras).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Físico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Descrição técnica de como os dados são armazenados no hardware.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Elementos:&lt;/strong&gt; Tipos de arquivos, ordenação de registros, métodos de acesso e criação de &lt;u&gt;índices&lt;/u&gt; para performance.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Independência de Dados&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Capacidade de alterar um nível (ex: mudar o hardware no nível físico) sem impactar os níveis superiores (conceitual e lógico).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F270" t="n">
         <v>0</v>
       </c>
@@ -15112,7 +15149,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -15126,65 +15163,10 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
+          <t>Abordagem Orientada a Dados (Data-Driven) vs. Processos</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Representação abstrata e global dos dados da organização. Foca no negócio e ignora detalhes de implementação.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; DER (Diagrama Entidade-Relacionamento).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Lógico&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Tradução do modelo conceitual para uma estrutura que o SGBD compreenda (tabelas e relações).&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; Modelo Relacional (Chaves Primárias e Estrangeiras).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Nível Físico&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Descrição técnica de como os dados são armazenados no hardware.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Elementos:&lt;/strong&gt; Tipos de arquivos, ordenação de registros, métodos de acesso e criação de &lt;u&gt;índices&lt;/u&gt; para performance.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Independência de Dados&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Capacidade de alterar um nível (ex: mudar o hardware no nível físico) sem impactar os níveis superiores (conceitual e lógico).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F271" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="n">
-        <v>363</v>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>Abordagem Orientada a Dados (Data-Driven) vs. Processos</t>
-        </is>
-      </c>
-      <c r="E272" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Filosofia Data-Driven&lt;/strong&gt;
@@ -15203,33 +15185,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F272" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="n">
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
         <v>364</v>
       </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D272" t="inlineStr">
         <is>
           <t>Indicadores de Disponibilidade e Manutenção (Conceitos)</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E272" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Principais Indicadores de Tempo&lt;/strong&gt;
@@ -15256,33 +15238,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F273" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="n">
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
         <v>365</v>
       </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
         <is>
           <t>Gestão da Manutenção e Confiabilidade</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
+      <c r="D273" t="inlineStr">
         <is>
           <t>Engenharia de Confiabilidade (Modelagem Matemática)</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E273" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Distribuição Exponencial (Regime de Falhas Constantes)&lt;/strong&gt;
@@ -15317,6 +15299,59 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F273" t="n">
+        <v>0</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>366</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>BPM e BPMS</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;BPM (Business Process Management)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Natureza:&lt;/strong&gt; Disciplina de gestão (metodologia) e não apenas um software.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Gestão ponta a ponta. Ele é &lt;u&gt;transversal&lt;/u&gt;, atravessando silos departamentais e múltiplos sistemas.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;O Ciclo de Vida BPM&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Planejamento -&gt; Modelagem -&gt; Simulação -&gt; Execução -&gt; Monitoramento -&gt; Otimização.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;BPMS (O Suporte Tecnológico)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Ferramenta que automatiza a lógica do BPM. Pode ser um sistema independente que se "conecta" ao ERP para buscar ou inserir dados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Diferença de Hierarquia:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;O ERP é focado na &lt;u&gt;transação e registro&lt;/u&gt;. O BPM é focado no &lt;u&gt;fluxo e desempenho&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F274" t="n">
         <v>0</v>
       </c>
@@ -15326,7 +15361,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -15340,63 +15375,10 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>BPM e BPMS</t>
+          <t>CRM (Customer Relationship Management)</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;BPM (Business Process Management)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Natureza:&lt;/strong&gt; Disciplina de gestão (metodologia) e não apenas um software.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Foco:&lt;/strong&gt; Gestão ponta a ponta. Ele é &lt;u&gt;transversal&lt;/u&gt;, atravessando silos departamentais e múltiplos sistemas.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;O Ciclo de Vida BPM&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Planejamento -&gt; Modelagem -&gt; Simulação -&gt; Execução -&gt; Monitoramento -&gt; Otimização.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;BPMS (O Suporte Tecnológico)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Ferramenta que automatiza a lógica do BPM. Pode ser um sistema independente que se "conecta" ao ERP para buscar ou inserir dados.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Diferença de Hierarquia:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;O ERP é focado na &lt;u&gt;transação e registro&lt;/u&gt;. O BPM é focado no &lt;u&gt;fluxo e desempenho&lt;/u&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F275" t="n">
-        <v>0</v>
-      </c>
-      <c r="G275" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="n">
-        <v>367</v>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>CRM (Customer Relationship Management)</t>
-        </is>
-      </c>
-      <c r="E276" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Definição e Foco&lt;/strong&gt;
@@ -15420,6 +15402,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F275" t="n">
+        <v>0</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>368</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>axonomia de Software (Sistema vs. Aplicativo)</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Atua como intermediário entre o hardware e o usuário/aplicativo. Coordena as operações básicas do computador.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; &lt;u&gt;Sistemas Operacionais&lt;/u&gt; (Windows, Linux), Drivers de dispositivo e utilitários de sistema (desfragmentadores, compiladores).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Software Aplicativo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Programas projetados para permitir que o usuário realize tarefas específicas, profissionais ou pessoais.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Planilhas eletrônicas, processadores de texto, navegadores, ERPs, CRMs e bancos de dados.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F276" t="n">
         <v>0</v>
       </c>
@@ -15429,7 +15455,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -15443,54 +15469,10 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>axonomia de Software (Sistema vs. Aplicativo)</t>
+          <t>Aquisição de Software (Prateleira vs. Customizado)</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Software de Sistema&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Atua como intermediário entre o hardware e o usuário/aplicativo. Coordena as operações básicas do computador.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; &lt;u&gt;Sistemas Operacionais&lt;/u&gt; (Windows, Linux), Drivers de dispositivo e utilitários de sistema (desfragmentadores, compiladores).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Software Aplicativo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Papel:&lt;/strong&gt; Programas projetados para permitir que o usuário realize tarefas específicas, profissionais ou pessoais.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Exemplos:&lt;/strong&gt; Planilhas eletrônicas, processadores de texto, navegadores, ERPs, CRMs e bancos de dados.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F277" t="n">
-        <v>0</v>
-      </c>
-      <c r="G277" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="n">
-        <v>369</v>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>Aquisição de Software (Prateleira vs. Customizado)</t>
-        </is>
-      </c>
-      <c r="E278" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Software de Prateleira (Off-the-shelf)&lt;/strong&gt;
@@ -15511,33 +15493,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F278" t="n">
-        <v>0</v>
-      </c>
-      <c r="G278" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="n">
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
         <v>370</v>
       </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
+      <c r="D278" t="inlineStr">
         <is>
           <t>Indústria 4.0 (Conceitos e Paradigmas)</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr">
+      <c r="E278" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Origem e Definição&lt;/strong&gt;
@@ -15562,33 +15544,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F279" t="n">
-        <v>0</v>
-      </c>
-      <c r="G279" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="n">
+      <c r="F278" t="n">
+        <v>0</v>
+      </c>
+      <c r="G278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
         <v>371</v>
       </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
+      <c r="D279" t="inlineStr">
         <is>
           <t>Tecnologias Habilitadoras (Os 9 Pilares da Indústria 4.0)</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr">
+      <c r="E279" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Pilares de Processamento e Dados&lt;/strong&gt;
@@ -15615,33 +15597,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F280" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="n">
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
         <v>372</v>
       </c>
-      <c r="B281" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
+      <c r="C280" t="inlineStr">
         <is>
           <t>Taxas</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
+      <c r="D280" t="inlineStr">
         <is>
           <t>Taxas Reais, Nominais e Impacto do IR (Equação de Fisher)</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
+      <c r="E280" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos de Base&lt;/strong&gt;
@@ -15683,33 +15665,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F281" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="n">
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
         <v>373</v>
       </c>
-      <c r="B282" t="inlineStr">
+      <c r="B281" t="inlineStr">
         <is>
           <t>Contabilidade De Custos</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
+      <c r="C281" t="inlineStr">
         <is>
           <t>Equivalentes de Produção</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
+      <c r="D281" t="inlineStr">
         <is>
           <t>Equivalente de Produção e Custeio por Processo</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
+      <c r="E281" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Equivalente de Produção (EP)&lt;/strong&gt;
@@ -15738,10 +15720,10 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F282" t="n">
-        <v>0</v>
-      </c>
-      <c r="G282" t="n">
+      <c r="F281" t="n">
+        <v>0</v>
+      </c>
+      <c r="G281" t="n">
         <v>0</v>
       </c>
     </row>

--- a/banco_de_dados/flashcards.xlsx
+++ b/banco_de_dados/flashcards.xlsx
@@ -1099,8 +1099,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>24</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1119,17 +1121,33 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;Manutenção não-planejada&lt;/b&gt;
-&lt;ul&gt;
-	&lt;li&gt;Corretiva&lt;/li&gt;
-&lt;/ul&gt;
-&lt;b&gt;Manutenção planejada&lt;/b&gt;
-&lt;ul&gt;
-	&lt;li&gt;Corretiva&lt;/li&gt;
-	&lt;li&gt;Preventiva&lt;/li&gt;
-	&lt;li&gt;Preditiva&lt;/li&gt;
-	&lt;li&gt;Prescritiva&lt;/li&gt;
-	&lt;li&gt;Detectiva&lt;/li&gt;
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Manutenção Não-Planejada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Corretiva Emergencial:&lt;/strong&gt; Atuação após falha funcional súbita.
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Padrão Visual:&lt;/strong&gt; Quebra abrupta que ocorre antes do tempo previsto ou sem aviso dos indicadores.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Manutenção Planejada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Preventiva:&lt;/strong&gt; Atuação baseada em &lt;u&gt;intervalos fixos&lt;/u&gt; (Tempo, Ciclos, Km).
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Gatilho:&lt;/strong&gt; Calendário ou horímetro. A troca ocorre mesmo se o item estiver em perfeitas condições. No gráfico, os intervalos são constantes ($\Delta t$).&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Preditiva:&lt;/strong&gt; Atuação baseada no &lt;u&gt;estado real&lt;/u&gt; via monitoramento de variáveis (Vibração, Temperatura, Termografia).
+        &lt;ul&gt;
+          &lt;li&gt;&lt;strong&gt;Gatilho:&lt;/strong&gt; Quando a variável monitorada atinge um limite de alerta. O intervalo entre intervenções é variável.&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Corretiva Planejada:&lt;/strong&gt; Estratégia de "rodar até falhar", mas com logística e recursos já prontos para a troca imediata após o limite de desempenho.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Detectiva:&lt;/strong&gt; Focada em sistemas de proteção (ex: alarmes, geradores de reserva). Busca identificar "falhas ocultas" que só seriam percebidas em uma emergência.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Prescritiva:&lt;/strong&gt; Evolução da preditiva que utiliza análise de dados para sugerir "o que fazer" para evitar a falha, agindo na causa raiz operacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
 &lt;/ul&gt;</t>
         </is>
       </c>
@@ -1137,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1199,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1236,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1257,20 +1275,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>etapas do FMEA (Análise de Modo e Efeitos de Falha)</t>
+          <t>etapas da Análise de Modo e Efeitos de Falha (FMEA - Failure Mode and Effect Analysis)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
-	&lt;li&gt;Função do equipamento&lt;/li&gt;
-	&lt;li&gt;Falha funcional&lt;/li&gt;
-	&lt;li&gt;Componente&lt;/li&gt;
-	&lt;li&gt;Modo (s) de falha potencial&lt;/li&gt;
-	&lt;li&gt;Efeito (s) potencial (is) da falha&lt;/li&gt;
-	&lt;li&gt;Causa (s) potencial (is) de falha&lt;/li&gt;
-	&lt;li&gt;Controles atuais&lt;/li&gt;
-	&lt;li&gt;Frequência do processo atual&lt;/li&gt;
+	&lt;li&gt;Definição e Identificação &lt;ol&gt; &lt;li&gt;Função do equipament&lt;/li&gt; &lt;li&gt;Falha funcional&lt;/li&gt; &lt;li&gt;Componente&lt;/li&gt; &lt;li&gt;Modo (s) de falha potencial&lt;/li&gt; &lt;li&gt;Efeito (s) potencial (is) da falha&lt;/li&gt; &lt;li&gt;Causa (s) potencial (is) de falha&lt;/li&gt; &lt;li&gt;Controles atuais&lt;/li&gt; &lt;li&gt;Frequência do processo atual&lt;/li&gt; &lt;/ol&gt;&lt;/li&gt;
+	&lt;li&gt;quantificação do risco de cada modo de falha &lt;ul&gt; &lt;li&gt;usando um número de prioridade de risco (NPR) &lt;ul&gt; &lt;li&gt;NPR = SEV x OCC x DET &lt;ul&gt; &lt;li&gt;Gravidade ou Severidade (SEV)&lt;/li&gt; &lt;li&gt;Probabilidade de ocorrência (OCC)&lt;/li&gt; &lt;li&gt;Probabilidade de detecção (DET)&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;minimizar o risco &lt;ul&gt; &lt;li&gt;priorização pelo NPR &lt;ul&gt; &lt;li&gt;20% principais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Implementando Soluções&lt;/li&gt;
 &lt;/ol&gt;</t>
         </is>
       </c>
@@ -1278,12 +1292,14 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>41</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1297,7 +1313,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Etapas do processo do RCFA</t>
+          <t>Etapas do processo da análise da causa raiz da falha (RCFA - Root Cause FailureAnalisys)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1316,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1353,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -5128,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
@@ -5161,12 +5177,14 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
-        <v>202</v>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -5185,14 +5203,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Qualquer dado gerado ou acumulado</t>
+          <t>Qualquer dado gerado ou acumulado pelos entes públicos que não esteja sob sigilo ou sob restrição de acesso nos termos da Lei nº 12.527, de 18 de novembro de 2011 (Lei de Acesso à Informação);</t>
         </is>
       </c>
       <c r="F121" t="n">
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122">
@@ -5258,13 +5276,13 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>207</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5279,25 +5297,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Laboratório de inovação</t>
+          <t>Registros de referência</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Espaço aberto à participação e à colaboração da sociedade para o desenvolvimento de ideias, de ferramentas e de métodos inovadores para a gestão pública, a prestação de serviços públicos e a participação do cidadão para o exercício do controle sobre a administração pública;</t>
+          <t>Informação íntegra e precisa oriunda de uma ou mais fontes de dados, centralizadas ou descentralizadas, sobre elementos fundamentais para a prestação de serviços e para a gestão de políticas públicas;</t>
         </is>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>208</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5312,25 +5330,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Registros de referência</t>
+          <t>Transparência ativa</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Informação íntegra e precisa oriunda de uma ou mais fontes de dados, centralizadas ou descentralizadas, sobre elementos fundamentais para a prestação de serviços e para a gestão de políticas públicas;</t>
+          <t>Disponibilização de dados pela administração pública independentemente de solicitações.</t>
         </is>
       </c>
       <c r="F125" t="n">
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5345,43 +5363,10 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Transparência ativa</t>
+          <t>Governo Digital</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
-        <is>
-          <t>Disponibilização de dados pela administração pública independentemente de solicitações.</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Lei nº 14.129-2021</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Governo Digital</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação padrão digital
@@ -5431,14 +5416,23 @@
       &lt;li&gt;classificação conforme a LAI&lt;/li&gt;
       &lt;li&gt;assegurar preservação e acesso
         &lt;ul&gt;
-          &lt;li&gt;normas arquivísticas&lt;/li&gt;
+          &lt;li&gt;normas da instituição arquivística pública responsável (ex: Arq. Nacional)&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;prestação digital de serviços
     &lt;ul&gt;
-      &lt;li&gt;tecnologias acessíveis&lt;/li&gt;
+      &lt;li&gt;tecnologias acessíveis à população
+&lt;ul&gt;
+	&lt;li&gt;incluindo
+&lt;ul&gt;
+	&lt;li&gt;baixa renda&lt;/li&gt;
+	&lt;li&gt;áreas rurais ou isoladas&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
       &lt;li&gt;atendimento presencial
         &lt;ul&gt;
           &lt;li&gt;permanece como direito&lt;/li&gt;
@@ -5453,42 +5447,43 @@
       &lt;li&gt;entes federados podem elaborar a própria
         &lt;ul&gt;
           &lt;li&gt;alinhada à nacional&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+&lt;li style="color: #e74c3c;"&gt;Independe de delegação formal ou Lei Complementar (Autonomia)&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B127" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>Redes de Conhecimento</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Criadas pelo Poder Executivo federal&lt;/li&gt;
@@ -5498,35 +5493,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B128" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Componentes do Governo Digital</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt;
@@ -5537,33 +5532,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
         <v>212</v>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>Princípios do governo digital</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;acesso centralizado&lt;/li&gt;
@@ -5576,33 +5571,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
         <v>213</v>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Base Nacional de Serviços Públicos</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;estrutura destinada a concentrar informações essenciais sobre a oferta de serviços públicos&lt;/li&gt;
@@ -5611,17 +5606,51 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Plataformas de Governo Digital</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instrumentos para que os entes federativos disponibilizem seus serviços públicos
+devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt; padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
+        </is>
+      </c>
       <c r="F131" t="n">
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5636,13 +5665,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Plataformas de Governo Digital</t>
+          <t>Prestação Digital dos Serviços Públicos</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">instrumentos para que os entes federativos disponibilizem seus serviços públicos
-devem oferecer, no mínimo, uma ferramenta que permita &lt;ul&gt; &lt;li&gt;a solicitação&lt;/li&gt; &lt;li&gt;e o acompanhamento dos serviços e um painel destinado ao monitoramento do desempenho&lt;/li&gt; &lt;/ul&gt; padrões de interoperabilidade e integrar dados entre órgãos e entidades </t>
+          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -5653,58 +5681,25 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
+      <c r="A133" t="n">
+        <v>216</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Engenharia do Trabalho</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Prestação Digital dos Serviços Públicos</t>
+          <t>Normas Regulamentadoras do Trabalho</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
-        <is>
-          <t>Os órgãos e entidades devem adotar ações para garantir eficiência, qualidade e atualização contínua &lt;ul&gt; &lt;li&gt;manter atualizadas &lt;ul&gt; &lt;li&gt;Cartas de Serviços ao Usuário&lt;/li&gt; &lt;li&gt;Base Nacional de Serviços Públicos&lt;/li&gt; &lt;li&gt;Plataformas de Governo Digital&lt;/li&gt; &lt;li&gt;informações institucionais&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;melhoria dos serviços&lt;/li&gt; &lt;li&gt;integração dos serviços&lt;/li&gt; &lt;li&gt;exigências simplificadas&lt;/li&gt; &lt;li&gt;evitar a duplicação de registros&lt;/li&gt; &lt;li&gt;dados interoperáveis&lt;/li&gt; &lt;li&gt;políticas públicas com base em dados e evidências&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>216</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Normas Regulamentadoras do Trabalho</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;obrigações, direitos e deveres&lt;/li&gt;
@@ -5713,35 +5708,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>217</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>NR 1</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 &lt;li&gt;Disposições Gerais e Gerenciamento de Riscos Ocupacionais&lt;/li&gt;
@@ -5752,33 +5747,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F135" t="n">
-        <v>0</v>
-      </c>
-      <c r="G135" t="n">
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
+    <row r="135">
+      <c r="A135" t="n">
         <v>219</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>NR 3</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Embargo e Interdição&lt;/li&gt;
@@ -5788,6 +5783,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>220</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Engenharia do Trabalho</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NR 4</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
+	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F136" t="n">
         <v>0</v>
       </c>
@@ -5797,7 +5826,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -5811,27 +5840,24 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NR 4</t>
+          <t>NR 5</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;SERVIÇOS ESPECIALIZADOS EM ENGENHARIA DE SEGURANÇA E EM MEDICINA DO TRABALHO&lt;/li&gt;
-	&lt;li&gt;Profissionais do SESMT &lt;ul&gt; &lt;li&gt;Médico do Trabalho;&lt;/li&gt; &lt;li&gt;Engenheiro de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Técnico de Segurança do Trabalho;&lt;/li&gt; &lt;li&gt;Enfermeiro do Trabalho e&lt;/li&gt; &lt;li&gt;Auxiliar ou Técnico em Enfermagem do Trabalho.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -5845,41 +5871,10 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NR 5</t>
+          <t>NR 6</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
-        <is>
-          <t>COMISSÃO INTERNA DE PREVENÇÃO DE ACIDENTES</t>
-        </is>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>222</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Engenharia do Trabalho</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>NR 6</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;EQUIPAMENTO DE PROTEÇÃO INDIVIDUAL - EPI&lt;/li&gt;
@@ -5892,33 +5887,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
+    <row r="139">
+      <c r="A139" t="n">
         <v>223</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>NR 7</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;PROGRAMA DE CONTROLE MÉDICO DE SAÚDE OCUPACIONAL&lt;/li&gt;
@@ -5926,35 +5921,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>0</v>
-      </c>
-      <c r="G140" t="n">
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
+    <row r="140">
+      <c r="A140" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>NR 8</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E140" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;EDIFICAÇÕES&lt;/li&gt;
@@ -5963,33 +5958,33 @@
 </t>
         </is>
       </c>
-      <c r="F141" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" t="n">
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" t="n">
+    <row r="141">
+      <c r="A141" t="n">
         <v>225</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D141" t="inlineStr">
         <is>
           <t>NR 9</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E141" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;AVALIAÇÃO E CONTROLE DAS EXPOSIÇÕES OCUPACIONAIS A AGENTES FÍSICOS, QUÍMICOS E BIOLÓGICOS&lt;/li&gt;
@@ -6001,33 +5996,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="G142" t="n">
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="142">
+      <c r="A142" t="n">
         <v>226</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D142" t="inlineStr">
         <is>
           <t>produção intermitente</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="E142" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de fabricação flexível&lt;/li&gt;
@@ -6038,33 +6033,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F143" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" t="n">
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="143">
+      <c r="A143" t="n">
         <v>227</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>cable belt (correia de cabo)</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E143" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;sistema de transporte de materiais de alta eficiência&lt;/li&gt;
@@ -6074,33 +6069,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F144" t="n">
-        <v>0</v>
-      </c>
-      <c r="G144" t="n">
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="144">
+      <c r="A144" t="n">
         <v>228</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
+      <c r="D144" t="inlineStr">
         <is>
           <t>KPIs (Key Performance Indicators) na Gestão de Projetos (Kerzner, 2009)</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E144" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;medem a qualidade do processo interno durante a execução&lt;/li&gt;
@@ -6109,33 +6104,33 @@
 </t>
         </is>
       </c>
-      <c r="F145" t="n">
-        <v>0</v>
-      </c>
-      <c r="G145" t="n">
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="145">
+      <c r="A145" t="n">
         <v>229</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
+      <c r="D145" t="inlineStr">
         <is>
           <t>Planejamento Estratégico na Gestão de Projetos (Kerzner, 2015)</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="E145" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;seleção e priorização de projetos &lt;ul&gt; &lt;li&gt;devem ser feitas com base na disponibilidade de recursos qualificados&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6145,33 +6140,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="G146" t="n">
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
+    <row r="146">
+      <c r="A146" t="n">
         <v>230</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>BI (Business Intelligence)</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E146" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Dados estruturados&lt;/li&gt;
@@ -6180,33 +6175,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="G147" t="n">
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="147">
+      <c r="A147" t="n">
         <v>231</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>licenciamento de patentes</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E147" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;proteção de ativos intelectuais &lt;ul&gt; &lt;li&gt;mapeamento de competências&lt;/li&gt; &lt;li&gt;proteção de PI (Propriedade Intelectual)&lt;/li&gt; &lt;li&gt;alinhamento com os objetivos de negócio&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6217,33 +6212,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="G148" t="n">
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="148">
+      <c r="A148" t="n">
         <v>233</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>Índices Financeiros</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t xml:space="preserve">&lt;ul&gt;
 	&lt;li&gt;ÍNDICES DE LIQUIDEZ &lt;ul&gt; &lt;li&gt;Índice de liquidez corrente = Ativo circulante/Passivo circulante&lt;/li&gt; &lt;li&gt;Indice de liquidez seca = (Ativo circulante – Estoques)/Passivo circulante&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -6254,33 +6249,33 @@
 </t>
         </is>
       </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="G149" t="n">
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="149">
+      <c r="A149" t="n">
         <v>234</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
         <is>
           <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>Fatores que Aumentam o Risco de Mercado (Renda Fixa)</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Maior Prazo de Vencimento&lt;/li&gt;
@@ -6290,35 +6285,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" t="n">
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
+    <row r="150">
+      <c r="A150" t="inlineStr">
         <is>
           <t>235</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
         <is>
           <t>Engenharia de Produto</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D150" t="inlineStr">
         <is>
           <t>Processo de Desenvolvimento de Produto</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E150" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;I. PRÉ-DESENVOLVIMENTO&lt;/strong&gt;
@@ -6351,35 +6346,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="G151" t="n">
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>236</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
         <is>
           <t>Gestão da Produção e Operações</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>sistema ERP</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Arquitetura Técnica&lt;/strong&gt;
@@ -6417,16 +6412,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>237</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Back-office vs. Front-office</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F152" t="n">
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -6435,49 +6464,15 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Back-office vs. Front-office</t>
+          <t>Hierarquia na Aquisição de Tecnologia</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Back-office (Retaguarda) &lt;ul&gt; &lt;li&gt;Processos internos que o cliente não vê&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Contabilidade&lt;/li&gt; &lt;li&gt;Estoque&lt;/li&gt; &lt;li&gt;RH&lt;/li&gt; &lt;li&gt;Produção&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Front-office (Frente) &lt;ul&gt; &lt;li&gt;Interface direta com o mercado e o cliente&lt;/li&gt; &lt;li&gt;ex: &lt;ul&gt; &lt;li&gt;Vendas/CRM&lt;/li&gt; &lt;li&gt;Suporte&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>238</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Hierarquia na Aquisição de Tecnologia</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;1º Requisitos de Negócio: Consulta ao Gestor da Área (o que precisa ser feito).&lt;/li&gt;
@@ -6486,16 +6481,50 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>239</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Processos Decisórios</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Critérios de Decisão no AHP</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
+	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F154" t="n">
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -6504,49 +6533,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Processos Decisórios</t>
+          <t>Gestão da Tecnologia</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Critérios de Decisão no AHP</t>
+          <t>Tendências e Tecnologias em Gestão da Informação</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Devem ser completos, operacionais e NÃO REDUNDANTES&lt;/li&gt;
-	&lt;li&gt;Hierarquia em níveis (Objetivo -&gt; Critérios -&gt; Subcritérios -&gt; Alternativas) com comparações paridárias (Matriz de Saaty).&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F155" t="n">
-        <v>0</v>
-      </c>
-      <c r="G155" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>240</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Gestão da Tecnologia</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Tendências e Tecnologias em Gestão da Informação</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Computação em Nuvem (Cloud Computing)&lt;/li&gt;
@@ -6556,33 +6551,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F156" t="n">
-        <v>0</v>
-      </c>
-      <c r="G156" t="n">
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" t="n">
+    <row r="156">
+      <c r="A156" t="n">
         <v>241</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>Gestão da Inovação</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>EDI (Electronic Data Interchange)</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Troca eletrônica de documentos comerciais entre sistemas em um formato padrão (sem papel).&lt;/li&gt;
@@ -6592,33 +6587,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F157" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" t="n">
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="157">
+      <c r="A157" t="n">
         <v>242</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
+      <c r="D157" t="inlineStr">
         <is>
           <t>Técnica Nominal de Grupo (TNG)</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="E157" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Processo estruturado de tomada de decisão em grupo que combina geração individual de ideias com julgamento coletivo.&lt;/li&gt;
@@ -6628,33 +6623,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F158" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" t="n">
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="158">
+      <c r="A158" t="n">
         <v>243</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
         <is>
           <t>Processos Decisórios</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D158" t="inlineStr">
         <is>
           <t>Delphi x Brainstorming x TNG (Técnica nominal de grupo)</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E158" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Delphi&lt;/b&gt;: Especialistas anônimos, não se encontram, várias rodadas.&lt;/li&gt;
@@ -6663,33 +6658,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
+      <c r="F158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G158" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="159">
+      <c r="A159" t="n">
         <v>244</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D159" t="inlineStr">
         <is>
           <t>Gestão Ambiental: Reativa vs. Proativa</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E159" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Reativa (Controle)&lt;/b&gt;: Foco no "fim de linha" (end-of-pipe). Preocupação com tratamento de efluentes e disposição de resíduos.&lt;/li&gt;
@@ -6698,33 +6693,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F159" t="n">
         <v>2</v>
       </c>
-      <c r="G160" t="n">
+      <c r="G159" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
+    <row r="160">
+      <c r="A160" t="n">
         <v>245</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>Variável Ambiental no Negócio</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Fator Crítico: Depende do grau de conscientização e comprometimento da Alta Administração.&lt;/li&gt;
@@ -6733,33 +6728,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F161" t="n">
-        <v>0</v>
-      </c>
-      <c r="G161" t="n">
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" t="n">
+    <row r="161">
+      <c r="A161" t="n">
         <v>246</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Classificação de Resíduos Sólidos (NBR 10.004)</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;Classe I (Perigosos): Apresentam periculosidade (inflamabilidade, corrosividade, toxicidade, etc.).&lt;/li&gt;
@@ -6768,33 +6763,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F162" t="n">
-        <v>0</v>
-      </c>
-      <c r="G162" t="n">
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" t="n">
+    <row r="162">
+      <c r="A162" t="n">
         <v>247</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D162" t="inlineStr">
         <is>
           <t>Ordem de Prioridade PNRS (Lei 12.305)</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E162" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Não geração.&lt;/li&gt;
@@ -6807,35 +6802,35 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
-      <c r="F163" t="n">
-        <v>0</v>
-      </c>
-      <c r="G163" t="n">
+      <c r="F162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G162" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
+    <row r="163">
+      <c r="A163" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>Diferença entre Estéril e Rejeito (Mineração) e Métodos de Disposição</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="E163" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;&lt;b&gt;Estéril&lt;/b&gt;: Material removido para acessar a jazida. NÃO passa pelo processo de beneficiamento (é rocha/solo "bruto").&lt;/li&gt;
@@ -6844,33 +6839,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F164" t="n">
-        <v>0</v>
-      </c>
-      <c r="G164" t="n">
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" t="n">
+    <row r="164">
+      <c r="A164" t="n">
         <v>249</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>Cadeia de Valor (Michael Porter)</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>D&lt;ul&gt;
 	&lt;li&gt;esagregação da organização em atividades estrategicamente relevantes.&lt;/li&gt;
@@ -6881,67 +6876,67 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>250</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Informática</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Lei nº 14.129-2021</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Número suficiente para identificação</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F165" t="n">
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Informática</t>
+          <t>Matemática Financeira</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lei nº 14.129-2021</t>
+          <t>Análise de Investimentos</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Número suficiente para identificação</t>
+          <t>Critérios de Viabilidade e Relações (VPL, TIR e TMA)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;CPF e CNPJ &lt;ul&gt; &lt;li&gt;número suficiente para identificação&lt;/li&gt; &lt;li&gt;gratuidade da inscrição e das alterações nesses cadastros.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;CPF &lt;ul&gt; &lt;li&gt;constar em diversos cadastros e documentos emitidos&lt;/li&gt; &lt;li&gt;Se requerente não inscrito &lt;ul&gt; &lt;li&gt;próprio órgão de identificação realiza inscrição &lt;ul&gt; &lt;li&gt;Se possui integração com a base da Receita&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F166" t="n">
-        <v>0</v>
-      </c>
-      <c r="G166" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>251</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Matemática Financeira</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Análise de Investimentos</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Critérios de Viabilidade e Relações (VPL, TIR e TMA)</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Reinvestimento&lt;/strong&gt;
@@ -6973,16 +6968,47 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>256</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Aspectos Introdutórios</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Princípio da Entidade</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Autonomia da pessoa jurídica</t>
+        </is>
+      </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -6991,46 +7017,15 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Aspectos Introdutórios</t>
+          <t>Contabilidade Básica</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Princípio da Entidade</t>
+          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
-        <is>
-          <t>Autonomia da pessoa jurídica</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>257</v>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>VARIAÇÕES NO PATRIMÔNIO LÍQUIDO</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
         <is>
           <t>Entradas e saídas de capital
 &lt;ul&gt;
@@ -7048,18 +7043,74 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Contabilidade Gerencial</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Contabilidade Básica</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Receitas</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;aumento nos ativos
+    &lt;ul&gt;
+      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;diminuição de passivo
+    &lt;ul&gt;
+      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;reconhecimento
+    &lt;ul&gt;
+      &lt;li&gt;acarreta aumento do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;transações com sócios
+    &lt;ul&gt;
+      &lt;li&gt;não representam receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F169" t="n">
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="A170" t="n">
+        <v>259</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -7073,34 +7124,35 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Receitas</t>
+          <t>Despesas</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
-  &lt;li&gt;aumento nos ativos
-    &lt;ul&gt;
-      &lt;li&gt;dinheiro ou direitos&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;diminuição de passivo
-    &lt;ul&gt;
-      &lt;li&gt;sem entrega de ativo&lt;/li&gt;
+  &lt;li&gt;consumo de bens ou serviços
+    &lt;ul&gt;
+      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;representam
+    &lt;ul&gt;
+      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
+      &lt;li&gt;aumento no passivo&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;reconhecimento
     &lt;ul&gt;
-      &lt;li&gt;acarreta aumento do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem todo aumento representa receita&lt;/li&gt;
+      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
+        &lt;ul&gt;
+          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
   &lt;li&gt;transações com sócios
     &lt;ul&gt;
-      &lt;li&gt;não representam receitas&lt;/li&gt;
+      &lt;li&gt;não representam despesas&lt;/li&gt;
     &lt;/ul&gt;
   &lt;/li&gt;
 &lt;/ul&gt;</t>
@@ -7115,7 +7167,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -7129,67 +7181,10 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Despesas</t>
+          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;consumo de bens ou serviços
-    &lt;ul&gt;
-      &lt;li&gt;esforço para obter receitas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;representam
-    &lt;ul&gt;
-      &lt;li&gt;diminuição nos ativos&lt;/li&gt;
-      &lt;li&gt;aumento no passivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;reconhecimento
-    &lt;ul&gt;
-      &lt;li&gt;acarreta diminuição do Patrimônio Líquido
-        &lt;ul&gt;
-          &lt;li&gt;nem toda diminuição representa despesa&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;transações com sócios
-    &lt;ul&gt;
-      &lt;li&gt;não representam despesas&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F171" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>260</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Contabilidade Gerencial</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Contabilidade Básica</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>CONTAS E RESPECTIVAS CLASSIFICAÇÕES</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
     &lt;li&gt;Contas contábeis
@@ -7271,33 +7266,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F172" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" t="n">
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="n">
+    <row r="172">
+      <c r="A172" t="n">
         <v>261</v>
       </c>
-      <c r="B173" t="inlineStr">
+      <c r="B172" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>Outras Equivalências e Negações</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E172" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Negações da conjunção (e) para a forma condicional
@@ -7345,35 +7340,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F173" t="n">
-        <v>0</v>
-      </c>
-      <c r="G173" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
         <is>
           <t>262</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr">
+      <c r="B173" t="inlineStr">
         <is>
           <t>Raciocínio Lógico</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C173" t="inlineStr">
         <is>
           <t>Equivalências e Negações Lógicas</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D173" t="inlineStr">
         <is>
           <t>Álgebra de proposições</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E173" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Propriedade Comutativa
@@ -7425,33 +7420,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F174" t="n">
-        <v>0</v>
-      </c>
-      <c r="G174" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
+      <c r="F173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
         <v>263</v>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B174" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>Relações de Coordenação entre Orações e entre Termos da Oração</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>Os Três Tipos de Discurso</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>Discurso Direto
 &lt;ul&gt;
@@ -7469,33 +7464,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F175" t="n">
-        <v>0</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
+      <c r="F174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
         <v>264</v>
       </c>
-      <c r="B176" t="inlineStr">
+      <c r="B175" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>Semântica</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>Prescrever vs. Facultativo</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="E175" t="inlineStr">
         <is>
           <t>Prescrever
 &lt;ul&gt;
@@ -7505,35 +7500,35 @@
 Facultativo &lt;ul&gt; &lt;li&gt;Significa opcional, que depende da vontade. É uma escolha.&lt;/li&gt; &lt;li&gt;Ex:&lt;/li&gt; &lt;li&gt;&lt;ul&gt; &lt;li&gt;O voto é facultativo para analfabetos.&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F176" t="n">
-        <v>0</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
         <is>
           <t>265</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr">
+      <c r="B176" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>Interoperabilidade de Dados entre Órgãos Públicos</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E176" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;interoperabilidade de dados
@@ -7601,33 +7596,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F177" t="n">
-        <v>0</v>
-      </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>266</v>
-      </c>
-      <c r="B178" t="inlineStr">
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
+      <c r="C177" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
+      <c r="D177" t="inlineStr">
         <is>
           <t>Domicílio Eletrônico</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E177" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;comunicações, notificações e intimações por meios digitais
@@ -7635,7 +7632,11 @@
       &lt;li&gt;opção do usuário
         &lt;ul&gt;
           &lt;li&gt;não constitui direito se indisponível&lt;/li&gt;
-          &lt;li&gt;pode encerrar recebimento a qualquer momento&lt;/li&gt;
+          &lt;li&gt;pode encerrar recebimento a qualquer momento
+&lt;ul&gt;
+	&lt;li&gt;sem necessidade de justificar&lt;/li&gt;
+&lt;/ul&gt;
+&lt;/li&gt;
         &lt;/ul&gt;
       &lt;/li&gt;
     &lt;/ul&gt;
@@ -7662,33 +7663,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F178" t="n">
-        <v>0</v>
-      </c>
-      <c r="G178" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
         <v>267</v>
       </c>
-      <c r="B179" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
+      <c r="C178" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
+      <c r="D178" t="inlineStr">
         <is>
           <t>Laboratórios de Inovação</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="E178" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;instituídos pelos entes públicos
@@ -7746,35 +7747,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
+      <c r="F178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G178" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
         <is>
           <t>268</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr">
+      <c r="B179" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
+      <c r="C179" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D179" t="inlineStr">
         <is>
           <t>Governança, Gestão de Riscos, Controle e Auditoria</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E179" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;governança, gestão de riscos, controle e auditoria
@@ -7824,35 +7825,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F180" t="n">
-        <v>0</v>
-      </c>
-      <c r="G180" t="n">
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
+    <row r="180">
+      <c r="A180" t="inlineStr">
         <is>
           <t>269</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr">
+      <c r="B180" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
+      <c r="C180" t="inlineStr">
         <is>
           <t>Lei nº 14.129-2021</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
+      <c r="D180" t="inlineStr">
         <is>
           <t>Diretrizes da Lei 14.129/2021</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E180" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
       &lt;li&gt;respeito a normas existentes
@@ -7928,33 +7929,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="n">
+    <row r="181">
+      <c r="A181" t="n">
         <v>270</v>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Matemática Financeira</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Análise de Investimentos</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>Taxa Interna de Retorno Modificada (TIRM)</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
 	&lt;li&gt;transporte de fluxos &lt;ul&gt; &lt;li&gt;negativos para Valor Presente &lt;ul&gt; &lt;li&gt;Taxa de Financiamento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;li&gt;positivos para Valor Futuro &lt;ul&gt; &lt;li&gt;Taxa de Reinvestimento&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
@@ -7963,6 +7964,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>271</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Análise de Investimentos</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>PAYBACK SIMPLES</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
@@ -7972,7 +8004,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -7986,24 +8018,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>PAYBACK SIMPLES</t>
+          <t>PAYBACK DESCONTADO</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>limitações &lt;ul&gt; &lt;li&gt;Não considera o Valor do dinheiro no tempo.&lt;/li&gt; &lt;li&gt;Despreza os Fluxos futuros após o Capital ter sido recuperado&lt;/li&gt; &lt;li&gt;não mede a Rentabilidade, apenas o tempo de retorno.&lt;/li&gt; &lt;/ul&gt;</t>
+          <t>&lt;ul&gt;
+	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
+&lt;/ul&gt;</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
-        <v>272</v>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -8017,76 +8053,41 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>PAYBACK DESCONTADO</t>
+          <t>Taxa (ou Índice) de Rentabilidade</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;forma de mitigar a limitação do Payback simples&lt;/li&gt;
-&lt;/ul&gt;</t>
+          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
         </is>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
+      <c r="A185" t="n">
+        <v>275</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Conhecimentos Específicos</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Análise de Investimentos</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Taxa (ou Índice) de Rentabilidade</t>
+          <t>Processo de Gestão de Risco</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
-        <is>
-          <t>$$IL = 1 + \frac{VPL}{Inv.\ Inicial}$$</t>
-        </is>
-      </c>
-      <c r="F185" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>275</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Processo de Gestão de Risco</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Processo de gestão de riscos
@@ -8152,68 +8153,68 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-      <c r="G186" t="n">
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
+    <row r="186">
+      <c r="A186" t="inlineStr">
         <is>
           <t>276</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D186" t="inlineStr">
         <is>
           <t>Subdivisão do Conhecimento Organizacional</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E186" t="inlineStr">
         <is>
           <t xml:space="preserve">Tácito &lt;ul&gt; &lt;li&gt;reside nas pessoas&lt;/li&gt; &lt;li&gt;é subjetivo, pessoal, difícil de formalizar&lt;/li&gt; &lt;li&gt;dimensão técnica &lt;ul&gt; &lt;li&gt;&lt;i&gt;know-how&lt;/i&gt;&lt;/li&gt; &lt;li&gt;habilidades motoras&lt;/li&gt; &lt;li&gt;perceptivas difíceis de verbalizar&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;li&gt;dimensão cognitiva &lt;ul&gt; &lt;li&gt;modelos mentais&lt;/li&gt; &lt;li&gt;crenças&lt;/li&gt; &lt;li&gt;valores&lt;/li&gt; &lt;li&gt;percepções&lt;/li&gt; &lt;li&gt;intuições&lt;/li&gt; &lt;/ul&gt; &lt;/li&gt; &lt;/ul&gt;
 Explícito &lt;ul&gt; &lt;li&gt;pode ser formalizado&lt;/li&gt; &lt;li&gt;é documentado, codificado e sistematizado em procedimentos, manuais, relatórios, sistemas de informação, bancos de dados&lt;/li&gt; &lt;li&gt;mais fácil de ser transferido entre pessoas, de ser replicado e armazenado&lt;/li&gt; &lt;/ul&gt;
 </t>
         </is>
       </c>
-      <c r="F187" t="n">
-        <v>0</v>
-      </c>
-      <c r="G187" t="n">
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="n">
+    <row r="187">
+      <c r="A187" t="n">
         <v>277</v>
       </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
+      <c r="D187" t="inlineStr">
         <is>
           <t>Níveis de Aprendizado Organizacional</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="E187" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Aprendizado de Círculo Simples (Single-loop Learning)
@@ -8266,6 +8267,40 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>278</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Gestão do Conhecimento</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>teoria da organização e da gestão da informação</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
+	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
@@ -8275,7 +8310,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -8284,49 +8319,15 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Gestão do Conhecimento</t>
+          <t>Gestão da Inovação</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>teoria da organização e da gestão da informação</t>
+          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;organização é vista como um sistema aberto que processa informações para se adaptar e sobreviver&lt;/li&gt;
-	&lt;li&gt;objetivo final &lt;ul&gt; &lt;li&gt;capacidade de dar sentido e interpretar o ambiente externo &lt;ul&gt; &lt;li&gt;permite à empresa tomar decisões estratégicas e agir&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F189" t="n">
-        <v>0</v>
-      </c>
-      <c r="G189" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>279</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>Gestão da Inovação</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>ICT – Instituições de Ciência, Tecnologia e Inovação</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;definição e natureza jurídica&lt;/strong&gt;
@@ -8395,33 +8396,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F190" t="n">
-        <v>0</v>
-      </c>
-      <c r="G190" t="n">
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="n">
+    <row r="190">
+      <c r="A190" t="n">
         <v>281</v>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D190" t="inlineStr">
         <is>
           <t>fundamentos da gestão para excelência do Modelo de Excelência da Gestão (MEG) da Fundação Nacional da Qualidade (FNQ)</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="E190" t="inlineStr">
         <is>
           <t>&lt;ol&gt;
 	&lt;li&gt;Pensamento Sistêmico&lt;/li&gt;
@@ -8435,6 +8436,37 @@
 &lt;/ol&gt;</t>
         </is>
       </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>282</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>índice de capacidade do processo (Cp)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
@@ -8444,7 +8476,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -8458,41 +8490,10 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>índice de capacidade do processo (Cp)</t>
+          <t>ISO 19443; ISO 26000; e ISO 45001</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
-        <is>
-          <t>Cp = (LSE−LIE)/6σ &lt;ul&gt; &lt;li&gt;LSE = Limite Superior de Especificação&lt;/li&gt; &lt;li&gt;LIE = Limite Inferior de Especificação&lt;/li&gt; &lt;li&gt;σ = DP do processo&lt;/li&gt; &lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>283</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>ISO 19443; ISO 26000; e ISO 45001</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;ISO 19443&lt;/strong&gt;
@@ -8519,35 +8520,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F193" t="n">
-        <v>0</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
         <is>
           <t>284</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>Benchmarking</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Benchmarking&lt;/strong&gt;
@@ -8577,6 +8578,40 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>285</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Ciclo PDCA</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
@@ -8586,7 +8621,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -8600,44 +8635,10 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Ciclo PDCA</t>
+          <t>Gestão da Qualidade Total (TQM)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-	&lt;li&gt;Idealizado &lt;ul&gt; &lt;li&gt;Walter Shewhart&lt;/li&gt; &lt;li&gt;década de 1930&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-	&lt;li&gt;Disseminador &lt;ul&gt; &lt;li&gt;William Deming&lt;/li&gt; &lt;li&gt;década de 1950&lt;/li&gt; &lt;/ul&gt;&lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>286</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade Total (TQM)</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
         <is>
           <t>"A qualidade é responsabilidade de todos." — W. Edwards Deming.
 &lt;ul&gt;
@@ -8727,33 +8728,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
         <v>287</v>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D196" t="inlineStr">
         <is>
           <t>Custos na TQM</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="E196" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;custos de conformidade&lt;/strong&gt;
@@ -8812,33 +8813,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
         <v>288</v>
       </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
+      <c r="D197" t="inlineStr">
         <is>
           <t>Gurus da Qualidade</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E197" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Walter A. Shewhart (Anos 20/30)&lt;/strong&gt;
@@ -8898,33 +8899,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="198">
+      <c r="A198" t="n">
         <v>289</v>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
+      <c r="D198" t="inlineStr">
         <is>
           <t>Waterfall (modelo cascata)</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E198" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;modelo sequencial e linear
@@ -8983,33 +8984,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F199" t="n">
-        <v>0</v>
-      </c>
-      <c r="G199" t="n">
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="199">
+      <c r="A199" t="n">
         <v>290</v>
       </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
+      <c r="D199" t="inlineStr">
         <is>
           <t>Extreme Programming (XP)</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="E199" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;valores fundamentais&lt;/strong&gt;
@@ -9086,33 +9087,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="200">
+      <c r="A200" t="n">
         <v>291</v>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
+      <c r="D200" t="inlineStr">
         <is>
           <t>Feature-Driven Development (FDD)</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E200" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceitos fundamentais&lt;/strong&gt;
@@ -9184,33 +9185,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
         <v>292</v>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>Lean Development (ou Lean Software Development - LSD)</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;filosofia central&lt;/strong&gt;
@@ -9272,33 +9273,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F202" t="n">
-        <v>0</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
         <v>293</v>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D202" t="inlineStr">
         <is>
           <t>Scrum</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E202" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;pilares do empirismo&lt;/strong&gt;
@@ -9387,33 +9388,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" t="n">
+    <row r="203">
+      <c r="A203" t="n">
         <v>294</v>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
         <is>
           <t>Gestão de Projetos</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D203" t="inlineStr">
         <is>
           <t>Kanban</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E203" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;princípios fundamentais&lt;/strong&gt;
@@ -9486,33 +9487,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
         <v>295</v>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
         <is>
           <t>Gestão do Conhecimento</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D204" t="inlineStr">
         <is>
           <t>Sinais de Mudança no Ambiente Externo (Ansoff)</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E204" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito de sinais de mudança&lt;/strong&gt;
@@ -9557,33 +9558,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F205" t="n">
-        <v>0</v>
-      </c>
-      <c r="G205" t="n">
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" t="n">
+    <row r="205">
+      <c r="A205" t="n">
         <v>296</v>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D205" t="inlineStr">
         <is>
           <t>SMED</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E205" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -9638,6 +9639,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>297</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Dimensões da Qualidade em Serviços</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;instalações físicas
+        &lt;ul&gt;
+          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;materiais
+        &lt;ul&gt;
+          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços explícitos
+        &lt;ul&gt;
+          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;serviços complementares
+        &lt;ul&gt;
+          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F206" t="n">
         <v>0</v>
       </c>
@@ -9647,7 +9704,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -9661,66 +9718,10 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Dimensões da Qualidade em Serviços</t>
+          <t>CCQ – Círculos de Controle de Qualidade</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Dimensões da Qualidade em Serviços (Modelo de Pacote)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;instalações físicas
-        &lt;ul&gt;
-          &lt;li&gt;infraestrutura e recursos de apoio necessários para a prestação&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;materiais
-        &lt;ul&gt;
-          &lt;li&gt;bens facilitadores consumidos ou fornecidos durante o processo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços explícitos
-        &lt;ul&gt;
-          &lt;li&gt;benefícios centrais, intrínsecos e observáveis pelos sentidos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;serviços complementares
-        &lt;ul&gt;
-          &lt;li&gt;elementos periféricos ou implícitos que agregam valor à experiência&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>0</v>
-      </c>
-      <c r="G207" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>298</v>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>CCQ – Círculos de Controle de Qualidade</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo primordial&lt;/strong&gt;
@@ -9752,6 +9753,71 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>299</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
+      &lt;li&gt;utilizadas como manobra para "promover para fora"
+        &lt;ul&gt;
+          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
+          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
+        &lt;ul&gt;
+          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
+      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
@@ -9761,7 +9827,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -9775,75 +9841,10 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>A Visão de Deming sobre Avaliações de Desempenho</t>
+          <t>Seis Sigma</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações positivas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;podem ser distorcidas por interesses políticos&lt;/li&gt;
-      &lt;li&gt;utilizadas como manobra para "promover para fora"
-        &lt;ul&gt;
-          &lt;li&gt;remover alguém indesejado através de promoção para outro setor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;avaliações negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;ignoram a natureza sistêmica do erro&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;regra dos 85 – 15%&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;85% dos problemas pertencem ao sistema&lt;/li&gt;
-          &lt;li&gt;15% são responsabilidade do indivíduo&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;imputação indevida de culpa ao funcionário&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;classificação por mérito (ranking)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;desencoraja a tomada de riscos&lt;/strong&gt;
-        &lt;ul&gt;
-          &lt;li&gt;foco em metas seguras para garantir a nota&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;mata a inovação e o espírito de equipe&lt;/li&gt;
-      &lt;li&gt;gera medo e comportamento defensivo&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F209" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>300</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Seis Sigma</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;objetivo fundamental&lt;/strong&gt;
@@ -9913,6 +9914,37 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>301</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Capabilidade</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
+        </is>
+      </c>
       <c r="F210" t="n">
         <v>0</v>
       </c>
@@ -9922,7 +9954,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -9931,46 +9963,15 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Gestão da Qualidade</t>
+          <t>Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Capabilidade</t>
+          <t>Macrofluxo da Gestão do Conhecimento</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
-        <is>
-          <t>índice Cp (Capabilidade do Processo) = tolerância especificada (LSE - LIE)/variação natural do processo (6 desvios, 6σ)</t>
-        </is>
-      </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>302</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>Macrofluxo da Gestão do Conhecimento</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Aquisição&lt;/strong&gt; (Criação/Captura)
@@ -10014,33 +10015,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" t="n">
+    <row r="212">
+      <c r="A212" t="n">
         <v>303</v>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D212" t="inlineStr">
         <is>
           <t>Gráficos de Controle por Variáveis e por Atributos</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E212" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gráficos de Controle por Variáveis&lt;/strong&gt;
@@ -10089,33 +10090,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F213" t="n">
-        <v>0</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
         <v>304</v>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D213" t="inlineStr">
         <is>
           <t>Técnica de Moderação por Cartelas</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E213" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Técnica de Moderação por cartelas
@@ -10145,6 +10146,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F213" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>305</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Diagrama de Interação do Processo</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;Diagrama de Interação do Processo
+    &lt;ul&gt;
+      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
+      &lt;li&gt;foco nas interfaces
+        &lt;ul&gt;
+          &lt;li&gt;entradas e saídas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;elementos
+        &lt;ul&gt;
+          &lt;li&gt;blocos de processos macro&lt;/li&gt;
+          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;objetivos
+        &lt;ul&gt;
+          &lt;li&gt;identificar dependências&lt;/li&gt;
+          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+      &lt;li&gt;distinção
+        &lt;ul&gt;
+          &lt;li&gt;foco externo ao processo&lt;/li&gt;
+          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
+        &lt;/ul&gt;
+      &lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
@@ -10154,7 +10215,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -10168,70 +10229,10 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Diagrama de Interação do Processo</t>
+          <t>Requisitos e Rotinas da ISO 9001:2015</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;Diagrama de Interação do Processo
-    &lt;ul&gt;
-      &lt;li&gt;mapeamento de visão sistêmica&lt;/li&gt;
-      &lt;li&gt;foco nas interfaces
-        &lt;ul&gt;
-          &lt;li&gt;entradas e saídas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;elementos
-        &lt;ul&gt;
-          &lt;li&gt;blocos de processos macro&lt;/li&gt;
-          &lt;li&gt;clientes e fornecedores internos&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;objetivos
-        &lt;ul&gt;
-          &lt;li&gt;identificar dependências&lt;/li&gt;
-          &lt;li&gt;alinhar fluxos de valor&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-      &lt;li&gt;distinção
-        &lt;ul&gt;
-          &lt;li&gt;foco externo ao processo&lt;/li&gt;
-          &lt;li&gt;não detalha atividades internas&lt;/li&gt;
-        &lt;/ul&gt;
-      &lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F215" t="n">
-        <v>0</v>
-      </c>
-      <c r="G215" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>306</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Requisitos e Rotinas da ISO 9001:2015</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;contexto e liderança&lt;/strong&gt;
@@ -10263,35 +10264,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
+    <row r="216">
+      <c r="A216" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B216" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D216" t="inlineStr">
         <is>
           <t>Débito na Contabilidade</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;conceito fundamental&lt;/strong&gt;
@@ -10327,33 +10328,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F217" t="n">
-        <v>0</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="n">
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
         <v>308</v>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D217" t="inlineStr">
         <is>
           <t>Tipos de Contas e Retificadoras</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E217" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Contas Patrimoniais&lt;/strong&gt;
@@ -10379,33 +10380,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F218" t="n">
-        <v>0</v>
-      </c>
-      <c r="G218" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="n">
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
         <v>309</v>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr">
+      <c r="C218" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D218" t="inlineStr">
         <is>
           <t>Diferenças Tributárias</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E218" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Impostos a Recolher / Pagar&lt;/strong&gt;
@@ -10425,33 +10426,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F219" t="n">
-        <v>0</v>
-      </c>
-      <c r="G219" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="n">
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
         <v>310</v>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C220" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>Teoria Patrimonialista e Despesas</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E219" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Divisão das Contas (Teoria Patrimonialista)&lt;/strong&gt;
@@ -10476,33 +10477,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="n">
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
         <v>311</v>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C221" t="inlineStr">
+      <c r="C220" t="inlineStr">
         <is>
           <t>Contabilidade Básica</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D220" t="inlineStr">
         <is>
           <t>O Ativo ao Final do Exercício</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E220" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;O Ativo ao Final do Exercício&lt;/strong&gt;
@@ -10522,33 +10523,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="n">
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
         <v>312</v>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B221" t="inlineStr">
         <is>
           <t>Contabilidade Gerencial</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr">
+      <c r="C221" t="inlineStr">
         <is>
           <t>Aspectos Introdutórios</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D221" t="inlineStr">
         <is>
           <t>Azienda</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E221" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Azienda (Conceito)&lt;/strong&gt;
@@ -10574,33 +10575,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F222" t="n">
-        <v>0</v>
-      </c>
-      <c r="G222" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="n">
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
         <v>313</v>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D222" t="inlineStr">
         <is>
           <t>NR 10</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E222" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança em Eletricidade&lt;/strong&gt;
@@ -10716,33 +10717,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F223" t="n">
-        <v>0</v>
-      </c>
-      <c r="G223" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="n">
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
         <v>314</v>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D223" t="inlineStr">
         <is>
           <t>NR 11</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E223" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Equipamentos de movimentação&lt;/strong&gt;
@@ -10870,33 +10871,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F224" t="n">
-        <v>0</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="n">
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
         <v>315</v>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D224" t="inlineStr">
         <is>
           <t>NR 12</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E224" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Princípios Gerais&lt;/strong&gt;
@@ -11014,33 +11015,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F225" t="n">
-        <v>0</v>
-      </c>
-      <c r="G225" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="n">
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
         <v>316</v>
       </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>NR 13</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;Gestão da integridade estrutural
@@ -11158,33 +11159,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F226" t="n">
-        <v>0</v>
-      </c>
-      <c r="G226" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="n">
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
         <v>317</v>
       </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D226" t="inlineStr">
         <is>
           <t>NR 14</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E226" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;operação com segurança
@@ -11232,35 +11233,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F227" t="n">
-        <v>0</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>NR 15</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Agente Físico: Ruído (Anexo 1)&lt;/strong&gt;
@@ -11294,33 +11295,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="n">
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
         <v>319</v>
       </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D228" t="inlineStr">
         <is>
           <t>NR 16</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E228" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adicional de Periculosidade&lt;/strong&gt;
@@ -11425,33 +11426,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="n">
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
         <v>320</v>
       </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>NR 17</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Adaptação às características psicofisiológicas&lt;/strong&gt;
@@ -11541,33 +11542,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="n">
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
         <v>321</v>
       </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D230" t="inlineStr">
         <is>
           <t>NR 18</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E230" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Indústria da construção&lt;/strong&gt;
@@ -11688,33 +11689,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F231" t="n">
-        <v>0</v>
-      </c>
-      <c r="G231" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="n">
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
         <v>322</v>
       </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D231" t="inlineStr">
         <is>
           <t>NR 19</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E231" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Disposições Gerais&lt;/strong&gt;
@@ -11813,33 +11814,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F232" t="n">
-        <v>0</v>
-      </c>
-      <c r="G232" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="n">
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
         <v>323</v>
       </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D232" t="inlineStr">
         <is>
           <t>NR 20</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E232" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de inflamáveis e combustíveis&lt;/strong&gt;
@@ -11939,33 +11940,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="n">
+      <c r="F232" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
         <v>324</v>
       </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D233" t="inlineStr">
         <is>
           <t>NR 21</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E233" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Proteção do trabalhador&lt;/strong&gt;
@@ -12045,33 +12046,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F234" t="n">
-        <v>0</v>
-      </c>
-      <c r="G234" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="n">
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
         <v>325</v>
       </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D234" t="inlineStr">
         <is>
           <t>NR 22</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E234" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidade&lt;/strong&gt;
@@ -12199,35 +12200,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F235" t="n">
-        <v>0</v>
-      </c>
-      <c r="G235" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
         <is>
           <t>326</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D235" t="inlineStr">
         <is>
           <t>NR 23</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E235" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Medidas de prevenção contra incêndios&lt;/strong&gt;
@@ -12264,35 +12265,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F236" t="n">
-        <v>0</v>
-      </c>
-      <c r="G236" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
         <is>
           <t>327</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D236" t="inlineStr">
         <is>
           <t>NR 24</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E236" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Dimensionamento&lt;/strong&gt;
@@ -12390,35 +12391,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>0</v>
-      </c>
-      <c r="G237" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
         <is>
           <t>328</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D237" t="inlineStr">
         <is>
           <t>NR 25</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E237" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gerenciamento de resíduos industriais&lt;/strong&gt;
@@ -12490,33 +12491,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F238" t="n">
-        <v>0</v>
-      </c>
-      <c r="G238" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="n">
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
         <v>329</v>
       </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D238" t="inlineStr">
         <is>
           <t>NR 26</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E238" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Sinalização e identificação de segurança&lt;/strong&gt;
@@ -12587,35 +12588,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F239" t="n">
-        <v>0</v>
-      </c>
-      <c r="G239" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
         <is>
           <t>330</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D239" t="inlineStr">
         <is>
           <t>NR 28</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E239" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fiscalização do Trabalho&lt;/strong&gt;
@@ -12688,35 +12689,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F240" t="n">
-        <v>0</v>
-      </c>
-      <c r="G240" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D240" t="inlineStr">
         <is>
           <t>NR 29</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E240" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -12823,33 +12824,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="n">
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
         <v>333</v>
       </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
+      <c r="D241" t="inlineStr">
         <is>
           <t>NR 30</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="E241" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Riscos e Saúde&lt;/strong&gt;
@@ -12955,33 +12956,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="n">
+      <c r="F241" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
         <v>334</v>
       </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>NR 31</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Campo de Aplicação&lt;/strong&gt;
@@ -13174,33 +13175,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="n">
+      <c r="F242" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
         <v>335</v>
       </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
+      <c r="D243" t="inlineStr">
         <is>
           <t>NR 32</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E243" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Segurança e Saúde em Serviços de Saúde (NR 32)&lt;/strong&gt;
@@ -13274,33 +13275,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F244" t="n">
-        <v>0</v>
-      </c>
-      <c r="G244" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="n">
+      <c r="F243" t="n">
+        <v>0</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
         <v>336</v>
       </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
+      <c r="D244" t="inlineStr">
         <is>
           <t>NR 33</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="E244" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Espaço Confinado&lt;/strong&gt;
@@ -13389,33 +13390,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F245" t="n">
-        <v>0</v>
-      </c>
-      <c r="G245" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="n">
+      <c r="F244" t="n">
+        <v>0</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
         <v>337</v>
       </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D245" t="inlineStr">
         <is>
           <t>NR 34</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E245" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão e Responsabilidades&lt;/strong&gt;
@@ -13561,33 +13562,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F246" t="n">
-        <v>0</v>
-      </c>
-      <c r="G246" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="n">
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
         <v>338</v>
       </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
+      <c r="D246" t="inlineStr">
         <is>
           <t>NR 35</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E246" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Campo de Aplicação&lt;/strong&gt;
@@ -13710,33 +13711,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F247" t="n">
-        <v>0</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="n">
+      <c r="F246" t="n">
+        <v>0</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
         <v>339</v>
       </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>NR 36</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivo e Aplicação&lt;/strong&gt;
@@ -13839,33 +13840,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F248" t="n">
-        <v>0</v>
-      </c>
-      <c r="G248" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="n">
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
         <v>340</v>
       </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
         <is>
           <t>Engenharia do Trabalho</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
+      <c r="D248" t="inlineStr">
         <is>
           <t>NR 37</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E248" t="inlineStr">
         <is>
           <t>&lt;li&gt;segurança operacional
     &lt;ul&gt;
@@ -13907,33 +13908,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F249" t="n">
-        <v>0</v>
-      </c>
-      <c r="G249" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="n">
+      <c r="F248" t="n">
+        <v>0</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
         <v>341</v>
       </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
         <is>
           <t>Engenharia de Métodos e Processos</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
+      <c r="D249" t="inlineStr">
         <is>
           <t>Fluxograma</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E249" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Fluxograma&lt;/strong&gt;
@@ -13974,33 +13975,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F250" t="n">
-        <v>0</v>
-      </c>
-      <c r="G250" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="n">
+      <c r="F249" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
         <v>342</v>
       </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
+      <c r="D250" t="inlineStr">
         <is>
           <t>Histograma</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="E250" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Objetivos e Diagnóstico&lt;/strong&gt;
@@ -14045,33 +14046,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F251" t="n">
-        <v>0</v>
-      </c>
-      <c r="G251" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="n">
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
         <v>343</v>
       </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D251" t="inlineStr">
         <is>
           <t>Diagrama de Causa e Efeito</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E251" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Diagrama de Causa e Efeito&lt;/strong&gt;
@@ -14103,33 +14104,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F252" t="n">
-        <v>0</v>
-      </c>
-      <c r="G252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="n">
+      <c r="F251" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
         <v>344</v>
       </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
         <is>
           <t>Sustentabilidade</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D252" t="inlineStr">
         <is>
           <t>ações de Gestão Ambiental Organizacional</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E252" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Gestão de Resíduos&lt;/strong&gt;
@@ -14169,33 +14170,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F253" t="n">
-        <v>0</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="n">
+      <c r="F252" t="n">
+        <v>0</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
         <v>345</v>
       </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>Engenharia Organizacional</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>principais termos técnicos de tipos e mudanças nas estruturas organizacionais</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Processos de Reestruturação&lt;/strong&gt;
@@ -14223,6 +14224,62 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F253" t="n">
+        <v>0</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>346</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Gestão da Qualidade</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Mentalidade de Risco e Prevenção</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F254" t="n">
         <v>0</v>
       </c>
@@ -14232,7 +14289,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -14246,66 +14303,10 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Mentalidade de Risco e Prevenção</t>
+          <t>ARL (Average Run Length)</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Mentalidade de Risco como Base da Prevenção&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Abordagem Proativa:&lt;/strong&gt; Identificar perigos potenciais para agir antes da ocorrência da não conformidade.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Integração ao Processo:&lt;/strong&gt; A prevenção deixa de ser um evento isolado e torna-se parte natural do fluxo de trabalho.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Riscos na Reestruturação Organizacional&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Downsizing:&lt;/strong&gt; O risco é a perda de talentos; a prevenção é o planejamento sucessório.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Delayering:&lt;/strong&gt; O risco é o vácuo de liderança; a prevenção é a automação de relatórios de controle.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Gestão de Autoridade e Riscos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Empowerment:&lt;/strong&gt; Previne a lentidão burocrática, mas exige controle de risco sobre a competência técnica da base.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Span of Control:&lt;/strong&gt; Uma amplitude muito larga sem suporte tecnológico gera risco de falha humana por sobrecarga.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Estruturas e Controles Preventivos&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Matrix (Matricial):&lt;/strong&gt; Exige protocolos de resolução de conflitos para prevenir a quebra da Unidade de Comando.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Flat (Achatada):&lt;/strong&gt; Requer alta maturidade da equipe para prevenir a falta de direção estratégica.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F255" t="n">
-        <v>0</v>
-      </c>
-      <c r="G255" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="n">
-        <v>347</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Gestão da Qualidade</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>ARL (Average Run Length)</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Curva OC (Operating Characteristic)&lt;/strong&gt;
@@ -14330,33 +14331,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F256" t="n">
-        <v>0</v>
-      </c>
-      <c r="G256" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="n">
+      <c r="F255" t="n">
+        <v>0</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
         <v>348</v>
       </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D256" t="inlineStr">
         <is>
           <t>Gestão da tecnologia</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E256" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito de Gestão da Tecnologia&lt;/strong&gt;
@@ -14389,33 +14390,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F257" t="n">
-        <v>0</v>
-      </c>
-      <c r="G257" t="n">
+      <c r="F256" t="n">
+        <v>0</v>
+      </c>
+      <c r="G256" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258" t="n">
+    <row r="257">
+      <c r="A257" t="n">
         <v>349</v>
       </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
         <is>
           <t>Gestão da Qualidade</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D257" t="inlineStr">
         <is>
           <t>QFD - Modelo de 4 Matrizes</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E257" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito do QFD (Quality Function Deployment)&lt;/strong&gt;
@@ -14459,33 +14460,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="n">
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
         <v>350</v>
       </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
         <is>
           <t>Logística</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
+      <c r="D258" t="inlineStr">
         <is>
           <t>Sistemas de Codificação de Materiais</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E258" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Numeração Arbitrária (Sequencial)&lt;/strong&gt;
@@ -14511,6 +14512,66 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>351</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Engenharia Organizacional</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>BSC (Perspectivas)</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
+      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
+      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F259" t="n">
         <v>0</v>
       </c>
@@ -14520,7 +14581,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -14529,75 +14590,15 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Engenharia Organizacional</t>
+          <t>Gestão de Investimentos e Risco</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>BSC (Perspectivas)</t>
+          <t>modelo CAPM (Capital Asset Pricing Model)</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva Financeira (Resultados Diretos)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco no valor para o acionista (ROI, Lucro, EBITDA).&lt;/li&gt;
-      &lt;li&gt;Representa o objetivo final da estratégia (Efeito).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva do Cliente (Mercado)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na satisfação e retenção de clientes.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Processos Internos (Eficiência)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco na excelência das atividades operacionais.&lt;/li&gt;
-      &lt;li&gt;Inclui indicadores como &lt;strong&gt;Custo por Pedido&lt;/strong&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Perspectiva de Aprendizado e Crescimento (Infraestrutura)&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Foco em pessoas, sistemas e cultura organizacional.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;NOTA DE ATENÇÃO:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;&lt;strong&gt;Regra:&lt;/strong&gt; Apenas índices que medem o desempenho financeiro &lt;u&gt;diretamente&lt;/u&gt; entram na Perspectiva Financeira.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Cuidado:&lt;/strong&gt; Evite classificar indicadores de "meio" (como custos operacionais ou taxas de conversão) como financeiros, mesmo que eles impactem o lucro &lt;u&gt;indiretamente&lt;/u&gt;.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F260" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="n">
-        <v>352</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Gestão de Investimentos e Risco</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>modelo CAPM (Capital Asset Pricing Model)</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito CAPM (Capital Asset Pricing Model)&lt;/strong&gt;
@@ -14627,33 +14628,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F261" t="n">
-        <v>0</v>
-      </c>
-      <c r="G261" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="n">
+      <c r="F260" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
         <v>354</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C261" t="inlineStr">
         <is>
           <t>Verbos</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D261" t="inlineStr">
         <is>
           <t>Presente Histórico e Paralelismo Temporal</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E261" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceitos de Verbo para o Cebraspe&lt;/strong&gt;
@@ -14676,35 +14677,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="F261" t="n">
+        <v>0</v>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
+      <c r="C262" t="inlineStr">
         <is>
           <t>Compreensão e Interpretação de Textos</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D262" t="inlineStr">
         <is>
           <t>Iterpretação x Inferência textual</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E262" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Compreensão (Literal)&lt;/strong&gt;
@@ -14734,33 +14735,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F263" t="n">
-        <v>0</v>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="n">
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
         <v>356</v>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>Informática</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
+      <c r="C263" t="inlineStr">
         <is>
           <t>Dados</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D263" t="inlineStr">
         <is>
           <t>DAMA-DMBOK</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E263" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Governança de Dados (DAMA-DMBOK)&lt;/strong&gt;
@@ -14786,33 +14787,33 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F264" t="n">
-        <v>0</v>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="n">
+      <c r="F263" t="n">
+        <v>0</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
         <v>357</v>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>Português</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>Mecanismos de Coesão Textual</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D264" t="inlineStr">
         <is>
           <t>Paralelismo</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E264" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Paralelismo Sintático&lt;/strong&gt;
@@ -14836,97 +14837,97 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F264" t="n">
+        <v>0</v>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Matemática Financeira</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Taxas</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Inflação Acumulada</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
+      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
+      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+&lt;/ul&gt;</t>
+        </is>
+      </c>
       <c r="F265" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G265" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Matemática Financeira</t>
+          <t>Informática</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Taxas</t>
+          <t>Proteção contra vírus</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Inflação Acumulada</t>
+          <t>Aplicativos Antivírus</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
-        <is>
-          <t>&lt;ul&gt;
-  &lt;li&gt;&lt;strong&gt;Conceito de Inflação Acumulada&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Representa o aumento real de preços em uma sequência de períodos.&lt;/li&gt;
-      &lt;li&gt;&lt;strong&gt;Regra de Ouro:&lt;/strong&gt; Taxas de inflação (ou juros) &lt;u&gt;nunca se somam&lt;/u&gt; aritmeticamente; elas são capitalizadas (multiplicadas).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Fórmula de Cálculo&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para taxas $i_1, i_2, ..., i_n$, a fórmula é: $I_{acc} = [(1 + i_1) \cdot (1 + i_2) \cdot ... \cdot (1 + i_n)] - 1$.&lt;/li&gt;
-      &lt;li&gt;Exemplo: Inflação de 10% e 10% no mês seguinte vira $(1,10 \cdot 1,10) - 1 = 21\%$.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Deflação e Variações Negativas&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Se houver queda de preços (ex: -2%), o fator de multiplicação será menor que 1 (ex: $1 - 0,02 = 0,98$).&lt;/li&gt;
-      &lt;li&gt;O processo de multiplicação entre os períodos permanece idêntico.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Média da Inflação&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;Para achar a inflação média periódica a partir da acumulada, utiliza-se a &lt;strong&gt;Média Geométrica&lt;/strong&gt; (raiz enésima do fator total).&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-  &lt;li&gt;&lt;strong&gt;Dica para Petrobras/ANSA:&lt;/strong&gt;
-    &lt;ul&gt;
-      &lt;li&gt;A banca adora colocar a soma simples nas alternativas para te induzir ao erro. Sempre transforme em fator ($1 + i$) antes de operar.&lt;/li&gt;
-    &lt;/ul&gt;
-  &lt;/li&gt;
-&lt;/ul&gt;</t>
-        </is>
-      </c>
-      <c r="F266" t="n">
-        <v>1</v>
-      </c>
-      <c r="G266" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Informática</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Proteção contra vírus</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>Aplicativos Antivírus</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;1ª Geração (Assinatura / Escaneamento Simples)&lt;/strong&gt;
@@ -14962,35 +14963,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F267" t="n">
-        <v>0</v>
-      </c>
-      <c r="G267" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
+      <c r="D267" t="inlineStr">
         <is>
           <t>Sistemas de Informação (SI)</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E267" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Conceito e Dimensões do SI&lt;/strong&gt;
@@ -15038,35 +15039,35 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
-      <c r="F268" t="n">
-        <v>0</v>
-      </c>
-      <c r="G268" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>Conhecimentos Específicos</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
         <is>
           <t>Gestão da Tecnologia</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
+      <c r="D268" t="inlineStr">
         <is>
           <t>Engenharia de Requisitos e Planejamento de SI</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="E268" t="inlineStr">
         <is>
           <t>&lt;ul&gt;
   &lt;li&gt;&lt;strong&gt;Premissas de Planejamento&lt;/strong&gt;
@@ -15085,6 +15086,61 @@
 &lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>362</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Conhecimentos Específicos</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Gestão da Tecnologia</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Arquitetura de Modelagem de Dados (ANSI/SPARC)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>&lt;ul&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Conceitual&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Representação abstrata e global dos dados da organização. Foca no negócio e ignora detalhes de implementação.&lt;/li&gt;
+      &lt;li&gt;&lt;strong&gt;Ferramenta:&lt;/strong&gt; DER (Diagrama Entidade-Relacionamento).&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/li&gt;
+  &lt;li&gt;&lt;strong&gt;Nível Lógico&lt;/strong&gt;
+    &lt;ul&gt;
+      &lt;li&gt;&lt;strong&gt;Definição:&lt;/strong&gt; Tradução do modelo conceitual para uma 